--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -1283,6 +1283,9 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -256,70 +256,58 @@
     <t>1_4000|2_4000|3_0|4_0</t>
   </si>
   <si>
+    <t>1_0|2_8000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_5000|3_5000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_5000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4000|3_6000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_10000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_10000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_7000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>高牌</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_9000|4_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_4000|2_4000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_10000|4_0</t>
+  </si>
+  <si>
     <t>1_0|2_4000|3_4000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_0|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_2000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_8000|4_0</t>
+    <t>1_0|2_2000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_6000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_11000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>高牌</t>
-  </si>
-  <si>
-    <t>1_0|2_8000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_4000|2_4000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_11000|4_0</t>
   </si>
 </sst>
 </file>
@@ -5177,10 +5165,10 @@
         <v>63</v>
       </c>
       <c r="L86" t="s">
+        <v>56</v>
+      </c>
+      <c r="N86" t="s">
         <v>64</v>
-      </c>
-      <c r="N86" t="s">
-        <v>62</v>
       </c>
       <c r="O86" t="s">
         <v>62</v>
@@ -5189,13 +5177,13 @@
         <v>56</v>
       </c>
       <c r="R86" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="S86" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T86" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -5229,25 +5217,25 @@
         <v>63</v>
       </c>
       <c r="L87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N87" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O87" t="s">
         <v>62</v>
       </c>
       <c r="P87" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R87" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="S87" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T87" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -5281,25 +5269,25 @@
         <v>63</v>
       </c>
       <c r="L88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N88" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O88" t="s">
         <v>62</v>
       </c>
       <c r="P88" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S88" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T88" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -5333,25 +5321,25 @@
         <v>63</v>
       </c>
       <c r="L89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N89" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O89" t="s">
         <v>62</v>
       </c>
       <c r="P89" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R89" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S89" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T89" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -5385,25 +5373,25 @@
         <v>63</v>
       </c>
       <c r="L90" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N90" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O90" t="s">
         <v>62</v>
       </c>
       <c r="P90" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R90" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="S90" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T90" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -5437,25 +5425,25 @@
         <v>63</v>
       </c>
       <c r="L91" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N91" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O91" t="s">
         <v>62</v>
       </c>
       <c r="P91" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R91" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="S91" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T91" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -5483,31 +5471,31 @@
         <v>61</v>
       </c>
       <c r="J92" t="s">
+        <v>68</v>
+      </c>
+      <c r="K92" t="s">
         <v>69</v>
       </c>
-      <c r="K92" t="s">
-        <v>71</v>
-      </c>
       <c r="L92" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O92" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P92" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S92" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="T92" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -5535,31 +5523,31 @@
         <v>61</v>
       </c>
       <c r="J93" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K93" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L93" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N93" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O93" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="P93" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="R93" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="S93" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="T93" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -5587,31 +5575,31 @@
         <v>61</v>
       </c>
       <c r="J94" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K94" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L94" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N94" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O94" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="P94" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="R94" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="S94" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="T94" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -5639,31 +5627,31 @@
         <v>61</v>
       </c>
       <c r="J95" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K95" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L95" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N95" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O95" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="P95" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="R95" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="S95" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="T95" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -5691,31 +5679,31 @@
         <v>61</v>
       </c>
       <c r="J96" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K96" t="s">
+        <v>69</v>
+      </c>
+      <c r="L96" t="s">
         <v>71</v>
       </c>
-      <c r="L96" t="s">
-        <v>76</v>
-      </c>
       <c r="N96" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O96" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="P96" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="R96" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="S96" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="T96" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -5743,31 +5731,31 @@
         <v>61</v>
       </c>
       <c r="J97" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K97" t="s">
+        <v>69</v>
+      </c>
+      <c r="L97" t="s">
         <v>71</v>
       </c>
-      <c r="L97" t="s">
-        <v>76</v>
-      </c>
       <c r="N97" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O97" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="P97" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="R97" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="S97" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="T97" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -5776,7 +5764,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -5788,37 +5776,37 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H98" t="s">
         <v>61</v>
       </c>
       <c r="J98" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L98" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N98" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O98" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P98" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="R98" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="S98" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="T98" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -5827,7 +5815,7 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C99">
         <f>C98</f>
@@ -5840,37 +5828,37 @@
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H99" t="s">
         <v>61</v>
       </c>
       <c r="J99" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="K99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L99" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N99" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O99" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="P99" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R99" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="S99" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="T99" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -5879,7 +5867,7 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
@@ -5892,37 +5880,37 @@
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H100" t="s">
         <v>61</v>
       </c>
       <c r="J100" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="K100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L100" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N100" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O100" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="P100" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R100" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="S100" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="T100" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -5931,7 +5919,7 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
@@ -5947,34 +5935,34 @@
         <v>59</v>
       </c>
       <c r="H101" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J101" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="K101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L101" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N101" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O101" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="P101" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R101" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="S101" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="T101" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -5983,7 +5971,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -5999,34 +5987,34 @@
         <v>59</v>
       </c>
       <c r="H102" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J102" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="K102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L102" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N102" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O102" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="P102" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R102" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="S102" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="T102" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -6035,7 +6023,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -6051,34 +6039,34 @@
         <v>62</v>
       </c>
       <c r="H103" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J103" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K103" t="s">
+        <v>68</v>
+      </c>
+      <c r="L103" t="s">
         <v>76</v>
       </c>
-      <c r="L103" t="s">
-        <v>84</v>
-      </c>
       <c r="N103" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O103" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="P103" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R103" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="S103" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="T103" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="1:20">
@@ -6087,7 +6075,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -6103,34 +6091,34 @@
         <v>62</v>
       </c>
       <c r="H104" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J104" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K104" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L104" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N104" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O104" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="P104" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R104" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="S104" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="T104" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -6139,7 +6127,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -6155,34 +6143,34 @@
         <v>62</v>
       </c>
       <c r="H105" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J105" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K105" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L105" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N105" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O105" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="P105" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R105" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="S105" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="T105" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -6191,7 +6179,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -6204,37 +6192,37 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J106" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="K106" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L106" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N106" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O106" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="P106" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R106" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="S106" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="T106" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -6243,7 +6231,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -6256,37 +6244,37 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J107" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="K107" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L107" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N107" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O107" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="P107" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R107" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="S107" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="T107" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -6295,7 +6283,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -6308,37 +6296,37 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H108" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J108" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="K108" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L108" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N108" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O108" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="P108" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R108" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="S108" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="T108" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -6347,7 +6335,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -6360,37 +6348,37 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J109" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="K109" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="L109" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N109" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O109" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="P109" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R109" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="S109" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="T109" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -154,24 +154,42 @@
     <t>1_10000|2_10000|3_0|4_3000</t>
   </si>
   <si>
+    <t>1_0|2_10000|3_10000|4_0</t>
+  </si>
+  <si>
     <t>1_10000|2_10000|3_0|4_5000</t>
   </si>
   <si>
+    <t>1_0|2_5000|3_10000|4_0</t>
+  </si>
+  <si>
     <t>1_10000|2_10000|3_0|4_10000</t>
   </si>
   <si>
+    <t>1_0|2_2500|3_10000|4_0</t>
+  </si>
+  <si>
     <t>同花顺</t>
   </si>
   <si>
     <t>1_8000|2_8000|3_0|4_3000</t>
   </si>
   <si>
+    <t>1_0|2_8000|3_8000|4_0</t>
+  </si>
+  <si>
     <t>1_8000|2_8000|3_0|4_5000</t>
   </si>
   <si>
+    <t>1_0|2_4000|3_8000|4_0</t>
+  </si>
+  <si>
     <t>1_8000|2_8000|3_0|4_10000</t>
   </si>
   <si>
+    <t>1_0|2_2000|3_8000|4_0</t>
+  </si>
+  <si>
     <t>K</t>
   </si>
   <si>
@@ -205,7 +223,13 @@
     <t>两对</t>
   </si>
   <si>
-    <t>1_0|2_8000|3_2000|4_0</t>
+    <t>1_0|2_2000|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_500|3_2000|4_0</t>
   </si>
   <si>
     <t>1_6000|2_6000|3_0|4_3000</t>
@@ -217,24 +241,21 @@
     <t>1_6000|2_6000|3_0|4_8000</t>
   </si>
   <si>
-    <t>1_0|2_6000|3_2000|4_0</t>
-  </si>
-  <si>
     <t>1_6000|2_6000|3_0|4_2000</t>
   </si>
   <si>
+    <t>1_0|2_0|3_3000|4_0</t>
+  </si>
+  <si>
     <t>1_6000|2_6000|3_0|4_7000</t>
   </si>
   <si>
-    <t>1_0|2_6000|3_3000|4_0</t>
+    <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
     <t>1_6000|2_6000|3_0|4_6000</t>
   </si>
   <si>
-    <t>1_0|2_6000|3_4000|4_0</t>
-  </si>
-  <si>
     <t>一对</t>
   </si>
   <si>
@@ -259,13 +280,13 @@
     <t>1_0|2_8000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_0|2_5000|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_6000|4_0</t>
+    <t>1_0|2_0|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_5000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_6000|4_0</t>
   </si>
   <si>
     <t>1_0|2_10000|3_0|4_0</t>
@@ -274,16 +295,16 @@
     <t>1_2000|2_10000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_0|2_3000|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_8000|4_0</t>
+    <t>1_0|2_0|3_7000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_8000|4_0</t>
   </si>
   <si>
     <t>高牌</t>
   </si>
   <si>
-    <t>1_0|2_1000|3_9000|4_0</t>
+    <t>1_0|2_0|3_9000|4_0</t>
   </si>
   <si>
     <t>1_6000|2_6000|3_0|4_1000</t>
@@ -295,19 +316,19 @@
     <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
+    <t>1_0|2_4000|3_1000|4_0</t>
+  </si>
+  <si>
     <t>1_0|2_4000|3_4000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_2000|3_0|4_0</t>
+    <t>1_0|2_2000|3_500|4_0</t>
   </si>
   <si>
     <t>1_0|2_2000|3_6000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_11000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
   </si>
 </sst>
 </file>
@@ -934,9 +955,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1256,6 +1280,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
     <col min="7" max="8" width="32.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="12" width="29.75" customWidth="1"/>
@@ -1333,37 +1358,37 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1422,7 +1447,7 @@
       <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E5">
@@ -1435,25 +1460,25 @@
         <v>29</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1462,43 +1487,43 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E6">
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1507,44 +1532,44 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>36</v>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1553,44 +1578,44 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1599,44 +1624,44 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1645,44 +1670,44 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1691,44 +1716,44 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T11" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1737,44 +1762,44 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1783,44 +1808,44 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>7</v>
       </c>
       <c r="E13">
         <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1829,44 +1854,44 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
       </c>
       <c r="J14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1875,43 +1900,43 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>7</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T15" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1920,44 +1945,44 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
-      <c r="D16" t="s">
-        <v>36</v>
+      <c r="D16" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1966,44 +1991,44 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
-      <c r="D17" t="s">
-        <v>37</v>
+      <c r="D17" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="J17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R17" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S17" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -2012,44 +2037,44 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D18" t="s">
-        <v>38</v>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="J18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -2058,44 +2083,44 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>10</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T19" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -2104,44 +2129,44 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>9</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R20" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S20" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -2150,44 +2175,44 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="J21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -2196,44 +2221,44 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>7</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
       <c r="J22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2242,44 +2267,44 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>6</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
       <c r="J23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R23" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S23" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T23" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -2288,44 +2313,44 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
       <c r="J24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P24" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2334,44 +2359,44 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>4</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N25" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O25" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R25" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S25" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T25" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2380,44 +2405,44 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="J26" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O26" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T26" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2426,44 +2451,44 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="J27" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R27" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S27" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T27" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2472,43 +2497,43 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E28">
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T28" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2517,44 +2542,44 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
-      <c r="D29" t="s">
-        <v>36</v>
+      <c r="D29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="J29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L29" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2563,44 +2588,44 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
-      <c r="D30" t="s">
-        <v>37</v>
+      <c r="D30" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="J30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T30" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -2609,44 +2634,44 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D31" t="s">
-        <v>38</v>
+      <c r="D31" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="J31" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R31" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S31" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T31" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2655,44 +2680,44 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>10</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N32" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O32" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T32" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -2701,44 +2726,44 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>9</v>
       </c>
       <c r="E33">
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N33" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O33" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P33" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R33" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S33" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T33" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -2747,44 +2772,44 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="J34" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N34" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O34" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P34" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R34" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S34" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T34" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2793,44 +2818,44 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
         <v>7</v>
       </c>
       <c r="E35">
         <v>7</v>
       </c>
       <c r="J35" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R35" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S35" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2839,44 +2864,44 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>6</v>
       </c>
       <c r="E36">
         <v>6</v>
       </c>
       <c r="J36" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L36" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N36" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O36" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P36" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T36" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -2885,44 +2910,44 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
       <c r="J37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N37" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O37" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P37" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R37" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S37" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T37" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -2931,44 +2956,44 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>4</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L38" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P38" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R38" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S38" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T38" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -2977,44 +3002,44 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>3</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="J39" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L39" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P39" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R39" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S39" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T39" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -3023,44 +3048,44 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="J40" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K40" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L40" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P40" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R40" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S40" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T40" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -3069,43 +3094,43 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P41" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R41" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S41" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T41" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -3114,44 +3139,44 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
-      <c r="D42" t="s">
-        <v>36</v>
+      <c r="D42" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="J42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L42" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P42" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R42" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S42" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T42" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3160,44 +3185,44 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
-      <c r="D43" t="s">
-        <v>37</v>
+      <c r="D43" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="J43" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L43" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P43" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T43" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3206,44 +3231,44 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D44" t="s">
-        <v>38</v>
+      <c r="D44" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="J44" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K44" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L44" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P44" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R44" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S44" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T44" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3252,44 +3277,44 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>10</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
       <c r="J45" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L45" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P45" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R45" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S45" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T45" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3298,44 +3323,44 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>9</v>
       </c>
       <c r="E46">
         <v>9</v>
       </c>
       <c r="J46" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L46" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N46" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O46" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P46" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R46" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S46" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T46" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3344,44 +3369,44 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>8</v>
       </c>
       <c r="E47">
         <v>8</v>
       </c>
       <c r="J47" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L47" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R47" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S47" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T47" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -3390,44 +3415,44 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>7</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
       <c r="J48" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L48" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P48" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R48" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S48" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T48" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -3436,44 +3461,44 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>6</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="J49" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N49" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O49" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P49" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R49" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S49" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T49" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -3482,43 +3507,43 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E50">
         <v>14</v>
       </c>
       <c r="J50" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L50" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N50" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O50" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P50" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R50" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S50" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T50" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -3527,44 +3552,44 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
-      <c r="D51" t="s">
-        <v>36</v>
+      <c r="D51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="J51" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P51" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R51" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S51" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T51" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3573,44 +3598,44 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
-      <c r="D52" t="s">
-        <v>37</v>
+      <c r="D52" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="J52" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L52" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P52" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R52" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S52" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T52" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -3619,44 +3644,44 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D53" t="s">
-        <v>38</v>
+      <c r="D53" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="J53" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L53" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N53" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O53" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P53" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R53" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S53" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T53" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -3665,44 +3690,44 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>10</v>
       </c>
       <c r="E54">
         <v>10</v>
       </c>
       <c r="J54" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L54" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P54" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T54" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -3711,44 +3736,44 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
         <v>9</v>
       </c>
       <c r="E55">
         <v>9</v>
       </c>
       <c r="J55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P55" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R55" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S55" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T55" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -3757,44 +3782,44 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>8</v>
       </c>
       <c r="E56">
         <v>8</v>
       </c>
       <c r="J56" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L56" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N56" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O56" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P56" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R56" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S56" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T56" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -3803,44 +3828,44 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
         <v>7</v>
       </c>
       <c r="E57">
         <v>7</v>
       </c>
       <c r="J57" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L57" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N57" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O57" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P57" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R57" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S57" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T57" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -3849,44 +3874,44 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>6</v>
       </c>
       <c r="E58">
         <v>6</v>
       </c>
       <c r="J58" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L58" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N58" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O58" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P58" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R58" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S58" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T58" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -3895,43 +3920,43 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E59">
         <v>14</v>
       </c>
       <c r="J59" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L59" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P59" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R59" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S59" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T59" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -3940,44 +3965,44 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
-      <c r="D60" t="s">
-        <v>36</v>
+      <c r="D60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="J60" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L60" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N60" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O60" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P60" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R60" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S60" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T60" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -3986,44 +4011,44 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
-      <c r="D61" t="s">
-        <v>37</v>
+      <c r="D61" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="J61" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N61" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O61" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P61" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R61" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S61" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T61" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -4032,44 +4057,44 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D62" t="s">
-        <v>38</v>
+      <c r="D62" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="J62" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K62" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L62" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N62" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O62" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P62" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R62" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S62" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T62" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -4078,44 +4103,44 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>10</v>
       </c>
       <c r="E63">
         <v>10</v>
       </c>
       <c r="J63" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K63" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L63" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N63" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O63" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P63" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R63" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S63" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T63" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -4124,44 +4149,44 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>9</v>
       </c>
       <c r="E64">
         <v>9</v>
       </c>
       <c r="J64" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K64" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L64" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N64" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O64" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P64" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R64" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S64" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T64" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -4170,44 +4195,44 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>8</v>
       </c>
       <c r="E65">
         <v>8</v>
       </c>
       <c r="J65" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K65" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L65" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N65" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O65" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P65" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R65" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S65" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T65" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -4216,44 +4241,44 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>7</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
       <c r="J66" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K66" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L66" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N66" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O66" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P66" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R66" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S66" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T66" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -4262,44 +4287,44 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>6</v>
       </c>
       <c r="E67">
         <v>6</v>
       </c>
       <c r="J67" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K67" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L67" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N67" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O67" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P67" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R67" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S67" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T67" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -4308,44 +4333,44 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68">
         <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K68" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L68" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N68" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O68" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P68" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R68" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S68" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T68" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -4354,44 +4379,44 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>4</v>
       </c>
       <c r="E69">
         <v>4</v>
       </c>
       <c r="J69" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L69" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N69" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O69" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P69" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R69" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S69" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T69" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -4400,44 +4425,44 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>3</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
       <c r="J70" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K70" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L70" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N70" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O70" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P70" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R70" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S70" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T70" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -4446,44 +4471,44 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>2</v>
       </c>
       <c r="E71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K71" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L71" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N71" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O71" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P71" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R71" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S71" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T71" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -4492,43 +4517,43 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E72">
         <v>14</v>
       </c>
       <c r="J72" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K72" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L72" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N72" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O72" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P72" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R72" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S72" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T72" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -4537,44 +4562,44 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
-      <c r="D73" t="s">
-        <v>36</v>
+      <c r="D73" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="J73" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K73" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L73" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N73" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O73" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P73" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R73" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S73" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T73" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -4583,44 +4608,44 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
-      <c r="D74" t="s">
-        <v>37</v>
+      <c r="D74" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="J74" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L74" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N74" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O74" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P74" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="R74" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="S74" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T74" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -4629,44 +4654,44 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D75" t="s">
-        <v>38</v>
+      <c r="D75" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="J75" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L75" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N75" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O75" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P75" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R75" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="S75" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T75" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -4675,44 +4700,44 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76">
         <v>10</v>
       </c>
       <c r="J76" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K76" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L76" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N76" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O76" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P76" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R76" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="S76" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T76" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -4721,44 +4746,44 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>9</v>
       </c>
       <c r="E77">
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K77" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L77" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N77" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O77" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P77" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R77" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="S77" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="T77" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -4767,44 +4792,44 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
         <v>8</v>
       </c>
       <c r="E78">
         <v>8</v>
       </c>
       <c r="J78" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K78" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L78" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N78" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O78" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P78" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R78" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="S78" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="T78" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -4813,44 +4838,44 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>7</v>
       </c>
       <c r="E79">
         <v>7</v>
       </c>
       <c r="J79" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K79" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L79" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N79" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O79" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P79" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R79" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="S79" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="T79" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -4859,44 +4884,44 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>6</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
       <c r="J80" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K80" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L80" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N80" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O80" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P80" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R80" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="S80" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="T80" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -4905,44 +4930,44 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
         <v>5</v>
       </c>
       <c r="E81">
         <v>5</v>
       </c>
       <c r="J81" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K81" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L81" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N81" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O81" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P81" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R81" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="S81" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="T81" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -4951,44 +4976,44 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>4</v>
       </c>
       <c r="E82">
         <v>4</v>
       </c>
       <c r="J82" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K82" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L82" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N82" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O82" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P82" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R82" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="S82" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="T82" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -4997,44 +5022,44 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
         <v>3</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K83" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L83" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="N83" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="O83" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P83" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="R83" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="S83" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="T83" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -5043,44 +5068,44 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
         <v>2</v>
       </c>
       <c r="E84">
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K84" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L84" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="N84" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="O84" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P84" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="R84" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="S84" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="T84" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -5089,49 +5114,49 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E85">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J85" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K85" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L85" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N85" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="O85" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="P85" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="R85" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="S85" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="T85" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -5140,50 +5165,50 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
-      <c r="D86" t="s">
-        <v>36</v>
+      <c r="D86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H86" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J86" t="s">
+        <v>69</v>
+      </c>
+      <c r="K86" t="s">
+        <v>70</v>
+      </c>
+      <c r="L86" t="s">
         <v>62</v>
       </c>
-      <c r="K86" t="s">
-        <v>63</v>
-      </c>
-      <c r="L86" t="s">
-        <v>56</v>
-      </c>
       <c r="N86" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O86" t="s">
+        <v>69</v>
+      </c>
+      <c r="P86" t="s">
         <v>62</v>
       </c>
-      <c r="P86" t="s">
-        <v>56</v>
-      </c>
       <c r="R86" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="S86" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T86" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -5192,50 +5217,50 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
-      <c r="D87" t="s">
-        <v>37</v>
+      <c r="D87" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H87" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J87" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K87" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L87" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N87" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O87" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P87" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="R87" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S87" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T87" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -5244,50 +5269,50 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D88" t="s">
-        <v>38</v>
+      <c r="D88" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H88" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J88" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K88" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L88" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N88" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O88" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P88" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="R88" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S88" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T88" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -5296,50 +5321,50 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
         <v>10</v>
       </c>
       <c r="E89">
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H89" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J89" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K89" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L89" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N89" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O89" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P89" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="R89" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="S89" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T89" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -5348,50 +5373,50 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
         <v>9</v>
       </c>
       <c r="E90">
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H90" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J90" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K90" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L90" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N90" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O90" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P90" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R90" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="S90" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T90" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -5400,50 +5425,50 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="1">
         <v>8</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H91" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J91" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K91" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L91" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N91" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O91" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P91" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R91" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="S91" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T91" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -5452,50 +5477,50 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="1">
         <v>7</v>
       </c>
       <c r="E92">
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H92" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J92" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K92" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L92" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N92" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O92" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P92" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R92" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S92" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T92" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -5504,50 +5529,50 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="1">
         <v>6</v>
       </c>
       <c r="E93">
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H93" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J93" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K93" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L93" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N93" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O93" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P93" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="R93" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S93" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T93" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -5556,50 +5581,50 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
         <v>5</v>
       </c>
       <c r="E94">
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H94" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J94" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K94" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L94" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N94" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O94" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P94" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="R94" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S94" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T94" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -5608,50 +5633,50 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>4</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H95" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J95" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K95" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L95" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N95" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O95" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P95" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="R95" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S95" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T95" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -5660,50 +5685,50 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H96" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J96" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K96" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L96" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N96" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O96" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P96" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R96" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S96" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T96" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -5712,50 +5737,50 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="1">
         <v>2</v>
       </c>
       <c r="E97">
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H97" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J97" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K97" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L97" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N97" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O97" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P97" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R97" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S97" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T97" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -5764,49 +5789,49 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E98">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H98" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J98" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K98" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L98" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N98" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O98" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P98" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R98" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S98" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T98" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -5815,50 +5840,50 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
-      <c r="D99" t="s">
-        <v>36</v>
+      <c r="D99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H99" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J99" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K99" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L99" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="N99" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O99" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P99" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="R99" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S99" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T99" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -5867,50 +5892,50 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
-      <c r="D100" t="s">
-        <v>37</v>
+      <c r="D100" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H100" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J100" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K100" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L100" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="N100" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O100" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P100" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="R100" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S100" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T100" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -5919,50 +5944,50 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D101" t="s">
-        <v>38</v>
+      <c r="D101" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H101" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J101" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K101" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L101" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="N101" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O101" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P101" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="R101" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S101" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T101" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -5971,50 +5996,50 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>10</v>
       </c>
       <c r="E102">
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H102" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J102" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K102" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L102" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="N102" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O102" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P102" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="R102" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S102" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T102" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -6023,50 +6048,50 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="1">
         <v>9</v>
       </c>
       <c r="E103">
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H103" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J103" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K103" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L103" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N103" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O103" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P103" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="R103" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S103" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T103" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="1:20">
@@ -6075,50 +6100,50 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="1">
         <v>8</v>
       </c>
       <c r="E104">
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="H104" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J104" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K104" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L104" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N104" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O104" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P104" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="R104" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S104" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T104" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -6127,50 +6152,50 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="1">
         <v>7</v>
       </c>
       <c r="E105">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="H105" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J105" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K105" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L105" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N105" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O105" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P105" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="R105" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S105" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T105" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -6179,50 +6204,50 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>6</v>
       </c>
       <c r="E106">
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H106" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J106" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K106" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L106" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N106" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O106" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P106" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R106" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S106" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T106" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -6231,50 +6256,50 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>5</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H107" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J107" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K107" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L107" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N107" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O107" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P107" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R107" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S107" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T107" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -6283,50 +6308,50 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="1">
         <v>4</v>
       </c>
       <c r="E108">
         <v>4</v>
       </c>
       <c r="G108" t="s">
+        <v>86</v>
+      </c>
+      <c r="H108" t="s">
         <v>78</v>
       </c>
-      <c r="H108" t="s">
-        <v>81</v>
-      </c>
       <c r="J108" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K108" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L108" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N108" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O108" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P108" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R108" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S108" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T108" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -6335,50 +6360,50 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="G109" t="s">
+        <v>86</v>
+      </c>
+      <c r="H109" t="s">
         <v>78</v>
       </c>
-      <c r="H109" t="s">
-        <v>81</v>
-      </c>
       <c r="J109" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K109" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L109" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N109" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="O109" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="P109" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="R109" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="S109" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T109" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="chessTexasStrategy" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="91">
   <si>
     <t>ID</t>
   </si>
@@ -151,19 +151,19 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_3000</t>
+    <t>1_3000|2_10000|3_0|4_3000</t>
   </si>
   <si>
     <t>1_0|2_10000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_5000</t>
+    <t>1_3000|2_10000|3_0|4_5000</t>
   </si>
   <si>
     <t>1_0|2_5000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_10000</t>
+    <t>1_3000|2_10000|3_0|4_10000</t>
   </si>
   <si>
     <t>1_0|2_2500|3_10000|4_0</t>
@@ -172,19 +172,19 @@
     <t>同花顺</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_3000</t>
+    <t>1_3000|2_8000|3_0|4_3000</t>
   </si>
   <si>
     <t>1_0|2_8000|3_8000|4_0</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_5000</t>
+    <t>1_3000|2_8000|3_0|4_5000</t>
   </si>
   <si>
     <t>1_0|2_4000|3_8000|4_0</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_10000</t>
+    <t>1_3000|2_8000|3_0|4_10000</t>
   </si>
   <si>
     <t>1_0|2_2000|3_8000|4_0</t>
@@ -211,10 +211,13 @@
     <t>顺子</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_8000</t>
+    <t>1_2000|2_8000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2000|2_8000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2000|2_8000|3_0|4_8000</t>
   </si>
   <si>
     <t>三条</t>
@@ -232,49 +235,49 @@
     <t>1_0|2_500|3_2000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_2000</t>
+    <t>1_2000|2_6000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2000|2_6000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2000|2_6000|3_0|4_8000</t>
+  </si>
+  <si>
+    <t>1_2000|2_6000|3_0|4_2000</t>
   </si>
   <si>
     <t>1_0|2_0|3_3000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_7000</t>
+    <t>1_2000|2_6000|3_0|4_7000</t>
   </si>
   <si>
     <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_6000</t>
+    <t>1_2000|2_6000|3_0|4_6000</t>
   </si>
   <si>
     <t>一对</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_1000</t>
+    <t>1_3000|2_10000|3_0|4_1000</t>
   </si>
   <si>
     <t>1_0|2_6000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_1000</t>
+    <t>1_2000|2_6000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_3000|2_8000|3_0|4_1000</t>
   </si>
   <si>
     <t>1_0|2_4000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_4000|2_4000|3_0|4_0</t>
+    <t>1_1000|2_4000|3_0|4_0</t>
   </si>
   <si>
     <t>1_0|2_8000|3_0|4_0</t>
@@ -292,7 +295,7 @@
     <t>1_0|2_10000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_2000|2_10000|3_0|4_0</t>
+    <t>1_1000|2_10000|3_0|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_7000|4_0</t>
@@ -304,13 +307,16 @@
     <t>高牌</t>
   </si>
   <si>
+    <t>1_2000|2_8000|3_0|4_1000</t>
+  </si>
+  <si>
     <t>1_0|2_0|3_9000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_4000|2_4000|3_0|4_1000</t>
+    <t>1_2000|2_6000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_1000|2_4000|3_0|4_1000</t>
   </si>
   <si>
     <t>1_0|2_0|3_10000|4_0</t>
@@ -3887,28 +3893,28 @@
         <v>6</v>
       </c>
       <c r="J58" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K58" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L58" t="s">
         <v>37</v>
       </c>
       <c r="N58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P58" t="s">
         <v>39</v>
       </c>
       <c r="R58" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S58" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T58" t="s">
         <v>41</v>
@@ -3920,7 +3926,7 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -3932,28 +3938,28 @@
         <v>14</v>
       </c>
       <c r="J59" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K59" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L59" t="s">
         <v>37</v>
       </c>
       <c r="N59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P59" t="s">
         <v>39</v>
       </c>
       <c r="R59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S59" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T59" t="s">
         <v>41</v>
@@ -3965,7 +3971,7 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C60">
         <f>C59</f>
@@ -3978,28 +3984,28 @@
         <v>13</v>
       </c>
       <c r="J60" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K60" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L60" t="s">
         <v>37</v>
       </c>
       <c r="N60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O60" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P60" t="s">
         <v>39</v>
       </c>
       <c r="R60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T60" t="s">
         <v>41</v>
@@ -4011,7 +4017,7 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
@@ -4024,28 +4030,28 @@
         <v>12</v>
       </c>
       <c r="J61" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K61" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L61" t="s">
         <v>37</v>
       </c>
       <c r="N61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P61" t="s">
         <v>39</v>
       </c>
       <c r="R61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T61" t="s">
         <v>41</v>
@@ -4057,7 +4063,7 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
@@ -4070,28 +4076,28 @@
         <v>11</v>
       </c>
       <c r="J62" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K62" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L62" t="s">
         <v>37</v>
       </c>
       <c r="N62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P62" t="s">
         <v>39</v>
       </c>
       <c r="R62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T62" t="s">
         <v>41</v>
@@ -4103,7 +4109,7 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -4116,28 +4122,28 @@
         <v>10</v>
       </c>
       <c r="J63" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K63" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L63" t="s">
         <v>37</v>
       </c>
       <c r="N63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P63" t="s">
         <v>39</v>
       </c>
       <c r="R63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T63" t="s">
         <v>41</v>
@@ -4149,7 +4155,7 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -4162,28 +4168,28 @@
         <v>9</v>
       </c>
       <c r="J64" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K64" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L64" t="s">
         <v>37</v>
       </c>
       <c r="N64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P64" t="s">
         <v>39</v>
       </c>
       <c r="R64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T64" t="s">
         <v>41</v>
@@ -4195,7 +4201,7 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -4208,28 +4214,28 @@
         <v>8</v>
       </c>
       <c r="J65" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K65" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L65" t="s">
         <v>37</v>
       </c>
       <c r="N65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P65" t="s">
         <v>39</v>
       </c>
       <c r="R65" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S65" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T65" t="s">
         <v>41</v>
@@ -4241,7 +4247,7 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -4254,28 +4260,28 @@
         <v>7</v>
       </c>
       <c r="J66" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K66" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L66" t="s">
         <v>37</v>
       </c>
       <c r="N66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P66" t="s">
         <v>39</v>
       </c>
       <c r="R66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T66" t="s">
         <v>41</v>
@@ -4287,7 +4293,7 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -4300,28 +4306,28 @@
         <v>6</v>
       </c>
       <c r="J67" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K67" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L67" t="s">
         <v>37</v>
       </c>
       <c r="N67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P67" t="s">
         <v>39</v>
       </c>
       <c r="R67" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S67" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T67" t="s">
         <v>41</v>
@@ -4333,7 +4339,7 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -4346,28 +4352,28 @@
         <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K68" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L68" t="s">
         <v>37</v>
       </c>
       <c r="N68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P68" t="s">
         <v>39</v>
       </c>
       <c r="R68" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S68" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T68" t="s">
         <v>41</v>
@@ -4379,7 +4385,7 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -4392,28 +4398,28 @@
         <v>4</v>
       </c>
       <c r="J69" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K69" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L69" t="s">
         <v>37</v>
       </c>
       <c r="N69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P69" t="s">
         <v>39</v>
       </c>
       <c r="R69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T69" t="s">
         <v>41</v>
@@ -4425,7 +4431,7 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -4438,28 +4444,28 @@
         <v>3</v>
       </c>
       <c r="J70" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K70" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L70" t="s">
         <v>37</v>
       </c>
       <c r="N70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P70" t="s">
         <v>39</v>
       </c>
       <c r="R70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T70" t="s">
         <v>41</v>
@@ -4471,7 +4477,7 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -4484,28 +4490,28 @@
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K71" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L71" t="s">
         <v>37</v>
       </c>
       <c r="N71" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O71" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P71" t="s">
         <v>39</v>
       </c>
       <c r="R71" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S71" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T71" t="s">
         <v>41</v>
@@ -4517,7 +4523,7 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -4529,28 +4535,28 @@
         <v>14</v>
       </c>
       <c r="J72" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K72" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L72" t="s">
         <v>37</v>
       </c>
       <c r="N72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P72" t="s">
         <v>39</v>
       </c>
       <c r="R72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T72" t="s">
         <v>41</v>
@@ -4562,7 +4568,7 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C73">
         <f>C72</f>
@@ -4575,28 +4581,28 @@
         <v>13</v>
       </c>
       <c r="J73" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K73" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L73" t="s">
         <v>37</v>
       </c>
       <c r="N73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P73" t="s">
         <v>39</v>
       </c>
       <c r="R73" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S73" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T73" t="s">
         <v>41</v>
@@ -4608,7 +4614,7 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
@@ -4621,31 +4627,31 @@
         <v>12</v>
       </c>
       <c r="J74" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K74" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -4654,7 +4660,7 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
@@ -4667,31 +4673,31 @@
         <v>11</v>
       </c>
       <c r="J75" t="s">
+        <v>57</v>
+      </c>
+      <c r="K75" t="s">
+        <v>57</v>
+      </c>
+      <c r="L75" t="s">
+        <v>54</v>
+      </c>
+      <c r="N75" t="s">
+        <v>58</v>
+      </c>
+      <c r="O75" t="s">
+        <v>58</v>
+      </c>
+      <c r="P75" t="s">
+        <v>55</v>
+      </c>
+      <c r="R75" t="s">
+        <v>59</v>
+      </c>
+      <c r="S75" t="s">
+        <v>59</v>
+      </c>
+      <c r="T75" t="s">
         <v>56</v>
-      </c>
-      <c r="K75" t="s">
-        <v>56</v>
-      </c>
-      <c r="L75" t="s">
-        <v>53</v>
-      </c>
-      <c r="N75" t="s">
-        <v>57</v>
-      </c>
-      <c r="O75" t="s">
-        <v>57</v>
-      </c>
-      <c r="P75" t="s">
-        <v>54</v>
-      </c>
-      <c r="R75" t="s">
-        <v>58</v>
-      </c>
-      <c r="S75" t="s">
-        <v>58</v>
-      </c>
-      <c r="T75" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -4700,7 +4706,7 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -4713,31 +4719,31 @@
         <v>10</v>
       </c>
       <c r="J76" t="s">
+        <v>57</v>
+      </c>
+      <c r="K76" t="s">
+        <v>57</v>
+      </c>
+      <c r="L76" t="s">
+        <v>54</v>
+      </c>
+      <c r="N76" t="s">
+        <v>58</v>
+      </c>
+      <c r="O76" t="s">
+        <v>58</v>
+      </c>
+      <c r="P76" t="s">
+        <v>55</v>
+      </c>
+      <c r="R76" t="s">
+        <v>59</v>
+      </c>
+      <c r="S76" t="s">
+        <v>59</v>
+      </c>
+      <c r="T76" t="s">
         <v>56</v>
-      </c>
-      <c r="K76" t="s">
-        <v>56</v>
-      </c>
-      <c r="L76" t="s">
-        <v>53</v>
-      </c>
-      <c r="N76" t="s">
-        <v>57</v>
-      </c>
-      <c r="O76" t="s">
-        <v>57</v>
-      </c>
-      <c r="P76" t="s">
-        <v>54</v>
-      </c>
-      <c r="R76" t="s">
-        <v>58</v>
-      </c>
-      <c r="S76" t="s">
-        <v>58</v>
-      </c>
-      <c r="T76" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -4746,7 +4752,7 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -4759,31 +4765,31 @@
         <v>9</v>
       </c>
       <c r="J77" t="s">
+        <v>57</v>
+      </c>
+      <c r="K77" t="s">
+        <v>57</v>
+      </c>
+      <c r="L77" t="s">
+        <v>54</v>
+      </c>
+      <c r="N77" t="s">
+        <v>58</v>
+      </c>
+      <c r="O77" t="s">
+        <v>58</v>
+      </c>
+      <c r="P77" t="s">
+        <v>55</v>
+      </c>
+      <c r="R77" t="s">
+        <v>59</v>
+      </c>
+      <c r="S77" t="s">
+        <v>59</v>
+      </c>
+      <c r="T77" t="s">
         <v>56</v>
-      </c>
-      <c r="K77" t="s">
-        <v>56</v>
-      </c>
-      <c r="L77" t="s">
-        <v>53</v>
-      </c>
-      <c r="N77" t="s">
-        <v>57</v>
-      </c>
-      <c r="O77" t="s">
-        <v>57</v>
-      </c>
-      <c r="P77" t="s">
-        <v>54</v>
-      </c>
-      <c r="R77" t="s">
-        <v>58</v>
-      </c>
-      <c r="S77" t="s">
-        <v>58</v>
-      </c>
-      <c r="T77" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -4792,7 +4798,7 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -4805,31 +4811,31 @@
         <v>8</v>
       </c>
       <c r="J78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N78" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O78" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R78" t="s">
+        <v>62</v>
+      </c>
+      <c r="S78" t="s">
+        <v>62</v>
+      </c>
+      <c r="T78" t="s">
         <v>61</v>
-      </c>
-      <c r="S78" t="s">
-        <v>61</v>
-      </c>
-      <c r="T78" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -4838,7 +4844,7 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -4851,31 +4857,31 @@
         <v>7</v>
       </c>
       <c r="J79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R79" t="s">
+        <v>62</v>
+      </c>
+      <c r="S79" t="s">
+        <v>62</v>
+      </c>
+      <c r="T79" t="s">
         <v>61</v>
-      </c>
-      <c r="S79" t="s">
-        <v>61</v>
-      </c>
-      <c r="T79" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -4884,7 +4890,7 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -4897,31 +4903,31 @@
         <v>6</v>
       </c>
       <c r="J80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R80" t="s">
+        <v>62</v>
+      </c>
+      <c r="S80" t="s">
+        <v>62</v>
+      </c>
+      <c r="T80" t="s">
         <v>61</v>
-      </c>
-      <c r="S80" t="s">
-        <v>61</v>
-      </c>
-      <c r="T80" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -4930,7 +4936,7 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -4943,31 +4949,31 @@
         <v>5</v>
       </c>
       <c r="J81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R81" t="s">
+        <v>62</v>
+      </c>
+      <c r="S81" t="s">
+        <v>62</v>
+      </c>
+      <c r="T81" t="s">
         <v>61</v>
-      </c>
-      <c r="S81" t="s">
-        <v>61</v>
-      </c>
-      <c r="T81" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -4976,7 +4982,7 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -4989,31 +4995,31 @@
         <v>4</v>
       </c>
       <c r="J82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L82" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P82" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R82" t="s">
+        <v>62</v>
+      </c>
+      <c r="S82" t="s">
+        <v>62</v>
+      </c>
+      <c r="T82" t="s">
         <v>61</v>
-      </c>
-      <c r="S82" t="s">
-        <v>61</v>
-      </c>
-      <c r="T82" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -5022,7 +5028,7 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -5035,31 +5041,31 @@
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L83" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P83" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R83" t="s">
+        <v>64</v>
+      </c>
+      <c r="S83" t="s">
+        <v>64</v>
+      </c>
+      <c r="T83" t="s">
         <v>63</v>
-      </c>
-      <c r="S83" t="s">
-        <v>63</v>
-      </c>
-      <c r="T83" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -5068,7 +5074,7 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -5081,31 +5087,31 @@
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L84" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P84" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R84" t="s">
+        <v>64</v>
+      </c>
+      <c r="S84" t="s">
+        <v>64</v>
+      </c>
+      <c r="T84" t="s">
         <v>63</v>
-      </c>
-      <c r="S84" t="s">
-        <v>63</v>
-      </c>
-      <c r="T84" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -5114,7 +5120,7 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -5126,37 +5132,37 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K85" t="s">
+        <v>68</v>
+      </c>
+      <c r="L85" t="s">
+        <v>63</v>
+      </c>
+      <c r="N85" t="s">
         <v>67</v>
       </c>
-      <c r="L85" t="s">
-        <v>62</v>
-      </c>
-      <c r="N85" t="s">
-        <v>66</v>
-      </c>
       <c r="O85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P85" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T85" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -5165,7 +5171,7 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C86">
         <f>C85</f>
@@ -5178,37 +5184,37 @@
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H86" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J86" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K86" t="s">
+        <v>71</v>
+      </c>
+      <c r="L86" t="s">
+        <v>63</v>
+      </c>
+      <c r="N86" t="s">
+        <v>72</v>
+      </c>
+      <c r="O86" t="s">
         <v>70</v>
       </c>
-      <c r="L86" t="s">
-        <v>62</v>
-      </c>
-      <c r="N86" t="s">
-        <v>71</v>
-      </c>
-      <c r="O86" t="s">
-        <v>69</v>
-      </c>
       <c r="P86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R86" t="s">
+        <v>73</v>
+      </c>
+      <c r="S86" t="s">
         <v>72</v>
       </c>
-      <c r="S86" t="s">
-        <v>71</v>
-      </c>
       <c r="T86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -5217,7 +5223,7 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
@@ -5230,37 +5236,37 @@
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H87" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J87" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K87" t="s">
+        <v>71</v>
+      </c>
+      <c r="L87" t="s">
+        <v>74</v>
+      </c>
+      <c r="N87" t="s">
+        <v>72</v>
+      </c>
+      <c r="O87" t="s">
         <v>70</v>
       </c>
-      <c r="L87" t="s">
+      <c r="P87" t="s">
+        <v>74</v>
+      </c>
+      <c r="R87" t="s">
         <v>73</v>
       </c>
-      <c r="N87" t="s">
-        <v>71</v>
-      </c>
-      <c r="O87" t="s">
-        <v>69</v>
-      </c>
-      <c r="P87" t="s">
-        <v>73</v>
-      </c>
-      <c r="R87" t="s">
+      <c r="S87" t="s">
         <v>72</v>
       </c>
-      <c r="S87" t="s">
-        <v>71</v>
-      </c>
       <c r="T87" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -5269,7 +5275,7 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
@@ -5282,37 +5288,37 @@
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H88" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J88" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K88" t="s">
+        <v>71</v>
+      </c>
+      <c r="L88" t="s">
+        <v>74</v>
+      </c>
+      <c r="N88" t="s">
+        <v>72</v>
+      </c>
+      <c r="O88" t="s">
         <v>70</v>
       </c>
-      <c r="L88" t="s">
+      <c r="P88" t="s">
+        <v>74</v>
+      </c>
+      <c r="R88" t="s">
         <v>73</v>
       </c>
-      <c r="N88" t="s">
-        <v>71</v>
-      </c>
-      <c r="O88" t="s">
-        <v>69</v>
-      </c>
-      <c r="P88" t="s">
-        <v>73</v>
-      </c>
-      <c r="R88" t="s">
+      <c r="S88" t="s">
         <v>72</v>
       </c>
-      <c r="S88" t="s">
-        <v>71</v>
-      </c>
       <c r="T88" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -5321,7 +5327,7 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -5334,37 +5340,37 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H89" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J89" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K89" t="s">
+        <v>71</v>
+      </c>
+      <c r="L89" t="s">
+        <v>74</v>
+      </c>
+      <c r="N89" t="s">
+        <v>72</v>
+      </c>
+      <c r="O89" t="s">
         <v>70</v>
       </c>
-      <c r="L89" t="s">
+      <c r="P89" t="s">
+        <v>74</v>
+      </c>
+      <c r="R89" t="s">
         <v>73</v>
       </c>
-      <c r="N89" t="s">
-        <v>71</v>
-      </c>
-      <c r="O89" t="s">
-        <v>69</v>
-      </c>
-      <c r="P89" t="s">
-        <v>73</v>
-      </c>
-      <c r="R89" t="s">
+      <c r="S89" t="s">
         <v>72</v>
       </c>
-      <c r="S89" t="s">
-        <v>71</v>
-      </c>
       <c r="T89" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -5373,7 +5379,7 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -5386,37 +5392,37 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H90" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K90" t="s">
+        <v>71</v>
+      </c>
+      <c r="L90" t="s">
+        <v>75</v>
+      </c>
+      <c r="N90" t="s">
+        <v>72</v>
+      </c>
+      <c r="O90" t="s">
         <v>70</v>
       </c>
-      <c r="L90" t="s">
-        <v>74</v>
-      </c>
-      <c r="N90" t="s">
-        <v>71</v>
-      </c>
-      <c r="O90" t="s">
-        <v>69</v>
-      </c>
       <c r="P90" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R90" t="s">
+        <v>73</v>
+      </c>
+      <c r="S90" t="s">
         <v>72</v>
       </c>
-      <c r="S90" t="s">
-        <v>71</v>
-      </c>
       <c r="T90" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -5425,7 +5431,7 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -5438,37 +5444,37 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H91" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K91" t="s">
+        <v>71</v>
+      </c>
+      <c r="L91" t="s">
+        <v>75</v>
+      </c>
+      <c r="N91" t="s">
+        <v>72</v>
+      </c>
+      <c r="O91" t="s">
         <v>70</v>
       </c>
-      <c r="L91" t="s">
-        <v>74</v>
-      </c>
-      <c r="N91" t="s">
-        <v>71</v>
-      </c>
-      <c r="O91" t="s">
-        <v>69</v>
-      </c>
       <c r="P91" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R91" t="s">
+        <v>73</v>
+      </c>
+      <c r="S91" t="s">
         <v>72</v>
       </c>
-      <c r="S91" t="s">
-        <v>71</v>
-      </c>
       <c r="T91" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -5477,7 +5483,7 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -5490,37 +5496,37 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J92" t="s">
+        <v>76</v>
+      </c>
+      <c r="K92" t="s">
+        <v>77</v>
+      </c>
+      <c r="L92" t="s">
         <v>75</v>
       </c>
-      <c r="K92" t="s">
-        <v>76</v>
-      </c>
-      <c r="L92" t="s">
-        <v>74</v>
-      </c>
       <c r="N92" t="s">
+        <v>76</v>
+      </c>
+      <c r="O92" t="s">
+        <v>76</v>
+      </c>
+      <c r="P92" t="s">
         <v>75</v>
       </c>
-      <c r="O92" t="s">
+      <c r="R92" t="s">
+        <v>76</v>
+      </c>
+      <c r="S92" t="s">
+        <v>76</v>
+      </c>
+      <c r="T92" t="s">
         <v>75</v>
-      </c>
-      <c r="P92" t="s">
-        <v>74</v>
-      </c>
-      <c r="R92" t="s">
-        <v>75</v>
-      </c>
-      <c r="S92" t="s">
-        <v>75</v>
-      </c>
-      <c r="T92" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -5529,7 +5535,7 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -5542,37 +5548,37 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K93" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -5581,7 +5587,7 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -5594,37 +5600,37 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K94" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -5633,7 +5639,7 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -5646,37 +5652,37 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H95" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K95" t="s">
         <v>76</v>
       </c>
       <c r="L95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -5685,7 +5691,7 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -5698,37 +5704,37 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J96" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K96" t="s">
         <v>76</v>
       </c>
       <c r="L96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N96" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O96" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R96" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S96" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -5737,7 +5743,7 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -5750,37 +5756,37 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K97" t="s">
         <v>76</v>
       </c>
       <c r="L97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -5789,7 +5795,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -5801,37 +5807,37 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H98" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J98" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K98" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N98" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O98" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R98" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S98" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -5840,7 +5846,7 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C99">
         <f>C98</f>
@@ -5853,37 +5859,37 @@
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H99" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L99" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P99" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T99" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -5892,7 +5898,7 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
@@ -5905,37 +5911,37 @@
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H100" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="J100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L100" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P100" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T100" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -5944,7 +5950,7 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
@@ -5957,37 +5963,37 @@
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H101" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L101" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P101" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T101" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -5996,7 +6002,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -6009,37 +6015,37 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H102" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L102" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P102" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T102" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -6048,7 +6054,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -6061,37 +6067,37 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H103" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L103" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P103" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T103" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104" spans="1:20">
@@ -6100,7 +6106,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -6113,37 +6119,37 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H104" t="s">
+        <v>87</v>
+      </c>
+      <c r="J104" t="s">
+        <v>76</v>
+      </c>
+      <c r="K104" t="s">
+        <v>76</v>
+      </c>
+      <c r="L104" t="s">
         <v>85</v>
       </c>
-      <c r="J104" t="s">
-        <v>75</v>
-      </c>
-      <c r="K104" t="s">
-        <v>75</v>
-      </c>
-      <c r="L104" t="s">
-        <v>83</v>
-      </c>
       <c r="N104" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O104" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P104" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R104" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S104" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T104" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -6152,7 +6158,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -6165,37 +6171,37 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H105" t="s">
+        <v>87</v>
+      </c>
+      <c r="J105" t="s">
+        <v>76</v>
+      </c>
+      <c r="K105" t="s">
+        <v>76</v>
+      </c>
+      <c r="L105" t="s">
         <v>85</v>
       </c>
-      <c r="J105" t="s">
-        <v>75</v>
-      </c>
-      <c r="K105" t="s">
-        <v>75</v>
-      </c>
-      <c r="L105" t="s">
-        <v>83</v>
-      </c>
       <c r="N105" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O105" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P105" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R105" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S105" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T105" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -6204,7 +6210,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -6217,37 +6223,37 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H106" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L106" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P106" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T106" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -6256,7 +6262,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -6269,37 +6275,37 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H107" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L107" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P107" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S107" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T107" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -6308,7 +6314,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -6321,37 +6327,37 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H108" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L108" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P108" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T108" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -6360,7 +6366,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -6373,37 +6379,37 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H109" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J109" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K109" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L109" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N109" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O109" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P109" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R109" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S109" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T109" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="chessTexasStrategy" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="82">
   <si>
     <t>ID</t>
   </si>
@@ -151,190 +151,163 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_3000|2_10000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_10000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_10000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_10000|3_0|4_10000</t>
-  </si>
-  <si>
-    <t>1_0|2_2500|3_10000|4_0</t>
+    <t>1_10000|2_10000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_10000|2_10000|3_0|4_5000</t>
+  </si>
+  <si>
+    <t>1_10000|2_10000|3_0|4_10000</t>
   </si>
   <si>
     <t>同花顺</t>
   </si>
   <si>
-    <t>1_3000|2_8000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_8000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_8000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_8000|3_0|4_10000</t>
+    <t>1_8000|2_8000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_8000|2_8000|3_0|4_5000</t>
+  </si>
+  <si>
+    <t>1_8000|2_8000|3_0|4_10000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>1_8000|2_8000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_8000|2_8000|3_0|4_8000</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>1_0|2_8000|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_8000</t>
+  </si>
+  <si>
+    <t>1_0|2_6000|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_7000</t>
+  </si>
+  <si>
+    <t>1_0|2_6000|3_3000|4_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6000|3_4000|4_0</t>
+  </si>
+  <si>
+    <t>一对</t>
+  </si>
+  <si>
+    <t>1_10000|2_10000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_0|2_6000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_8000|2_8000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_0|2_4000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_4000|2_4000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_8000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_5000|3_5000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_5000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4000|3_6000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_10000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_10000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_7000|4_0</t>
   </si>
   <si>
     <t>1_0|2_2000|3_8000|4_0</t>
   </si>
   <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>1_2000|2_8000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2000|2_8000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2000|2_8000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_500|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_7000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>一对</t>
-  </si>
-  <si>
-    <t>1_3000|2_10000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_8000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_1000|2_4000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_8000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_10000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_1000|2_10000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_7000|4_0</t>
+    <t>高牌</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_9000|4_0</t>
+  </si>
+  <si>
+    <t>1_6000|2_6000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_4000|2_4000|3_0|4_1000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4000|3_4000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_6000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_11000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>高牌</t>
-  </si>
-  <si>
-    <t>1_2000|2_8000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_1000|2_4000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_1000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_500|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_11000|4_0</t>
   </si>
 </sst>
 </file>
@@ -961,12 +934,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1286,7 +1256,6 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
     <col min="7" max="8" width="32.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="12" width="29.75" customWidth="1"/>
@@ -1364,37 +1333,37 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1453,7 +1422,7 @@
       <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>28</v>
       </c>
       <c r="E5">
@@ -1466,25 +1435,25 @@
         <v>29</v>
       </c>
       <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
         <v>30</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
         <v>31</v>
       </c>
-      <c r="O5" t="s">
+      <c r="S5" t="s">
         <v>31</v>
       </c>
-      <c r="P5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>33</v>
-      </c>
-      <c r="S5" t="s">
-        <v>33</v>
-      </c>
       <c r="T5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1493,43 +1462,43 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
       <c r="E6">
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1538,44 +1507,44 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>42</v>
+      <c r="D7" t="s">
+        <v>36</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1584,44 +1553,44 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>43</v>
+      <c r="D8" t="s">
+        <v>37</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1630,44 +1599,44 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>44</v>
+      <c r="D9" t="s">
+        <v>38</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1676,44 +1645,44 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1722,44 +1691,44 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1768,44 +1737,44 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1814,44 +1783,44 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>7</v>
       </c>
       <c r="E13">
         <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1860,44 +1829,44 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
       </c>
       <c r="J14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1906,43 +1875,43 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>7</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>28</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L15" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1951,44 +1920,44 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>42</v>
+      <c r="D16" t="s">
+        <v>36</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T16" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1997,44 +1966,44 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>43</v>
+      <c r="D17" t="s">
+        <v>37</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="J17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R17" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S17" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -2043,44 +2012,44 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>44</v>
+      <c r="D18" t="s">
+        <v>38</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="J18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -2089,44 +2058,44 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>10</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R19" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S19" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -2135,44 +2104,44 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20">
         <v>9</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
       <c r="J20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T20" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -2181,44 +2150,44 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="J21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P21" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T21" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -2227,44 +2196,44 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22">
         <v>7</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
       <c r="J22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R22" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S22" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T22" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2273,44 +2242,44 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
       <c r="J23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O23" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P23" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R23" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S23" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T23" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -2319,44 +2288,44 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24">
         <v>5</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
       <c r="J24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O24" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R24" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T24" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2365,44 +2334,44 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25">
         <v>4</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P25" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2411,44 +2380,44 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26">
         <v>3</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="J26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P26" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R26" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S26" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2457,44 +2426,44 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27">
         <v>2</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="J27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L27" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T27" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2503,43 +2472,43 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>28</v>
       </c>
       <c r="E28">
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L28" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R28" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S28" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T28" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2548,44 +2517,44 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>42</v>
+      <c r="D29" t="s">
+        <v>36</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="J29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L29" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N29" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O29" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P29" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T29" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2594,44 +2563,44 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>43</v>
+      <c r="D30" t="s">
+        <v>37</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="J30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L30" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N30" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O30" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T30" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -2640,44 +2609,44 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>44</v>
+      <c r="D31" t="s">
+        <v>38</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="J31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L31" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N31" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O31" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P31" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R31" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T31" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -2686,44 +2655,44 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32">
         <v>10</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L32" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O32" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P32" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R32" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -2732,44 +2701,44 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33">
         <v>9</v>
       </c>
       <c r="E33">
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K33" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L33" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P33" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R33" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T33" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -2778,44 +2747,44 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34">
         <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="J34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L34" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P34" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R34" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S34" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T34" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2824,44 +2793,44 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35">
         <v>7</v>
       </c>
       <c r="E35">
         <v>7</v>
       </c>
       <c r="J35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P35" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R35" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S35" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2870,44 +2839,44 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36">
         <v>6</v>
       </c>
       <c r="E36">
         <v>6</v>
       </c>
       <c r="J36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O36" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P36" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R36" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S36" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -2916,44 +2885,44 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37">
         <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
       <c r="J37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L37" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N37" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O37" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P37" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R37" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S37" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T37" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -2962,44 +2931,44 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38">
         <v>4</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O38" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P38" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T38" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -3008,44 +2977,44 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39">
         <v>3</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="J39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L39" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P39" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R39" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S39" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T39" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -3054,44 +3023,44 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40">
         <v>2</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="J40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L40" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P40" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R40" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S40" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T40" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -3100,43 +3069,43 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>28</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L41" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N41" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O41" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P41" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R41" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S41" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T41" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -3145,44 +3114,44 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>42</v>
+      <c r="D42" t="s">
+        <v>36</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="J42" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K42" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L42" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P42" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R42" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S42" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T42" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3191,44 +3160,44 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>43</v>
+      <c r="D43" t="s">
+        <v>37</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="J43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L43" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P43" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R43" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S43" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T43" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3237,44 +3206,44 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>44</v>
+      <c r="D44" t="s">
+        <v>38</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="J44" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K44" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L44" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N44" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O44" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P44" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R44" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S44" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T44" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3283,44 +3252,44 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45">
         <v>10</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
       <c r="J45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L45" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N45" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O45" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P45" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R45" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S45" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T45" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3329,44 +3298,44 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46">
         <v>9</v>
       </c>
       <c r="E46">
         <v>9</v>
       </c>
       <c r="J46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L46" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O46" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P46" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R46" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S46" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T46" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3375,44 +3344,44 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47">
         <v>8</v>
       </c>
       <c r="E47">
         <v>8</v>
       </c>
       <c r="J47" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K47" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L47" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N47" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O47" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P47" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R47" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T47" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -3421,44 +3390,44 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48">
         <v>7</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
       <c r="J48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O48" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P48" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R48" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S48" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T48" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -3467,44 +3436,44 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49">
         <v>6</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="J49" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L49" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N49" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O49" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P49" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R49" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S49" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T49" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -3513,43 +3482,43 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>28</v>
       </c>
       <c r="E50">
         <v>14</v>
       </c>
       <c r="J50" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K50" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L50" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N50" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O50" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P50" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R50" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S50" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T50" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -3558,44 +3527,44 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>42</v>
+      <c r="D51" t="s">
+        <v>36</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="J51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L51" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N51" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O51" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P51" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R51" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S51" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T51" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3604,44 +3573,44 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>43</v>
+      <c r="D52" t="s">
+        <v>37</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="J52" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K52" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L52" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N52" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O52" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P52" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R52" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S52" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T52" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -3650,44 +3619,44 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>44</v>
+      <c r="D53" t="s">
+        <v>38</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="J53" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K53" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L53" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N53" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O53" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P53" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R53" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T53" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -3696,44 +3665,44 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54">
         <v>10</v>
       </c>
       <c r="E54">
         <v>10</v>
       </c>
       <c r="J54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L54" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N54" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O54" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P54" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R54" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T54" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -3742,44 +3711,44 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55">
         <v>9</v>
       </c>
       <c r="E55">
         <v>9</v>
       </c>
       <c r="J55" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K55" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L55" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O55" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P55" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R55" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S55" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T55" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -3788,44 +3757,44 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56">
         <v>8</v>
       </c>
       <c r="E56">
         <v>8</v>
       </c>
       <c r="J56" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K56" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L56" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N56" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O56" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P56" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R56" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S56" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T56" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -3834,44 +3803,44 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57">
         <v>7</v>
       </c>
       <c r="E57">
         <v>7</v>
       </c>
       <c r="J57" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K57" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L57" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N57" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O57" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P57" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R57" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S57" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T57" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -3880,44 +3849,44 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58">
         <v>6</v>
       </c>
       <c r="E58">
         <v>6</v>
       </c>
       <c r="J58" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K58" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L58" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N58" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O58" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P58" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R58" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S58" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T58" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -3926,43 +3895,43 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" t="s">
         <v>28</v>
       </c>
       <c r="E59">
         <v>14</v>
       </c>
       <c r="J59" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K59" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L59" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O59" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P59" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R59" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S59" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T59" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -3971,44 +3940,44 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>42</v>
+      <c r="D60" t="s">
+        <v>36</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="J60" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K60" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L60" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O60" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P60" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R60" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S60" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T60" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -4017,44 +3986,44 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>43</v>
+      <c r="D61" t="s">
+        <v>37</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="J61" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K61" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L61" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N61" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O61" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P61" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R61" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S61" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T61" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -4063,44 +4032,44 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>44</v>
+      <c r="D62" t="s">
+        <v>38</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="J62" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K62" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L62" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N62" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O62" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P62" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R62" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S62" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T62" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -4109,44 +4078,44 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63">
         <v>10</v>
       </c>
       <c r="E63">
         <v>10</v>
       </c>
       <c r="J63" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K63" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L63" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N63" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O63" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P63" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R63" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S63" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T63" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -4155,44 +4124,44 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64">
         <v>9</v>
       </c>
       <c r="E64">
         <v>9</v>
       </c>
       <c r="J64" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K64" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L64" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O64" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P64" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R64" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S64" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T64" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -4201,44 +4170,44 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65">
         <v>8</v>
       </c>
       <c r="E65">
         <v>8</v>
       </c>
       <c r="J65" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K65" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L65" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N65" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O65" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P65" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R65" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S65" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T65" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -4247,44 +4216,44 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66">
         <v>7</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
       <c r="J66" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K66" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L66" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N66" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O66" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P66" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R66" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S66" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T66" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -4293,44 +4262,44 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67">
         <v>6</v>
       </c>
       <c r="E67">
         <v>6</v>
       </c>
       <c r="J67" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K67" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L67" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N67" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O67" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P67" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R67" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S67" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T67" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -4339,44 +4308,44 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68">
         <v>5</v>
       </c>
       <c r="E68">
         <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K68" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L68" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O68" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P68" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R68" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S68" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T68" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -4385,44 +4354,44 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69">
         <v>4</v>
       </c>
       <c r="E69">
         <v>4</v>
       </c>
       <c r="J69" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K69" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L69" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O69" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P69" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R69" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S69" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T69" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -4431,44 +4400,44 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70">
         <v>3</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
       <c r="J70" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K70" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L70" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N70" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O70" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P70" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R70" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S70" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T70" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -4477,44 +4446,44 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71">
         <v>2</v>
       </c>
       <c r="E71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K71" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L71" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N71" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O71" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P71" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R71" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S71" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T71" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -4523,43 +4492,43 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" t="s">
         <v>28</v>
       </c>
       <c r="E72">
         <v>14</v>
       </c>
       <c r="J72" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K72" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L72" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N72" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O72" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P72" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R72" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S72" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T72" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -4568,44 +4537,44 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>42</v>
+      <c r="D73" t="s">
+        <v>36</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="J73" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K73" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L73" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N73" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O73" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P73" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R73" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S73" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T73" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -4614,44 +4583,44 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>43</v>
+      <c r="D74" t="s">
+        <v>37</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="J74" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K74" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="L74" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O74" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P74" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="R74" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S74" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T74" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:20">
@@ -4660,44 +4629,44 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>44</v>
+      <c r="D75" t="s">
+        <v>38</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="J75" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K75" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L75" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N75" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O75" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P75" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="R75" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="S75" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T75" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -4706,44 +4675,44 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76">
         <v>10</v>
       </c>
       <c r="E76">
         <v>10</v>
       </c>
       <c r="J76" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K76" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L76" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N76" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O76" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P76" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="R76" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="S76" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T76" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -4752,44 +4721,44 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77">
         <v>9</v>
       </c>
       <c r="E77">
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K77" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L77" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N77" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O77" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P77" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="R77" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="S77" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T77" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -4798,44 +4767,44 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78">
         <v>8</v>
       </c>
       <c r="E78">
         <v>8</v>
       </c>
       <c r="J78" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K78" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L78" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N78" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O78" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P78" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="R78" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="S78" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="T78" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:20">
@@ -4844,44 +4813,44 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79">
         <v>7</v>
       </c>
       <c r="E79">
         <v>7</v>
       </c>
       <c r="J79" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K79" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L79" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N79" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O79" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P79" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="R79" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="S79" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="T79" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -4890,44 +4859,44 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80">
         <v>6</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
       <c r="J80" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K80" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L80" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N80" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O80" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P80" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="R80" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="S80" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="T80" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -4936,44 +4905,44 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81">
         <v>5</v>
       </c>
       <c r="E81">
         <v>5</v>
       </c>
       <c r="J81" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K81" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L81" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N81" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O81" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P81" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="R81" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="S81" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="T81" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -4982,44 +4951,44 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82">
         <v>4</v>
       </c>
       <c r="E82">
         <v>4</v>
       </c>
       <c r="J82" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K82" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L82" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="N82" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O82" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P82" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="R82" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="S82" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="T82" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -5028,44 +4997,44 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83">
         <v>3</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K83" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L83" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="N83" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="O83" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P83" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="R83" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S83" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T83" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -5074,44 +5043,44 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84">
         <v>2</v>
       </c>
       <c r="E84">
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K84" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L84" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="N84" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="O84" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P84" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="R84" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S84" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T84" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -5120,49 +5089,49 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" t="s">
         <v>28</v>
       </c>
       <c r="E85">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H85" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J85" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="K85" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L85" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="N85" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="O85" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="P85" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="R85" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="S85" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="T85" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:20">
@@ -5171,50 +5140,50 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>42</v>
+      <c r="D86" t="s">
+        <v>36</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H86" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J86" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K86" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L86" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="N86" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O86" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P86" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="R86" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="S86" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T86" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -5223,50 +5192,50 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>43</v>
+      <c r="D87" t="s">
+        <v>37</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H87" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J87" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K87" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L87" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="N87" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O87" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P87" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="R87" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="S87" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T87" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -5275,50 +5244,50 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>44</v>
+      <c r="D88" t="s">
+        <v>38</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H88" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J88" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K88" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L88" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="N88" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O88" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P88" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="R88" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="S88" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T88" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -5327,50 +5296,50 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89">
         <v>10</v>
       </c>
       <c r="E89">
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H89" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J89" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K89" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L89" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="N89" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O89" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P89" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="R89" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="S89" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T89" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:20">
@@ -5379,50 +5348,50 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90">
         <v>9</v>
       </c>
       <c r="E90">
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H90" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J90" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K90" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L90" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N90" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O90" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P90" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R90" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="S90" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T90" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:20">
@@ -5431,50 +5400,50 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D91">
         <v>8</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H91" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J91" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K91" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L91" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N91" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O91" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P91" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R91" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="S91" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="T91" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -5483,50 +5452,50 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D92">
         <v>7</v>
       </c>
       <c r="E92">
         <v>7</v>
       </c>
       <c r="G92" t="s">
+        <v>61</v>
+      </c>
+      <c r="H92" t="s">
+        <v>61</v>
+      </c>
+      <c r="J92" t="s">
+        <v>68</v>
+      </c>
+      <c r="K92" t="s">
         <v>69</v>
       </c>
-      <c r="H92" t="s">
-        <v>69</v>
-      </c>
-      <c r="J92" t="s">
-        <v>76</v>
-      </c>
-      <c r="K92" t="s">
-        <v>77</v>
-      </c>
       <c r="L92" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N92" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O92" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P92" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R92" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S92" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T92" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -5535,50 +5504,50 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D93">
         <v>6</v>
       </c>
       <c r="E93">
         <v>6</v>
       </c>
       <c r="G93" t="s">
+        <v>61</v>
+      </c>
+      <c r="H93" t="s">
+        <v>61</v>
+      </c>
+      <c r="J93" t="s">
+        <v>68</v>
+      </c>
+      <c r="K93" t="s">
         <v>69</v>
       </c>
-      <c r="H93" t="s">
-        <v>69</v>
-      </c>
-      <c r="J93" t="s">
-        <v>76</v>
-      </c>
-      <c r="K93" t="s">
-        <v>77</v>
-      </c>
       <c r="L93" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N93" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O93" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P93" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R93" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S93" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T93" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -5587,50 +5556,50 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D94">
         <v>5</v>
       </c>
       <c r="E94">
         <v>5</v>
       </c>
       <c r="G94" t="s">
+        <v>61</v>
+      </c>
+      <c r="H94" t="s">
+        <v>61</v>
+      </c>
+      <c r="J94" t="s">
+        <v>68</v>
+      </c>
+      <c r="K94" t="s">
         <v>69</v>
       </c>
-      <c r="H94" t="s">
-        <v>69</v>
-      </c>
-      <c r="J94" t="s">
-        <v>76</v>
-      </c>
-      <c r="K94" t="s">
-        <v>77</v>
-      </c>
       <c r="L94" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N94" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O94" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P94" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R94" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S94" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T94" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:20">
@@ -5639,50 +5608,50 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D95">
         <v>4</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="G95" t="s">
+        <v>61</v>
+      </c>
+      <c r="H95" t="s">
+        <v>61</v>
+      </c>
+      <c r="J95" t="s">
+        <v>68</v>
+      </c>
+      <c r="K95" t="s">
         <v>69</v>
       </c>
-      <c r="H95" t="s">
-        <v>69</v>
-      </c>
-      <c r="J95" t="s">
-        <v>76</v>
-      </c>
-      <c r="K95" t="s">
-        <v>76</v>
-      </c>
       <c r="L95" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N95" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O95" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P95" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R95" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S95" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T95" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:20">
@@ -5691,50 +5660,50 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D96" s="1">
+      <c r="D96">
         <v>3</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="G96" t="s">
+        <v>61</v>
+      </c>
+      <c r="H96" t="s">
+        <v>61</v>
+      </c>
+      <c r="J96" t="s">
+        <v>68</v>
+      </c>
+      <c r="K96" t="s">
         <v>69</v>
       </c>
-      <c r="H96" t="s">
-        <v>69</v>
-      </c>
-      <c r="J96" t="s">
-        <v>76</v>
-      </c>
-      <c r="K96" t="s">
-        <v>76</v>
-      </c>
       <c r="L96" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N96" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O96" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P96" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="R96" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S96" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T96" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -5743,50 +5712,50 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D97">
         <v>2</v>
       </c>
       <c r="E97">
         <v>2</v>
       </c>
       <c r="G97" t="s">
+        <v>61</v>
+      </c>
+      <c r="H97" t="s">
+        <v>61</v>
+      </c>
+      <c r="J97" t="s">
+        <v>68</v>
+      </c>
+      <c r="K97" t="s">
         <v>69</v>
       </c>
-      <c r="H97" t="s">
-        <v>69</v>
-      </c>
-      <c r="J97" t="s">
-        <v>76</v>
-      </c>
-      <c r="K97" t="s">
-        <v>76</v>
-      </c>
       <c r="L97" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N97" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O97" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P97" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="R97" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S97" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T97" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -5795,49 +5764,49 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" t="s">
         <v>28</v>
       </c>
       <c r="E98">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H98" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L98" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P98" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="R98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S98" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T98" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -5846,50 +5815,50 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>42</v>
+      <c r="D99" t="s">
+        <v>36</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H99" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="J99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L99" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="N99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P99" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="R99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S99" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T99" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -5898,50 +5867,50 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>43</v>
+      <c r="D100" t="s">
+        <v>37</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H100" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="J100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L100" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="N100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P100" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="R100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S100" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T100" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="1:20">
@@ -5950,50 +5919,50 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>44</v>
+      <c r="D101" t="s">
+        <v>38</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H101" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L101" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="N101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P101" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="R101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S101" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T101" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -6002,50 +5971,50 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D102">
         <v>10</v>
       </c>
       <c r="E102">
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H102" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L102" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="N102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P102" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="R102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S102" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T102" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" spans="1:20">
@@ -6054,50 +6023,50 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D103">
         <v>9</v>
       </c>
       <c r="E103">
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H103" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J103" t="s">
+        <v>68</v>
+      </c>
+      <c r="K103" t="s">
+        <v>68</v>
+      </c>
+      <c r="L103" t="s">
         <v>76</v>
       </c>
-      <c r="K103" t="s">
+      <c r="N103" t="s">
+        <v>68</v>
+      </c>
+      <c r="O103" t="s">
+        <v>68</v>
+      </c>
+      <c r="P103" t="s">
         <v>76</v>
       </c>
-      <c r="L103" t="s">
-        <v>85</v>
-      </c>
-      <c r="N103" t="s">
+      <c r="R103" t="s">
+        <v>68</v>
+      </c>
+      <c r="S103" t="s">
+        <v>68</v>
+      </c>
+      <c r="T103" t="s">
         <v>76</v>
-      </c>
-      <c r="O103" t="s">
-        <v>76</v>
-      </c>
-      <c r="P103" t="s">
-        <v>85</v>
-      </c>
-      <c r="R103" t="s">
-        <v>76</v>
-      </c>
-      <c r="S103" t="s">
-        <v>76</v>
-      </c>
-      <c r="T103" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="104" spans="1:20">
@@ -6106,50 +6075,50 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D104">
         <v>8</v>
       </c>
       <c r="E104">
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="H104" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J104" t="s">
+        <v>68</v>
+      </c>
+      <c r="K104" t="s">
+        <v>68</v>
+      </c>
+      <c r="L104" t="s">
         <v>76</v>
       </c>
-      <c r="K104" t="s">
+      <c r="N104" t="s">
+        <v>68</v>
+      </c>
+      <c r="O104" t="s">
+        <v>68</v>
+      </c>
+      <c r="P104" t="s">
         <v>76</v>
       </c>
-      <c r="L104" t="s">
-        <v>85</v>
-      </c>
-      <c r="N104" t="s">
+      <c r="R104" t="s">
+        <v>68</v>
+      </c>
+      <c r="S104" t="s">
+        <v>68</v>
+      </c>
+      <c r="T104" t="s">
         <v>76</v>
-      </c>
-      <c r="O104" t="s">
-        <v>76</v>
-      </c>
-      <c r="P104" t="s">
-        <v>85</v>
-      </c>
-      <c r="R104" t="s">
-        <v>76</v>
-      </c>
-      <c r="S104" t="s">
-        <v>76</v>
-      </c>
-      <c r="T104" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -6158,50 +6127,50 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D105">
         <v>7</v>
       </c>
       <c r="E105">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="H105" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J105" t="s">
+        <v>68</v>
+      </c>
+      <c r="K105" t="s">
+        <v>68</v>
+      </c>
+      <c r="L105" t="s">
         <v>76</v>
       </c>
-      <c r="K105" t="s">
+      <c r="N105" t="s">
+        <v>68</v>
+      </c>
+      <c r="O105" t="s">
+        <v>68</v>
+      </c>
+      <c r="P105" t="s">
         <v>76</v>
       </c>
-      <c r="L105" t="s">
-        <v>85</v>
-      </c>
-      <c r="N105" t="s">
+      <c r="R105" t="s">
+        <v>68</v>
+      </c>
+      <c r="S105" t="s">
+        <v>68</v>
+      </c>
+      <c r="T105" t="s">
         <v>76</v>
-      </c>
-      <c r="O105" t="s">
-        <v>76</v>
-      </c>
-      <c r="P105" t="s">
-        <v>85</v>
-      </c>
-      <c r="R105" t="s">
-        <v>76</v>
-      </c>
-      <c r="S105" t="s">
-        <v>76</v>
-      </c>
-      <c r="T105" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -6210,50 +6179,50 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D106">
         <v>6</v>
       </c>
       <c r="E106">
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J106" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K106" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L106" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N106" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O106" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P106" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R106" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S106" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T106" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -6262,50 +6231,50 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D107">
         <v>5</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J107" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K107" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L107" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N107" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O107" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P107" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R107" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S107" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T107" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -6314,50 +6283,50 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D108" s="1">
+      <c r="D108">
         <v>4</v>
       </c>
       <c r="E108">
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H108" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J108" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K108" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L108" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N108" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O108" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P108" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R108" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S108" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T108" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -6366,50 +6335,50 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D109" s="1">
+      <c r="D109">
         <v>3</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J109" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K109" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L109" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N109" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O109" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P109" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R109" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S109" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="T109" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -79,16 +79,13 @@
     <t>无人加注的行为权重</t>
   </si>
   <si>
-    <t>他人加注的行为权重</t>
-  </si>
-  <si>
-    <t>第二轮</t>
-  </si>
-  <si>
     <t>他人加注的行为权重-我方牌大</t>
   </si>
   <si>
     <t>他人加注的行为权重-我方牌小</t>
+  </si>
+  <si>
+    <t>第二轮</t>
   </si>
   <si>
     <t>第三轮</t>
@@ -115,7 +112,10 @@
     <t>proactiveStrategy_1</t>
   </si>
   <si>
-    <t>passiveStrategy_1</t>
+    <t>passiveStrategyWin_1</t>
+  </si>
+  <si>
+    <t>passiveStrategyFailed_1</t>
   </si>
   <si>
     <t>proactiveStrategy_2</t>
@@ -151,43 +151,22 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_3000|2_10000|3_0|4_3000</t>
+    <t>1_1000|2_3000|3_0|4_3000</t>
   </si>
   <si>
-    <t>1_0|2_10000|3_10000|4_0</t>
+    <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_3000|2_10000|3_0|4_5000</t>
+    <t>1_1000|2_3000|3_0|4_5000</t>
   </si>
   <si>
-    <t>1_0|2_5000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_10000|3_0|4_10000</t>
-  </si>
-  <si>
-    <t>1_0|2_2500|3_10000|4_0</t>
+    <t>1_1000|2_3000|3_0|4_10000</t>
   </si>
   <si>
     <t>同花顺</t>
   </si>
   <si>
-    <t>1_3000|2_8000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_8000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_8000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_8000|3_0|4_10000</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_8000|4_0</t>
+    <t>1_0|2_0|3_8000|4_0</t>
   </si>
   <si>
     <t>K</t>
@@ -211,79 +190,46 @@
     <t>顺子</t>
   </si>
   <si>
-    <t>1_2000|2_8000|3_0|4_3000</t>
+    <t>1_1000|2_2000|3_0|4_3000</t>
   </si>
   <si>
-    <t>1_2000|2_8000|3_0|4_4000</t>
+    <t>1_1000|2_2000|3_0|4_4000</t>
   </si>
   <si>
-    <t>1_2000|2_8000|3_0|4_8000</t>
+    <t>1_1000|2_2000|3_0|4_8000</t>
   </si>
   <si>
     <t>三条</t>
   </si>
   <si>
+    <t>1_1000|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1000|2_3000|3_0|4_8000</t>
+  </si>
+  <si>
     <t>两对</t>
   </si>
   <si>
-    <t>1_0|2_2000|3_2000|4_0</t>
+    <t>1_0|2_0|3_2000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_1000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_500|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_2000</t>
+    <t>1_0|2_3000|3_0|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_3000|4_0</t>
   </si>
   <si>
-    <t>1_2000|2_6000|3_0|4_7000</t>
+    <t>1_0|2_3000|3_2000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
-    <t>1_2000|2_6000|3_0|4_6000</t>
-  </si>
-  <si>
     <t>一对</t>
   </si>
   <si>
-    <t>1_3000|2_10000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_8000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_1000|2_4000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_8000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_0|4_0</t>
+    <t>1_0|2_2000|3_0|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_5000|4_0</t>
@@ -292,46 +238,25 @@
     <t>1_0|2_0|3_6000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_10000|3_0|4_0</t>
+    <t>1_0|2_3000|3_4000|4_0</t>
   </si>
   <si>
-    <t>1_1000|2_10000|3_0|4_0</t>
+    <t>1_0|2_10000|3_0|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_7000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
     <t>高牌</t>
   </si>
   <si>
-    <t>1_2000|2_8000|3_0|4_1000</t>
+    <t>1_0|2_4000|3_0|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_9000|4_0</t>
   </si>
   <si>
-    <t>1_2000|2_6000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_1000|2_4000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_1000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_500|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_6000|4_0</t>
+    <t>1_0|2_0|3_500|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_11000|4_0</t>
@@ -500,23 +425,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -837,7 +768,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -861,16 +792,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -879,96 +810,102 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1282,20 +1219,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="7" max="8" width="32.5" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="12" width="29.75" customWidth="1"/>
-    <col min="14" max="16" width="27.85" customWidth="1"/>
-    <col min="17" max="17" width="20.7166666666667" customWidth="1"/>
-    <col min="18" max="20" width="26.0666666666667" customWidth="1"/>
+    <col min="9" max="9" width="29.75" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="13" width="29.75" customWidth="1"/>
+    <col min="15" max="17" width="27.85" customWidth="1"/>
+    <col min="18" max="18" width="20.7166666666667" customWidth="1"/>
+    <col min="19" max="21" width="26.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1314,135 +1252,144 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
       <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>20</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>21</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>22</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>23</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>24</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>25</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:21">
       <c r="A5">
         <f>100000+C5*1000+E5</f>
         <v>109014</v>
@@ -1459,41 +1406,50 @@
       <c r="E5">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
-        <v>29</v>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
       </c>
       <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
         <v>30</v>
       </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
       <c r="O5" t="s">
         <v>31</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>30</v>
       </c>
       <c r="S5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <f t="shared" ref="A6:A37" si="0">100000+C6*1000+E6</f>
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1504,179 +1460,215 @@
       <c r="E6">
         <v>14</v>
       </c>
-      <c r="J6" t="s">
-        <v>36</v>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R6" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
-      <c r="J7" t="s">
-        <v>36</v>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R7" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
-      <c r="J8" t="s">
-        <v>36</v>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P8" t="s">
-        <v>39</v>
-      </c>
-      <c r="R8" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
-      <c r="J9" t="s">
-        <v>36</v>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P9" t="s">
-        <v>39</v>
-      </c>
-      <c r="R9" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -1688,41 +1680,50 @@
       <c r="E10">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
-        <v>36</v>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
+        <v>34</v>
       </c>
       <c r="O10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
-      </c>
-      <c r="R10" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -1734,41 +1735,50 @@
       <c r="E11">
         <v>9</v>
       </c>
-      <c r="J11" t="s">
-        <v>36</v>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N11" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
-      </c>
-      <c r="R11" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -1780,41 +1790,50 @@
       <c r="E12">
         <v>8</v>
       </c>
-      <c r="J12" t="s">
-        <v>36</v>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
       </c>
       <c r="K12" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
-      </c>
-      <c r="R12" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -1826,41 +1845,50 @@
       <c r="E13">
         <v>7</v>
       </c>
-      <c r="J13" t="s">
-        <v>36</v>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
-      </c>
-      <c r="N13" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
+        <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R13" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -1872,41 +1900,50 @@
       <c r="E14">
         <v>6</v>
       </c>
-      <c r="J14" t="s">
-        <v>36</v>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
-      </c>
-      <c r="N14" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
+        <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
-      </c>
-      <c r="R14" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>34</v>
       </c>
       <c r="S14" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1917,179 +1954,215 @@
       <c r="E15">
         <v>14</v>
       </c>
-      <c r="J15" t="s">
-        <v>36</v>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
-      <c r="J16" t="s">
-        <v>36</v>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L16" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M16" t="s">
+        <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
-      </c>
-      <c r="R16" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
-      <c r="J17" t="s">
-        <v>36</v>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>34</v>
       </c>
       <c r="K17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
-      </c>
-      <c r="N17" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M17" t="s">
+        <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
-      </c>
-      <c r="R17" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>34</v>
       </c>
       <c r="S17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
-      <c r="J18" t="s">
-        <v>36</v>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
+        <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N18" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M18" t="s">
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P18" t="s">
-        <v>39</v>
-      </c>
-      <c r="R18" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>34</v>
       </c>
       <c r="S18" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -2101,41 +2174,50 @@
       <c r="E19">
         <v>10</v>
       </c>
-      <c r="J19" t="s">
-        <v>36</v>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M19" t="s">
+        <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P19" t="s">
-        <v>39</v>
-      </c>
-      <c r="R19" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>34</v>
       </c>
       <c r="S19" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -2147,41 +2229,50 @@
       <c r="E20">
         <v>9</v>
       </c>
-      <c r="J20" t="s">
-        <v>36</v>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M20" t="s">
+        <v>34</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
-      </c>
-      <c r="R20" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -2193,41 +2284,50 @@
       <c r="E21">
         <v>8</v>
       </c>
-      <c r="J21" t="s">
-        <v>36</v>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L21" t="s">
-        <v>37</v>
-      </c>
-      <c r="N21" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M21" t="s">
+        <v>34</v>
       </c>
       <c r="O21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P21" t="s">
-        <v>39</v>
-      </c>
-      <c r="R21" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -2239,41 +2339,50 @@
       <c r="E22">
         <v>7</v>
       </c>
-      <c r="J22" t="s">
-        <v>36</v>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M22" t="s">
+        <v>34</v>
       </c>
       <c r="O22" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P22" t="s">
-        <v>39</v>
-      </c>
-      <c r="R22" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -2285,41 +2394,50 @@
       <c r="E23">
         <v>6</v>
       </c>
-      <c r="J23" t="s">
-        <v>36</v>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>34</v>
       </c>
       <c r="K23" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M23" t="s">
+        <v>34</v>
       </c>
       <c r="O23" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P23" t="s">
-        <v>39</v>
-      </c>
-      <c r="R23" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -2331,41 +2449,50 @@
       <c r="E24">
         <v>5</v>
       </c>
-      <c r="J24" t="s">
-        <v>36</v>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>34</v>
       </c>
       <c r="K24" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
-      </c>
-      <c r="N24" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M24" t="s">
+        <v>34</v>
       </c>
       <c r="O24" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P24" t="s">
-        <v>39</v>
-      </c>
-      <c r="R24" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -2377,41 +2504,50 @@
       <c r="E25">
         <v>4</v>
       </c>
-      <c r="J25" t="s">
-        <v>36</v>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" t="s">
+        <v>34</v>
       </c>
       <c r="K25" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L25" t="s">
-        <v>37</v>
-      </c>
-      <c r="N25" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M25" t="s">
+        <v>34</v>
       </c>
       <c r="O25" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P25" t="s">
-        <v>39</v>
-      </c>
-      <c r="R25" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -2423,41 +2559,50 @@
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="J26" t="s">
-        <v>36</v>
+      <c r="G26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" t="s">
+        <v>34</v>
       </c>
       <c r="K26" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
-      </c>
-      <c r="N26" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M26" t="s">
+        <v>34</v>
       </c>
       <c r="O26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P26" t="s">
-        <v>39</v>
-      </c>
-      <c r="R26" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -2469,41 +2614,50 @@
       <c r="E27">
         <v>2</v>
       </c>
-      <c r="J27" t="s">
-        <v>36</v>
+      <c r="G27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>34</v>
       </c>
       <c r="K27" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L27" t="s">
-        <v>37</v>
-      </c>
-      <c r="N27" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
+        <v>34</v>
       </c>
       <c r="O27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P27" t="s">
-        <v>39</v>
-      </c>
-      <c r="R27" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>34</v>
       </c>
       <c r="S27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -2514,179 +2668,215 @@
       <c r="E28">
         <v>14</v>
       </c>
-      <c r="J28" t="s">
-        <v>36</v>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>34</v>
       </c>
       <c r="K28" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N28" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M28" t="s">
+        <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P28" t="s">
-        <v>39</v>
-      </c>
-      <c r="R28" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>34</v>
       </c>
       <c r="S28" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
-      <c r="J29" t="s">
-        <v>36</v>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>34</v>
       </c>
       <c r="K29" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L29" t="s">
-        <v>37</v>
-      </c>
-      <c r="N29" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M29" t="s">
+        <v>34</v>
       </c>
       <c r="O29" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P29" t="s">
-        <v>39</v>
-      </c>
-      <c r="R29" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>34</v>
       </c>
       <c r="S29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
-      <c r="J30" t="s">
-        <v>36</v>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" t="s">
+        <v>34</v>
       </c>
       <c r="K30" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L30" t="s">
-        <v>37</v>
-      </c>
-      <c r="N30" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M30" t="s">
+        <v>34</v>
       </c>
       <c r="O30" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P30" t="s">
-        <v>39</v>
-      </c>
-      <c r="R30" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>34</v>
       </c>
       <c r="S30" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
-      <c r="J31" t="s">
-        <v>36</v>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>34</v>
       </c>
       <c r="K31" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L31" t="s">
-        <v>37</v>
-      </c>
-      <c r="N31" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M31" t="s">
+        <v>34</v>
       </c>
       <c r="O31" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P31" t="s">
-        <v>39</v>
-      </c>
-      <c r="R31" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>34</v>
       </c>
       <c r="S31" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -2698,41 +2888,50 @@
       <c r="E32">
         <v>10</v>
       </c>
-      <c r="J32" t="s">
-        <v>36</v>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" t="s">
+        <v>34</v>
       </c>
       <c r="K32" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L32" t="s">
-        <v>37</v>
-      </c>
-      <c r="N32" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
+        <v>34</v>
       </c>
       <c r="O32" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R32" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>34</v>
       </c>
       <c r="S32" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -2744,41 +2943,50 @@
       <c r="E33">
         <v>9</v>
       </c>
-      <c r="J33" t="s">
-        <v>36</v>
+      <c r="G33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" t="s">
+        <v>34</v>
       </c>
       <c r="K33" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L33" t="s">
-        <v>37</v>
-      </c>
-      <c r="N33" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M33" t="s">
+        <v>34</v>
       </c>
       <c r="O33" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P33" t="s">
-        <v>39</v>
-      </c>
-      <c r="R33" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>34</v>
       </c>
       <c r="S33" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -2790,41 +2998,50 @@
       <c r="E34">
         <v>8</v>
       </c>
-      <c r="J34" t="s">
-        <v>36</v>
+      <c r="G34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" t="s">
+        <v>34</v>
       </c>
       <c r="K34" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L34" t="s">
-        <v>37</v>
-      </c>
-      <c r="N34" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M34" t="s">
+        <v>34</v>
       </c>
       <c r="O34" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P34" t="s">
-        <v>39</v>
-      </c>
-      <c r="R34" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>34</v>
       </c>
       <c r="S34" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -2836,41 +3053,50 @@
       <c r="E35">
         <v>7</v>
       </c>
-      <c r="J35" t="s">
-        <v>36</v>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" t="s">
+        <v>34</v>
       </c>
       <c r="K35" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L35" t="s">
-        <v>37</v>
-      </c>
-      <c r="N35" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M35" t="s">
+        <v>34</v>
       </c>
       <c r="O35" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P35" t="s">
-        <v>39</v>
-      </c>
-      <c r="R35" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -2882,41 +3108,50 @@
       <c r="E36">
         <v>6</v>
       </c>
-      <c r="J36" t="s">
-        <v>36</v>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" t="s">
+        <v>34</v>
       </c>
       <c r="K36" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L36" t="s">
-        <v>37</v>
-      </c>
-      <c r="N36" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
+        <v>34</v>
       </c>
       <c r="O36" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P36" t="s">
-        <v>39</v>
-      </c>
-      <c r="R36" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>34</v>
       </c>
       <c r="S36" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -2928,41 +3163,50 @@
       <c r="E37">
         <v>5</v>
       </c>
-      <c r="J37" t="s">
-        <v>36</v>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" t="s">
+        <v>34</v>
       </c>
       <c r="K37" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L37" t="s">
-        <v>37</v>
-      </c>
-      <c r="N37" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M37" t="s">
+        <v>34</v>
       </c>
       <c r="O37" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P37" t="s">
-        <v>39</v>
-      </c>
-      <c r="R37" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>34</v>
       </c>
       <c r="S37" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38">
         <f t="shared" ref="A38:A69" si="4">100000+C38*1000+E38</f>
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -2974,41 +3218,50 @@
       <c r="E38">
         <v>4</v>
       </c>
-      <c r="J38" t="s">
-        <v>36</v>
+      <c r="G38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" t="s">
+        <v>34</v>
       </c>
       <c r="K38" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L38" t="s">
-        <v>37</v>
-      </c>
-      <c r="N38" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M38" t="s">
+        <v>34</v>
       </c>
       <c r="O38" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P38" t="s">
-        <v>39</v>
-      </c>
-      <c r="R38" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>34</v>
       </c>
       <c r="S38" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39">
         <f t="shared" si="4"/>
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -3020,41 +3273,50 @@
       <c r="E39">
         <v>3</v>
       </c>
-      <c r="J39" t="s">
-        <v>36</v>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" t="s">
+        <v>34</v>
       </c>
       <c r="K39" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L39" t="s">
-        <v>37</v>
-      </c>
-      <c r="N39" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M39" t="s">
+        <v>34</v>
       </c>
       <c r="O39" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P39" t="s">
-        <v>39</v>
-      </c>
-      <c r="R39" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>34</v>
       </c>
       <c r="S39" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40">
         <f t="shared" si="4"/>
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -3066,41 +3328,50 @@
       <c r="E40">
         <v>2</v>
       </c>
-      <c r="J40" t="s">
-        <v>36</v>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" t="s">
+        <v>34</v>
       </c>
       <c r="K40" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L40" t="s">
-        <v>37</v>
-      </c>
-      <c r="N40" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M40" t="s">
+        <v>34</v>
       </c>
       <c r="O40" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P40" t="s">
-        <v>39</v>
-      </c>
-      <c r="R40" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>34</v>
       </c>
       <c r="S40" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41">
         <f t="shared" si="4"/>
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -3111,179 +3382,215 @@
       <c r="E41">
         <v>14</v>
       </c>
-      <c r="J41" t="s">
-        <v>36</v>
+      <c r="G41" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" t="s">
+        <v>34</v>
       </c>
       <c r="K41" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L41" t="s">
-        <v>37</v>
-      </c>
-      <c r="N41" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M41" t="s">
+        <v>34</v>
       </c>
       <c r="O41" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P41" t="s">
-        <v>39</v>
-      </c>
-      <c r="R41" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>34</v>
       </c>
       <c r="S41" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42">
         <f t="shared" si="4"/>
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
-      <c r="J42" t="s">
-        <v>36</v>
+      <c r="G42" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" t="s">
+        <v>34</v>
       </c>
       <c r="K42" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N42" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M42" t="s">
+        <v>34</v>
       </c>
       <c r="O42" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P42" t="s">
-        <v>39</v>
-      </c>
-      <c r="R42" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43">
         <f t="shared" si="4"/>
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
-      <c r="J43" t="s">
-        <v>36</v>
+      <c r="G43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" t="s">
+        <v>34</v>
       </c>
       <c r="K43" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L43" t="s">
-        <v>37</v>
-      </c>
-      <c r="N43" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M43" t="s">
+        <v>34</v>
       </c>
       <c r="O43" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P43" t="s">
-        <v>39</v>
-      </c>
-      <c r="R43" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>34</v>
       </c>
       <c r="S43" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44">
         <f t="shared" si="4"/>
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
-      <c r="J44" t="s">
-        <v>36</v>
+      <c r="G44" t="s">
+        <v>29</v>
+      </c>
+      <c r="H44" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44" t="s">
+        <v>34</v>
       </c>
       <c r="K44" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L44" t="s">
-        <v>37</v>
-      </c>
-      <c r="N44" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M44" t="s">
+        <v>34</v>
       </c>
       <c r="O44" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P44" t="s">
-        <v>39</v>
-      </c>
-      <c r="R44" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>34</v>
       </c>
       <c r="S44" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U44" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45">
         <f t="shared" si="4"/>
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
@@ -3295,41 +3602,50 @@
       <c r="E45">
         <v>10</v>
       </c>
-      <c r="J45" t="s">
-        <v>36</v>
+      <c r="G45" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" t="s">
+        <v>34</v>
       </c>
       <c r="K45" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L45" t="s">
-        <v>37</v>
-      </c>
-      <c r="N45" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M45" t="s">
+        <v>34</v>
       </c>
       <c r="O45" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P45" t="s">
-        <v>39</v>
-      </c>
-      <c r="R45" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>34</v>
       </c>
       <c r="S45" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T45" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U45" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46">
         <f t="shared" si="4"/>
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
@@ -3341,41 +3657,50 @@
       <c r="E46">
         <v>9</v>
       </c>
-      <c r="J46" t="s">
-        <v>36</v>
+      <c r="G46" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>34</v>
       </c>
       <c r="K46" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L46" t="s">
-        <v>37</v>
-      </c>
-      <c r="N46" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M46" t="s">
+        <v>34</v>
       </c>
       <c r="O46" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P46" t="s">
-        <v>39</v>
-      </c>
-      <c r="R46" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>34</v>
       </c>
       <c r="S46" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T46" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47">
         <f t="shared" si="4"/>
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
@@ -3387,41 +3712,50 @@
       <c r="E47">
         <v>8</v>
       </c>
-      <c r="J47" t="s">
-        <v>36</v>
+      <c r="G47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" t="s">
+        <v>34</v>
       </c>
       <c r="K47" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L47" t="s">
-        <v>37</v>
-      </c>
-      <c r="N47" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M47" t="s">
+        <v>34</v>
       </c>
       <c r="O47" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P47" t="s">
-        <v>39</v>
-      </c>
-      <c r="R47" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>34</v>
       </c>
       <c r="S47" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T47" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48">
         <f t="shared" si="4"/>
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
@@ -3433,41 +3767,50 @@
       <c r="E48">
         <v>7</v>
       </c>
-      <c r="J48" t="s">
-        <v>36</v>
+      <c r="G48" t="s">
+        <v>29</v>
+      </c>
+      <c r="H48" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" t="s">
+        <v>34</v>
       </c>
       <c r="K48" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
-      </c>
-      <c r="N48" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M48" t="s">
+        <v>34</v>
       </c>
       <c r="O48" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P48" t="s">
-        <v>39</v>
-      </c>
-      <c r="R48" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>34</v>
       </c>
       <c r="S48" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T48" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49">
         <f t="shared" si="4"/>
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
@@ -3479,41 +3822,50 @@
       <c r="E49">
         <v>6</v>
       </c>
-      <c r="J49" t="s">
-        <v>36</v>
+      <c r="G49" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" t="s">
+        <v>34</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L49" t="s">
-        <v>37</v>
-      </c>
-      <c r="N49" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M49" t="s">
+        <v>34</v>
       </c>
       <c r="O49" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P49" t="s">
-        <v>39</v>
-      </c>
-      <c r="R49" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>34</v>
       </c>
       <c r="S49" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U49" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50">
         <f t="shared" si="4"/>
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -3524,179 +3876,215 @@
       <c r="E50">
         <v>14</v>
       </c>
-      <c r="J50" t="s">
-        <v>36</v>
+      <c r="G50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I50" t="s">
+        <v>34</v>
       </c>
       <c r="K50" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>37</v>
-      </c>
-      <c r="N50" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M50" t="s">
+        <v>34</v>
       </c>
       <c r="O50" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P50" t="s">
-        <v>39</v>
-      </c>
-      <c r="R50" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>34</v>
       </c>
       <c r="S50" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T50" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U50" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51">
         <f t="shared" si="4"/>
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
-      <c r="J51" t="s">
-        <v>36</v>
+      <c r="G51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" t="s">
+        <v>34</v>
       </c>
       <c r="K51" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
-        <v>37</v>
-      </c>
-      <c r="N51" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M51" t="s">
+        <v>34</v>
       </c>
       <c r="O51" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P51" t="s">
-        <v>39</v>
-      </c>
-      <c r="R51" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>34</v>
       </c>
       <c r="S51" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T51" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U51" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52">
         <f t="shared" si="4"/>
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
-      <c r="J52" t="s">
-        <v>36</v>
+      <c r="G52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" t="s">
+        <v>34</v>
       </c>
       <c r="K52" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L52" t="s">
-        <v>37</v>
-      </c>
-      <c r="N52" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M52" t="s">
+        <v>34</v>
       </c>
       <c r="O52" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P52" t="s">
-        <v>39</v>
-      </c>
-      <c r="R52" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>34</v>
       </c>
       <c r="S52" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T52" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53">
         <f t="shared" si="4"/>
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
-      <c r="J53" t="s">
-        <v>36</v>
+      <c r="G53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H53" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" t="s">
+        <v>34</v>
       </c>
       <c r="K53" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L53" t="s">
-        <v>37</v>
-      </c>
-      <c r="N53" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M53" t="s">
+        <v>34</v>
       </c>
       <c r="O53" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P53" t="s">
-        <v>39</v>
-      </c>
-      <c r="R53" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>34</v>
       </c>
       <c r="S53" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U53" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54">
         <f t="shared" si="4"/>
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
@@ -3708,41 +4096,50 @@
       <c r="E54">
         <v>10</v>
       </c>
-      <c r="J54" t="s">
-        <v>36</v>
+      <c r="G54" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" t="s">
+        <v>34</v>
       </c>
       <c r="K54" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L54" t="s">
-        <v>37</v>
-      </c>
-      <c r="N54" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M54" t="s">
+        <v>34</v>
       </c>
       <c r="O54" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P54" t="s">
-        <v>39</v>
-      </c>
-      <c r="R54" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>34</v>
       </c>
       <c r="S54" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55">
         <f t="shared" si="4"/>
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
@@ -3754,41 +4151,50 @@
       <c r="E55">
         <v>9</v>
       </c>
-      <c r="J55" t="s">
-        <v>36</v>
+      <c r="G55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" t="s">
+        <v>34</v>
       </c>
       <c r="K55" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L55" t="s">
-        <v>37</v>
-      </c>
-      <c r="N55" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M55" t="s">
+        <v>34</v>
       </c>
       <c r="O55" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P55" t="s">
-        <v>39</v>
-      </c>
-      <c r="R55" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>34</v>
       </c>
       <c r="S55" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56">
         <f t="shared" si="4"/>
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
@@ -3800,41 +4206,50 @@
       <c r="E56">
         <v>8</v>
       </c>
-      <c r="J56" t="s">
-        <v>36</v>
+      <c r="G56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H56" t="s">
+        <v>29</v>
+      </c>
+      <c r="I56" t="s">
+        <v>34</v>
       </c>
       <c r="K56" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L56" t="s">
-        <v>37</v>
-      </c>
-      <c r="N56" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M56" t="s">
+        <v>34</v>
       </c>
       <c r="O56" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P56" t="s">
-        <v>39</v>
-      </c>
-      <c r="R56" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>34</v>
       </c>
       <c r="S56" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T56" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57">
         <f t="shared" si="4"/>
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
@@ -3846,41 +4261,50 @@
       <c r="E57">
         <v>7</v>
       </c>
-      <c r="J57" t="s">
-        <v>36</v>
+      <c r="G57" t="s">
+        <v>29</v>
+      </c>
+      <c r="H57" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" t="s">
+        <v>34</v>
       </c>
       <c r="K57" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L57" t="s">
-        <v>37</v>
-      </c>
-      <c r="N57" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="M57" t="s">
+        <v>34</v>
       </c>
       <c r="O57" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P57" t="s">
-        <v>39</v>
-      </c>
-      <c r="R57" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>34</v>
       </c>
       <c r="S57" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="T57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58">
         <f t="shared" si="4"/>
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
@@ -3892,41 +4316,50 @@
       <c r="E58">
         <v>6</v>
       </c>
-      <c r="J58" t="s">
-        <v>49</v>
+      <c r="G58" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" t="s">
+        <v>34</v>
       </c>
       <c r="K58" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L58" t="s">
-        <v>37</v>
-      </c>
-      <c r="N58" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M58" t="s">
+        <v>34</v>
       </c>
       <c r="O58" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P58" t="s">
-        <v>39</v>
-      </c>
-      <c r="R58" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>34</v>
       </c>
       <c r="S58" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T58" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U58" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59">
         <f t="shared" si="4"/>
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -3937,179 +4370,215 @@
       <c r="E59">
         <v>14</v>
       </c>
-      <c r="J59" t="s">
-        <v>49</v>
+      <c r="G59" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" t="s">
+        <v>34</v>
       </c>
       <c r="K59" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L59" t="s">
-        <v>37</v>
-      </c>
-      <c r="N59" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M59" t="s">
+        <v>34</v>
       </c>
       <c r="O59" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P59" t="s">
-        <v>39</v>
-      </c>
-      <c r="R59" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>34</v>
       </c>
       <c r="S59" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T59" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U59" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60">
         <f t="shared" si="4"/>
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
-      <c r="J60" t="s">
-        <v>49</v>
+      <c r="G60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" t="s">
+        <v>34</v>
       </c>
       <c r="K60" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L60" t="s">
-        <v>37</v>
-      </c>
-      <c r="N60" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M60" t="s">
+        <v>34</v>
       </c>
       <c r="O60" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P60" t="s">
-        <v>39</v>
-      </c>
-      <c r="R60" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>34</v>
       </c>
       <c r="S60" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61">
         <f t="shared" si="4"/>
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="J61" t="s">
-        <v>49</v>
+      <c r="G61" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" t="s">
+        <v>34</v>
       </c>
       <c r="K61" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L61" t="s">
-        <v>37</v>
-      </c>
-      <c r="N61" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M61" t="s">
+        <v>34</v>
       </c>
       <c r="O61" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P61" t="s">
-        <v>39</v>
-      </c>
-      <c r="R61" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>34</v>
       </c>
       <c r="S61" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T61" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U61" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62">
         <f t="shared" si="4"/>
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
-      <c r="J62" t="s">
-        <v>49</v>
+      <c r="G62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" t="s">
+        <v>34</v>
       </c>
       <c r="K62" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L62" t="s">
-        <v>37</v>
-      </c>
-      <c r="N62" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M62" t="s">
+        <v>34</v>
       </c>
       <c r="O62" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P62" t="s">
-        <v>39</v>
-      </c>
-      <c r="R62" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>34</v>
       </c>
       <c r="S62" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T62" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U62" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63">
         <f t="shared" si="4"/>
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -4121,41 +4590,50 @@
       <c r="E63">
         <v>10</v>
       </c>
-      <c r="J63" t="s">
-        <v>49</v>
+      <c r="G63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" t="s">
+        <v>34</v>
       </c>
       <c r="K63" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L63" t="s">
-        <v>37</v>
-      </c>
-      <c r="N63" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M63" t="s">
+        <v>34</v>
       </c>
       <c r="O63" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P63" t="s">
-        <v>39</v>
-      </c>
-      <c r="R63" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>34</v>
       </c>
       <c r="S63" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T63" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64">
         <f t="shared" si="4"/>
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -4167,41 +4645,50 @@
       <c r="E64">
         <v>9</v>
       </c>
-      <c r="J64" t="s">
-        <v>49</v>
+      <c r="G64" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" t="s">
+        <v>42</v>
+      </c>
+      <c r="I64" t="s">
+        <v>34</v>
       </c>
       <c r="K64" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L64" t="s">
-        <v>37</v>
-      </c>
-      <c r="N64" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="M64" t="s">
+        <v>34</v>
       </c>
       <c r="O64" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="P64" t="s">
-        <v>39</v>
-      </c>
-      <c r="R64" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>34</v>
       </c>
       <c r="S64" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T64" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U64" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65">
         <f t="shared" si="4"/>
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -4213,41 +4700,50 @@
       <c r="E65">
         <v>8</v>
       </c>
-      <c r="J65" t="s">
-        <v>49</v>
+      <c r="G65" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65" t="s">
+        <v>34</v>
       </c>
       <c r="K65" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L65" t="s">
-        <v>37</v>
-      </c>
-      <c r="N65" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M65" t="s">
+        <v>34</v>
       </c>
       <c r="O65" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P65" t="s">
-        <v>39</v>
-      </c>
-      <c r="R65" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>34</v>
       </c>
       <c r="S65" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T65" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66">
         <f t="shared" si="4"/>
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -4259,41 +4755,50 @@
       <c r="E66">
         <v>7</v>
       </c>
-      <c r="J66" t="s">
-        <v>49</v>
+      <c r="G66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" t="s">
+        <v>34</v>
       </c>
       <c r="K66" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L66" t="s">
-        <v>37</v>
-      </c>
-      <c r="N66" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M66" t="s">
+        <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P66" t="s">
-        <v>39</v>
-      </c>
-      <c r="R66" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>34</v>
       </c>
       <c r="S66" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T66" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U66" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67">
         <f t="shared" si="4"/>
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -4305,41 +4810,50 @@
       <c r="E67">
         <v>6</v>
       </c>
-      <c r="J67" t="s">
-        <v>49</v>
+      <c r="G67" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" t="s">
+        <v>34</v>
       </c>
       <c r="K67" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L67" t="s">
-        <v>37</v>
-      </c>
-      <c r="N67" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M67" t="s">
+        <v>34</v>
       </c>
       <c r="O67" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P67" t="s">
-        <v>39</v>
-      </c>
-      <c r="R67" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>34</v>
       </c>
       <c r="S67" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U67" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68">
         <f t="shared" si="4"/>
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -4351,41 +4865,50 @@
       <c r="E68">
         <v>5</v>
       </c>
-      <c r="J68" t="s">
-        <v>49</v>
+      <c r="G68" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68" t="s">
+        <v>29</v>
+      </c>
+      <c r="I68" t="s">
+        <v>34</v>
       </c>
       <c r="K68" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L68" t="s">
-        <v>37</v>
-      </c>
-      <c r="N68" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M68" t="s">
+        <v>34</v>
       </c>
       <c r="O68" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P68" t="s">
-        <v>39</v>
-      </c>
-      <c r="R68" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>34</v>
       </c>
       <c r="S68" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T68" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U68" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69">
         <f t="shared" si="4"/>
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -4397,41 +4920,50 @@
       <c r="E69">
         <v>4</v>
       </c>
-      <c r="J69" t="s">
-        <v>49</v>
+      <c r="G69" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69" t="s">
+        <v>29</v>
+      </c>
+      <c r="I69" t="s">
+        <v>34</v>
       </c>
       <c r="K69" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L69" t="s">
-        <v>37</v>
-      </c>
-      <c r="N69" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M69" t="s">
+        <v>34</v>
       </c>
       <c r="O69" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P69" t="s">
-        <v>39</v>
-      </c>
-      <c r="R69" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>34</v>
       </c>
       <c r="S69" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T69" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70">
         <f t="shared" ref="A70:A109" si="8">100000+C70*1000+E70</f>
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -4443,41 +4975,50 @@
       <c r="E70">
         <v>3</v>
       </c>
-      <c r="J70" t="s">
-        <v>49</v>
+      <c r="G70" t="s">
+        <v>29</v>
+      </c>
+      <c r="H70" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70" t="s">
+        <v>34</v>
       </c>
       <c r="K70" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L70" t="s">
-        <v>37</v>
-      </c>
-      <c r="N70" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M70" t="s">
+        <v>34</v>
       </c>
       <c r="O70" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P70" t="s">
-        <v>39</v>
-      </c>
-      <c r="R70" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>34</v>
       </c>
       <c r="S70" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T70" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U70" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71">
         <f t="shared" si="8"/>
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -4489,41 +5030,50 @@
       <c r="E71">
         <v>2</v>
       </c>
-      <c r="J71" t="s">
-        <v>49</v>
+      <c r="G71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" t="s">
+        <v>29</v>
+      </c>
+      <c r="I71" t="s">
+        <v>34</v>
       </c>
       <c r="K71" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L71" t="s">
-        <v>37</v>
-      </c>
-      <c r="N71" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M71" t="s">
+        <v>34</v>
       </c>
       <c r="O71" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P71" t="s">
-        <v>39</v>
-      </c>
-      <c r="R71" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>34</v>
       </c>
       <c r="S71" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T71" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U71" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72">
         <f t="shared" si="8"/>
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -4534,179 +5084,215 @@
       <c r="E72">
         <v>14</v>
       </c>
-      <c r="J72" t="s">
-        <v>49</v>
+      <c r="G72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" t="s">
+        <v>29</v>
+      </c>
+      <c r="I72" t="s">
+        <v>34</v>
       </c>
       <c r="K72" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L72" t="s">
-        <v>37</v>
-      </c>
-      <c r="N72" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M72" t="s">
+        <v>34</v>
       </c>
       <c r="O72" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P72" t="s">
-        <v>39</v>
-      </c>
-      <c r="R72" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>34</v>
       </c>
       <c r="S72" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T72" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U72" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73">
         <f t="shared" si="8"/>
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
-      <c r="J73" t="s">
-        <v>49</v>
+      <c r="G73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73" t="s">
+        <v>29</v>
+      </c>
+      <c r="I73" t="s">
+        <v>34</v>
       </c>
       <c r="K73" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L73" t="s">
-        <v>37</v>
-      </c>
-      <c r="N73" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="M73" t="s">
+        <v>34</v>
       </c>
       <c r="O73" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P73" t="s">
-        <v>39</v>
-      </c>
-      <c r="R73" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>34</v>
       </c>
       <c r="S73" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T73" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U73" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74">
         <f t="shared" si="8"/>
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
-      <c r="J74" t="s">
+      <c r="G74" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" t="s">
+        <v>29</v>
+      </c>
+      <c r="I74" t="s">
         <v>49</v>
       </c>
       <c r="K74" t="s">
+        <v>29</v>
+      </c>
+      <c r="L74" t="s">
+        <v>29</v>
+      </c>
+      <c r="M74" t="s">
         <v>49</v>
       </c>
-      <c r="L74" t="s">
-        <v>54</v>
-      </c>
-      <c r="N74" t="s">
-        <v>50</v>
-      </c>
       <c r="O74" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P74" t="s">
-        <v>55</v>
-      </c>
-      <c r="R74" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>49</v>
       </c>
       <c r="S74" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T74" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U74" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75">
         <f t="shared" si="8"/>
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
-      <c r="J75" t="s">
-        <v>57</v>
+      <c r="G75" t="s">
+        <v>29</v>
+      </c>
+      <c r="H75" t="s">
+        <v>29</v>
+      </c>
+      <c r="I75" t="s">
+        <v>49</v>
       </c>
       <c r="K75" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="L75" t="s">
-        <v>54</v>
-      </c>
-      <c r="N75" t="s">
-        <v>58</v>
+        <v>29</v>
+      </c>
+      <c r="M75" t="s">
+        <v>49</v>
       </c>
       <c r="O75" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="P75" t="s">
-        <v>55</v>
-      </c>
-      <c r="R75" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>49</v>
       </c>
       <c r="S75" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="T75" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U75" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76">
         <f t="shared" si="8"/>
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -4718,41 +5304,50 @@
       <c r="E76">
         <v>10</v>
       </c>
-      <c r="J76" t="s">
-        <v>57</v>
+      <c r="G76" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" t="s">
+        <v>49</v>
       </c>
       <c r="K76" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="L76" t="s">
-        <v>54</v>
-      </c>
-      <c r="N76" t="s">
-        <v>58</v>
+        <v>29</v>
+      </c>
+      <c r="M76" t="s">
+        <v>49</v>
       </c>
       <c r="O76" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="P76" t="s">
-        <v>55</v>
-      </c>
-      <c r="R76" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>49</v>
       </c>
       <c r="S76" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="T76" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U76" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77">
         <f t="shared" si="8"/>
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -4764,41 +5359,50 @@
       <c r="E77">
         <v>9</v>
       </c>
-      <c r="J77" t="s">
-        <v>57</v>
+      <c r="G77" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" t="s">
+        <v>29</v>
+      </c>
+      <c r="I77" t="s">
+        <v>49</v>
       </c>
       <c r="K77" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="L77" t="s">
-        <v>54</v>
-      </c>
-      <c r="N77" t="s">
-        <v>58</v>
+        <v>29</v>
+      </c>
+      <c r="M77" t="s">
+        <v>49</v>
       </c>
       <c r="O77" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="P77" t="s">
-        <v>55</v>
-      </c>
-      <c r="R77" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>49</v>
       </c>
       <c r="S77" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="T77" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78">
         <f t="shared" si="8"/>
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -4810,41 +5414,50 @@
       <c r="E78">
         <v>8</v>
       </c>
-      <c r="J78" t="s">
-        <v>60</v>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" t="s">
+        <v>50</v>
+      </c>
+      <c r="I78" t="s">
+        <v>51</v>
       </c>
       <c r="K78" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L78" t="s">
-        <v>61</v>
-      </c>
-      <c r="N78" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="M78" t="s">
+        <v>51</v>
       </c>
       <c r="O78" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P78" t="s">
-        <v>61</v>
-      </c>
-      <c r="R78" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>51</v>
       </c>
       <c r="S78" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="T78" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79">
         <f t="shared" si="8"/>
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -4856,41 +5469,50 @@
       <c r="E79">
         <v>7</v>
       </c>
-      <c r="J79" t="s">
-        <v>60</v>
+      <c r="G79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79" t="s">
+        <v>51</v>
       </c>
       <c r="K79" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L79" t="s">
-        <v>61</v>
-      </c>
-      <c r="N79" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="M79" t="s">
+        <v>51</v>
       </c>
       <c r="O79" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P79" t="s">
-        <v>61</v>
-      </c>
-      <c r="R79" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>51</v>
       </c>
       <c r="S79" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="T79" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80">
         <f t="shared" si="8"/>
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -4902,41 +5524,50 @@
       <c r="E80">
         <v>6</v>
       </c>
-      <c r="J80" t="s">
-        <v>60</v>
+      <c r="G80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80" t="s">
+        <v>51</v>
       </c>
       <c r="K80" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L80" t="s">
-        <v>61</v>
-      </c>
-      <c r="N80" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="M80" t="s">
+        <v>51</v>
       </c>
       <c r="O80" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P80" t="s">
-        <v>61</v>
-      </c>
-      <c r="R80" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>51</v>
       </c>
       <c r="S80" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="T80" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81">
         <f t="shared" si="8"/>
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -4948,41 +5579,50 @@
       <c r="E81">
         <v>5</v>
       </c>
-      <c r="J81" t="s">
-        <v>60</v>
+      <c r="G81" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81" t="s">
+        <v>51</v>
       </c>
       <c r="K81" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L81" t="s">
-        <v>61</v>
-      </c>
-      <c r="N81" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="M81" t="s">
+        <v>51</v>
       </c>
       <c r="O81" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P81" t="s">
-        <v>61</v>
-      </c>
-      <c r="R81" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>51</v>
       </c>
       <c r="S81" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="T81" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82">
         <f t="shared" si="8"/>
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -4994,41 +5634,50 @@
       <c r="E82">
         <v>4</v>
       </c>
-      <c r="J82" t="s">
-        <v>60</v>
+      <c r="G82" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82" t="s">
+        <v>51</v>
       </c>
       <c r="K82" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L82" t="s">
-        <v>61</v>
-      </c>
-      <c r="N82" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="M82" t="s">
+        <v>51</v>
       </c>
       <c r="O82" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P82" t="s">
-        <v>61</v>
-      </c>
-      <c r="R82" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>51</v>
       </c>
       <c r="S82" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="T82" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83">
         <f t="shared" si="8"/>
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -5040,41 +5689,50 @@
       <c r="E83">
         <v>3</v>
       </c>
-      <c r="J83" t="s">
-        <v>60</v>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" t="s">
+        <v>50</v>
+      </c>
+      <c r="I83" t="s">
+        <v>53</v>
       </c>
       <c r="K83" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L83" t="s">
-        <v>63</v>
-      </c>
-      <c r="N83" t="s">
-        <v>57</v>
+        <v>50</v>
+      </c>
+      <c r="M83" t="s">
+        <v>53</v>
       </c>
       <c r="O83" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="P83" t="s">
-        <v>63</v>
-      </c>
-      <c r="R83" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>53</v>
       </c>
       <c r="S83" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="T83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84">
         <f t="shared" si="8"/>
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -5086,41 +5744,50 @@
       <c r="E84">
         <v>2</v>
       </c>
-      <c r="J84" t="s">
-        <v>60</v>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="s">
+        <v>50</v>
+      </c>
+      <c r="I84" t="s">
+        <v>53</v>
       </c>
       <c r="K84" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L84" t="s">
-        <v>63</v>
-      </c>
-      <c r="N84" t="s">
-        <v>57</v>
+        <v>50</v>
+      </c>
+      <c r="M84" t="s">
+        <v>53</v>
       </c>
       <c r="O84" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="P84" t="s">
-        <v>63</v>
-      </c>
-      <c r="R84" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>53</v>
       </c>
       <c r="S84" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="T84" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85">
         <f t="shared" si="8"/>
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -5132,202 +5799,214 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H85" t="s">
-        <v>66</v>
-      </c>
-      <c r="J85" t="s">
-        <v>67</v>
+        <v>50</v>
+      </c>
+      <c r="I85" t="s">
+        <v>53</v>
       </c>
       <c r="K85" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L85" t="s">
-        <v>63</v>
-      </c>
-      <c r="N85" t="s">
-        <v>67</v>
+        <v>50</v>
+      </c>
+      <c r="M85" t="s">
+        <v>53</v>
       </c>
       <c r="O85" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="P85" t="s">
-        <v>63</v>
-      </c>
-      <c r="R85" t="s">
-        <v>67</v>
+        <v>50</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>53</v>
       </c>
       <c r="S85" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="T85" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86">
         <f t="shared" si="8"/>
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H86" t="s">
-        <v>69</v>
-      </c>
-      <c r="J86" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="I86" t="s">
+        <v>53</v>
       </c>
       <c r="K86" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="L86" t="s">
-        <v>63</v>
-      </c>
-      <c r="N86" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="M86" t="s">
+        <v>53</v>
       </c>
       <c r="O86" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="P86" t="s">
-        <v>63</v>
-      </c>
-      <c r="R86" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>53</v>
       </c>
       <c r="S86" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="T86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U86" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87">
         <f t="shared" si="8"/>
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H87" t="s">
-        <v>69</v>
-      </c>
-      <c r="J87" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="I87" t="s">
+        <v>56</v>
       </c>
       <c r="K87" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="L87" t="s">
-        <v>74</v>
-      </c>
-      <c r="N87" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="M87" t="s">
+        <v>56</v>
       </c>
       <c r="O87" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="P87" t="s">
-        <v>74</v>
-      </c>
-      <c r="R87" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>56</v>
       </c>
       <c r="S87" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="T87" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88">
         <f t="shared" si="8"/>
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H88" t="s">
-        <v>69</v>
-      </c>
-      <c r="J88" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="I88" t="s">
+        <v>56</v>
       </c>
       <c r="K88" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="L88" t="s">
-        <v>74</v>
-      </c>
-      <c r="N88" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="M88" t="s">
+        <v>56</v>
       </c>
       <c r="O88" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="P88" t="s">
-        <v>74</v>
-      </c>
-      <c r="R88" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>56</v>
       </c>
       <c r="S88" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="T88" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U88" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89">
         <f t="shared" si="8"/>
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -5340,46 +6019,49 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H89" t="s">
-        <v>69</v>
-      </c>
-      <c r="J89" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="I89" t="s">
+        <v>56</v>
       </c>
       <c r="K89" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="L89" t="s">
-        <v>74</v>
-      </c>
-      <c r="N89" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="M89" t="s">
+        <v>56</v>
       </c>
       <c r="O89" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="P89" t="s">
-        <v>74</v>
-      </c>
-      <c r="R89" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>56</v>
       </c>
       <c r="S89" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="T89" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U89" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90">
         <f t="shared" si="8"/>
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -5392,46 +6074,49 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H90" t="s">
-        <v>69</v>
-      </c>
-      <c r="J90" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="I90" t="s">
+        <v>57</v>
       </c>
       <c r="K90" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="L90" t="s">
-        <v>75</v>
-      </c>
-      <c r="N90" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="M90" t="s">
+        <v>57</v>
       </c>
       <c r="O90" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="P90" t="s">
-        <v>75</v>
-      </c>
-      <c r="R90" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>57</v>
       </c>
       <c r="S90" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="T90" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U90" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91">
         <f t="shared" si="8"/>
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -5444,46 +6129,49 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H91" t="s">
-        <v>69</v>
-      </c>
-      <c r="J91" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="I91" t="s">
+        <v>57</v>
       </c>
       <c r="K91" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="L91" t="s">
-        <v>75</v>
-      </c>
-      <c r="N91" t="s">
-        <v>72</v>
+        <v>50</v>
+      </c>
+      <c r="M91" t="s">
+        <v>57</v>
       </c>
       <c r="O91" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="P91" t="s">
-        <v>75</v>
-      </c>
-      <c r="R91" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>57</v>
       </c>
       <c r="S91" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="T91" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U91" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92">
         <f t="shared" si="8"/>
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -5496,46 +6184,49 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H92" t="s">
-        <v>69</v>
-      </c>
-      <c r="J92" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I92" t="s">
+        <v>57</v>
       </c>
       <c r="K92" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="L92" t="s">
-        <v>75</v>
-      </c>
-      <c r="N92" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M92" t="s">
+        <v>57</v>
       </c>
       <c r="O92" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P92" t="s">
-        <v>75</v>
-      </c>
-      <c r="R92" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>57</v>
       </c>
       <c r="S92" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T92" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U92" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93">
         <f t="shared" si="8"/>
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -5548,46 +6239,49 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H93" t="s">
-        <v>69</v>
-      </c>
-      <c r="J93" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I93" t="s">
+        <v>60</v>
       </c>
       <c r="K93" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="L93" t="s">
-        <v>78</v>
-      </c>
-      <c r="N93" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M93" t="s">
+        <v>60</v>
       </c>
       <c r="O93" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P93" t="s">
-        <v>78</v>
-      </c>
-      <c r="R93" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>60</v>
       </c>
       <c r="S93" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T93" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U93" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94">
         <f t="shared" si="8"/>
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -5600,46 +6294,49 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H94" t="s">
-        <v>69</v>
-      </c>
-      <c r="J94" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I94" t="s">
+        <v>60</v>
       </c>
       <c r="K94" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="L94" t="s">
-        <v>78</v>
-      </c>
-      <c r="N94" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M94" t="s">
+        <v>60</v>
       </c>
       <c r="O94" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P94" t="s">
-        <v>78</v>
-      </c>
-      <c r="R94" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>60</v>
       </c>
       <c r="S94" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T94" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U94" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95">
         <f t="shared" si="8"/>
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -5652,46 +6349,49 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H95" t="s">
-        <v>69</v>
-      </c>
-      <c r="J95" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I95" t="s">
+        <v>60</v>
       </c>
       <c r="K95" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="L95" t="s">
-        <v>78</v>
-      </c>
-      <c r="N95" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M95" t="s">
+        <v>60</v>
       </c>
       <c r="O95" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P95" t="s">
-        <v>78</v>
-      </c>
-      <c r="R95" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>60</v>
       </c>
       <c r="S95" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T95" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U95" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96">
         <f t="shared" si="8"/>
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -5704,46 +6404,49 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H96" t="s">
-        <v>69</v>
-      </c>
-      <c r="J96" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I96" t="s">
+        <v>34</v>
       </c>
       <c r="K96" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="L96" t="s">
-        <v>79</v>
-      </c>
-      <c r="N96" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M96" t="s">
+        <v>34</v>
       </c>
       <c r="O96" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P96" t="s">
-        <v>79</v>
-      </c>
-      <c r="R96" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>34</v>
       </c>
       <c r="S96" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T96" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U96" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97">
         <f t="shared" si="8"/>
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -5756,46 +6459,49 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="H97" t="s">
-        <v>69</v>
-      </c>
-      <c r="J97" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I97" t="s">
+        <v>34</v>
       </c>
       <c r="K97" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="L97" t="s">
-        <v>79</v>
-      </c>
-      <c r="N97" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M97" t="s">
+        <v>34</v>
       </c>
       <c r="O97" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P97" t="s">
-        <v>79</v>
-      </c>
-      <c r="R97" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>34</v>
       </c>
       <c r="S97" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T97" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U97" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98">
         <f t="shared" si="8"/>
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -5807,202 +6513,214 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H98" t="s">
-        <v>69</v>
-      </c>
-      <c r="J98" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I98" t="s">
+        <v>34</v>
       </c>
       <c r="K98" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L98" t="s">
-        <v>79</v>
-      </c>
-      <c r="N98" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M98" t="s">
+        <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P98" t="s">
-        <v>79</v>
-      </c>
-      <c r="R98" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>34</v>
       </c>
       <c r="S98" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T98" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U98" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99">
         <f t="shared" si="8"/>
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H99" t="s">
-        <v>81</v>
-      </c>
-      <c r="J99" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I99" t="s">
+        <v>63</v>
       </c>
       <c r="K99" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L99" t="s">
-        <v>82</v>
-      </c>
-      <c r="N99" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M99" t="s">
+        <v>63</v>
       </c>
       <c r="O99" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P99" t="s">
-        <v>82</v>
-      </c>
-      <c r="R99" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>63</v>
       </c>
       <c r="S99" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T99" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U99" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100">
         <f t="shared" si="8"/>
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H100" t="s">
-        <v>81</v>
-      </c>
-      <c r="J100" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I100" t="s">
+        <v>63</v>
       </c>
       <c r="K100" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="L100" t="s">
-        <v>82</v>
-      </c>
-      <c r="N100" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M100" t="s">
+        <v>63</v>
       </c>
       <c r="O100" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P100" t="s">
-        <v>82</v>
-      </c>
-      <c r="R100" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>63</v>
       </c>
       <c r="S100" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T100" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101">
         <f t="shared" si="8"/>
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H101" t="s">
-        <v>83</v>
-      </c>
-      <c r="J101" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I101" t="s">
+        <v>63</v>
       </c>
       <c r="K101" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L101" t="s">
-        <v>82</v>
-      </c>
-      <c r="N101" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M101" t="s">
+        <v>63</v>
       </c>
       <c r="O101" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P101" t="s">
-        <v>82</v>
-      </c>
-      <c r="R101" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>63</v>
       </c>
       <c r="S101" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T101" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U101" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102">
         <f t="shared" si="8"/>
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -6015,46 +6733,49 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H102" t="s">
-        <v>83</v>
-      </c>
-      <c r="J102" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I102" t="s">
+        <v>63</v>
       </c>
       <c r="K102" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L102" t="s">
-        <v>82</v>
-      </c>
-      <c r="N102" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M102" t="s">
+        <v>63</v>
       </c>
       <c r="O102" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P102" t="s">
-        <v>82</v>
-      </c>
-      <c r="R102" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>63</v>
       </c>
       <c r="S102" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T102" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U102" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103">
         <f t="shared" si="8"/>
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -6067,46 +6788,49 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H103" t="s">
-        <v>84</v>
-      </c>
-      <c r="J103" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I103" t="s">
+        <v>30</v>
       </c>
       <c r="K103" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L103" t="s">
-        <v>85</v>
-      </c>
-      <c r="N103" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M103" t="s">
+        <v>30</v>
       </c>
       <c r="O103" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P103" t="s">
-        <v>85</v>
-      </c>
-      <c r="R103" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>30</v>
       </c>
       <c r="S103" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T103" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104">
         <f t="shared" si="8"/>
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -6119,46 +6843,49 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H104" t="s">
-        <v>87</v>
-      </c>
-      <c r="J104" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I104" t="s">
+        <v>30</v>
       </c>
       <c r="K104" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L104" t="s">
-        <v>85</v>
-      </c>
-      <c r="N104" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M104" t="s">
+        <v>30</v>
       </c>
       <c r="O104" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P104" t="s">
-        <v>85</v>
-      </c>
-      <c r="R104" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>30</v>
       </c>
       <c r="S104" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T104" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U104" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105">
         <f t="shared" si="8"/>
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -6171,46 +6898,49 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H105" t="s">
-        <v>87</v>
-      </c>
-      <c r="J105" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I105" t="s">
+        <v>30</v>
       </c>
       <c r="K105" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L105" t="s">
-        <v>85</v>
-      </c>
-      <c r="N105" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M105" t="s">
+        <v>30</v>
       </c>
       <c r="O105" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P105" t="s">
-        <v>85</v>
-      </c>
-      <c r="R105" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>30</v>
       </c>
       <c r="S105" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T105" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U105" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106">
         <f t="shared" si="8"/>
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -6223,46 +6953,49 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H106" t="s">
-        <v>89</v>
-      </c>
-      <c r="J106" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="I106" t="s">
+        <v>65</v>
       </c>
       <c r="K106" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L106" t="s">
-        <v>90</v>
-      </c>
-      <c r="N106" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="M106" t="s">
+        <v>65</v>
       </c>
       <c r="O106" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P106" t="s">
-        <v>90</v>
-      </c>
-      <c r="R106" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>65</v>
       </c>
       <c r="S106" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T106" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U106" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107">
         <f t="shared" si="8"/>
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -6275,46 +7008,49 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H107" t="s">
-        <v>89</v>
-      </c>
-      <c r="J107" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="I107" t="s">
+        <v>65</v>
       </c>
       <c r="K107" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L107" t="s">
-        <v>90</v>
-      </c>
-      <c r="N107" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="M107" t="s">
+        <v>65</v>
       </c>
       <c r="O107" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P107" t="s">
-        <v>90</v>
-      </c>
-      <c r="R107" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>65</v>
       </c>
       <c r="S107" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T107" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U107" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108">
         <f t="shared" si="8"/>
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -6327,46 +7063,49 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H108" t="s">
-        <v>79</v>
-      </c>
-      <c r="J108" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="I108" t="s">
+        <v>65</v>
       </c>
       <c r="K108" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L108" t="s">
-        <v>90</v>
-      </c>
-      <c r="N108" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="M108" t="s">
+        <v>65</v>
       </c>
       <c r="O108" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P108" t="s">
-        <v>90</v>
-      </c>
-      <c r="R108" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>65</v>
       </c>
       <c r="S108" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T108" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U108" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109">
         <f t="shared" si="8"/>
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -6379,37 +7118,40 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H109" t="s">
-        <v>79</v>
-      </c>
-      <c r="J109" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="I109" t="s">
+        <v>65</v>
       </c>
       <c r="K109" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L109" t="s">
-        <v>90</v>
-      </c>
-      <c r="N109" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="M109" t="s">
+        <v>65</v>
       </c>
       <c r="O109" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="P109" t="s">
-        <v>90</v>
-      </c>
-      <c r="R109" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>65</v>
       </c>
       <c r="S109" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T109" t="s">
-        <v>90</v>
+        <v>59</v>
+      </c>
+      <c r="U109" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="chessTexasStrategy" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -79,16 +79,13 @@
     <t>无人加注的行为权重</t>
   </si>
   <si>
-    <t>他人加注的行为权重</t>
-  </si>
-  <si>
-    <t>第二轮</t>
-  </si>
-  <si>
     <t>他人加注的行为权重-我方牌大</t>
   </si>
   <si>
     <t>他人加注的行为权重-我方牌小</t>
+  </si>
+  <si>
+    <t>第二轮</t>
   </si>
   <si>
     <t>第三轮</t>
@@ -115,7 +112,10 @@
     <t>proactiveStrategy_1</t>
   </si>
   <si>
-    <t>passiveStrategy_1</t>
+    <t>passiveStrategyWin_1</t>
+  </si>
+  <si>
+    <t>passiveStrategyFailed_1</t>
   </si>
   <si>
     <t>proactiveStrategy_2</t>
@@ -151,25 +151,22 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_3000</t>
+    <t>1_1000|2_3000|3_0|4_3000</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_5000</t>
+    <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_10000</t>
+    <t>1_1000|2_3000|3_0|4_5000</t>
+  </si>
+  <si>
+    <t>1_1000|2_3000|3_0|4_10000</t>
   </si>
   <si>
     <t>同花顺</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_10000</t>
+    <t>1_0|2_0|3_8000|4_0</t>
   </si>
   <si>
     <t>K</t>
@@ -193,121 +190,76 @@
     <t>顺子</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_4000</t>
+    <t>1_1000|2_2000|3_0|4_3000</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_8000</t>
+    <t>1_1000|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1000|2_2000|3_0|4_8000</t>
   </si>
   <si>
     <t>三条</t>
   </si>
   <si>
+    <t>1_1000|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1000|2_3000|3_0|4_8000</t>
+  </si>
+  <si>
     <t>两对</t>
   </si>
   <si>
-    <t>1_0|2_8000|3_2000|4_0</t>
+    <t>1_0|2_0|3_2000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_3000</t>
+    <t>1_0|2_3000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_4000</t>
+    <t>1_0|2_0|3_3000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_8000</t>
+    <t>1_0|2_3000|3_2000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_6000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_7000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_4000|4_0</t>
+    <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
     <t>一对</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_1000</t>
+    <t>1_0|2_2000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_0|2_6000|3_0|4_0</t>
+    <t>1_0|2_0|3_5000|4_0</t>
   </si>
   <si>
-    <t>1_6000|2_6000|3_0|4_0</t>
+    <t>1_0|2_0|3_6000|4_0</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_1000</t>
+    <t>1_0|2_3000|3_4000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_10000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_7000|4_0</t>
+  </si>
+  <si>
+    <t>高牌</t>
   </si>
   <si>
     <t>1_0|2_4000|3_0|4_0</t>
   </si>
   <si>
-    <t>1_4000|2_4000|3_0|4_0</t>
+    <t>1_0|2_0|3_9000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_8000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_10000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_10000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>高牌</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_4000|2_4000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_6000|4_0</t>
+    <t>1_0|2_0|3_500|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_11000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
   </si>
 </sst>
 </file>
@@ -473,23 +425,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -810,7 +768,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -834,16 +792,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -852,93 +810,102 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1252,19 +1219,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
     <col min="7" max="8" width="32.5" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="12" width="29.75" customWidth="1"/>
-    <col min="14" max="16" width="27.85" customWidth="1"/>
-    <col min="17" max="17" width="20.7166666666667" customWidth="1"/>
-    <col min="18" max="20" width="26.0666666666667" customWidth="1"/>
+    <col min="9" max="9" width="29.75" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="13" width="29.75" customWidth="1"/>
+    <col min="15" max="17" width="27.85" customWidth="1"/>
+    <col min="18" max="18" width="20.7166666666667" customWidth="1"/>
+    <col min="19" max="21" width="26.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1283,135 +1252,144 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
       <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>20</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>21</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>22</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>23</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>24</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>25</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:21">
       <c r="A5">
         <f>100000+C5*1000+E5</f>
         <v>109014</v>
@@ -1422,14 +1400,20 @@
       <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E5">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
-        <v>29</v>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
@@ -1437,2441 +1421,2918 @@
       <c r="L5" t="s">
         <v>29</v>
       </c>
-      <c r="N5" t="s">
+      <c r="M5" t="s">
         <v>30</v>
       </c>
       <c r="O5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
         <v>30</v>
       </c>
-      <c r="P5" t="s">
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
         <v>30</v>
       </c>
-      <c r="R5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <f t="shared" ref="A6:A37" si="0">100000+C6*1000+E6</f>
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E6">
         <v>14</v>
       </c>
-      <c r="J6" t="s">
-        <v>33</v>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
         <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>36</v>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
-      <c r="J7" t="s">
-        <v>33</v>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
         <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
-      </c>
-      <c r="R7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
-      <c r="J8" t="s">
-        <v>33</v>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
         <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
+      <c r="D9" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
-      <c r="J9" t="s">
-        <v>33</v>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
         <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
-        <v>33</v>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
         <v>34</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
-      </c>
-      <c r="R10" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
-      <c r="J11" t="s">
-        <v>33</v>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
         <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
-      </c>
-      <c r="R11" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
       </c>
-      <c r="J12" t="s">
-        <v>33</v>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
         <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>7</v>
       </c>
       <c r="E13">
         <v>7</v>
       </c>
-      <c r="J13" t="s">
-        <v>33</v>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>34</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
         <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
-      </c>
-      <c r="R13" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
       </c>
-      <c r="J14" t="s">
-        <v>33</v>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>34</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
         <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
-      </c>
-      <c r="R14" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>34</v>
       </c>
       <c r="S14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>7</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
-      <c r="J15" t="s">
-        <v>33</v>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
         <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
-      <c r="D16" t="s">
-        <v>36</v>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
-      <c r="J16" t="s">
-        <v>33</v>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" t="s">
         <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
-      <c r="D17" t="s">
-        <v>37</v>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
-      <c r="J17" t="s">
-        <v>33</v>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>34</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" t="s">
         <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P17" t="s">
-        <v>34</v>
-      </c>
-      <c r="R17" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>34</v>
       </c>
       <c r="S17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D18" t="s">
-        <v>38</v>
+      <c r="D18" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
-      <c r="J18" t="s">
-        <v>33</v>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" t="s">
+        <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
-      </c>
-      <c r="N18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" t="s">
         <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
-      </c>
-      <c r="R18" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>34</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>10</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
-      <c r="J19" t="s">
-        <v>33</v>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
-      </c>
-      <c r="N19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" t="s">
         <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>34</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>9</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
-      <c r="J20" t="s">
-        <v>33</v>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
-      </c>
-      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" t="s">
         <v>34</v>
       </c>
       <c r="O20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
-      </c>
-      <c r="R20" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
-      <c r="J21" t="s">
-        <v>33</v>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>34</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
-      </c>
-      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" t="s">
         <v>34</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
-      </c>
-      <c r="R21" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>7</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
-      <c r="J22" t="s">
-        <v>33</v>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>34</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
-      </c>
-      <c r="N22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" t="s">
         <v>34</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
-      </c>
-      <c r="R22" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>6</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
-      <c r="J23" t="s">
-        <v>33</v>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>34</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
-      </c>
-      <c r="N23" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" t="s">
         <v>34</v>
       </c>
       <c r="O23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
-      </c>
-      <c r="R23" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
-      <c r="J24" t="s">
-        <v>33</v>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>34</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" t="s">
         <v>34</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P24" t="s">
-        <v>34</v>
-      </c>
-      <c r="R24" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>4</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
-      <c r="J25" t="s">
-        <v>33</v>
+      <c r="G25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" t="s">
+        <v>34</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L25" t="s">
-        <v>33</v>
-      </c>
-      <c r="N25" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" t="s">
         <v>34</v>
       </c>
       <c r="O25" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
-      </c>
-      <c r="R25" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="J26" t="s">
-        <v>33</v>
+      <c r="G26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" t="s">
+        <v>34</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
-      </c>
-      <c r="N26" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s">
         <v>34</v>
       </c>
       <c r="O26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
-      </c>
-      <c r="R26" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
-      <c r="J27" t="s">
-        <v>33</v>
+      <c r="G27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>34</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L27" t="s">
-        <v>33</v>
-      </c>
-      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
         <v>34</v>
       </c>
       <c r="O27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P27" t="s">
-        <v>34</v>
-      </c>
-      <c r="R27" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>34</v>
       </c>
       <c r="S27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E28">
         <v>14</v>
       </c>
-      <c r="J28" t="s">
-        <v>33</v>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>34</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L28" t="s">
-        <v>33</v>
-      </c>
-      <c r="N28" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28" t="s">
         <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
-      </c>
-      <c r="R28" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>34</v>
       </c>
       <c r="S28" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
-      <c r="D29" t="s">
-        <v>36</v>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
-      <c r="J29" t="s">
-        <v>33</v>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>34</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L29" t="s">
-        <v>33</v>
-      </c>
-      <c r="N29" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" t="s">
         <v>34</v>
       </c>
       <c r="O29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P29" t="s">
-        <v>34</v>
-      </c>
-      <c r="R29" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>34</v>
       </c>
       <c r="S29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
-      <c r="D30" t="s">
-        <v>37</v>
+      <c r="D30" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
-      <c r="J30" t="s">
-        <v>33</v>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" t="s">
+        <v>34</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
-      </c>
-      <c r="N30" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" t="s">
         <v>34</v>
       </c>
       <c r="O30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
-      </c>
-      <c r="R30" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>34</v>
       </c>
       <c r="S30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D31" t="s">
-        <v>38</v>
+      <c r="D31" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
-      <c r="J31" t="s">
-        <v>33</v>
+      <c r="G31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>34</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
-      </c>
-      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" t="s">
         <v>34</v>
       </c>
       <c r="O31" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P31" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>34</v>
       </c>
       <c r="S31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>10</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
-      <c r="J32" t="s">
-        <v>33</v>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" t="s">
+        <v>34</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
-      </c>
-      <c r="N32" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
         <v>34</v>
       </c>
       <c r="O32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
-      </c>
-      <c r="R32" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>34</v>
       </c>
       <c r="S32" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>9</v>
       </c>
       <c r="E33">
         <v>9</v>
       </c>
-      <c r="J33" t="s">
-        <v>33</v>
+      <c r="G33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" t="s">
+        <v>34</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
-      </c>
-      <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" t="s">
         <v>34</v>
       </c>
       <c r="O33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P33" t="s">
-        <v>34</v>
-      </c>
-      <c r="R33" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>34</v>
       </c>
       <c r="S33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
-      <c r="J34" t="s">
-        <v>33</v>
+      <c r="G34" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" t="s">
+        <v>34</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
-      </c>
-      <c r="N34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s">
         <v>34</v>
       </c>
       <c r="O34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P34" t="s">
-        <v>34</v>
-      </c>
-      <c r="R34" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>34</v>
       </c>
       <c r="S34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
         <v>7</v>
       </c>
       <c r="E35">
         <v>7</v>
       </c>
-      <c r="J35" t="s">
-        <v>33</v>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" t="s">
+        <v>34</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
-      </c>
-      <c r="N35" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" t="s">
         <v>34</v>
       </c>
       <c r="O35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
-      </c>
-      <c r="R35" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>6</v>
       </c>
       <c r="E36">
         <v>6</v>
       </c>
-      <c r="J36" t="s">
-        <v>33</v>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" t="s">
+        <v>34</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L36" t="s">
-        <v>33</v>
-      </c>
-      <c r="N36" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
         <v>34</v>
       </c>
       <c r="O36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P36" t="s">
-        <v>34</v>
-      </c>
-      <c r="R36" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>34</v>
       </c>
       <c r="S36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
-      <c r="J37" t="s">
-        <v>33</v>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" t="s">
+        <v>34</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N37" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" t="s">
         <v>34</v>
       </c>
       <c r="O37" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P37" t="s">
-        <v>34</v>
-      </c>
-      <c r="R37" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>34</v>
       </c>
       <c r="S37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38">
         <f t="shared" ref="A38:A69" si="4">100000+C38*1000+E38</f>
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>4</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
-      <c r="J38" t="s">
-        <v>33</v>
+      <c r="G38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" t="s">
+        <v>34</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L38" t="s">
-        <v>33</v>
-      </c>
-      <c r="N38" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" t="s">
         <v>34</v>
       </c>
       <c r="O38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P38" t="s">
-        <v>34</v>
-      </c>
-      <c r="R38" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>34</v>
       </c>
       <c r="S38" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39">
         <f t="shared" si="4"/>
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>3</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
-      <c r="J39" t="s">
-        <v>33</v>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" t="s">
+        <v>34</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L39" t="s">
-        <v>33</v>
-      </c>
-      <c r="N39" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" t="s">
         <v>34</v>
       </c>
       <c r="O39" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P39" t="s">
-        <v>34</v>
-      </c>
-      <c r="R39" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>34</v>
       </c>
       <c r="S39" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40">
         <f t="shared" si="4"/>
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
-      <c r="J40" t="s">
-        <v>33</v>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" t="s">
+        <v>34</v>
       </c>
       <c r="K40" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N40" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" t="s">
         <v>34</v>
       </c>
       <c r="O40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P40" t="s">
-        <v>34</v>
-      </c>
-      <c r="R40" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>34</v>
       </c>
       <c r="S40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41">
         <f t="shared" si="4"/>
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
-      <c r="J41" t="s">
-        <v>33</v>
+      <c r="G41" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" t="s">
+        <v>34</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
-      </c>
-      <c r="N41" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" t="s">
         <v>34</v>
       </c>
       <c r="O41" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P41" t="s">
-        <v>34</v>
-      </c>
-      <c r="R41" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>34</v>
       </c>
       <c r="S41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42">
         <f t="shared" si="4"/>
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
-      <c r="D42" t="s">
-        <v>36</v>
+      <c r="D42" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
-      <c r="J42" t="s">
-        <v>33</v>
+      <c r="G42" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" t="s">
+        <v>34</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L42" t="s">
-        <v>33</v>
-      </c>
-      <c r="N42" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" t="s">
         <v>34</v>
       </c>
       <c r="O42" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P42" t="s">
-        <v>34</v>
-      </c>
-      <c r="R42" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T42" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43">
         <f t="shared" si="4"/>
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
-      <c r="D43" t="s">
-        <v>37</v>
+      <c r="D43" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
-      <c r="J43" t="s">
-        <v>33</v>
+      <c r="G43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" t="s">
+        <v>34</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L43" t="s">
-        <v>33</v>
-      </c>
-      <c r="N43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M43" t="s">
         <v>34</v>
       </c>
       <c r="O43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P43" t="s">
-        <v>34</v>
-      </c>
-      <c r="R43" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>34</v>
       </c>
       <c r="S43" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44">
         <f t="shared" si="4"/>
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D44" t="s">
-        <v>38</v>
+      <c r="D44" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
-      <c r="J44" t="s">
-        <v>33</v>
+      <c r="G44" t="s">
+        <v>29</v>
+      </c>
+      <c r="H44" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44" t="s">
+        <v>34</v>
       </c>
       <c r="K44" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L44" t="s">
-        <v>33</v>
-      </c>
-      <c r="N44" t="s">
+        <v>29</v>
+      </c>
+      <c r="M44" t="s">
         <v>34</v>
       </c>
       <c r="O44" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P44" t="s">
-        <v>34</v>
-      </c>
-      <c r="R44" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>34</v>
       </c>
       <c r="S44" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U44" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45">
         <f t="shared" si="4"/>
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>10</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
-      <c r="J45" t="s">
-        <v>33</v>
+      <c r="G45" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" t="s">
+        <v>34</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L45" t="s">
-        <v>33</v>
-      </c>
-      <c r="N45" t="s">
+        <v>29</v>
+      </c>
+      <c r="M45" t="s">
         <v>34</v>
       </c>
       <c r="O45" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P45" t="s">
-        <v>34</v>
-      </c>
-      <c r="R45" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>34</v>
       </c>
       <c r="S45" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T45" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U45" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46">
         <f t="shared" si="4"/>
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>9</v>
       </c>
       <c r="E46">
         <v>9</v>
       </c>
-      <c r="J46" t="s">
-        <v>33</v>
+      <c r="G46" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>34</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L46" t="s">
-        <v>33</v>
-      </c>
-      <c r="N46" t="s">
+        <v>29</v>
+      </c>
+      <c r="M46" t="s">
         <v>34</v>
       </c>
       <c r="O46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P46" t="s">
-        <v>34</v>
-      </c>
-      <c r="R46" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>34</v>
       </c>
       <c r="S46" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47">
         <f t="shared" si="4"/>
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>8</v>
       </c>
       <c r="E47">
         <v>8</v>
       </c>
-      <c r="J47" t="s">
-        <v>33</v>
+      <c r="G47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" t="s">
+        <v>34</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L47" t="s">
-        <v>33</v>
-      </c>
-      <c r="N47" t="s">
+        <v>29</v>
+      </c>
+      <c r="M47" t="s">
         <v>34</v>
       </c>
       <c r="O47" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P47" t="s">
-        <v>34</v>
-      </c>
-      <c r="R47" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>34</v>
       </c>
       <c r="S47" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U47" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48">
         <f t="shared" si="4"/>
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>7</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
-      <c r="J48" t="s">
-        <v>33</v>
+      <c r="G48" t="s">
+        <v>29</v>
+      </c>
+      <c r="H48" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" t="s">
+        <v>34</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L48" t="s">
-        <v>33</v>
-      </c>
-      <c r="N48" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48" t="s">
         <v>34</v>
       </c>
       <c r="O48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P48" t="s">
-        <v>34</v>
-      </c>
-      <c r="R48" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>34</v>
       </c>
       <c r="S48" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T48" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49">
         <f t="shared" si="4"/>
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>6</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
-      <c r="J49" t="s">
-        <v>33</v>
+      <c r="G49" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" t="s">
+        <v>34</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
-      </c>
-      <c r="N49" t="s">
+        <v>29</v>
+      </c>
+      <c r="M49" t="s">
         <v>34</v>
       </c>
       <c r="O49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P49" t="s">
-        <v>34</v>
-      </c>
-      <c r="R49" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>34</v>
       </c>
       <c r="S49" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U49" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50">
         <f t="shared" si="4"/>
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E50">
         <v>14</v>
       </c>
-      <c r="J50" t="s">
-        <v>33</v>
+      <c r="G50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I50" t="s">
+        <v>34</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>33</v>
-      </c>
-      <c r="N50" t="s">
+        <v>29</v>
+      </c>
+      <c r="M50" t="s">
         <v>34</v>
       </c>
       <c r="O50" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P50" t="s">
-        <v>34</v>
-      </c>
-      <c r="R50" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>34</v>
       </c>
       <c r="S50" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T50" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U50" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51">
         <f t="shared" si="4"/>
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
-      <c r="D51" t="s">
-        <v>36</v>
+      <c r="D51" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
-      <c r="J51" t="s">
-        <v>33</v>
+      <c r="G51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" t="s">
+        <v>34</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
-      </c>
-      <c r="N51" t="s">
+        <v>29</v>
+      </c>
+      <c r="M51" t="s">
         <v>34</v>
       </c>
       <c r="O51" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P51" t="s">
-        <v>34</v>
-      </c>
-      <c r="R51" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>34</v>
       </c>
       <c r="S51" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U51" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52">
         <f t="shared" si="4"/>
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
-      <c r="D52" t="s">
-        <v>37</v>
+      <c r="D52" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
-      <c r="J52" t="s">
-        <v>33</v>
+      <c r="G52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" t="s">
+        <v>34</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L52" t="s">
-        <v>33</v>
-      </c>
-      <c r="N52" t="s">
+        <v>29</v>
+      </c>
+      <c r="M52" t="s">
         <v>34</v>
       </c>
       <c r="O52" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P52" t="s">
-        <v>34</v>
-      </c>
-      <c r="R52" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>34</v>
       </c>
       <c r="S52" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53">
         <f t="shared" si="4"/>
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D53" t="s">
-        <v>38</v>
+      <c r="D53" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
-      <c r="J53" t="s">
-        <v>33</v>
+      <c r="G53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H53" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" t="s">
+        <v>34</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L53" t="s">
-        <v>33</v>
-      </c>
-      <c r="N53" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" t="s">
         <v>34</v>
       </c>
       <c r="O53" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P53" t="s">
-        <v>34</v>
-      </c>
-      <c r="R53" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>34</v>
       </c>
       <c r="S53" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U53" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54">
         <f t="shared" si="4"/>
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>10</v>
       </c>
       <c r="E54">
         <v>10</v>
       </c>
-      <c r="J54" t="s">
-        <v>33</v>
+      <c r="G54" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" t="s">
+        <v>34</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L54" t="s">
-        <v>33</v>
-      </c>
-      <c r="N54" t="s">
+        <v>29</v>
+      </c>
+      <c r="M54" t="s">
         <v>34</v>
       </c>
       <c r="O54" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P54" t="s">
-        <v>34</v>
-      </c>
-      <c r="R54" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>34</v>
       </c>
       <c r="S54" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55">
         <f t="shared" si="4"/>
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
         <v>9</v>
       </c>
       <c r="E55">
         <v>9</v>
       </c>
-      <c r="J55" t="s">
-        <v>33</v>
+      <c r="G55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" t="s">
+        <v>34</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
-      </c>
-      <c r="N55" t="s">
+        <v>29</v>
+      </c>
+      <c r="M55" t="s">
         <v>34</v>
       </c>
       <c r="O55" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P55" t="s">
-        <v>34</v>
-      </c>
-      <c r="R55" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>34</v>
       </c>
       <c r="S55" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56">
         <f t="shared" si="4"/>
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>8</v>
       </c>
       <c r="E56">
         <v>8</v>
       </c>
-      <c r="J56" t="s">
-        <v>33</v>
+      <c r="G56" t="s">
+        <v>29</v>
+      </c>
+      <c r="H56" t="s">
+        <v>29</v>
+      </c>
+      <c r="I56" t="s">
+        <v>34</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L56" t="s">
-        <v>33</v>
-      </c>
-      <c r="N56" t="s">
+        <v>29</v>
+      </c>
+      <c r="M56" t="s">
         <v>34</v>
       </c>
       <c r="O56" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P56" t="s">
-        <v>34</v>
-      </c>
-      <c r="R56" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>34</v>
       </c>
       <c r="S56" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57">
         <f t="shared" si="4"/>
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
         <v>7</v>
       </c>
       <c r="E57">
         <v>7</v>
       </c>
-      <c r="J57" t="s">
-        <v>33</v>
+      <c r="G57" t="s">
+        <v>29</v>
+      </c>
+      <c r="H57" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" t="s">
+        <v>34</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L57" t="s">
-        <v>33</v>
-      </c>
-      <c r="N57" t="s">
+        <v>29</v>
+      </c>
+      <c r="M57" t="s">
         <v>34</v>
       </c>
       <c r="O57" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P57" t="s">
-        <v>34</v>
-      </c>
-      <c r="R57" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>34</v>
       </c>
       <c r="S57" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20">
+        <v>32</v>
+      </c>
+      <c r="U57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58">
         <f t="shared" si="4"/>
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>6</v>
       </c>
       <c r="E58">
         <v>6</v>
       </c>
-      <c r="J58" t="s">
-        <v>33</v>
+      <c r="G58" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" t="s">
+        <v>34</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L58" t="s">
-        <v>33</v>
-      </c>
-      <c r="N58" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M58" t="s">
+        <v>34</v>
       </c>
       <c r="O58" t="s">
         <v>43</v>
@@ -3879,8 +4340,8 @@
       <c r="P58" t="s">
         <v>43</v>
       </c>
-      <c r="R58" t="s">
-        <v>44</v>
+      <c r="Q58" t="s">
+        <v>34</v>
       </c>
       <c r="S58" t="s">
         <v>44</v>
@@ -3888,8 +4349,11 @@
       <c r="T58" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59">
         <f t="shared" si="4"/>
         <v>103014</v>
@@ -3900,23 +4364,29 @@
       <c r="C59">
         <v>3</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E59">
         <v>14</v>
       </c>
-      <c r="J59" t="s">
-        <v>33</v>
+      <c r="G59" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" t="s">
+        <v>34</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L59" t="s">
-        <v>33</v>
-      </c>
-      <c r="N59" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M59" t="s">
+        <v>34</v>
       </c>
       <c r="O59" t="s">
         <v>43</v>
@@ -3924,8 +4394,8 @@
       <c r="P59" t="s">
         <v>43</v>
       </c>
-      <c r="R59" t="s">
-        <v>44</v>
+      <c r="Q59" t="s">
+        <v>34</v>
       </c>
       <c r="S59" t="s">
         <v>44</v>
@@ -3933,8 +4403,11 @@
       <c r="T59" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60">
         <f t="shared" si="4"/>
         <v>103013</v>
@@ -3946,23 +4419,29 @@
         <f>C59</f>
         <v>3</v>
       </c>
-      <c r="D60" t="s">
-        <v>36</v>
+      <c r="D60" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
-      <c r="J60" t="s">
-        <v>33</v>
+      <c r="G60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" t="s">
+        <v>34</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L60" t="s">
-        <v>33</v>
-      </c>
-      <c r="N60" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M60" t="s">
+        <v>34</v>
       </c>
       <c r="O60" t="s">
         <v>43</v>
@@ -3970,8 +4449,8 @@
       <c r="P60" t="s">
         <v>43</v>
       </c>
-      <c r="R60" t="s">
-        <v>44</v>
+      <c r="Q60" t="s">
+        <v>34</v>
       </c>
       <c r="S60" t="s">
         <v>44</v>
@@ -3979,8 +4458,11 @@
       <c r="T60" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61">
         <f t="shared" si="4"/>
         <v>103012</v>
@@ -3992,23 +4474,29 @@
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
-      <c r="D61" t="s">
-        <v>37</v>
+      <c r="D61" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="J61" t="s">
-        <v>33</v>
+      <c r="G61" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" t="s">
+        <v>34</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
-      </c>
-      <c r="N61" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M61" t="s">
+        <v>34</v>
       </c>
       <c r="O61" t="s">
         <v>43</v>
@@ -4016,8 +4504,8 @@
       <c r="P61" t="s">
         <v>43</v>
       </c>
-      <c r="R61" t="s">
-        <v>44</v>
+      <c r="Q61" t="s">
+        <v>34</v>
       </c>
       <c r="S61" t="s">
         <v>44</v>
@@ -4025,8 +4513,11 @@
       <c r="T61" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62">
         <f t="shared" si="4"/>
         <v>103011</v>
@@ -4038,23 +4529,29 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D62" t="s">
-        <v>38</v>
+      <c r="D62" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
-      <c r="J62" t="s">
-        <v>33</v>
+      <c r="G62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" t="s">
+        <v>34</v>
       </c>
       <c r="K62" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L62" t="s">
-        <v>33</v>
-      </c>
-      <c r="N62" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M62" t="s">
+        <v>34</v>
       </c>
       <c r="O62" t="s">
         <v>43</v>
@@ -4062,8 +4559,8 @@
       <c r="P62" t="s">
         <v>43</v>
       </c>
-      <c r="R62" t="s">
-        <v>44</v>
+      <c r="Q62" t="s">
+        <v>34</v>
       </c>
       <c r="S62" t="s">
         <v>44</v>
@@ -4071,8 +4568,11 @@
       <c r="T62" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63">
         <f t="shared" si="4"/>
         <v>103010</v>
@@ -4084,23 +4584,29 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>10</v>
       </c>
       <c r="E63">
         <v>10</v>
       </c>
-      <c r="J63" t="s">
-        <v>33</v>
+      <c r="G63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" t="s">
+        <v>34</v>
       </c>
       <c r="K63" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L63" t="s">
-        <v>33</v>
-      </c>
-      <c r="N63" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M63" t="s">
+        <v>34</v>
       </c>
       <c r="O63" t="s">
         <v>43</v>
@@ -4108,8 +4614,8 @@
       <c r="P63" t="s">
         <v>43</v>
       </c>
-      <c r="R63" t="s">
-        <v>44</v>
+      <c r="Q63" t="s">
+        <v>34</v>
       </c>
       <c r="S63" t="s">
         <v>44</v>
@@ -4117,8 +4623,11 @@
       <c r="T63" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64">
         <f t="shared" si="4"/>
         <v>103009</v>
@@ -4130,23 +4639,29 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>9</v>
       </c>
       <c r="E64">
         <v>9</v>
       </c>
-      <c r="J64" t="s">
-        <v>33</v>
+      <c r="G64" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" t="s">
+        <v>42</v>
+      </c>
+      <c r="I64" t="s">
+        <v>34</v>
       </c>
       <c r="K64" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L64" t="s">
-        <v>33</v>
-      </c>
-      <c r="N64" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="M64" t="s">
+        <v>34</v>
       </c>
       <c r="O64" t="s">
         <v>43</v>
@@ -4154,8 +4669,8 @@
       <c r="P64" t="s">
         <v>43</v>
       </c>
-      <c r="R64" t="s">
-        <v>44</v>
+      <c r="Q64" t="s">
+        <v>34</v>
       </c>
       <c r="S64" t="s">
         <v>44</v>
@@ -4163,8 +4678,11 @@
       <c r="T64" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
+      <c r="U64" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65">
         <f t="shared" si="4"/>
         <v>103008</v>
@@ -4176,41 +4694,50 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>8</v>
       </c>
       <c r="E65">
         <v>8</v>
       </c>
-      <c r="J65" t="s">
-        <v>33</v>
+      <c r="G65" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65" t="s">
+        <v>34</v>
       </c>
       <c r="K65" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L65" t="s">
-        <v>33</v>
-      </c>
-      <c r="N65" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M65" t="s">
+        <v>34</v>
       </c>
       <c r="O65" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P65" t="s">
-        <v>43</v>
-      </c>
-      <c r="R65" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>34</v>
       </c>
       <c r="S65" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T65" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66">
         <f t="shared" si="4"/>
         <v>103007</v>
@@ -4222,41 +4749,50 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>7</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
-      <c r="J66" t="s">
-        <v>33</v>
+      <c r="G66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" t="s">
+        <v>34</v>
       </c>
       <c r="K66" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L66" t="s">
-        <v>33</v>
-      </c>
-      <c r="N66" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M66" t="s">
+        <v>34</v>
       </c>
       <c r="O66" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P66" t="s">
-        <v>43</v>
-      </c>
-      <c r="R66" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>34</v>
       </c>
       <c r="S66" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T66" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U66" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67">
         <f t="shared" si="4"/>
         <v>103006</v>
@@ -4268,41 +4804,50 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>6</v>
       </c>
       <c r="E67">
         <v>6</v>
       </c>
-      <c r="J67" t="s">
-        <v>33</v>
+      <c r="G67" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" t="s">
+        <v>34</v>
       </c>
       <c r="K67" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L67" t="s">
-        <v>33</v>
-      </c>
-      <c r="N67" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M67" t="s">
+        <v>34</v>
       </c>
       <c r="O67" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P67" t="s">
-        <v>43</v>
-      </c>
-      <c r="R67" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>34</v>
       </c>
       <c r="S67" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T67" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U67" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68">
         <f t="shared" si="4"/>
         <v>103005</v>
@@ -4314,41 +4859,50 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68">
         <v>5</v>
       </c>
-      <c r="J68" t="s">
-        <v>33</v>
+      <c r="G68" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68" t="s">
+        <v>29</v>
+      </c>
+      <c r="I68" t="s">
+        <v>34</v>
       </c>
       <c r="K68" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L68" t="s">
-        <v>33</v>
-      </c>
-      <c r="N68" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M68" t="s">
+        <v>34</v>
       </c>
       <c r="O68" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P68" t="s">
-        <v>43</v>
-      </c>
-      <c r="R68" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>34</v>
       </c>
       <c r="S68" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T68" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U68" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69">
         <f t="shared" si="4"/>
         <v>103004</v>
@@ -4360,41 +4914,50 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>4</v>
       </c>
       <c r="E69">
         <v>4</v>
       </c>
-      <c r="J69" t="s">
-        <v>33</v>
+      <c r="G69" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69" t="s">
+        <v>29</v>
+      </c>
+      <c r="I69" t="s">
+        <v>34</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L69" t="s">
-        <v>33</v>
-      </c>
-      <c r="N69" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M69" t="s">
+        <v>34</v>
       </c>
       <c r="O69" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P69" t="s">
-        <v>43</v>
-      </c>
-      <c r="R69" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>34</v>
       </c>
       <c r="S69" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T69" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70">
         <f t="shared" ref="A70:A109" si="8">100000+C70*1000+E70</f>
         <v>103003</v>
@@ -4406,41 +4969,50 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>3</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
-      <c r="J70" t="s">
-        <v>33</v>
+      <c r="G70" t="s">
+        <v>29</v>
+      </c>
+      <c r="H70" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70" t="s">
+        <v>34</v>
       </c>
       <c r="K70" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L70" t="s">
-        <v>33</v>
-      </c>
-      <c r="N70" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M70" t="s">
+        <v>34</v>
       </c>
       <c r="O70" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P70" t="s">
-        <v>43</v>
-      </c>
-      <c r="R70" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>34</v>
       </c>
       <c r="S70" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T70" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U70" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71">
         <f t="shared" si="8"/>
         <v>103002</v>
@@ -4452,1933 +5024,2134 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>2</v>
       </c>
       <c r="E71">
         <v>2</v>
       </c>
-      <c r="J71" t="s">
-        <v>33</v>
+      <c r="G71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" t="s">
+        <v>29</v>
+      </c>
+      <c r="I71" t="s">
+        <v>34</v>
       </c>
       <c r="K71" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L71" t="s">
-        <v>33</v>
-      </c>
-      <c r="N71" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M71" t="s">
+        <v>34</v>
       </c>
       <c r="O71" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P71" t="s">
-        <v>43</v>
-      </c>
-      <c r="R71" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>34</v>
       </c>
       <c r="S71" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T71" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U71" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72">
         <f t="shared" si="8"/>
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E72">
         <v>14</v>
       </c>
-      <c r="J72" t="s">
-        <v>33</v>
+      <c r="G72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" t="s">
+        <v>29</v>
+      </c>
+      <c r="I72" t="s">
+        <v>34</v>
       </c>
       <c r="K72" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L72" t="s">
-        <v>33</v>
-      </c>
-      <c r="N72" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M72" t="s">
+        <v>34</v>
       </c>
       <c r="O72" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P72" t="s">
-        <v>43</v>
-      </c>
-      <c r="R72" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>34</v>
       </c>
       <c r="S72" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T72" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U72" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73">
         <f t="shared" si="8"/>
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
-      <c r="D73" t="s">
-        <v>36</v>
+      <c r="D73" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
-      <c r="J73" t="s">
-        <v>33</v>
+      <c r="G73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73" t="s">
+        <v>29</v>
+      </c>
+      <c r="I73" t="s">
+        <v>34</v>
       </c>
       <c r="K73" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L73" t="s">
-        <v>33</v>
-      </c>
-      <c r="N73" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M73" t="s">
+        <v>34</v>
       </c>
       <c r="O73" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P73" t="s">
-        <v>43</v>
-      </c>
-      <c r="R73" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>34</v>
       </c>
       <c r="S73" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T73" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="U73" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74">
         <f t="shared" si="8"/>
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
-      <c r="D74" t="s">
-        <v>37</v>
+      <c r="D74" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
-      <c r="J74" t="s">
-        <v>33</v>
+      <c r="G74" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" t="s">
+        <v>29</v>
+      </c>
+      <c r="I74" t="s">
+        <v>49</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L74" t="s">
-        <v>33</v>
-      </c>
-      <c r="N74" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="M74" t="s">
+        <v>49</v>
       </c>
       <c r="O74" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P74" t="s">
-        <v>43</v>
-      </c>
-      <c r="R74" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>49</v>
       </c>
       <c r="S74" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T74" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="75" spans="1:20">
+      <c r="U74" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75">
         <f t="shared" si="8"/>
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D75" t="s">
-        <v>38</v>
+      <c r="D75" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
-      <c r="J75" t="s">
-        <v>48</v>
+      <c r="G75" t="s">
+        <v>29</v>
+      </c>
+      <c r="H75" t="s">
+        <v>29</v>
+      </c>
+      <c r="I75" t="s">
+        <v>49</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="L75" t="s">
-        <v>48</v>
-      </c>
-      <c r="N75" t="s">
+        <v>29</v>
+      </c>
+      <c r="M75" t="s">
         <v>49</v>
       </c>
       <c r="O75" t="s">
+        <v>46</v>
+      </c>
+      <c r="P75" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q75" t="s">
         <v>49</v>
       </c>
-      <c r="P75" t="s">
+      <c r="S75" t="s">
+        <v>47</v>
+      </c>
+      <c r="T75" t="s">
+        <v>47</v>
+      </c>
+      <c r="U75" t="s">
         <v>49</v>
       </c>
-      <c r="R75" t="s">
-        <v>50</v>
-      </c>
-      <c r="S75" t="s">
-        <v>50</v>
-      </c>
-      <c r="T75" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76">
         <f t="shared" si="8"/>
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76">
         <v>10</v>
       </c>
-      <c r="J76" t="s">
-        <v>48</v>
+      <c r="G76" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" t="s">
+        <v>49</v>
       </c>
       <c r="K76" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="L76" t="s">
-        <v>48</v>
-      </c>
-      <c r="N76" t="s">
+        <v>29</v>
+      </c>
+      <c r="M76" t="s">
         <v>49</v>
       </c>
       <c r="O76" t="s">
+        <v>46</v>
+      </c>
+      <c r="P76" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q76" t="s">
         <v>49</v>
       </c>
-      <c r="P76" t="s">
+      <c r="S76" t="s">
+        <v>47</v>
+      </c>
+      <c r="T76" t="s">
+        <v>47</v>
+      </c>
+      <c r="U76" t="s">
         <v>49</v>
       </c>
-      <c r="R76" t="s">
-        <v>50</v>
-      </c>
-      <c r="S76" t="s">
-        <v>50</v>
-      </c>
-      <c r="T76" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77">
         <f t="shared" si="8"/>
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>9</v>
       </c>
       <c r="E77">
         <v>9</v>
       </c>
-      <c r="J77" t="s">
-        <v>48</v>
+      <c r="G77" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" t="s">
+        <v>29</v>
+      </c>
+      <c r="I77" t="s">
+        <v>49</v>
       </c>
       <c r="K77" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="L77" t="s">
-        <v>48</v>
-      </c>
-      <c r="N77" t="s">
+        <v>29</v>
+      </c>
+      <c r="M77" t="s">
         <v>49</v>
       </c>
       <c r="O77" t="s">
+        <v>46</v>
+      </c>
+      <c r="P77" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q77" t="s">
         <v>49</v>
       </c>
-      <c r="P77" t="s">
+      <c r="S77" t="s">
+        <v>47</v>
+      </c>
+      <c r="T77" t="s">
+        <v>47</v>
+      </c>
+      <c r="U77" t="s">
         <v>49</v>
       </c>
-      <c r="R77" t="s">
-        <v>50</v>
-      </c>
-      <c r="S77" t="s">
-        <v>50</v>
-      </c>
-      <c r="T77" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78">
         <f t="shared" si="8"/>
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
         <v>8</v>
       </c>
       <c r="E78">
         <v>8</v>
       </c>
-      <c r="J78" t="s">
-        <v>52</v>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" t="s">
+        <v>50</v>
+      </c>
+      <c r="I78" t="s">
+        <v>51</v>
       </c>
       <c r="K78" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L78" t="s">
-        <v>52</v>
-      </c>
-      <c r="N78" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="M78" t="s">
+        <v>51</v>
       </c>
       <c r="O78" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P78" t="s">
-        <v>49</v>
-      </c>
-      <c r="R78" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>51</v>
       </c>
       <c r="S78" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79">
         <f t="shared" si="8"/>
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>7</v>
       </c>
       <c r="E79">
         <v>7</v>
       </c>
-      <c r="J79" t="s">
-        <v>52</v>
+      <c r="G79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>50</v>
+      </c>
+      <c r="I79" t="s">
+        <v>51</v>
       </c>
       <c r="K79" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L79" t="s">
-        <v>52</v>
-      </c>
-      <c r="N79" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="M79" t="s">
+        <v>51</v>
       </c>
       <c r="O79" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P79" t="s">
-        <v>49</v>
-      </c>
-      <c r="R79" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>51</v>
       </c>
       <c r="S79" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80">
         <f t="shared" si="8"/>
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>6</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
-      <c r="J80" t="s">
-        <v>52</v>
+      <c r="G80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80" t="s">
+        <v>51</v>
       </c>
       <c r="K80" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L80" t="s">
-        <v>52</v>
-      </c>
-      <c r="N80" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="M80" t="s">
+        <v>51</v>
       </c>
       <c r="O80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P80" t="s">
-        <v>49</v>
-      </c>
-      <c r="R80" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>51</v>
       </c>
       <c r="S80" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81">
         <f t="shared" si="8"/>
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
         <v>5</v>
       </c>
       <c r="E81">
         <v>5</v>
       </c>
-      <c r="J81" t="s">
-        <v>52</v>
+      <c r="G81" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81" t="s">
+        <v>51</v>
       </c>
       <c r="K81" t="s">
         <v>52</v>
       </c>
       <c r="L81" t="s">
-        <v>52</v>
-      </c>
-      <c r="N81" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="M81" t="s">
+        <v>51</v>
       </c>
       <c r="O81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P81" t="s">
-        <v>49</v>
-      </c>
-      <c r="R81" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>51</v>
       </c>
       <c r="S81" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T81" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82">
         <f t="shared" si="8"/>
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>4</v>
       </c>
       <c r="E82">
         <v>4</v>
       </c>
-      <c r="J82" t="s">
-        <v>52</v>
+      <c r="G82" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82" t="s">
+        <v>51</v>
       </c>
       <c r="K82" t="s">
         <v>52</v>
       </c>
       <c r="L82" t="s">
-        <v>52</v>
-      </c>
-      <c r="N82" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="M82" t="s">
+        <v>51</v>
       </c>
       <c r="O82" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P82" t="s">
-        <v>49</v>
-      </c>
-      <c r="R82" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>51</v>
       </c>
       <c r="S82" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83">
         <f t="shared" si="8"/>
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
         <v>3</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
-      <c r="J83" t="s">
-        <v>52</v>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" t="s">
+        <v>50</v>
+      </c>
+      <c r="I83" t="s">
+        <v>53</v>
       </c>
       <c r="K83" t="s">
         <v>52</v>
       </c>
       <c r="L83" t="s">
-        <v>52</v>
-      </c>
-      <c r="N83" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="M83" t="s">
+        <v>53</v>
       </c>
       <c r="O83" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P83" t="s">
-        <v>48</v>
-      </c>
-      <c r="R83" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>53</v>
       </c>
       <c r="S83" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="T83" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84">
         <f t="shared" si="8"/>
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
         <v>2</v>
       </c>
       <c r="E84">
         <v>2</v>
       </c>
-      <c r="J84" t="s">
-        <v>52</v>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="s">
+        <v>50</v>
+      </c>
+      <c r="I84" t="s">
+        <v>53</v>
       </c>
       <c r="K84" t="s">
         <v>52</v>
       </c>
       <c r="L84" t="s">
-        <v>52</v>
-      </c>
-      <c r="N84" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="M84" t="s">
+        <v>53</v>
       </c>
       <c r="O84" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P84" t="s">
-        <v>48</v>
-      </c>
-      <c r="R84" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>53</v>
       </c>
       <c r="S84" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="T84" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85">
         <f t="shared" si="8"/>
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E85">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
-      </c>
-      <c r="J85" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="I85" t="s">
+        <v>53</v>
       </c>
       <c r="K85" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L85" t="s">
-        <v>56</v>
-      </c>
-      <c r="N85" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="M85" t="s">
+        <v>53</v>
       </c>
       <c r="O85" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P85" t="s">
-        <v>56</v>
-      </c>
-      <c r="R85" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>53</v>
       </c>
       <c r="S85" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T85" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20">
+        <v>50</v>
+      </c>
+      <c r="U85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86">
         <f t="shared" si="8"/>
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
-      <c r="D86" t="s">
-        <v>36</v>
+      <c r="D86" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H86" t="s">
-        <v>61</v>
-      </c>
-      <c r="J86" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="I86" t="s">
+        <v>53</v>
       </c>
       <c r="K86" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L86" t="s">
-        <v>56</v>
-      </c>
-      <c r="N86" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="M86" t="s">
+        <v>53</v>
       </c>
       <c r="O86" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P86" t="s">
-        <v>56</v>
-      </c>
-      <c r="R86" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>53</v>
       </c>
       <c r="S86" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T86" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U86" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87">
         <f t="shared" si="8"/>
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
-      <c r="D87" t="s">
-        <v>37</v>
+      <c r="D87" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H87" t="s">
-        <v>61</v>
-      </c>
-      <c r="J87" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="I87" t="s">
+        <v>56</v>
       </c>
       <c r="K87" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L87" t="s">
-        <v>65</v>
-      </c>
-      <c r="N87" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="M87" t="s">
+        <v>56</v>
       </c>
       <c r="O87" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P87" t="s">
-        <v>65</v>
-      </c>
-      <c r="R87" t="s">
-        <v>66</v>
+        <v>50</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>56</v>
       </c>
       <c r="S87" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T87" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88">
         <f t="shared" si="8"/>
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D88" t="s">
-        <v>38</v>
+      <c r="D88" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H88" t="s">
-        <v>61</v>
-      </c>
-      <c r="J88" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="I88" t="s">
+        <v>56</v>
       </c>
       <c r="K88" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L88" t="s">
-        <v>65</v>
-      </c>
-      <c r="N88" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="M88" t="s">
+        <v>56</v>
       </c>
       <c r="O88" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P88" t="s">
-        <v>65</v>
-      </c>
-      <c r="R88" t="s">
-        <v>66</v>
+        <v>50</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>56</v>
       </c>
       <c r="S88" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U88" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89">
         <f t="shared" si="8"/>
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
         <v>10</v>
       </c>
       <c r="E89">
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H89" t="s">
-        <v>61</v>
-      </c>
-      <c r="J89" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="I89" t="s">
+        <v>56</v>
       </c>
       <c r="K89" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L89" t="s">
-        <v>65</v>
-      </c>
-      <c r="N89" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="M89" t="s">
+        <v>56</v>
       </c>
       <c r="O89" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P89" t="s">
-        <v>65</v>
-      </c>
-      <c r="R89" t="s">
-        <v>66</v>
+        <v>50</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>56</v>
       </c>
       <c r="S89" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T89" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U89" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90">
         <f t="shared" si="8"/>
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
         <v>9</v>
       </c>
       <c r="E90">
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H90" t="s">
-        <v>61</v>
-      </c>
-      <c r="J90" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="I90" t="s">
+        <v>57</v>
       </c>
       <c r="K90" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L90" t="s">
-        <v>67</v>
-      </c>
-      <c r="N90" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="M90" t="s">
+        <v>57</v>
       </c>
       <c r="O90" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P90" t="s">
-        <v>67</v>
-      </c>
-      <c r="R90" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>57</v>
       </c>
       <c r="S90" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T90" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U90" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91">
         <f t="shared" si="8"/>
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="1">
         <v>8</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H91" t="s">
-        <v>61</v>
-      </c>
-      <c r="J91" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="I91" t="s">
+        <v>57</v>
       </c>
       <c r="K91" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L91" t="s">
-        <v>67</v>
-      </c>
-      <c r="N91" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="M91" t="s">
+        <v>57</v>
       </c>
       <c r="O91" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="P91" t="s">
-        <v>67</v>
-      </c>
-      <c r="R91" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>57</v>
       </c>
       <c r="S91" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="T91" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U91" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92">
         <f t="shared" si="8"/>
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="1">
         <v>7</v>
       </c>
       <c r="E92">
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H92" t="s">
-        <v>61</v>
-      </c>
-      <c r="J92" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I92" t="s">
+        <v>57</v>
       </c>
       <c r="K92" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L92" t="s">
-        <v>67</v>
-      </c>
-      <c r="N92" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M92" t="s">
+        <v>57</v>
       </c>
       <c r="O92" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P92" t="s">
-        <v>67</v>
-      </c>
-      <c r="R92" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>57</v>
       </c>
       <c r="S92" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T92" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U92" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93">
         <f t="shared" si="8"/>
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="1">
         <v>6</v>
       </c>
       <c r="E93">
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H93" t="s">
-        <v>61</v>
-      </c>
-      <c r="J93" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I93" t="s">
+        <v>60</v>
       </c>
       <c r="K93" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L93" t="s">
-        <v>70</v>
-      </c>
-      <c r="N93" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M93" t="s">
+        <v>60</v>
       </c>
       <c r="O93" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P93" t="s">
-        <v>70</v>
-      </c>
-      <c r="R93" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>60</v>
       </c>
       <c r="S93" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T93" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U93" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94">
         <f t="shared" si="8"/>
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
         <v>5</v>
       </c>
       <c r="E94">
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H94" t="s">
-        <v>61</v>
-      </c>
-      <c r="J94" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I94" t="s">
+        <v>60</v>
       </c>
       <c r="K94" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L94" t="s">
-        <v>70</v>
-      </c>
-      <c r="N94" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M94" t="s">
+        <v>60</v>
       </c>
       <c r="O94" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P94" t="s">
-        <v>70</v>
-      </c>
-      <c r="R94" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>60</v>
       </c>
       <c r="S94" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T94" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U94" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95">
         <f t="shared" si="8"/>
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>4</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H95" t="s">
-        <v>61</v>
-      </c>
-      <c r="J95" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I95" t="s">
+        <v>60</v>
       </c>
       <c r="K95" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L95" t="s">
-        <v>70</v>
-      </c>
-      <c r="N95" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M95" t="s">
+        <v>60</v>
       </c>
       <c r="O95" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P95" t="s">
-        <v>70</v>
-      </c>
-      <c r="R95" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>60</v>
       </c>
       <c r="S95" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T95" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U95" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96">
         <f t="shared" si="8"/>
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H96" t="s">
-        <v>61</v>
-      </c>
-      <c r="J96" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I96" t="s">
+        <v>34</v>
       </c>
       <c r="K96" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L96" t="s">
-        <v>71</v>
-      </c>
-      <c r="N96" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M96" t="s">
+        <v>34</v>
       </c>
       <c r="O96" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P96" t="s">
-        <v>71</v>
-      </c>
-      <c r="R96" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>34</v>
       </c>
       <c r="S96" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T96" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U96" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97">
         <f t="shared" si="8"/>
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="1">
         <v>2</v>
       </c>
       <c r="E97">
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H97" t="s">
-        <v>61</v>
-      </c>
-      <c r="J97" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I97" t="s">
+        <v>34</v>
       </c>
       <c r="K97" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L97" t="s">
-        <v>71</v>
-      </c>
-      <c r="N97" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M97" t="s">
+        <v>34</v>
       </c>
       <c r="O97" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P97" t="s">
-        <v>71</v>
-      </c>
-      <c r="R97" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>34</v>
       </c>
       <c r="S97" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T97" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U97" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98">
         <f t="shared" si="8"/>
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E98">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H98" t="s">
-        <v>61</v>
-      </c>
-      <c r="J98" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I98" t="s">
+        <v>34</v>
       </c>
       <c r="K98" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L98" t="s">
-        <v>71</v>
-      </c>
-      <c r="N98" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M98" t="s">
+        <v>34</v>
       </c>
       <c r="O98" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P98" t="s">
-        <v>71</v>
-      </c>
-      <c r="R98" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>34</v>
       </c>
       <c r="S98" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T98" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U98" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99">
         <f t="shared" si="8"/>
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
-      <c r="D99" t="s">
-        <v>36</v>
+      <c r="D99" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H99" t="s">
-        <v>61</v>
-      </c>
-      <c r="J99" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I99" t="s">
+        <v>63</v>
       </c>
       <c r="K99" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L99" t="s">
-        <v>73</v>
-      </c>
-      <c r="N99" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M99" t="s">
+        <v>63</v>
       </c>
       <c r="O99" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P99" t="s">
-        <v>73</v>
-      </c>
-      <c r="R99" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>63</v>
       </c>
       <c r="S99" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T99" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U99" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100">
         <f t="shared" si="8"/>
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
-      <c r="D100" t="s">
-        <v>37</v>
+      <c r="D100" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H100" t="s">
-        <v>61</v>
-      </c>
-      <c r="J100" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I100" t="s">
+        <v>63</v>
       </c>
       <c r="K100" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L100" t="s">
-        <v>73</v>
-      </c>
-      <c r="N100" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M100" t="s">
+        <v>63</v>
       </c>
       <c r="O100" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P100" t="s">
-        <v>73</v>
-      </c>
-      <c r="R100" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>63</v>
       </c>
       <c r="S100" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T100" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101">
         <f t="shared" si="8"/>
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D101" t="s">
-        <v>38</v>
+      <c r="D101" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
+        <v>62</v>
+      </c>
+      <c r="H101" t="s">
+        <v>50</v>
+      </c>
+      <c r="I101" t="s">
+        <v>63</v>
+      </c>
+      <c r="K101" t="s">
+        <v>57</v>
+      </c>
+      <c r="L101" t="s">
+        <v>50</v>
+      </c>
+      <c r="M101" t="s">
+        <v>63</v>
+      </c>
+      <c r="O101" t="s">
         <v>59</v>
       </c>
-      <c r="H101" t="s">
-        <v>74</v>
-      </c>
-      <c r="J101" t="s">
-        <v>68</v>
-      </c>
-      <c r="K101" t="s">
-        <v>68</v>
-      </c>
-      <c r="L101" t="s">
-        <v>73</v>
-      </c>
-      <c r="N101" t="s">
-        <v>68</v>
-      </c>
-      <c r="O101" t="s">
-        <v>68</v>
-      </c>
       <c r="P101" t="s">
-        <v>73</v>
-      </c>
-      <c r="R101" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>63</v>
       </c>
       <c r="S101" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T101" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U101" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102">
         <f t="shared" si="8"/>
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>10</v>
       </c>
       <c r="E102">
         <v>10</v>
       </c>
       <c r="G102" t="s">
+        <v>64</v>
+      </c>
+      <c r="H102" t="s">
+        <v>50</v>
+      </c>
+      <c r="I102" t="s">
+        <v>63</v>
+      </c>
+      <c r="K102" t="s">
+        <v>57</v>
+      </c>
+      <c r="L102" t="s">
+        <v>50</v>
+      </c>
+      <c r="M102" t="s">
+        <v>63</v>
+      </c>
+      <c r="O102" t="s">
         <v>59</v>
       </c>
-      <c r="H102" t="s">
-        <v>74</v>
-      </c>
-      <c r="J102" t="s">
-        <v>68</v>
-      </c>
-      <c r="K102" t="s">
-        <v>68</v>
-      </c>
-      <c r="L102" t="s">
-        <v>73</v>
-      </c>
-      <c r="N102" t="s">
-        <v>68</v>
-      </c>
-      <c r="O102" t="s">
-        <v>68</v>
-      </c>
       <c r="P102" t="s">
-        <v>73</v>
-      </c>
-      <c r="R102" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>63</v>
       </c>
       <c r="S102" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T102" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U102" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103">
         <f t="shared" si="8"/>
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="1">
         <v>9</v>
       </c>
       <c r="E103">
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H103" t="s">
-        <v>75</v>
-      </c>
-      <c r="J103" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I103" t="s">
+        <v>30</v>
       </c>
       <c r="K103" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L103" t="s">
-        <v>76</v>
-      </c>
-      <c r="N103" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M103" t="s">
+        <v>30</v>
       </c>
       <c r="O103" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P103" t="s">
-        <v>76</v>
-      </c>
-      <c r="R103" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>30</v>
       </c>
       <c r="S103" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T103" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104">
         <f t="shared" si="8"/>
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="1">
         <v>8</v>
       </c>
       <c r="E104">
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H104" t="s">
-        <v>77</v>
-      </c>
-      <c r="J104" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I104" t="s">
+        <v>30</v>
       </c>
       <c r="K104" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L104" t="s">
-        <v>76</v>
-      </c>
-      <c r="N104" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M104" t="s">
+        <v>30</v>
       </c>
       <c r="O104" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P104" t="s">
-        <v>76</v>
-      </c>
-      <c r="R104" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>30</v>
       </c>
       <c r="S104" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T104" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U104" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105">
         <f t="shared" si="8"/>
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="1">
         <v>7</v>
       </c>
       <c r="E105">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H105" t="s">
-        <v>77</v>
-      </c>
-      <c r="J105" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I105" t="s">
+        <v>30</v>
       </c>
       <c r="K105" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L105" t="s">
-        <v>76</v>
-      </c>
-      <c r="N105" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M105" t="s">
+        <v>30</v>
       </c>
       <c r="O105" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P105" t="s">
-        <v>76</v>
-      </c>
-      <c r="R105" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>30</v>
       </c>
       <c r="S105" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T105" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U105" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106">
         <f t="shared" si="8"/>
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>6</v>
       </c>
       <c r="E106">
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H106" t="s">
-        <v>79</v>
-      </c>
-      <c r="J106" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I106" t="s">
+        <v>65</v>
       </c>
       <c r="K106" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L106" t="s">
-        <v>80</v>
-      </c>
-      <c r="N106" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="M106" t="s">
+        <v>65</v>
       </c>
       <c r="O106" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P106" t="s">
-        <v>80</v>
-      </c>
-      <c r="R106" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>65</v>
       </c>
       <c r="S106" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T106" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U106" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107">
         <f t="shared" si="8"/>
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>5</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H107" t="s">
-        <v>79</v>
-      </c>
-      <c r="J107" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="I107" t="s">
+        <v>65</v>
       </c>
       <c r="K107" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L107" t="s">
-        <v>80</v>
-      </c>
-      <c r="N107" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="M107" t="s">
+        <v>65</v>
       </c>
       <c r="O107" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P107" t="s">
-        <v>80</v>
-      </c>
-      <c r="R107" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>65</v>
       </c>
       <c r="S107" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T107" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U107" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108">
         <f t="shared" si="8"/>
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="1">
         <v>4</v>
       </c>
       <c r="E108">
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H108" t="s">
-        <v>81</v>
-      </c>
-      <c r="J108" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="I108" t="s">
+        <v>65</v>
       </c>
       <c r="K108" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L108" t="s">
-        <v>80</v>
-      </c>
-      <c r="N108" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="M108" t="s">
+        <v>65</v>
       </c>
       <c r="O108" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P108" t="s">
-        <v>80</v>
-      </c>
-      <c r="R108" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>65</v>
       </c>
       <c r="S108" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T108" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20">
+        <v>59</v>
+      </c>
+      <c r="U108" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109">
         <f t="shared" si="8"/>
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H109" t="s">
-        <v>81</v>
-      </c>
-      <c r="J109" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="I109" t="s">
+        <v>65</v>
       </c>
       <c r="K109" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L109" t="s">
-        <v>80</v>
-      </c>
-      <c r="N109" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="M109" t="s">
+        <v>65</v>
       </c>
       <c r="O109" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="P109" t="s">
-        <v>80</v>
-      </c>
-      <c r="R109" t="s">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>65</v>
       </c>
       <c r="S109" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T109" t="s">
-        <v>80</v>
+        <v>59</v>
+      </c>
+      <c r="U109" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="336">
   <si>
     <t>ID</t>
   </si>
@@ -151,112 +151,922 @@
     <t>A</t>
   </si>
   <si>
+    <t>1_500|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_10000|4_0</t>
+  </si>
+  <si>
     <t>1_1000|2_3000|3_0|4_3000</t>
   </si>
   <si>
+    <t>1_1400|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1500|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2250|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3000|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>1_495|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1386|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1485|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2228|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>1_2970|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>1_490|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_980|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1372|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1470|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2205|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2940|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_485|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_970|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1358|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1455|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2183|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2910|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1344|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2880|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_475|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_950|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1330|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1425|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2138|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2850|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1316|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2115|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2820|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_465|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_930|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1302|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1395|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2093|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2790|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_460|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1288|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1380|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2070|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2760|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_455|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_910|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1274|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1365|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2048|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2730|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2025|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2700|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1232|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2640|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_435|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_870|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1218|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1305|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1958|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2610|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_430|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_860|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1204|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1290|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1935|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2580|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1176|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1890|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_415|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_830|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1162|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1245|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1868|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2490|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1148|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1845|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2460|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_400|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1120|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2400|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_395|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_790|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1106|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1185|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1778|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2370|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1092|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1755|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2340|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1064|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1710|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2280|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_370|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_740|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1036|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1110|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1665|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2220|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1008|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1080|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1620|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_350|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_700|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1050|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1575|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2100|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_340|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_680|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_952|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1020|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1530|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2040|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_330|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_924|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_315|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_882|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_945|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1418|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1890|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_305|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_610|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_854|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_915|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1373|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1830|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_295|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_590|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_826|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_885|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1328|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1770|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>1_285|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_570|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_798|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_855|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1283|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1710|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_280|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_560|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_784|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_840|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1260|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1680|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_270|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_540|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_756|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_810|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1215|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1620|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_265|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_530|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_742|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_795|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1193|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1590|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_255|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_510|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_714|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_765|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1148|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1530|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_250|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_500|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_700|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_750|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1125|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1500|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_672|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_235|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_658|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_705|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1058|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_225|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_675|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1013|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_220|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_616|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_210|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_588|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_205|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_574|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_615|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_923|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_195|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_546|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_585|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_878|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>1_190|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_532|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_570|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_855|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_150|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_300|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_115|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_230|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_322|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_345|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_518|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_690|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_80|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_160|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_224|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_45|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_90|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_126|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_135|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_203|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_270|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_10|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_20|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_28|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_30|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_45|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_60|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_3000|4_0</t>
+  </si>
+  <si>
     <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_1000|2_3000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_1000|2_3000|3_0|4_10000</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>1_1000|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1000|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1000|2_2000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>1_1000|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1000|2_3000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_2000|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
     <t>一对</t>
   </si>
   <si>
-    <t>1_0|2_2000|3_0|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_0|3_5000|4_0</t>
   </si>
   <si>
+    <t>1_0|2_3000|3_3000|4_0</t>
+  </si>
+  <si>
     <t>1_0|2_0|3_6000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_3000|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_10000|3_0|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_0|3_7000|4_0</t>
   </si>
   <si>
     <t>高牌</t>
   </si>
   <si>
-    <t>1_0|2_4000|3_0|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_0|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_500|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_11000|4_0</t>
@@ -425,12 +1235,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1416,31 +2226,31 @@
         <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
         <v>30</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="U5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -1449,7 +2259,7 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1461,40 +2271,40 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -1503,53 +2313,53 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O7" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1558,53 +2368,53 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1613,53 +2423,53 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1668,7 +2478,7 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -1681,40 +2491,40 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O10" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1723,7 +2533,7 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -1736,40 +2546,40 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1778,7 +2588,7 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -1791,40 +2601,40 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L12" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P12" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S12" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T12" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1833,7 +2643,7 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -1846,40 +2656,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O13" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P13" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S13" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T13" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1888,7 +2698,7 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -1901,40 +2711,40 @@
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O14" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P14" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S14" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T14" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1943,7 +2753,7 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1955,40 +2765,40 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L15" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P15" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S15" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T15" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1997,53 +2807,53 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L16" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O16" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q16" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S16" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T16" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -2052,53 +2862,53 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O17" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P17" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T17" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -2107,53 +2917,53 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P18" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S18" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T18" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -2162,7 +2972,7 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -2175,40 +2985,40 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H19" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K19" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P19" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q19" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S19" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T19" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U19" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -2217,7 +3027,7 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -2230,40 +3040,40 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O20" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P20" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q20" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S20" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T20" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -2272,7 +3082,7 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -2285,40 +3095,40 @@
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O21" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P21" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S21" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T21" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -2327,7 +3137,7 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -2340,40 +3150,40 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L22" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O22" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P22" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S22" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T22" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U22" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -2382,7 +3192,7 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -2395,40 +3205,40 @@
         <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H23" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O23" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q23" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S23" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T23" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -2437,7 +3247,7 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -2450,40 +3260,40 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H24" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K24" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O24" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P24" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q24" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S24" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T24" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U24" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -2492,7 +3302,7 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -2505,40 +3315,40 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H25" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K25" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L25" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O25" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P25" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S25" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T25" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U25" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -2547,7 +3357,7 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -2560,40 +3370,40 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K26" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O26" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P26" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q26" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S26" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T26" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U26" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -2602,7 +3412,7 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -2615,40 +3425,40 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L27" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O27" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P27" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q27" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S27" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T27" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U27" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -2657,7 +3467,7 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -2669,40 +3479,40 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I28" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K28" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="L28" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O28" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P28" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="Q28" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S28" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T28" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="U28" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -2711,53 +3521,53 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="M29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O29" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="P29" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="Q29" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S29" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="T29" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="U29" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -2766,53 +3576,53 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="H30" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K30" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="L30" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="M30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O30" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="P30" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="Q30" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S30" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="T30" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="U30" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -2821,53 +3631,53 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="H31" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K31" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L31" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="M31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O31" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="P31" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="Q31" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S31" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="T31" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="U31" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -2876,7 +3686,7 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -2889,40 +3699,40 @@
         <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="H32" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L32" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="M32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O32" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="P32" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="Q32" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S32" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="T32" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="U32" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -2931,7 +3741,7 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -2944,40 +3754,40 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="H33" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="I33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="M33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O33" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="P33" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="Q33" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S33" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="T33" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="U33" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -2986,7 +3796,7 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -2999,40 +3809,40 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="I34" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K34" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="L34" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="M34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O34" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="P34" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="Q34" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S34" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="T34" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="U34" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -3041,7 +3851,7 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -3054,40 +3864,40 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K35" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="M35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O35" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="P35" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="Q35" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S35" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="U35" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -3096,7 +3906,7 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -3109,40 +3919,40 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K36" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="M36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O36" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="P36" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="Q36" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S36" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="T36" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="U36" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -3151,7 +3961,7 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -3164,40 +3974,40 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="I37" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K37" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="L37" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O37" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="Q37" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S37" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="T37" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="U37" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -3206,7 +4016,7 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -3219,40 +4029,40 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K38" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="L38" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="M38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O38" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="P38" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="Q38" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S38" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="T38" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="U38" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -3261,7 +4071,7 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -3274,40 +4084,40 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K39" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="L39" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="M39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O39" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="Q39" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S39" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="T39" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="U39" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -3316,7 +4126,7 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -3329,40 +4139,40 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="H40" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="I40" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="M40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O40" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="P40" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="Q40" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S40" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="T40" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="U40" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -3371,7 +4181,7 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -3383,40 +4193,40 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="H41" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="I41" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O41" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="P41" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="Q41" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S41" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="T41" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="U41" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -3425,53 +4235,53 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="H42" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="I42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="M42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O42" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="Q42" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S42" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="T42" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="U42" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -3480,53 +4290,53 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="H43" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="I43" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="L43" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="M43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O43" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="P43" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="Q43" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S43" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="T43" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="U43" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -3535,53 +4345,53 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="I44" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="L44" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="M44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O44" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="P44" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="Q44" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S44" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="T44" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="U44" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -3590,7 +4400,7 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
@@ -3603,40 +4413,40 @@
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="H45" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="I45" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="L45" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="M45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O45" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="P45" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="Q45" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S45" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="T45" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="U45" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -3645,7 +4455,7 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
@@ -3658,40 +4468,40 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="H46" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="I46" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K46" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="M46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O46" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="P46" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="Q46" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S46" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="T46" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="U46" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -3700,7 +4510,7 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
@@ -3713,40 +4523,40 @@
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="H47" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="I47" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K47" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="L47" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="M47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O47" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="P47" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="Q47" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S47" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="T47" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="U47" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -3755,7 +4565,7 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
@@ -3768,40 +4578,40 @@
         <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="H48" t="s">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="I48" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K48" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="L48" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="M48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O48" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="P48" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="Q48" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S48" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="T48" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="U48" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -3810,7 +4620,7 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
@@ -3823,40 +4633,40 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="H49" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="I49" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K49" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="L49" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="M49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O49" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="P49" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="Q49" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S49" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
       <c r="T49" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
       <c r="U49" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -3865,7 +4675,7 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -3877,40 +4687,40 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="H50" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="I50" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K50" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="L50" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="M50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O50" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="P50" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="Q50" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S50" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="T50" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="U50" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -3919,53 +4729,53 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="H51" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="I51" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K51" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="L51" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="M51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O51" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="P51" t="s">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="Q51" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S51" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="T51" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="U51" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -3974,53 +4784,53 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="H52" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K52" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="L52" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="M52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O52" t="s">
-        <v>31</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="Q52" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S52" t="s">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="T52" t="s">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="U52" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -4029,53 +4839,53 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="H53" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="I53" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>29</v>
+        <v>180</v>
       </c>
       <c r="L53" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="M53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O53" t="s">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="P53" t="s">
-        <v>31</v>
+        <v>182</v>
       </c>
       <c r="Q53" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S53" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="T53" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="U53" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -4084,7 +4894,7 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
@@ -4097,40 +4907,40 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="I54" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K54" t="s">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="L54" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="M54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O54" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="P54" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="Q54" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S54" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="T54" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="U54" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -4139,7 +4949,7 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
@@ -4152,40 +4962,40 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="I55" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K55" t="s">
-        <v>29</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="M55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O55" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="P55" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Q55" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S55" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="T55" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="U55" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -4194,7 +5004,7 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
@@ -4207,40 +5017,40 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="H56" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="I56" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K56" t="s">
-        <v>29</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O56" t="s">
-        <v>31</v>
+        <v>198</v>
       </c>
       <c r="P56" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="Q56" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S56" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="T56" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="U56" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -4249,7 +5059,7 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
@@ -4262,40 +5072,40 @@
         <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>201</v>
       </c>
       <c r="H57" t="s">
-        <v>29</v>
+        <v>201</v>
       </c>
       <c r="I57" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="L57" t="s">
-        <v>29</v>
+        <v>203</v>
       </c>
       <c r="M57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O57" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="P57" t="s">
-        <v>31</v>
+        <v>205</v>
       </c>
       <c r="Q57" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S57" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="T57" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="U57" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -4304,7 +5114,7 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
@@ -4317,40 +5127,40 @@
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>42</v>
+        <v>207</v>
       </c>
       <c r="H58" t="s">
-        <v>42</v>
+        <v>207</v>
       </c>
       <c r="I58" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K58" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="L58" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="M58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O58" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="P58" t="s">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="Q58" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S58" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="T58" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="U58" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -4359,7 +5169,7 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -4371,40 +5181,40 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>42</v>
+        <v>214</v>
       </c>
       <c r="H59" t="s">
-        <v>42</v>
+        <v>214</v>
       </c>
       <c r="I59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="L59" t="s">
-        <v>42</v>
+        <v>216</v>
       </c>
       <c r="M59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O59" t="s">
-        <v>43</v>
+        <v>217</v>
       </c>
       <c r="P59" t="s">
-        <v>43</v>
+        <v>218</v>
       </c>
       <c r="Q59" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S59" t="s">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="T59" t="s">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="U59" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -4413,53 +5223,53 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="H60" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="I60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K60" t="s">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="L60" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="M60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O60" t="s">
-        <v>43</v>
+        <v>223</v>
       </c>
       <c r="P60" t="s">
-        <v>43</v>
+        <v>224</v>
       </c>
       <c r="Q60" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S60" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="T60" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="U60" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -4468,53 +5278,53 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="H61" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="I61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K61" t="s">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s">
-        <v>42</v>
+        <v>228</v>
       </c>
       <c r="M61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O61" t="s">
-        <v>43</v>
+        <v>229</v>
       </c>
       <c r="P61" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="Q61" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S61" t="s">
-        <v>44</v>
+        <v>231</v>
       </c>
       <c r="T61" t="s">
-        <v>44</v>
+        <v>231</v>
       </c>
       <c r="U61" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -4523,53 +5333,53 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="H62" t="s">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="I62" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K62" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="L62" t="s">
-        <v>42</v>
+        <v>234</v>
       </c>
       <c r="M62" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O62" t="s">
-        <v>43</v>
+        <v>235</v>
       </c>
       <c r="P62" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="Q62" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S62" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
       <c r="T62" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
       <c r="U62" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -4578,7 +5388,7 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -4591,40 +5401,40 @@
         <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="I63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" t="s">
-        <v>42</v>
+        <v>239</v>
       </c>
       <c r="L63" t="s">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="M63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O63" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="P63" t="s">
-        <v>43</v>
+        <v>242</v>
       </c>
       <c r="Q63" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S63" t="s">
-        <v>44</v>
+        <v>243</v>
       </c>
       <c r="T63" t="s">
-        <v>44</v>
+        <v>243</v>
       </c>
       <c r="U63" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -4633,7 +5443,7 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -4646,40 +5456,40 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
       <c r="H64" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
       <c r="I64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K64" t="s">
-        <v>42</v>
+        <v>245</v>
       </c>
       <c r="L64" t="s">
-        <v>42</v>
+        <v>246</v>
       </c>
       <c r="M64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O64" t="s">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="P64" t="s">
-        <v>43</v>
+        <v>248</v>
       </c>
       <c r="Q64" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S64" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="T64" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="U64" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -4688,7 +5498,7 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -4701,40 +5511,40 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="I65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K65" t="s">
-        <v>29</v>
+        <v>251</v>
       </c>
       <c r="L65" t="s">
-        <v>29</v>
+        <v>252</v>
       </c>
       <c r="M65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O65" t="s">
-        <v>46</v>
+        <v>253</v>
       </c>
       <c r="P65" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="Q65" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S65" t="s">
-        <v>47</v>
+        <v>254</v>
       </c>
       <c r="T65" t="s">
-        <v>47</v>
+        <v>254</v>
       </c>
       <c r="U65" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -4743,7 +5553,7 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -4756,40 +5566,40 @@
         <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>29</v>
+        <v>255</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>255</v>
       </c>
       <c r="I66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K66" t="s">
-        <v>29</v>
+        <v>256</v>
       </c>
       <c r="L66" t="s">
-        <v>29</v>
+        <v>257</v>
       </c>
       <c r="M66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O66" t="s">
-        <v>46</v>
+        <v>258</v>
       </c>
       <c r="P66" t="s">
-        <v>46</v>
+        <v>259</v>
       </c>
       <c r="Q66" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S66" t="s">
-        <v>47</v>
+        <v>260</v>
       </c>
       <c r="T66" t="s">
-        <v>47</v>
+        <v>260</v>
       </c>
       <c r="U66" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -4798,7 +5608,7 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -4811,40 +5621,40 @@
         <v>6</v>
       </c>
       <c r="G67" t="s">
-        <v>29</v>
+        <v>261</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>261</v>
       </c>
       <c r="I67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K67" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="L67" t="s">
-        <v>29</v>
+        <v>196</v>
       </c>
       <c r="M67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O67" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="P67" t="s">
-        <v>46</v>
+        <v>264</v>
       </c>
       <c r="Q67" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S67" t="s">
-        <v>47</v>
+        <v>265</v>
       </c>
       <c r="T67" t="s">
-        <v>47</v>
+        <v>265</v>
       </c>
       <c r="U67" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -4853,7 +5663,7 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -4866,40 +5676,40 @@
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="I68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K68" t="s">
-        <v>29</v>
+        <v>267</v>
       </c>
       <c r="L68" t="s">
-        <v>29</v>
+        <v>268</v>
       </c>
       <c r="M68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O68" t="s">
-        <v>46</v>
+        <v>269</v>
       </c>
       <c r="P68" t="s">
-        <v>46</v>
+        <v>193</v>
       </c>
       <c r="Q68" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S68" t="s">
-        <v>47</v>
+        <v>270</v>
       </c>
       <c r="T68" t="s">
-        <v>47</v>
+        <v>270</v>
       </c>
       <c r="U68" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -4908,7 +5718,7 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -4921,40 +5731,40 @@
         <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
       <c r="I69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K69" t="s">
-        <v>29</v>
+        <v>272</v>
       </c>
       <c r="L69" t="s">
-        <v>29</v>
+        <v>273</v>
       </c>
       <c r="M69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O69" t="s">
-        <v>46</v>
+        <v>274</v>
       </c>
       <c r="P69" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="Q69" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S69" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="T69" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="U69" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -4963,7 +5773,7 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -4976,40 +5786,40 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="I70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K70" t="s">
-        <v>29</v>
+        <v>277</v>
       </c>
       <c r="L70" t="s">
-        <v>29</v>
+        <v>278</v>
       </c>
       <c r="M70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O70" t="s">
-        <v>46</v>
+        <v>279</v>
       </c>
       <c r="P70" t="s">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="Q70" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S70" t="s">
-        <v>47</v>
+        <v>281</v>
       </c>
       <c r="T70" t="s">
-        <v>47</v>
+        <v>281</v>
       </c>
       <c r="U70" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -5018,7 +5828,7 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -5031,40 +5841,40 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>29</v>
+        <v>282</v>
       </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>282</v>
       </c>
       <c r="I71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K71" t="s">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c r="L71" t="s">
-        <v>29</v>
+        <v>284</v>
       </c>
       <c r="M71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O71" t="s">
-        <v>46</v>
+        <v>285</v>
       </c>
       <c r="P71" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="Q71" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S71" t="s">
-        <v>47</v>
+        <v>287</v>
       </c>
       <c r="T71" t="s">
-        <v>47</v>
+        <v>287</v>
       </c>
       <c r="U71" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -5073,7 +5883,7 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -5085,40 +5895,40 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="H72" t="s">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="I72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K72" t="s">
-        <v>29</v>
+        <v>290</v>
       </c>
       <c r="L72" t="s">
-        <v>29</v>
+        <v>291</v>
       </c>
       <c r="M72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O72" t="s">
-        <v>46</v>
+        <v>292</v>
       </c>
       <c r="P72" t="s">
-        <v>46</v>
+        <v>293</v>
       </c>
       <c r="Q72" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S72" t="s">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c r="T72" t="s">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c r="U72" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -5127,53 +5937,53 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="I73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K73" t="s">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="L73" t="s">
-        <v>29</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O73" t="s">
-        <v>46</v>
+        <v>297</v>
       </c>
       <c r="P73" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="Q73" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S73" t="s">
-        <v>47</v>
+        <v>298</v>
       </c>
       <c r="T73" t="s">
-        <v>47</v>
+        <v>298</v>
       </c>
       <c r="U73" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -5182,53 +5992,53 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="H74" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="I74" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="K74" t="s">
-        <v>29</v>
+        <v>300</v>
       </c>
       <c r="L74" t="s">
-        <v>29</v>
+        <v>301</v>
       </c>
       <c r="M74" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O74" t="s">
-        <v>46</v>
+        <v>302</v>
       </c>
       <c r="P74" t="s">
-        <v>46</v>
+        <v>303</v>
       </c>
       <c r="Q74" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
       <c r="S74" t="s">
-        <v>47</v>
+        <v>305</v>
       </c>
       <c r="T74" t="s">
-        <v>47</v>
+        <v>305</v>
       </c>
       <c r="U74" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -5237,53 +6047,53 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
       <c r="H75" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
       <c r="I75" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="K75" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
       <c r="L75" t="s">
-        <v>29</v>
+        <v>308</v>
       </c>
       <c r="M75" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O75" t="s">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="P75" t="s">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="Q75" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
       <c r="S75" t="s">
-        <v>47</v>
+        <v>311</v>
       </c>
       <c r="T75" t="s">
-        <v>47</v>
+        <v>311</v>
       </c>
       <c r="U75" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -5292,7 +6102,7 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -5305,40 +6115,40 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>29</v>
+        <v>312</v>
       </c>
       <c r="H76" t="s">
-        <v>29</v>
+        <v>312</v>
       </c>
       <c r="I76" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="K76" t="s">
-        <v>29</v>
+        <v>313</v>
       </c>
       <c r="L76" t="s">
-        <v>29</v>
+        <v>314</v>
       </c>
       <c r="M76" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O76" t="s">
-        <v>46</v>
+        <v>315</v>
       </c>
       <c r="P76" t="s">
-        <v>46</v>
+        <v>316</v>
       </c>
       <c r="Q76" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
       <c r="S76" t="s">
-        <v>47</v>
+        <v>317</v>
       </c>
       <c r="T76" t="s">
-        <v>47</v>
+        <v>317</v>
       </c>
       <c r="U76" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:21">
@@ -5347,7 +6157,7 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -5360,40 +6170,40 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>29</v>
+        <v>318</v>
       </c>
       <c r="H77" t="s">
-        <v>29</v>
+        <v>318</v>
       </c>
       <c r="I77" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="K77" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
       <c r="L77" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
       <c r="M77" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O77" t="s">
-        <v>46</v>
+        <v>321</v>
       </c>
       <c r="P77" t="s">
-        <v>46</v>
+        <v>322</v>
       </c>
       <c r="Q77" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
       <c r="S77" t="s">
-        <v>47</v>
+        <v>323</v>
       </c>
       <c r="T77" t="s">
-        <v>47</v>
+        <v>323</v>
       </c>
       <c r="U77" t="s">
-        <v>49</v>
+        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -5402,7 +6212,7 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -5415,40 +6225,40 @@
         <v>8</v>
       </c>
       <c r="G78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I78" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="L78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M78" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="O78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q78" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="S78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T78" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U78" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
     </row>
     <row r="79" spans="1:21">
@@ -5457,7 +6267,7 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -5470,40 +6280,40 @@
         <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I79" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="L79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M79" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="O79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q79" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="S79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T79" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U79" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -5512,7 +6322,7 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -5525,40 +6335,40 @@
         <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I80" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="L80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M80" t="s">
-        <v>51</v>
+        <v>326</v>
       </c>
       <c r="O80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q80" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="S80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T80" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U80" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
     </row>
     <row r="81" spans="1:21">
@@ -5567,7 +6377,7 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -5580,40 +6390,40 @@
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I81" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K81" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M81" t="s">
-        <v>51</v>
+        <v>326</v>
       </c>
       <c r="O81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q81" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="S81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T81" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U81" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" spans="1:21">
@@ -5622,7 +6432,7 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -5635,40 +6445,40 @@
         <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I82" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K82" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M82" t="s">
-        <v>51</v>
+        <v>326</v>
       </c>
       <c r="O82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q82" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="S82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T82" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U82" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83" spans="1:21">
@@ -5677,7 +6487,7 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -5690,40 +6500,40 @@
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I83" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="K83" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M83" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="O83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q83" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
       <c r="S83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T83" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U83" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84" spans="1:21">
@@ -5732,7 +6542,7 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -5745,40 +6555,40 @@
         <v>2</v>
       </c>
       <c r="G84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I84" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="K84" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M84" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="O84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q84" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
       <c r="S84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T84" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U84" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
     </row>
     <row r="85" spans="1:21">
@@ -5787,7 +6597,7 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -5799,40 +6609,40 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I85" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="K85" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M85" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="O85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="P85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q85" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
       <c r="S85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="T85" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="U85" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" spans="1:21">
@@ -5841,53 +6651,53 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H86" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I86" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="K86" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L86" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M86" t="s">
-        <v>53</v>
+        <v>326</v>
       </c>
       <c r="O86" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="P86" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q86" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
       <c r="S86" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="T86" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="U86" t="s">
-        <v>53</v>
+        <v>327</v>
       </c>
     </row>
     <row r="87" spans="1:21">
@@ -5896,53 +6706,53 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H87" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I87" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="K87" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L87" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M87" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="O87" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="P87" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q87" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
       <c r="S87" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="T87" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="U87" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -5951,53 +6761,53 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="H88" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I88" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="K88" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L88" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M88" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="O88" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="P88" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q88" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
       <c r="S88" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="T88" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="U88" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89" spans="1:21">
@@ -6006,7 +6816,7 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -6019,40 +6829,40 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H89" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I89" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="K89" t="s">
-        <v>52</v>
+        <v>330</v>
       </c>
       <c r="L89" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M89" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="O89" t="s">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="P89" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q89" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
       <c r="S89" t="s">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="T89" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="U89" t="s">
-        <v>56</v>
+        <v>329</v>
       </c>
     </row>
     <row r="90" spans="1:21">
@@ -6061,7 +6871,7 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -6074,40 +6884,40 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H90" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I90" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="K90" t="s">
-        <v>52</v>
+        <v>330</v>
       </c>
       <c r="L90" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M90" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="O90" t="s">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="P90" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q90" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="S90" t="s">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="T90" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="U90" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -6116,7 +6926,7 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -6129,40 +6939,40 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H91" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I91" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="K91" t="s">
-        <v>52</v>
+        <v>330</v>
       </c>
       <c r="L91" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M91" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="O91" t="s">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="P91" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q91" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="S91" t="s">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="T91" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="U91" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -6171,7 +6981,7 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -6184,40 +6994,40 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H92" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I92" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="K92" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="L92" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M92" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="O92" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P92" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q92" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="S92" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T92" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="U92" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -6226,7 +7036,7 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -6239,40 +7049,40 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H93" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I93" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="K93" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="L93" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M93" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="O93" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P93" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q93" t="s">
-        <v>60</v>
+        <v>332</v>
       </c>
       <c r="S93" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T93" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="U93" t="s">
-        <v>60</v>
+        <v>332</v>
       </c>
     </row>
     <row r="94" spans="1:21">
@@ -6281,7 +7091,7 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -6294,40 +7104,40 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H94" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I94" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="K94" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="L94" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M94" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="O94" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P94" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q94" t="s">
-        <v>60</v>
+        <v>332</v>
       </c>
       <c r="S94" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T94" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="U94" t="s">
-        <v>60</v>
+        <v>332</v>
       </c>
     </row>
     <row r="95" spans="1:21">
@@ -6336,7 +7146,7 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -6349,40 +7159,40 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H95" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I95" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="K95" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="L95" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M95" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="O95" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P95" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q95" t="s">
-        <v>60</v>
+        <v>332</v>
       </c>
       <c r="S95" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T95" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="U95" t="s">
-        <v>60</v>
+        <v>332</v>
       </c>
     </row>
     <row r="96" spans="1:21">
@@ -6391,7 +7201,7 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -6404,40 +7214,40 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H96" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I96" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="K96" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="L96" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M96" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="O96" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P96" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q96" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S96" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T96" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="U96" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:21">
@@ -6446,7 +7256,7 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>328</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -6459,40 +7269,40 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="H97" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="I97" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="K97" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="L97" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="M97" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="O97" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P97" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="Q97" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S97" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T97" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="U97" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:21">
@@ -6501,7 +7311,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -6513,40 +7323,40 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="H98" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="I98" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="K98" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="L98" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="M98" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="O98" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P98" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="Q98" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="S98" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T98" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="U98" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -6555,53 +7365,53 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="H99" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="I99" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="K99" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="L99" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="M99" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="O99" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P99" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="Q99" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="S99" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T99" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="U99" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -6610,53 +7420,53 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="H100" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="I100" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="K100" t="s">
-        <v>53</v>
+        <v>330</v>
       </c>
       <c r="L100" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="M100" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="O100" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P100" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="Q100" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="S100" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T100" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="U100" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
     </row>
     <row r="101" spans="1:21">
@@ -6665,53 +7475,53 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="H101" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="I101" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="K101" t="s">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="L101" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="M101" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="O101" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="P101" t="s">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="Q101" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="S101" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="T101" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="U101" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
     </row>
     <row r="102" spans="1:21">
@@ -6720,7 +7530,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -6733,40 +7543,40 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>64</v>
+        <v>325</v>
       </c>
       <c r="H102" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="I102" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="K102" t="s">
-        <v>57</v>
+        <v>325</v>
       </c>
       <c r="L102" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="M102" t="s">
-        <v>63</v>
+        <v>326</v>
       </c>
       <c r="O102" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="P102" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="Q102" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
       <c r="S102" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="T102" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="U102" t="s">
-        <v>63</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="1:21">
@@ -6775,7 +7585,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -6788,40 +7598,40 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>64</v>
+        <v>325</v>
       </c>
       <c r="H103" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="I103" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="K103" t="s">
-        <v>57</v>
+        <v>325</v>
       </c>
       <c r="L103" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="M103" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="O103" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="P103" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="Q103" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="S103" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="T103" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="U103" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -6830,7 +7640,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -6843,40 +7653,40 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="H104" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="I104" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="K104" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="L104" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="M104" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="O104" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="P104" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="Q104" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="S104" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="T104" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="U104" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
     </row>
     <row r="105" spans="1:21">
@@ -6885,7 +7695,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -6898,40 +7708,40 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="H105" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="I105" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="K105" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="L105" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="M105" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="O105" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="P105" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="Q105" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
       <c r="S105" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="T105" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="U105" t="s">
-        <v>30</v>
+        <v>326</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -6940,7 +7750,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -6953,40 +7763,40 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="H106" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="I106" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="K106" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="L106" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="M106" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="O106" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="P106" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="Q106" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
       <c r="S106" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="T106" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="U106" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
     </row>
     <row r="107" spans="1:21">
@@ -6995,7 +7805,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -7008,40 +7818,40 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="H107" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="I107" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="K107" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="L107" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="M107" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="O107" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="P107" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="Q107" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
       <c r="S107" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="T107" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="U107" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
     </row>
     <row r="108" spans="1:21">
@@ -7050,7 +7860,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -7063,40 +7873,40 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="H108" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="I108" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="K108" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="L108" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="M108" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="O108" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="P108" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="Q108" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
       <c r="S108" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="T108" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="U108" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
     </row>
     <row r="109" spans="1:21">
@@ -7105,7 +7915,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -7118,40 +7928,40 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="H109" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="I109" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="K109" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="L109" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="M109" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="O109" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="P109" t="s">
-        <v>57</v>
+        <v>331</v>
       </c>
       <c r="Q109" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
       <c r="S109" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="T109" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
       <c r="U109" t="s">
-        <v>65</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="428">
   <si>
     <t>ID</t>
   </si>
@@ -151,103 +151,868 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_500|2_3000|3_0|4_2000</t>
+    <t>1_1000|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1500|2_3000|3_0|4_2000</t>
   </si>
   <si>
     <t>1_0|2_2000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_1000|2_3000|3_0|4_3000</t>
+    <t>1_2000|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4000|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4400|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5280|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1485|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>1_4356|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5227|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>1_980|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2744|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4704|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4312|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5174|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_970|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1455|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2716|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4656|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4268|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5122|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2688|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3840|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4608|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5069|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_950|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1425|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4180|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5016|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2632|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4512|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4136|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4963|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_930|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1395|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1860|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2604|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4464|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4092|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4910|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2576|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4416|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4048|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4858|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_910|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1365|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2548|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4368|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4004|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4805|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3600|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2464|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3872|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4646|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_870|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1305|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1740|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2436|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3480|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4176|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3828|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4594|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_860|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1290|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1720|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2408|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4128|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3784|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4541|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2352|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4032|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3696|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4435|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_830|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1245|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2324|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3984|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3652|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4382|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2296|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3280|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3936|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3608|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4330|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_800|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2240|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_790|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1185|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1580|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2212|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3792|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3476|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4171|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2184|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3120|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3744|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3432|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4118|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2128|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3040|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3648|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3344|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4013|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_740|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1110|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1480|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2072|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3552|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3256|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3907|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1080|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3456|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3802|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_700|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1050|2_3000|3_0|4_2000</t>
   </si>
   <si>
     <t>1_1400|2_3000|3_0|4_3000</t>
   </si>
   <si>
-    <t>1_1500|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2250|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>1_495|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1386|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1485|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2228|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_2970|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>1_490|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_980|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1372|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1470|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2205|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2940|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_485|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_970|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1358|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1455|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2183|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2910|2_3000|3_0|4_6000</t>
+    <t>1_2800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3080|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_680|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1020|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1360|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1904|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3264|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2992|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3590|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2904|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3485|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_945|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1764|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3024|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3326|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_610|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_915|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1220|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1708|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2928|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2684|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3221|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_590|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_885|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1180|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1652|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2360|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2832|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2596|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3115|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>1_570|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_855|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1140|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1596|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2280|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2736|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2508|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3010|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_560|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1120|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1568|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2240|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2688|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2464|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2957|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_540|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_810|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1080|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1512|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2160|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2592|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2376|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2851|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_530|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_795|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1060|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1484|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2120|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2544|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2332|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2798|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_510|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_765|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1020|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1428|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2040|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2448|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2244|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2693|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_500|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_750|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1000|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1400|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2400|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2200|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2640|2_2000|3_0|4_6000</t>
   </si>
   <si>
     <t>1_480|2_3000|3_0|4_2000</t>
@@ -259,781 +1024,295 @@
     <t>1_1344|2_3000|3_0|4_3000</t>
   </si>
   <si>
+    <t>1_1920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2304|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2534|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_705|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1316|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2256|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2068|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2482|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_675|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2376|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1232|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1936|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2323|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1176|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2218|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_615|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1148|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1968|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1804|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2165|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_585|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1092|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1872|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1716|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2059|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_570|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1064|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1824|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1672|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2006|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_300|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
     <t>1_1440|2_3000|3_0|4_4000</t>
   </si>
   <si>
-    <t>1_2160|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2880|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_475|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_950|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1330|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1425|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2138|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2850|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_940|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1316|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2115|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2820|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_465|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_930|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1302|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1395|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2093|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2790|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_460|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_920|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1288|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1380|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2070|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2760|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_455|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_910|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1274|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1365|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2048|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2730|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2025|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2700|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_880|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1232|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2640|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_435|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_870|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1218|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1305|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1958|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2610|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_430|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_860|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1204|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1290|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1935|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2580|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_840|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1176|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1890|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2520|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_415|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_830|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1162|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1245|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1868|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2490|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_820|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1148|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1845|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2460|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_400|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_800|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1120|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1200|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2400|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_395|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_790|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1106|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1185|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1778|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2370|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_780|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1092|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1755|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2340|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_760|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1064|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1710|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2280|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_370|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_740|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1036|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1110|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1665|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2220|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_360|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1008|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1080|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1620|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2160|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_350|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_700|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1050|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1575|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2100|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_340|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_680|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_952|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1020|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1530|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2040|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_330|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_924|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_315|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_882|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_945|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1418|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1890|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_305|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_610|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_854|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_915|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1373|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1830|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_295|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_590|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_826|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_885|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1328|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1770|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>1_285|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_570|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_798|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_855|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1283|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1710|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_280|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_560|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_784|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_840|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1260|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1680|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_270|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_540|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_756|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_810|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1215|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1620|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_265|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_530|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_742|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_795|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1193|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1590|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_255|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_510|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_714|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_765|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1148|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1530|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_250|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_500|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_700|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_750|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1125|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1500|2_2000|3_0|4_6000</t>
+    <t>1_1320|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1584|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_345|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_460|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_644|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1104|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_1012|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1214|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_160|2_3000|3_0|4_2000</t>
   </si>
   <si>
     <t>1_240|2_3000|3_0|4_2000</t>
   </si>
   <si>
-    <t>1_480|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_672|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_235|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_658|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_705|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1058|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_225|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_675|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1013|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_220|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_616|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_210|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_588|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_205|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_574|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_615|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_923|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_195|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_546|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_585|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_878|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>1_190|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_532|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_570|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_855|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_150|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_300|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_115|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_230|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_322|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_345|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_518|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_690|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_80|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_160|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_224|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_240|2_3000|3_0|4_4000</t>
+    <t>1_320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_448|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_768|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_704|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_845|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_90|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_135|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_180|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_252|2_3000|3_0|4_3000</t>
   </si>
   <si>
     <t>1_360|2_3000|3_0|4_4000</t>
   </si>
   <si>
-    <t>1_480|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_45|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_90|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_126|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_135|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_203|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_270|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_10|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_20|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_28|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_30|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_45|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_60|2_3000|3_0|4_6000</t>
+    <t>1_432|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_396|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_475|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_20|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_30|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_40|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_56|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_80|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_96|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_88|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_106|2_3000|3_0|4_6000</t>
   </si>
   <si>
     <t>1_0|2_3000|3_0|4_0</t>
@@ -1042,9 +1321,6 @@
     <t>1_0|2_0|3_3000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
@@ -1054,16 +1330,16 @@
     <t>1_0|2_0|3_5000|4_0</t>
   </si>
   <si>
+    <t>1_0|2_0|3_6000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_7000|4_0</t>
+  </si>
+  <si>
+    <t>高牌</t>
+  </si>
+  <si>
     <t>1_0|2_3000|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>高牌</t>
   </si>
   <si>
     <t>1_0|2_0|3_9000|4_0</t>
@@ -2220,37 +2496,37 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2259,7 +2535,7 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -2271,40 +2547,40 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -2313,53 +2589,53 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -2368,53 +2644,53 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -2423,53 +2699,53 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -2478,7 +2754,7 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -2491,40 +2767,40 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -2533,7 +2809,7 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -2546,40 +2822,40 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -2588,7 +2864,7 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -2601,40 +2877,40 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -2643,7 +2919,7 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -2656,40 +2932,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -2698,7 +2974,7 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -2711,40 +2987,40 @@
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -2753,7 +3029,7 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -2765,40 +3041,40 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -2807,53 +3083,53 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -2862,53 +3138,53 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -2917,53 +3193,53 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -2972,7 +3248,7 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -2985,40 +3261,40 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3027,7 +3303,7 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -3040,40 +3316,40 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3082,7 +3358,7 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -3095,40 +3371,40 @@
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O21" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -3137,7 +3413,7 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -3150,40 +3426,40 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P22" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -3192,7 +3468,7 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -3205,40 +3481,40 @@
         <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P23" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -3247,7 +3523,7 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -3260,40 +3536,40 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L24" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -3302,7 +3578,7 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -3315,40 +3591,40 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -3357,7 +3633,7 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -3370,40 +3646,40 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L26" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -3412,7 +3688,7 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -3425,40 +3701,40 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O27" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -3467,7 +3743,7 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3479,40 +3755,40 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S28" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -3521,53 +3797,53 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L29" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O29" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P29" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="Q29" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S29" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T29" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U29" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -3576,53 +3852,53 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K30" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L30" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O30" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="P30" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q30" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="T30" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="U30" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -3631,53 +3907,53 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H31" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="L31" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O31" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="P31" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="Q31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S31" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="T31" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="U31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -3686,7 +3962,7 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -3699,40 +3975,40 @@
         <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K32" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="L32" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O32" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="P32" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="Q32" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S32" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="T32" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="U32" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -3741,7 +4017,7 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -3754,40 +4030,40 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L33" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O33" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="P33" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="Q33" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S33" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="T33" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="U33" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -3796,7 +4072,7 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -3809,40 +4085,40 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K34" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L34" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O34" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="P34" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="Q34" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S34" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="T34" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="U34" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -3851,7 +4127,7 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -3864,40 +4140,40 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K35" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L35" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O35" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="Q35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S35" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="T35" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="U35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -3906,7 +4182,7 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -3919,40 +4195,40 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="L36" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="M36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O36" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="P36" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="Q36" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S36" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="T36" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="U36" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -3961,7 +4237,7 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -3974,40 +4250,40 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K37" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="M37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O37" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="P37" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="Q37" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S37" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="T37" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="U37" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -4016,7 +4292,7 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -4029,40 +4305,40 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H38" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K38" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="L38" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="M38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O38" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="Q38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S38" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="T38" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="U38" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -4071,7 +4347,7 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -4084,40 +4360,40 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H39" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K39" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="L39" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="M39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O39" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="P39" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="Q39" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S39" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="T39" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="U39" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -4126,7 +4402,7 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -4139,40 +4415,40 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="H40" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K40" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="L40" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="M40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O40" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="P40" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="Q40" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S40" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="T40" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="U40" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -4181,7 +4457,7 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -4193,40 +4469,40 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="H41" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K41" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="L41" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="M41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O41" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="P41" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="Q41" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S41" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="T41" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="U41" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -4235,53 +4511,53 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K42" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="L42" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="M42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O42" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="P42" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="Q42" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S42" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="T42" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="U42" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -4290,53 +4566,53 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="G43" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" t="s">
+        <v>145</v>
+      </c>
+      <c r="I43" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L43" t="s">
+        <v>147</v>
+      </c>
+      <c r="M43" t="s">
+        <v>34</v>
+      </c>
+      <c r="O43" t="s">
+        <v>148</v>
+      </c>
+      <c r="P43" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>46</v>
+      </c>
+      <c r="S43" t="s">
+        <v>150</v>
+      </c>
+      <c r="T43" t="s">
+        <v>151</v>
+      </c>
+      <c r="U43" t="s">
         <v>118</v>
-      </c>
-      <c r="H43" t="s">
-        <v>118</v>
-      </c>
-      <c r="I43" t="s">
-        <v>30</v>
-      </c>
-      <c r="K43" t="s">
-        <v>119</v>
-      </c>
-      <c r="L43" t="s">
-        <v>120</v>
-      </c>
-      <c r="M43" t="s">
-        <v>35</v>
-      </c>
-      <c r="O43" t="s">
-        <v>121</v>
-      </c>
-      <c r="P43" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>43</v>
-      </c>
-      <c r="S43" t="s">
-        <v>123</v>
-      </c>
-      <c r="T43" t="s">
-        <v>123</v>
-      </c>
-      <c r="U43" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -4345,53 +4621,53 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="H44" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K44" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="M44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O44" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="P44" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="Q44" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S44" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="T44" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="U44" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -4400,7 +4676,7 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
@@ -4413,40 +4689,40 @@
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="H45" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K45" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="L45" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="M45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O45" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="P45" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="Q45" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S45" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="T45" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="U45" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -4455,7 +4731,7 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
@@ -4468,40 +4744,40 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K46" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="L46" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="M46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O46" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="P46" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="Q46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S46" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="T46" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="U46" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -4510,7 +4786,7 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
@@ -4523,40 +4799,40 @@
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="H47" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K47" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="L47" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="M47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O47" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="P47" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="Q47" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S47" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="T47" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="U47" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4565,7 +4841,7 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
@@ -4578,40 +4854,40 @@
         <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="H48" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="I48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K48" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="M48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O48" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="P48" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="Q48" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S48" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="T48" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="U48" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -4620,7 +4896,7 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
@@ -4633,40 +4909,40 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="H49" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K49" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="L49" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="M49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O49" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="P49" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="Q49" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S49" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="T49" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="U49" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -4675,7 +4951,7 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -4687,40 +4963,40 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="H50" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="I50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K50" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="L50" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="M50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O50" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="Q50" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="S50" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="T50" t="s">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="U50" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -4729,53 +5005,53 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="H51" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K51" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="M51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O51" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="Q51" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="S51" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="T51" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="U51" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -4784,53 +5060,53 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K52" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="L52" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="M52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O52" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="Q52" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="S52" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="T52" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="U52" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -4839,53 +5115,53 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="H53" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K53" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="L53" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O53" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="Q53" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="S53" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="T53" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="U53" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -4894,7 +5170,7 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
@@ -4907,40 +5183,40 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="H54" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K54" t="s">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="L54" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="M54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O54" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="Q54" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="S54" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="T54" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="U54" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -4949,7 +5225,7 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
@@ -4962,40 +5238,40 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="H55" t="s">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K55" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="L55" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="M55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O55" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="P55" t="s">
-        <v>41</v>
+        <v>240</v>
       </c>
       <c r="Q55" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="S55" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="T55" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="U55" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -5004,7 +5280,7 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
@@ -5017,40 +5293,40 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="H56" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K56" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="L56" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="M56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O56" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="Q56" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S56" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="T56" t="s">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U56" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -5059,7 +5335,7 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
@@ -5072,40 +5348,40 @@
         <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="H57" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K57" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="L57" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="M57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O57" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="Q57" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S57" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="T57" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="U57" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -5114,7 +5390,7 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
@@ -5127,40 +5403,40 @@
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="H58" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K58" t="s">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="L58" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="M58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O58" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="P58" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="Q58" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S58" t="s">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="T58" t="s">
-        <v>212</v>
+        <v>266</v>
       </c>
       <c r="U58" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -5169,7 +5445,7 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -5181,40 +5457,40 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>214</v>
+        <v>268</v>
       </c>
       <c r="H59" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="I59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K59" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="L59" t="s">
-        <v>216</v>
+        <v>271</v>
       </c>
       <c r="M59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O59" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>273</v>
       </c>
       <c r="Q59" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S59" t="s">
-        <v>219</v>
+        <v>274</v>
       </c>
       <c r="T59" t="s">
-        <v>219</v>
+        <v>275</v>
       </c>
       <c r="U59" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -5223,53 +5499,53 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="H60" t="s">
-        <v>220</v>
+        <v>277</v>
       </c>
       <c r="I60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K60" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="L60" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="M60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O60" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="Q60" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S60" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="T60" t="s">
-        <v>225</v>
+        <v>283</v>
       </c>
       <c r="U60" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -5278,53 +5554,53 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="H61" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="I61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K61" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="L61" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="M61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O61" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="Q61" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S61" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="T61" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="U61" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -5333,53 +5609,53 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="H62" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="I62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K62" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="L62" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="M62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O62" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="Q62" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S62" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="T62" t="s">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="U62" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -5388,7 +5664,7 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -5401,40 +5677,40 @@
         <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="H63" t="s">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="I63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="L63" t="s">
-        <v>240</v>
+        <v>303</v>
       </c>
       <c r="M63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O63" t="s">
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="Q63" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S63" t="s">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="T63" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="U63" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -5443,7 +5719,7 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -5456,40 +5732,40 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="H64" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="I64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K64" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="L64" t="s">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="M64" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O64" t="s">
-        <v>247</v>
+        <v>313</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="Q64" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S64" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="T64" t="s">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="U64" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -5498,7 +5774,7 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -5511,40 +5787,40 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
       <c r="H65" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="I65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K65" t="s">
-        <v>251</v>
+        <v>318</v>
       </c>
       <c r="L65" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="M65" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O65" t="s">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>321</v>
       </c>
       <c r="Q65" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S65" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
       <c r="T65" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="U65" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -5553,7 +5829,7 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -5566,40 +5842,40 @@
         <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="H66" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="I66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K66" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="L66" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="M66" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O66" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="Q66" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S66" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="T66" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
       <c r="U66" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -5608,7 +5884,7 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -5621,40 +5897,40 @@
         <v>6</v>
       </c>
       <c r="G67" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
       <c r="H67" t="s">
-        <v>261</v>
+        <v>333</v>
       </c>
       <c r="I67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K67" t="s">
-        <v>262</v>
+        <v>334</v>
       </c>
       <c r="L67" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="M67" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O67" t="s">
-        <v>263</v>
+        <v>335</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="Q67" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S67" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="T67" t="s">
-        <v>265</v>
+        <v>338</v>
       </c>
       <c r="U67" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -5663,7 +5939,7 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -5676,40 +5952,40 @@
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>266</v>
+        <v>339</v>
       </c>
       <c r="H68" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="I68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K68" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="L68" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="M68" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O68" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>343</v>
       </c>
       <c r="Q68" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S68" t="s">
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="T68" t="s">
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="U68" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -5718,7 +5994,7 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -5731,40 +6007,40 @@
         <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>271</v>
+        <v>346</v>
       </c>
       <c r="H69" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="I69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K69" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="L69" t="s">
-        <v>273</v>
+        <v>348</v>
       </c>
       <c r="M69" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O69" t="s">
-        <v>274</v>
+        <v>349</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>350</v>
       </c>
       <c r="Q69" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S69" t="s">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="T69" t="s">
-        <v>275</v>
+        <v>352</v>
       </c>
       <c r="U69" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -5773,7 +6049,7 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -5786,40 +6062,40 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="H70" t="s">
-        <v>276</v>
+        <v>354</v>
       </c>
       <c r="I70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K70" t="s">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c r="L70" t="s">
-        <v>278</v>
+        <v>356</v>
       </c>
       <c r="M70" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O70" t="s">
-        <v>279</v>
+        <v>357</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>358</v>
       </c>
       <c r="Q70" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S70" t="s">
-        <v>281</v>
+        <v>359</v>
       </c>
       <c r="T70" t="s">
-        <v>281</v>
+        <v>360</v>
       </c>
       <c r="U70" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -5828,7 +6104,7 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -5841,40 +6117,40 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
       <c r="H71" t="s">
-        <v>282</v>
+        <v>362</v>
       </c>
       <c r="I71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K71" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
       <c r="L71" t="s">
-        <v>284</v>
+        <v>364</v>
       </c>
       <c r="M71" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O71" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>366</v>
       </c>
       <c r="Q71" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S71" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="T71" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="U71" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -5883,7 +6159,7 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -5895,40 +6171,40 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>289</v>
+        <v>370</v>
       </c>
       <c r="H72" t="s">
-        <v>289</v>
+        <v>371</v>
       </c>
       <c r="I72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K72" t="s">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="L72" t="s">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="M72" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O72" t="s">
-        <v>292</v>
+        <v>374</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="Q72" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S72" t="s">
-        <v>294</v>
+        <v>376</v>
       </c>
       <c r="T72" t="s">
-        <v>294</v>
+        <v>377</v>
       </c>
       <c r="U72" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -5937,53 +6213,53 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>295</v>
+        <v>378</v>
       </c>
       <c r="H73" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="I73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K73" t="s">
-        <v>296</v>
+        <v>379</v>
       </c>
       <c r="L73" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="M73" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O73" t="s">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="P73" t="s">
-        <v>263</v>
+        <v>381</v>
       </c>
       <c r="Q73" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S73" t="s">
-        <v>298</v>
+        <v>382</v>
       </c>
       <c r="T73" t="s">
-        <v>298</v>
+        <v>383</v>
       </c>
       <c r="U73" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -5992,53 +6268,53 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>299</v>
+        <v>384</v>
       </c>
       <c r="H74" t="s">
-        <v>299</v>
+        <v>385</v>
       </c>
       <c r="I74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K74" t="s">
-        <v>300</v>
+        <v>386</v>
       </c>
       <c r="L74" t="s">
-        <v>301</v>
+        <v>387</v>
       </c>
       <c r="M74" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O74" t="s">
-        <v>302</v>
+        <v>388</v>
       </c>
       <c r="P74" t="s">
-        <v>303</v>
+        <v>389</v>
       </c>
       <c r="Q74" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="S74" t="s">
-        <v>305</v>
+        <v>391</v>
       </c>
       <c r="T74" t="s">
-        <v>305</v>
+        <v>392</v>
       </c>
       <c r="U74" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -6047,53 +6323,53 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>306</v>
+        <v>393</v>
       </c>
       <c r="H75" t="s">
-        <v>306</v>
+        <v>394</v>
       </c>
       <c r="I75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K75" t="s">
-        <v>307</v>
+        <v>395</v>
       </c>
       <c r="L75" t="s">
-        <v>308</v>
+        <v>396</v>
       </c>
       <c r="M75" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O75" t="s">
-        <v>309</v>
+        <v>397</v>
       </c>
       <c r="P75" t="s">
-        <v>310</v>
+        <v>398</v>
       </c>
       <c r="Q75" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="S75" t="s">
-        <v>311</v>
+        <v>399</v>
       </c>
       <c r="T75" t="s">
-        <v>311</v>
+        <v>400</v>
       </c>
       <c r="U75" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -6102,7 +6378,7 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -6115,40 +6391,40 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
+        <v>401</v>
+      </c>
+      <c r="H76" t="s">
+        <v>402</v>
+      </c>
+      <c r="I76" t="s">
+        <v>34</v>
+      </c>
+      <c r="K76" t="s">
+        <v>403</v>
+      </c>
+      <c r="L76" t="s">
+        <v>404</v>
+      </c>
+      <c r="M76" t="s">
         <v>312</v>
       </c>
-      <c r="H76" t="s">
-        <v>312</v>
-      </c>
-      <c r="I76" t="s">
-        <v>35</v>
-      </c>
-      <c r="K76" t="s">
-        <v>313</v>
-      </c>
-      <c r="L76" t="s">
-        <v>314</v>
-      </c>
-      <c r="M76" t="s">
-        <v>35</v>
-      </c>
       <c r="O76" t="s">
-        <v>315</v>
+        <v>405</v>
       </c>
       <c r="P76" t="s">
-        <v>316</v>
+        <v>406</v>
       </c>
       <c r="Q76" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="S76" t="s">
-        <v>317</v>
+        <v>407</v>
       </c>
       <c r="T76" t="s">
-        <v>317</v>
+        <v>408</v>
       </c>
       <c r="U76" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77" spans="1:21">
@@ -6157,7 +6433,7 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -6170,40 +6446,40 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>318</v>
+        <v>409</v>
       </c>
       <c r="H77" t="s">
-        <v>318</v>
+        <v>410</v>
       </c>
       <c r="I77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K77" t="s">
-        <v>319</v>
+        <v>411</v>
       </c>
       <c r="L77" t="s">
-        <v>320</v>
+        <v>412</v>
       </c>
       <c r="M77" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O77" t="s">
-        <v>321</v>
+        <v>413</v>
       </c>
       <c r="P77" t="s">
-        <v>322</v>
+        <v>414</v>
       </c>
       <c r="Q77" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
       <c r="S77" t="s">
-        <v>323</v>
+        <v>415</v>
       </c>
       <c r="T77" t="s">
-        <v>323</v>
+        <v>416</v>
       </c>
       <c r="U77" t="s">
-        <v>304</v>
+        <v>390</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -6212,7 +6488,7 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -6225,40 +6501,40 @@
         <v>8</v>
       </c>
       <c r="G78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M78" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q78" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="S78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T78" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U78" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
     </row>
     <row r="79" spans="1:21">
@@ -6267,7 +6543,7 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -6280,40 +6556,40 @@
         <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M79" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="O79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q79" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="S79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T79" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U79" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -6322,7 +6598,7 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -6335,40 +6611,40 @@
         <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M80" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q80" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="S80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T80" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U80" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
     </row>
     <row r="81" spans="1:21">
@@ -6377,7 +6653,7 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -6390,40 +6666,40 @@
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M81" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q81" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="S81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T81" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U81" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
     </row>
     <row r="82" spans="1:21">
@@ -6432,7 +6708,7 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -6445,40 +6721,40 @@
         <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M82" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q82" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="S82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T82" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U82" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
     </row>
     <row r="83" spans="1:21">
@@ -6487,7 +6763,7 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -6500,40 +6776,40 @@
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M83" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q83" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
       <c r="S83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T83" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U83" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
     </row>
     <row r="84" spans="1:21">
@@ -6542,7 +6818,7 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -6555,40 +6831,40 @@
         <v>2</v>
       </c>
       <c r="G84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I84" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M84" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q84" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
       <c r="S84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T84" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U84" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:21">
@@ -6597,7 +6873,7 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6609,40 +6885,40 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I85" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M85" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q85" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
       <c r="S85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T85" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U85" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
     </row>
     <row r="86" spans="1:21">
@@ -6651,53 +6927,53 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I86" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M86" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q86" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
       <c r="S86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T86" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U86" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
     </row>
     <row r="87" spans="1:21">
@@ -6706,53 +6982,53 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I87" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M87" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q87" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
       <c r="S87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T87" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U87" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -6761,53 +7037,53 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I88" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="L88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M88" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="P88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q88" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
       <c r="S88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="T88" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U88" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
     </row>
     <row r="89" spans="1:21">
@@ -6816,7 +7092,7 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -6829,40 +7105,40 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H89" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I89" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K89" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L89" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M89" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O89" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P89" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q89" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
       <c r="S89" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T89" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U89" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
     </row>
     <row r="90" spans="1:21">
@@ -6871,7 +7147,7 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -6884,40 +7160,40 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H90" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I90" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K90" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L90" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M90" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O90" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P90" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q90" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="S90" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T90" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U90" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -6926,7 +7202,7 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -6939,40 +7215,40 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H91" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I91" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K91" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L91" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M91" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O91" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P91" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q91" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="S91" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T91" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U91" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -6981,7 +7257,7 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -6994,40 +7270,40 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H92" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I92" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K92" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L92" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M92" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O92" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P92" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q92" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="S92" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T92" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U92" t="s">
-        <v>331</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -7036,7 +7312,7 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -7049,40 +7325,40 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H93" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I93" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K93" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L93" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M93" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O93" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P93" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q93" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
       <c r="S93" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T93" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U93" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
     </row>
     <row r="94" spans="1:21">
@@ -7091,7 +7367,7 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -7104,40 +7380,40 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H94" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I94" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K94" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L94" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M94" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O94" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P94" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q94" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
       <c r="S94" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T94" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U94" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
     </row>
     <row r="95" spans="1:21">
@@ -7146,7 +7422,7 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -7159,40 +7435,40 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H95" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I95" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K95" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L95" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M95" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O95" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P95" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q95" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
       <c r="S95" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T95" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U95" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
     </row>
     <row r="96" spans="1:21">
@@ -7201,7 +7477,7 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -7214,40 +7490,40 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H96" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I96" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K96" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L96" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M96" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O96" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P96" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q96" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S96" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T96" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U96" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="1:21">
@@ -7256,7 +7532,7 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -7269,40 +7545,40 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="H97" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="I97" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K97" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="L97" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="M97" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O97" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="P97" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="Q97" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S97" t="s">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="T97" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="U97" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:21">
@@ -7311,7 +7587,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -7323,40 +7599,40 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="H98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="I98" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="L98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="M98" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="P98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="Q98" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="S98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="T98" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="U98" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -7365,53 +7641,53 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="H99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="I99" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="L99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="M99" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="P99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="Q99" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
       <c r="S99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="T99" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="U99" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -7420,53 +7696,53 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="H100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="I100" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="L100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="M100" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="P100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="Q100" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
       <c r="S100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="T100" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="U100" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
     </row>
     <row r="101" spans="1:21">
@@ -7475,53 +7751,53 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="H101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="I101" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="L101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="M101" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="P101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="Q101" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
       <c r="S101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="T101" t="s">
-        <v>330</v>
+        <v>425</v>
       </c>
       <c r="U101" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="1:21">
@@ -7530,7 +7806,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -7543,40 +7819,40 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="H102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="I102" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="L102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="M102" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="P102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="Q102" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
       <c r="S102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="T102" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="U102" t="s">
-        <v>334</v>
+        <v>426</v>
       </c>
     </row>
     <row r="103" spans="1:21">
@@ -7585,7 +7861,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -7598,40 +7874,40 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="H103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="I103" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="L103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="M103" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="P103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="Q103" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="S103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="T103" t="s">
-        <v>325</v>
+        <v>418</v>
       </c>
       <c r="U103" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -7640,7 +7916,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -7653,40 +7929,40 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="H104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="I104" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="L104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="M104" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="Q104" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="S104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="T104" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="U104" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:21">
@@ -7695,7 +7971,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -7708,40 +7984,40 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="H105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="I105" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="L105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="M105" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="P105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="Q105" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="S105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="T105" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="U105" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -7750,7 +8026,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -7763,40 +8039,40 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="H106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="I106" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="L106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="M106" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="P106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="Q106" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
       <c r="S106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="T106" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="U106" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
     </row>
     <row r="107" spans="1:21">
@@ -7805,7 +8081,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -7818,40 +8094,40 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="H107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="I107" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="L107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="M107" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="P107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="Q107" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
       <c r="S107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="T107" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="U107" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
     </row>
     <row r="108" spans="1:21">
@@ -7860,7 +8136,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -7873,40 +8149,40 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="H108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="I108" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="L108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="M108" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="P108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="Q108" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
       <c r="S108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="T108" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="U108" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109" spans="1:21">
@@ -7915,7 +8191,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -7928,40 +8204,40 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="H109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="I109" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="K109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="L109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="M109" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="O109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="P109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="Q109" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
       <c r="S109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="T109" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="U109" t="s">
-        <v>335</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="chessTexasStrategy" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="336">
   <si>
     <t>ID</t>
   </si>
@@ -79,18 +79,15 @@
     <t>无人加注的行为权重</t>
   </si>
   <si>
-    <t>他人加注的行为权重</t>
+    <t>他人加注的行为权重-我方牌大</t>
+  </si>
+  <si>
+    <t>他人加注的行为权重-我方牌小</t>
   </si>
   <si>
     <t>第二轮</t>
   </si>
   <si>
-    <t>他人加注的行为权重-我方牌大</t>
-  </si>
-  <si>
-    <t>他人加注的行为权重-我方牌小</t>
-  </si>
-  <si>
     <t>第三轮</t>
   </si>
   <si>
@@ -115,7 +112,10 @@
     <t>proactiveStrategy_1</t>
   </si>
   <si>
-    <t>passiveStrategy_1</t>
+    <t>passiveStrategyWin_1</t>
+  </si>
+  <si>
+    <t>passiveStrategyFailed_1</t>
   </si>
   <si>
     <t>proactiveStrategy_2</t>
@@ -151,25 +151,52 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_10000|2_10000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_10000|2_10000|3_0|4_10000</t>
+    <t>1_500|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1000|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1400|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1500|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2250|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3000|2_3000|3_0|4_6000</t>
   </si>
   <si>
     <t>同花顺</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_5000</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_10000</t>
+    <t>1_495|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1386|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1485|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2228|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_1000|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>1_2970|2_3000|3_0|4_6000</t>
   </si>
   <si>
     <t>K</t>
@@ -187,127 +214,862 @@
     <t>葫芦</t>
   </si>
   <si>
+    <t>1_490|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_980|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1372|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1470|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2205|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2940|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_485|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_970|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1358|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1455|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2183|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2910|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1344|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2880|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_475|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_950|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1330|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1425|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2138|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2850|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1316|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2115|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2820|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_465|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_930|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1302|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1395|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2093|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2790|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_460|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1288|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1380|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2070|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2760|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_455|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_910|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1274|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1365|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2048|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2730|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_8000|4_0</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2025|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2700|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
     <t>同花</t>
   </si>
   <si>
+    <t>1_440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1232|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2640|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_435|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_870|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1218|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1305|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1958|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2610|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_430|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_860|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1204|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1290|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1935|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2580|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1176|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1890|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_415|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_830|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1162|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1245|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1868|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2490|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1148|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1845|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2460|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_400|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1120|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2400|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_395|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_790|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1106|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1185|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1778|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2370|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1092|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1755|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2340|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
     <t>顺子</t>
   </si>
   <si>
-    <t>1_8000|2_8000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_8000</t>
+    <t>1_380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1064|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1710|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2280|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_370|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_740|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1036|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1110|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1665|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2220|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1008|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1080|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1620|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_350|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_700|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1050|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1575|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2100|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_340|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_680|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_952|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1020|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1530|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2040|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_330|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_924|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_315|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_882|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_945|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1418|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1890|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_305|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_610|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_854|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_915|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1373|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1830|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_295|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_590|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_826|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_885|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1328|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1770|2_2000|3_0|4_6000</t>
   </si>
   <si>
     <t>三条</t>
   </si>
   <si>
+    <t>1_285|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_570|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_798|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_855|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1283|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1710|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_280|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_560|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_784|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_840|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1260|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1680|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_270|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_540|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_756|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_810|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1215|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1620|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_265|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_530|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_742|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_795|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1193|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1590|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_255|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_510|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_714|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_765|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1148|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1530|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_250|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_500|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_700|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_750|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1125|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1500|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_672|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_235|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_658|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_705|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1058|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_225|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_675|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1013|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_220|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_616|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_210|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_588|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_205|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_574|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_615|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_923|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_195|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_546|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_585|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_878|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
     <t>两对</t>
   </si>
   <si>
-    <t>1_0|2_8000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_8000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_7000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_4000|4_0</t>
+    <t>1_190|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_532|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_570|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_855|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_150|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_300|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_115|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_230|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_322|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_345|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_518|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_690|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_80|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_160|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_224|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_45|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_90|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_126|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_135|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_203|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_270|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_10|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_20|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_28|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_30|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_45|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_60|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_3000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_4000|4_0</t>
   </si>
   <si>
     <t>一对</t>
   </si>
   <si>
-    <t>1_10000|2_10000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_8000|2_8000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_4000|2_4000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_8000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_5000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_10000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_2000|2_10000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_8000|4_0</t>
+    <t>1_0|2_0|3_5000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_3000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_6000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_7000|4_0</t>
   </si>
   <si>
     <t>高牌</t>
   </si>
   <si>
-    <t>1_0|2_1000|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_6000|2_6000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_4000|2_4000|3_0|4_1000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_6000|4_0</t>
+    <t>1_0|2_0|3_9000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_11000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
   </si>
 </sst>
 </file>
@@ -484,12 +1246,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -810,7 +1578,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -834,16 +1602,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -852,93 +1620,102 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1252,19 +2029,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:U109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
     <col min="7" max="8" width="32.5" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="12" width="29.75" customWidth="1"/>
-    <col min="14" max="16" width="27.85" customWidth="1"/>
-    <col min="17" max="17" width="20.7166666666667" customWidth="1"/>
-    <col min="18" max="20" width="26.0666666666667" customWidth="1"/>
+    <col min="9" max="9" width="29.75" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="13" width="29.75" customWidth="1"/>
+    <col min="15" max="17" width="27.85" customWidth="1"/>
+    <col min="18" max="18" width="20.7166666666667" customWidth="1"/>
+    <col min="19" max="21" width="26.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1283,135 +2062,144 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
       <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>20</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>21</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>22</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>23</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>24</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>25</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:21">
       <c r="A5">
         <f>100000+C5*1000+E5</f>
         <v>109014</v>
@@ -1422,4963 +2210,5758 @@
       <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E5">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
+      <c r="G5" t="s">
         <v>29</v>
       </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
         <v>30</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
-      </c>
-      <c r="R5" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>35</v>
       </c>
       <c r="S5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <f t="shared" ref="A6:A37" si="0">100000+C6*1000+E6</f>
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E6">
         <v>14</v>
       </c>
-      <c r="J6" t="s">
-        <v>33</v>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>43</v>
       </c>
       <c r="S6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>36</v>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
-      <c r="J7" t="s">
-        <v>33</v>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
-      </c>
-      <c r="R7" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>43</v>
       </c>
       <c r="S7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
+      <c r="D8" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
-      <c r="J8" t="s">
-        <v>33</v>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M8" t="s">
+        <v>35</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>43</v>
       </c>
       <c r="S8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>38</v>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
-      <c r="J9" t="s">
-        <v>33</v>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M9" t="s">
+        <v>35</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>43</v>
       </c>
       <c r="S9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>10</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
-        <v>33</v>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
-      </c>
-      <c r="R10" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>43</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
-      <c r="J11" t="s">
-        <v>33</v>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M11" t="s">
+        <v>35</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
-      </c>
-      <c r="R11" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>43</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>8</v>
       </c>
       <c r="E12">
         <v>8</v>
       </c>
-      <c r="J12" t="s">
-        <v>33</v>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M12" t="s">
+        <v>35</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>43</v>
       </c>
       <c r="S12" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>7</v>
       </c>
       <c r="E13">
         <v>7</v>
       </c>
-      <c r="J13" t="s">
-        <v>33</v>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M13" t="s">
+        <v>35</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
-      </c>
-      <c r="R13" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>43</v>
       </c>
       <c r="S13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
       </c>
-      <c r="J14" t="s">
-        <v>33</v>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
-      </c>
-      <c r="R14" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>43</v>
       </c>
       <c r="S14" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>7</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
-      <c r="J15" t="s">
-        <v>33</v>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" t="s">
+        <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M15" t="s">
+        <v>35</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>43</v>
       </c>
       <c r="S15" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
-      <c r="D16" t="s">
-        <v>36</v>
+      <c r="D16" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
-      <c r="J16" t="s">
-        <v>33</v>
+      <c r="G16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" t="s">
+        <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>43</v>
       </c>
       <c r="S16" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
-      <c r="D17" t="s">
-        <v>37</v>
+      <c r="D17" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
-      <c r="J17" t="s">
-        <v>33</v>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M17" t="s">
+        <v>35</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P17" t="s">
-        <v>34</v>
-      </c>
-      <c r="R17" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>43</v>
       </c>
       <c r="S17" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D18" t="s">
-        <v>38</v>
+      <c r="D18" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
-      <c r="J18" t="s">
-        <v>33</v>
+      <c r="G18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
-      </c>
-      <c r="N18" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M18" t="s">
+        <v>35</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
-      </c>
-      <c r="R18" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>43</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>10</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
-      <c r="J19" t="s">
-        <v>33</v>
+      <c r="G19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" t="s">
+        <v>30</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
-      </c>
-      <c r="N19" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M19" t="s">
+        <v>35</v>
       </c>
       <c r="O19" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>43</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>9</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
-      <c r="J20" t="s">
-        <v>33</v>
+      <c r="G20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" t="s">
+        <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
-      </c>
-      <c r="N20" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M20" t="s">
+        <v>35</v>
       </c>
       <c r="O20" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
-      </c>
-      <c r="R20" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>43</v>
       </c>
       <c r="S20" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
-      <c r="J21" t="s">
-        <v>33</v>
+      <c r="G21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" t="s">
+        <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
-      </c>
-      <c r="N21" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M21" t="s">
+        <v>35</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
-      </c>
-      <c r="R21" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>43</v>
       </c>
       <c r="S21" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>7</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
-      <c r="J22" t="s">
-        <v>33</v>
+      <c r="G22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" t="s">
+        <v>30</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
-      </c>
-      <c r="N22" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M22" t="s">
+        <v>35</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
-      </c>
-      <c r="R22" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>43</v>
       </c>
       <c r="S22" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>6</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
-      <c r="J23" t="s">
-        <v>33</v>
+      <c r="G23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
+        <v>30</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
-      </c>
-      <c r="N23" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M23" t="s">
+        <v>35</v>
       </c>
       <c r="O23" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
-      </c>
-      <c r="R23" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>43</v>
       </c>
       <c r="S23" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
-      <c r="J24" t="s">
-        <v>33</v>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" t="s">
+        <v>30</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M24" t="s">
+        <v>35</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P24" t="s">
-        <v>34</v>
-      </c>
-      <c r="R24" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>43</v>
       </c>
       <c r="S24" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>4</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
-      <c r="J25" t="s">
-        <v>33</v>
+      <c r="G25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>30</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L25" t="s">
-        <v>33</v>
-      </c>
-      <c r="N25" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M25" t="s">
+        <v>35</v>
       </c>
       <c r="O25" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P25" t="s">
-        <v>34</v>
-      </c>
-      <c r="R25" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>43</v>
       </c>
       <c r="S25" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="J26" t="s">
-        <v>33</v>
+      <c r="G26" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" t="s">
+        <v>30</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
-      </c>
-      <c r="N26" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M26" t="s">
+        <v>35</v>
       </c>
       <c r="O26" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
-      </c>
-      <c r="R26" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>43</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
-      <c r="J27" t="s">
-        <v>33</v>
+      <c r="G27" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" t="s">
+        <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L27" t="s">
-        <v>33</v>
-      </c>
-      <c r="N27" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M27" t="s">
+        <v>35</v>
       </c>
       <c r="O27" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P27" t="s">
-        <v>34</v>
-      </c>
-      <c r="R27" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>43</v>
       </c>
       <c r="S27" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E28">
         <v>14</v>
       </c>
-      <c r="J28" t="s">
-        <v>33</v>
+      <c r="G28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" t="s">
+        <v>30</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L28" t="s">
-        <v>33</v>
-      </c>
-      <c r="N28" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="M28" t="s">
+        <v>35</v>
       </c>
       <c r="O28" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
-      </c>
-      <c r="R28" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>43</v>
       </c>
       <c r="S28" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="T28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>44</v>
+      </c>
+      <c r="U28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
-      <c r="D29" t="s">
-        <v>36</v>
+      <c r="D29" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
-      <c r="J29" t="s">
-        <v>33</v>
+      <c r="G29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" t="s">
+        <v>30</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
-        <v>33</v>
-      </c>
-      <c r="N29" t="s">
-        <v>34</v>
+        <v>52</v>
+      </c>
+      <c r="M29" t="s">
+        <v>35</v>
       </c>
       <c r="O29" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="P29" t="s">
-        <v>34</v>
-      </c>
-      <c r="R29" t="s">
-        <v>35</v>
+        <v>54</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>43</v>
       </c>
       <c r="S29" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="T29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>55</v>
+      </c>
+      <c r="U29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
-      <c r="D30" t="s">
-        <v>37</v>
+      <c r="D30" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
-      <c r="J30" t="s">
-        <v>33</v>
+      <c r="G30" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" t="s">
+        <v>30</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
-      </c>
-      <c r="N30" t="s">
-        <v>34</v>
+        <v>58</v>
+      </c>
+      <c r="M30" t="s">
+        <v>35</v>
       </c>
       <c r="O30" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
-      </c>
-      <c r="R30" t="s">
-        <v>35</v>
+        <v>60</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>43</v>
       </c>
       <c r="S30" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="T30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>61</v>
+      </c>
+      <c r="U30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D31" t="s">
-        <v>38</v>
+      <c r="D31" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
-      <c r="J31" t="s">
-        <v>33</v>
+      <c r="G31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" t="s">
+        <v>30</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
-      </c>
-      <c r="N31" t="s">
-        <v>34</v>
+        <v>64</v>
+      </c>
+      <c r="M31" t="s">
+        <v>35</v>
       </c>
       <c r="O31" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="P31" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" t="s">
-        <v>35</v>
+        <v>66</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>43</v>
       </c>
       <c r="S31" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="T31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>67</v>
+      </c>
+      <c r="U31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>10</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
-      <c r="J32" t="s">
-        <v>33</v>
+      <c r="G32" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" t="s">
+        <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
-      </c>
-      <c r="N32" t="s">
-        <v>34</v>
+        <v>64</v>
+      </c>
+      <c r="M32" t="s">
+        <v>35</v>
       </c>
       <c r="O32" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
-      </c>
-      <c r="R32" t="s">
-        <v>35</v>
+        <v>66</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>43</v>
       </c>
       <c r="S32" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="T32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <v>67</v>
+      </c>
+      <c r="U32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>9</v>
       </c>
       <c r="E33">
         <v>9</v>
       </c>
-      <c r="J33" t="s">
-        <v>33</v>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" t="s">
+        <v>68</v>
+      </c>
+      <c r="I33" t="s">
+        <v>30</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
-      </c>
-      <c r="N33" t="s">
-        <v>34</v>
+        <v>70</v>
+      </c>
+      <c r="M33" t="s">
+        <v>35</v>
       </c>
       <c r="O33" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="P33" t="s">
-        <v>34</v>
-      </c>
-      <c r="R33" t="s">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>43</v>
       </c>
       <c r="S33" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="T33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
-      <c r="J34" t="s">
-        <v>33</v>
+      <c r="G34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" t="s">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s">
+        <v>30</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
-      </c>
-      <c r="N34" t="s">
-        <v>34</v>
+        <v>76</v>
+      </c>
+      <c r="M34" t="s">
+        <v>35</v>
       </c>
       <c r="O34" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="P34" t="s">
-        <v>34</v>
-      </c>
-      <c r="R34" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>43</v>
       </c>
       <c r="S34" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="T34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
+        <v>79</v>
+      </c>
+      <c r="U34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
         <v>7</v>
       </c>
       <c r="E35">
         <v>7</v>
       </c>
-      <c r="J35" t="s">
-        <v>33</v>
+      <c r="G35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s">
+        <v>30</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
-      </c>
-      <c r="N35" t="s">
-        <v>34</v>
+        <v>76</v>
+      </c>
+      <c r="M35" t="s">
+        <v>35</v>
       </c>
       <c r="O35" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
-      </c>
-      <c r="R35" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>43</v>
       </c>
       <c r="S35" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>79</v>
+      </c>
+      <c r="U35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>6</v>
       </c>
       <c r="E36">
         <v>6</v>
       </c>
-      <c r="J36" t="s">
-        <v>33</v>
+      <c r="G36" t="s">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s">
+        <v>80</v>
+      </c>
+      <c r="I36" t="s">
+        <v>30</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="L36" t="s">
-        <v>33</v>
-      </c>
-      <c r="N36" t="s">
-        <v>34</v>
+        <v>82</v>
+      </c>
+      <c r="M36" t="s">
+        <v>35</v>
       </c>
       <c r="O36" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="P36" t="s">
-        <v>34</v>
-      </c>
-      <c r="R36" t="s">
-        <v>35</v>
+        <v>84</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>43</v>
       </c>
       <c r="S36" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="T36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>85</v>
+      </c>
+      <c r="U36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>5</v>
       </c>
       <c r="E37">
         <v>5</v>
       </c>
-      <c r="J37" t="s">
-        <v>33</v>
+      <c r="G37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I37" t="s">
+        <v>30</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N37" t="s">
-        <v>34</v>
+        <v>88</v>
+      </c>
+      <c r="M37" t="s">
+        <v>35</v>
       </c>
       <c r="O37" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>34</v>
-      </c>
-      <c r="R37" t="s">
-        <v>35</v>
+        <v>90</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>43</v>
       </c>
       <c r="S37" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="T37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>91</v>
+      </c>
+      <c r="U37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38">
         <f t="shared" ref="A38:A69" si="4">100000+C38*1000+E38</f>
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>4</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
-      <c r="J38" t="s">
-        <v>33</v>
+      <c r="G38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" t="s">
+        <v>92</v>
+      </c>
+      <c r="I38" t="s">
+        <v>30</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="L38" t="s">
-        <v>33</v>
-      </c>
-      <c r="N38" t="s">
-        <v>34</v>
+        <v>94</v>
+      </c>
+      <c r="M38" t="s">
+        <v>35</v>
       </c>
       <c r="O38" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="P38" t="s">
-        <v>34</v>
-      </c>
-      <c r="R38" t="s">
-        <v>35</v>
+        <v>96</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>43</v>
       </c>
       <c r="S38" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="T38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
+        <v>97</v>
+      </c>
+      <c r="U38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39">
         <f t="shared" si="4"/>
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>3</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
-      <c r="J39" t="s">
-        <v>33</v>
+      <c r="G39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
+      </c>
+      <c r="I39" t="s">
+        <v>30</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="L39" t="s">
-        <v>33</v>
-      </c>
-      <c r="N39" t="s">
-        <v>34</v>
+        <v>94</v>
+      </c>
+      <c r="M39" t="s">
+        <v>35</v>
       </c>
       <c r="O39" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="P39" t="s">
-        <v>34</v>
-      </c>
-      <c r="R39" t="s">
-        <v>35</v>
+        <v>96</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>43</v>
       </c>
       <c r="S39" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="T39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
+        <v>97</v>
+      </c>
+      <c r="U39" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40">
         <f t="shared" si="4"/>
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
-      <c r="J40" t="s">
-        <v>33</v>
+      <c r="G40" t="s">
+        <v>99</v>
+      </c>
+      <c r="H40" t="s">
+        <v>99</v>
+      </c>
+      <c r="I40" t="s">
+        <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N40" t="s">
-        <v>34</v>
+        <v>101</v>
+      </c>
+      <c r="M40" t="s">
+        <v>35</v>
       </c>
       <c r="O40" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="P40" t="s">
-        <v>34</v>
-      </c>
-      <c r="R40" t="s">
-        <v>35</v>
+        <v>103</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>43</v>
       </c>
       <c r="S40" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="T40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <v>104</v>
+      </c>
+      <c r="U40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41">
         <f t="shared" si="4"/>
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
-      <c r="J41" t="s">
-        <v>33</v>
+      <c r="G41" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" t="s">
+        <v>106</v>
+      </c>
+      <c r="I41" t="s">
+        <v>30</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
-      </c>
-      <c r="N41" t="s">
-        <v>34</v>
+        <v>108</v>
+      </c>
+      <c r="M41" t="s">
+        <v>35</v>
       </c>
       <c r="O41" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="P41" t="s">
-        <v>34</v>
-      </c>
-      <c r="R41" t="s">
-        <v>35</v>
+        <v>110</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>43</v>
       </c>
       <c r="S41" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="T41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
+        <v>111</v>
+      </c>
+      <c r="U41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42">
         <f t="shared" si="4"/>
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
-      <c r="D42" t="s">
-        <v>36</v>
+      <c r="D42" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
-      <c r="J42" t="s">
-        <v>33</v>
+      <c r="G42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H42" t="s">
+        <v>112</v>
+      </c>
+      <c r="I42" t="s">
+        <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s">
-        <v>33</v>
-      </c>
-      <c r="N42" t="s">
-        <v>34</v>
+        <v>114</v>
+      </c>
+      <c r="M42" t="s">
+        <v>35</v>
       </c>
       <c r="O42" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>34</v>
-      </c>
-      <c r="R42" t="s">
-        <v>35</v>
+        <v>116</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>43</v>
       </c>
       <c r="S42" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="T42" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
+        <v>117</v>
+      </c>
+      <c r="U42" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43">
         <f t="shared" si="4"/>
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
-      <c r="D43" t="s">
-        <v>37</v>
+      <c r="D43" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
-      <c r="J43" t="s">
-        <v>33</v>
+      <c r="G43" t="s">
+        <v>118</v>
+      </c>
+      <c r="H43" t="s">
+        <v>118</v>
+      </c>
+      <c r="I43" t="s">
+        <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="L43" t="s">
-        <v>33</v>
-      </c>
-      <c r="N43" t="s">
-        <v>34</v>
+        <v>120</v>
+      </c>
+      <c r="M43" t="s">
+        <v>35</v>
       </c>
       <c r="O43" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="P43" t="s">
-        <v>34</v>
-      </c>
-      <c r="R43" t="s">
-        <v>35</v>
+        <v>122</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>43</v>
       </c>
       <c r="S43" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="T43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
+        <v>123</v>
+      </c>
+      <c r="U43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44">
         <f t="shared" si="4"/>
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D44" t="s">
-        <v>38</v>
+      <c r="D44" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
-      <c r="J44" t="s">
-        <v>33</v>
+      <c r="G44" t="s">
+        <v>124</v>
+      </c>
+      <c r="H44" t="s">
+        <v>124</v>
+      </c>
+      <c r="I44" t="s">
+        <v>30</v>
       </c>
       <c r="K44" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="L44" t="s">
-        <v>33</v>
-      </c>
-      <c r="N44" t="s">
-        <v>34</v>
+        <v>126</v>
+      </c>
+      <c r="M44" t="s">
+        <v>35</v>
       </c>
       <c r="O44" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="P44" t="s">
-        <v>34</v>
-      </c>
-      <c r="R44" t="s">
-        <v>35</v>
+        <v>128</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>43</v>
       </c>
       <c r="S44" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="T44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
+        <v>129</v>
+      </c>
+      <c r="U44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45">
         <f t="shared" si="4"/>
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>10</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
-      <c r="J45" t="s">
-        <v>33</v>
+      <c r="G45" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" t="s">
+        <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="L45" t="s">
-        <v>33</v>
-      </c>
-      <c r="N45" t="s">
-        <v>34</v>
+        <v>132</v>
+      </c>
+      <c r="M45" t="s">
+        <v>35</v>
       </c>
       <c r="O45" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="P45" t="s">
-        <v>34</v>
-      </c>
-      <c r="R45" t="s">
-        <v>35</v>
+        <v>134</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>43</v>
       </c>
       <c r="S45" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="T45" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
+        <v>135</v>
+      </c>
+      <c r="U45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46">
         <f t="shared" si="4"/>
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>9</v>
       </c>
       <c r="E46">
         <v>9</v>
       </c>
-      <c r="J46" t="s">
-        <v>33</v>
+      <c r="G46" t="s">
+        <v>136</v>
+      </c>
+      <c r="H46" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" t="s">
+        <v>30</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s">
-        <v>33</v>
-      </c>
-      <c r="N46" t="s">
-        <v>34</v>
+        <v>138</v>
+      </c>
+      <c r="M46" t="s">
+        <v>35</v>
       </c>
       <c r="O46" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="P46" t="s">
-        <v>34</v>
-      </c>
-      <c r="R46" t="s">
-        <v>35</v>
+        <v>140</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>43</v>
       </c>
       <c r="S46" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="T46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
+        <v>141</v>
+      </c>
+      <c r="U46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47">
         <f t="shared" si="4"/>
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>8</v>
       </c>
       <c r="E47">
         <v>8</v>
       </c>
-      <c r="J47" t="s">
-        <v>33</v>
+      <c r="G47" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" t="s">
+        <v>142</v>
+      </c>
+      <c r="I47" t="s">
+        <v>30</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="L47" t="s">
-        <v>33</v>
-      </c>
-      <c r="N47" t="s">
-        <v>34</v>
+        <v>144</v>
+      </c>
+      <c r="M47" t="s">
+        <v>35</v>
       </c>
       <c r="O47" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="P47" t="s">
-        <v>34</v>
-      </c>
-      <c r="R47" t="s">
-        <v>35</v>
+        <v>146</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>43</v>
       </c>
       <c r="S47" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="T47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
+        <v>147</v>
+      </c>
+      <c r="U47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48">
         <f t="shared" si="4"/>
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
         <v>7</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
-      <c r="J48" t="s">
-        <v>33</v>
+      <c r="G48" t="s">
+        <v>148</v>
+      </c>
+      <c r="H48" t="s">
+        <v>148</v>
+      </c>
+      <c r="I48" t="s">
+        <v>30</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="L48" t="s">
-        <v>33</v>
-      </c>
-      <c r="N48" t="s">
-        <v>34</v>
+        <v>150</v>
+      </c>
+      <c r="M48" t="s">
+        <v>35</v>
       </c>
       <c r="O48" t="s">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="P48" t="s">
-        <v>34</v>
-      </c>
-      <c r="R48" t="s">
-        <v>35</v>
+        <v>152</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>43</v>
       </c>
       <c r="S48" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="T48" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <v>153</v>
+      </c>
+      <c r="U48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49">
         <f t="shared" si="4"/>
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>6</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
-      <c r="J49" t="s">
-        <v>33</v>
+      <c r="G49" t="s">
+        <v>154</v>
+      </c>
+      <c r="H49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" t="s">
+        <v>30</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
-      </c>
-      <c r="N49" t="s">
-        <v>34</v>
+        <v>156</v>
+      </c>
+      <c r="M49" t="s">
+        <v>35</v>
       </c>
       <c r="O49" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="P49" t="s">
-        <v>34</v>
-      </c>
-      <c r="R49" t="s">
-        <v>35</v>
+        <v>158</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>43</v>
       </c>
       <c r="S49" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="T49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
+        <v>159</v>
+      </c>
+      <c r="U49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50">
         <f t="shared" si="4"/>
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E50">
         <v>14</v>
       </c>
-      <c r="J50" t="s">
-        <v>33</v>
+      <c r="G50" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" t="s">
+        <v>161</v>
+      </c>
+      <c r="I50" t="s">
+        <v>30</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="L50" t="s">
-        <v>33</v>
-      </c>
-      <c r="N50" t="s">
-        <v>34</v>
+        <v>163</v>
+      </c>
+      <c r="M50" t="s">
+        <v>35</v>
       </c>
       <c r="O50" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="P50" t="s">
-        <v>34</v>
-      </c>
-      <c r="R50" t="s">
-        <v>35</v>
+        <v>165</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>43</v>
       </c>
       <c r="S50" t="s">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="T50" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+        <v>166</v>
+      </c>
+      <c r="U50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51">
         <f t="shared" si="4"/>
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
-      <c r="D51" t="s">
-        <v>36</v>
+      <c r="D51" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
-      <c r="J51" t="s">
-        <v>33</v>
+      <c r="G51" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" t="s">
+        <v>167</v>
+      </c>
+      <c r="I51" t="s">
+        <v>30</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
-      </c>
-      <c r="N51" t="s">
-        <v>34</v>
+        <v>169</v>
+      </c>
+      <c r="M51" t="s">
+        <v>35</v>
       </c>
       <c r="O51" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="P51" t="s">
-        <v>34</v>
-      </c>
-      <c r="R51" t="s">
-        <v>35</v>
+        <v>171</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>43</v>
       </c>
       <c r="S51" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="T51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
+        <v>172</v>
+      </c>
+      <c r="U51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52">
         <f t="shared" si="4"/>
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
-      <c r="D52" t="s">
-        <v>37</v>
+      <c r="D52" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
-      <c r="J52" t="s">
-        <v>33</v>
+      <c r="G52" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" t="s">
+        <v>173</v>
+      </c>
+      <c r="I52" t="s">
+        <v>30</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="L52" t="s">
-        <v>33</v>
-      </c>
-      <c r="N52" t="s">
-        <v>34</v>
+        <v>175</v>
+      </c>
+      <c r="M52" t="s">
+        <v>35</v>
       </c>
       <c r="O52" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s">
-        <v>34</v>
-      </c>
-      <c r="R52" t="s">
-        <v>35</v>
+        <v>177</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>43</v>
       </c>
       <c r="S52" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="T52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <v>178</v>
+      </c>
+      <c r="U52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53">
         <f t="shared" si="4"/>
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D53" t="s">
-        <v>38</v>
+      <c r="D53" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
-      <c r="J53" t="s">
-        <v>33</v>
+      <c r="G53" t="s">
+        <v>179</v>
+      </c>
+      <c r="H53" t="s">
+        <v>179</v>
+      </c>
+      <c r="I53" t="s">
+        <v>30</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="L53" t="s">
-        <v>33</v>
-      </c>
-      <c r="N53" t="s">
-        <v>34</v>
+        <v>51</v>
+      </c>
+      <c r="M53" t="s">
+        <v>35</v>
       </c>
       <c r="O53" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="P53" t="s">
-        <v>34</v>
-      </c>
-      <c r="R53" t="s">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>43</v>
       </c>
       <c r="S53" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="T53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20">
+        <v>183</v>
+      </c>
+      <c r="U53" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54">
         <f t="shared" si="4"/>
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>10</v>
       </c>
       <c r="E54">
         <v>10</v>
       </c>
-      <c r="J54" t="s">
-        <v>33</v>
+      <c r="G54" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" t="s">
+        <v>184</v>
+      </c>
+      <c r="I54" t="s">
+        <v>30</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
       <c r="L54" t="s">
-        <v>33</v>
-      </c>
-      <c r="N54" t="s">
-        <v>34</v>
+        <v>186</v>
+      </c>
+      <c r="M54" t="s">
+        <v>35</v>
       </c>
       <c r="O54" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="P54" t="s">
-        <v>34</v>
-      </c>
-      <c r="R54" t="s">
-        <v>35</v>
+        <v>188</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>43</v>
       </c>
       <c r="S54" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="T54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20">
+        <v>189</v>
+      </c>
+      <c r="U54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55">
         <f t="shared" si="4"/>
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
         <v>9</v>
       </c>
       <c r="E55">
         <v>9</v>
       </c>
-      <c r="J55" t="s">
-        <v>33</v>
+      <c r="G55" t="s">
+        <v>190</v>
+      </c>
+      <c r="H55" t="s">
+        <v>190</v>
+      </c>
+      <c r="I55" t="s">
+        <v>30</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
-      </c>
-      <c r="N55" t="s">
-        <v>34</v>
+        <v>192</v>
+      </c>
+      <c r="M55" t="s">
+        <v>35</v>
       </c>
       <c r="O55" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="P55" t="s">
-        <v>34</v>
-      </c>
-      <c r="R55" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>43</v>
       </c>
       <c r="S55" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="T55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
+        <v>194</v>
+      </c>
+      <c r="U55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56">
         <f t="shared" si="4"/>
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>8</v>
       </c>
       <c r="E56">
         <v>8</v>
       </c>
-      <c r="J56" t="s">
-        <v>33</v>
+      <c r="G56" t="s">
+        <v>195</v>
+      </c>
+      <c r="H56" t="s">
+        <v>195</v>
+      </c>
+      <c r="I56" t="s">
+        <v>30</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s">
-        <v>33</v>
-      </c>
-      <c r="N56" t="s">
-        <v>34</v>
+        <v>197</v>
+      </c>
+      <c r="M56" t="s">
+        <v>35</v>
       </c>
       <c r="O56" t="s">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="P56" t="s">
-        <v>34</v>
-      </c>
-      <c r="R56" t="s">
-        <v>35</v>
+        <v>199</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>98</v>
       </c>
       <c r="S56" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="T56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
+        <v>200</v>
+      </c>
+      <c r="U56" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57">
         <f t="shared" si="4"/>
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
         <v>7</v>
       </c>
       <c r="E57">
         <v>7</v>
       </c>
-      <c r="J57" t="s">
-        <v>33</v>
+      <c r="G57" t="s">
+        <v>201</v>
+      </c>
+      <c r="H57" t="s">
+        <v>201</v>
+      </c>
+      <c r="I57" t="s">
+        <v>30</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>202</v>
       </c>
       <c r="L57" t="s">
-        <v>33</v>
-      </c>
-      <c r="N57" t="s">
-        <v>34</v>
+        <v>203</v>
+      </c>
+      <c r="M57" t="s">
+        <v>35</v>
       </c>
       <c r="O57" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
       <c r="P57" t="s">
-        <v>34</v>
-      </c>
-      <c r="R57" t="s">
-        <v>35</v>
+        <v>205</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>98</v>
       </c>
       <c r="S57" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="T57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20">
+        <v>206</v>
+      </c>
+      <c r="U57" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58">
         <f t="shared" si="4"/>
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>6</v>
       </c>
       <c r="E58">
         <v>6</v>
       </c>
-      <c r="J58" t="s">
-        <v>33</v>
+      <c r="G58" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" t="s">
+        <v>207</v>
+      </c>
+      <c r="I58" t="s">
+        <v>30</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
       <c r="L58" t="s">
-        <v>33</v>
-      </c>
-      <c r="N58" t="s">
-        <v>43</v>
+        <v>209</v>
+      </c>
+      <c r="M58" t="s">
+        <v>35</v>
       </c>
       <c r="O58" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="P58" t="s">
-        <v>43</v>
-      </c>
-      <c r="R58" t="s">
-        <v>44</v>
+        <v>211</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>98</v>
       </c>
       <c r="S58" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="T58" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20">
+        <v>212</v>
+      </c>
+      <c r="U58" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59">
         <f t="shared" si="4"/>
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E59">
         <v>14</v>
       </c>
-      <c r="J59" t="s">
-        <v>33</v>
+      <c r="G59" t="s">
+        <v>214</v>
+      </c>
+      <c r="H59" t="s">
+        <v>214</v>
+      </c>
+      <c r="I59" t="s">
+        <v>35</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L59" t="s">
-        <v>33</v>
-      </c>
-      <c r="N59" t="s">
-        <v>43</v>
+        <v>216</v>
+      </c>
+      <c r="M59" t="s">
+        <v>35</v>
       </c>
       <c r="O59" t="s">
-        <v>43</v>
+        <v>217</v>
       </c>
       <c r="P59" t="s">
-        <v>43</v>
-      </c>
-      <c r="R59" t="s">
-        <v>44</v>
+        <v>218</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>98</v>
       </c>
       <c r="S59" t="s">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="T59" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20">
+        <v>219</v>
+      </c>
+      <c r="U59" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60">
         <f t="shared" si="4"/>
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
-      <c r="D60" t="s">
-        <v>36</v>
+      <c r="D60" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
-      <c r="J60" t="s">
-        <v>33</v>
+      <c r="G60" t="s">
+        <v>220</v>
+      </c>
+      <c r="H60" t="s">
+        <v>220</v>
+      </c>
+      <c r="I60" t="s">
+        <v>35</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
+        <v>221</v>
       </c>
       <c r="L60" t="s">
-        <v>33</v>
-      </c>
-      <c r="N60" t="s">
-        <v>43</v>
+        <v>222</v>
+      </c>
+      <c r="M60" t="s">
+        <v>35</v>
       </c>
       <c r="O60" t="s">
-        <v>43</v>
+        <v>223</v>
       </c>
       <c r="P60" t="s">
-        <v>43</v>
-      </c>
-      <c r="R60" t="s">
-        <v>44</v>
+        <v>224</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>98</v>
       </c>
       <c r="S60" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="T60" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20">
+        <v>225</v>
+      </c>
+      <c r="U60" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61">
         <f t="shared" si="4"/>
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
-      <c r="D61" t="s">
-        <v>37</v>
+      <c r="D61" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="J61" t="s">
-        <v>33</v>
+      <c r="G61" t="s">
+        <v>226</v>
+      </c>
+      <c r="H61" t="s">
+        <v>226</v>
+      </c>
+      <c r="I61" t="s">
+        <v>35</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
-      </c>
-      <c r="N61" t="s">
-        <v>43</v>
+        <v>228</v>
+      </c>
+      <c r="M61" t="s">
+        <v>35</v>
       </c>
       <c r="O61" t="s">
-        <v>43</v>
+        <v>229</v>
       </c>
       <c r="P61" t="s">
-        <v>43</v>
-      </c>
-      <c r="R61" t="s">
-        <v>44</v>
+        <v>230</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>98</v>
       </c>
       <c r="S61" t="s">
-        <v>44</v>
+        <v>231</v>
       </c>
       <c r="T61" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20">
+        <v>231</v>
+      </c>
+      <c r="U61" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62">
         <f t="shared" si="4"/>
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D62" t="s">
-        <v>38</v>
+      <c r="D62" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
-      <c r="J62" t="s">
-        <v>33</v>
+      <c r="G62" t="s">
+        <v>232</v>
+      </c>
+      <c r="H62" t="s">
+        <v>232</v>
+      </c>
+      <c r="I62" t="s">
+        <v>35</v>
       </c>
       <c r="K62" t="s">
-        <v>33</v>
+        <v>233</v>
       </c>
       <c r="L62" t="s">
-        <v>33</v>
-      </c>
-      <c r="N62" t="s">
-        <v>43</v>
+        <v>234</v>
+      </c>
+      <c r="M62" t="s">
+        <v>35</v>
       </c>
       <c r="O62" t="s">
-        <v>43</v>
+        <v>235</v>
       </c>
       <c r="P62" t="s">
-        <v>43</v>
-      </c>
-      <c r="R62" t="s">
-        <v>44</v>
+        <v>236</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>98</v>
       </c>
       <c r="S62" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
       <c r="T62" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20">
+        <v>237</v>
+      </c>
+      <c r="U62" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63">
         <f t="shared" si="4"/>
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>10</v>
       </c>
       <c r="E63">
         <v>10</v>
       </c>
-      <c r="J63" t="s">
-        <v>33</v>
+      <c r="G63" t="s">
+        <v>238</v>
+      </c>
+      <c r="H63" t="s">
+        <v>238</v>
+      </c>
+      <c r="I63" t="s">
+        <v>35</v>
       </c>
       <c r="K63" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="L63" t="s">
-        <v>33</v>
-      </c>
-      <c r="N63" t="s">
-        <v>43</v>
+        <v>240</v>
+      </c>
+      <c r="M63" t="s">
+        <v>35</v>
       </c>
       <c r="O63" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="P63" t="s">
-        <v>43</v>
-      </c>
-      <c r="R63" t="s">
-        <v>44</v>
+        <v>242</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>98</v>
       </c>
       <c r="S63" t="s">
-        <v>44</v>
+        <v>243</v>
       </c>
       <c r="T63" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20">
+        <v>243</v>
+      </c>
+      <c r="U63" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64">
         <f t="shared" si="4"/>
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>9</v>
       </c>
       <c r="E64">
         <v>9</v>
       </c>
-      <c r="J64" t="s">
-        <v>33</v>
+      <c r="G64" t="s">
+        <v>244</v>
+      </c>
+      <c r="H64" t="s">
+        <v>244</v>
+      </c>
+      <c r="I64" t="s">
+        <v>35</v>
       </c>
       <c r="K64" t="s">
-        <v>33</v>
+        <v>245</v>
       </c>
       <c r="L64" t="s">
-        <v>33</v>
-      </c>
-      <c r="N64" t="s">
-        <v>43</v>
+        <v>246</v>
+      </c>
+      <c r="M64" t="s">
+        <v>35</v>
       </c>
       <c r="O64" t="s">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="P64" t="s">
-        <v>43</v>
-      </c>
-      <c r="R64" t="s">
-        <v>44</v>
+        <v>248</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>98</v>
       </c>
       <c r="S64" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="T64" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
+        <v>249</v>
+      </c>
+      <c r="U64" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65">
         <f t="shared" si="4"/>
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>8</v>
       </c>
       <c r="E65">
         <v>8</v>
       </c>
-      <c r="J65" t="s">
-        <v>33</v>
+      <c r="G65" t="s">
+        <v>250</v>
+      </c>
+      <c r="H65" t="s">
+        <v>250</v>
+      </c>
+      <c r="I65" t="s">
+        <v>35</v>
       </c>
       <c r="K65" t="s">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c r="L65" t="s">
-        <v>33</v>
-      </c>
-      <c r="N65" t="s">
-        <v>43</v>
+        <v>252</v>
+      </c>
+      <c r="M65" t="s">
+        <v>35</v>
       </c>
       <c r="O65" t="s">
-        <v>43</v>
+        <v>253</v>
       </c>
       <c r="P65" t="s">
-        <v>43</v>
-      </c>
-      <c r="R65" t="s">
-        <v>44</v>
+        <v>176</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>98</v>
       </c>
       <c r="S65" t="s">
-        <v>44</v>
+        <v>254</v>
       </c>
       <c r="T65" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+        <v>254</v>
+      </c>
+      <c r="U65" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66">
         <f t="shared" si="4"/>
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>7</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
-      <c r="J66" t="s">
-        <v>33</v>
+      <c r="G66" t="s">
+        <v>255</v>
+      </c>
+      <c r="H66" t="s">
+        <v>255</v>
+      </c>
+      <c r="I66" t="s">
+        <v>35</v>
       </c>
       <c r="K66" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="L66" t="s">
-        <v>33</v>
-      </c>
-      <c r="N66" t="s">
-        <v>43</v>
+        <v>257</v>
+      </c>
+      <c r="M66" t="s">
+        <v>35</v>
       </c>
       <c r="O66" t="s">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="P66" t="s">
-        <v>43</v>
-      </c>
-      <c r="R66" t="s">
-        <v>44</v>
+        <v>259</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>98</v>
       </c>
       <c r="S66" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="T66" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20">
+        <v>260</v>
+      </c>
+      <c r="U66" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67">
         <f t="shared" si="4"/>
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>6</v>
       </c>
       <c r="E67">
         <v>6</v>
       </c>
-      <c r="J67" t="s">
-        <v>33</v>
+      <c r="G67" t="s">
+        <v>261</v>
+      </c>
+      <c r="H67" t="s">
+        <v>261</v>
+      </c>
+      <c r="I67" t="s">
+        <v>35</v>
       </c>
       <c r="K67" t="s">
-        <v>33</v>
+        <v>262</v>
       </c>
       <c r="L67" t="s">
-        <v>33</v>
-      </c>
-      <c r="N67" t="s">
-        <v>43</v>
+        <v>196</v>
+      </c>
+      <c r="M67" t="s">
+        <v>35</v>
       </c>
       <c r="O67" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="P67" t="s">
-        <v>43</v>
-      </c>
-      <c r="R67" t="s">
-        <v>44</v>
+        <v>264</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>98</v>
       </c>
       <c r="S67" t="s">
-        <v>44</v>
+        <v>265</v>
       </c>
       <c r="T67" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
+        <v>265</v>
+      </c>
+      <c r="U67" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68">
         <f t="shared" si="4"/>
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68">
         <v>5</v>
       </c>
-      <c r="J68" t="s">
-        <v>33</v>
+      <c r="G68" t="s">
+        <v>266</v>
+      </c>
+      <c r="H68" t="s">
+        <v>266</v>
+      </c>
+      <c r="I68" t="s">
+        <v>35</v>
       </c>
       <c r="K68" t="s">
-        <v>33</v>
+        <v>267</v>
       </c>
       <c r="L68" t="s">
-        <v>33</v>
-      </c>
-      <c r="N68" t="s">
-        <v>43</v>
+        <v>268</v>
+      </c>
+      <c r="M68" t="s">
+        <v>35</v>
       </c>
       <c r="O68" t="s">
-        <v>43</v>
+        <v>269</v>
       </c>
       <c r="P68" t="s">
-        <v>43</v>
-      </c>
-      <c r="R68" t="s">
-        <v>44</v>
+        <v>193</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>98</v>
       </c>
       <c r="S68" t="s">
-        <v>44</v>
+        <v>270</v>
       </c>
       <c r="T68" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
+        <v>270</v>
+      </c>
+      <c r="U68" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69">
         <f t="shared" si="4"/>
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>4</v>
       </c>
       <c r="E69">
         <v>4</v>
       </c>
-      <c r="J69" t="s">
-        <v>33</v>
+      <c r="G69" t="s">
+        <v>271</v>
+      </c>
+      <c r="H69" t="s">
+        <v>271</v>
+      </c>
+      <c r="I69" t="s">
+        <v>35</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
+        <v>272</v>
       </c>
       <c r="L69" t="s">
-        <v>33</v>
-      </c>
-      <c r="N69" t="s">
-        <v>43</v>
+        <v>273</v>
+      </c>
+      <c r="M69" t="s">
+        <v>35</v>
       </c>
       <c r="O69" t="s">
-        <v>43</v>
+        <v>274</v>
       </c>
       <c r="P69" t="s">
-        <v>43</v>
-      </c>
-      <c r="R69" t="s">
-        <v>44</v>
+        <v>198</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>98</v>
       </c>
       <c r="S69" t="s">
-        <v>44</v>
+        <v>275</v>
       </c>
       <c r="T69" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
+        <v>275</v>
+      </c>
+      <c r="U69" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70">
         <f t="shared" ref="A70:A109" si="8">100000+C70*1000+E70</f>
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>3</v>
       </c>
       <c r="E70">
         <v>3</v>
       </c>
-      <c r="J70" t="s">
-        <v>33</v>
+      <c r="G70" t="s">
+        <v>276</v>
+      </c>
+      <c r="H70" t="s">
+        <v>276</v>
+      </c>
+      <c r="I70" t="s">
+        <v>35</v>
       </c>
       <c r="K70" t="s">
-        <v>33</v>
+        <v>277</v>
       </c>
       <c r="L70" t="s">
-        <v>33</v>
-      </c>
-      <c r="N70" t="s">
-        <v>43</v>
+        <v>278</v>
+      </c>
+      <c r="M70" t="s">
+        <v>35</v>
       </c>
       <c r="O70" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="P70" t="s">
-        <v>43</v>
-      </c>
-      <c r="R70" t="s">
-        <v>44</v>
+        <v>280</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>98</v>
       </c>
       <c r="S70" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="T70" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
+        <v>281</v>
+      </c>
+      <c r="U70" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71">
         <f t="shared" si="8"/>
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>2</v>
       </c>
       <c r="E71">
         <v>2</v>
       </c>
-      <c r="J71" t="s">
-        <v>33</v>
+      <c r="G71" t="s">
+        <v>282</v>
+      </c>
+      <c r="H71" t="s">
+        <v>282</v>
+      </c>
+      <c r="I71" t="s">
+        <v>35</v>
       </c>
       <c r="K71" t="s">
-        <v>33</v>
+        <v>283</v>
       </c>
       <c r="L71" t="s">
-        <v>33</v>
-      </c>
-      <c r="N71" t="s">
-        <v>43</v>
+        <v>284</v>
+      </c>
+      <c r="M71" t="s">
+        <v>35</v>
       </c>
       <c r="O71" t="s">
-        <v>43</v>
+        <v>285</v>
       </c>
       <c r="P71" t="s">
-        <v>43</v>
-      </c>
-      <c r="R71" t="s">
-        <v>44</v>
+        <v>286</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>98</v>
       </c>
       <c r="S71" t="s">
-        <v>44</v>
+        <v>287</v>
       </c>
       <c r="T71" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
+        <v>287</v>
+      </c>
+      <c r="U71" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72">
         <f t="shared" si="8"/>
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E72">
         <v>14</v>
       </c>
-      <c r="J72" t="s">
-        <v>33</v>
+      <c r="G72" t="s">
+        <v>289</v>
+      </c>
+      <c r="H72" t="s">
+        <v>289</v>
+      </c>
+      <c r="I72" t="s">
+        <v>35</v>
       </c>
       <c r="K72" t="s">
-        <v>33</v>
+        <v>290</v>
       </c>
       <c r="L72" t="s">
-        <v>33</v>
-      </c>
-      <c r="N72" t="s">
-        <v>43</v>
+        <v>291</v>
+      </c>
+      <c r="M72" t="s">
+        <v>35</v>
       </c>
       <c r="O72" t="s">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="P72" t="s">
-        <v>43</v>
-      </c>
-      <c r="R72" t="s">
-        <v>44</v>
+        <v>293</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>98</v>
       </c>
       <c r="S72" t="s">
-        <v>44</v>
+        <v>294</v>
       </c>
       <c r="T72" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
+        <v>294</v>
+      </c>
+      <c r="U72" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73">
         <f t="shared" si="8"/>
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
-      <c r="D73" t="s">
-        <v>36</v>
+      <c r="D73" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
-      <c r="J73" t="s">
-        <v>33</v>
+      <c r="G73" t="s">
+        <v>295</v>
+      </c>
+      <c r="H73" t="s">
+        <v>295</v>
+      </c>
+      <c r="I73" t="s">
+        <v>35</v>
       </c>
       <c r="K73" t="s">
-        <v>33</v>
+        <v>296</v>
       </c>
       <c r="L73" t="s">
-        <v>33</v>
-      </c>
-      <c r="N73" t="s">
-        <v>43</v>
+        <v>272</v>
+      </c>
+      <c r="M73" t="s">
+        <v>35</v>
       </c>
       <c r="O73" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="P73" t="s">
-        <v>43</v>
-      </c>
-      <c r="R73" t="s">
-        <v>44</v>
+        <v>263</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>98</v>
       </c>
       <c r="S73" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="T73" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
+        <v>298</v>
+      </c>
+      <c r="U73" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74">
         <f t="shared" si="8"/>
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
-      <c r="D74" t="s">
-        <v>37</v>
+      <c r="D74" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
-      <c r="J74" t="s">
-        <v>33</v>
+      <c r="G74" t="s">
+        <v>299</v>
+      </c>
+      <c r="H74" t="s">
+        <v>299</v>
+      </c>
+      <c r="I74" t="s">
+        <v>35</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>300</v>
       </c>
       <c r="L74" t="s">
-        <v>33</v>
-      </c>
-      <c r="N74" t="s">
-        <v>43</v>
+        <v>301</v>
+      </c>
+      <c r="M74" t="s">
+        <v>35</v>
       </c>
       <c r="O74" t="s">
-        <v>43</v>
+        <v>302</v>
       </c>
       <c r="P74" t="s">
-        <v>43</v>
-      </c>
-      <c r="R74" t="s">
-        <v>44</v>
+        <v>303</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>304</v>
       </c>
       <c r="S74" t="s">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="T74" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20">
+        <v>305</v>
+      </c>
+      <c r="U74" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75">
         <f t="shared" si="8"/>
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D75" t="s">
-        <v>38</v>
+      <c r="D75" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
-      <c r="J75" t="s">
-        <v>48</v>
+      <c r="G75" t="s">
+        <v>306</v>
+      </c>
+      <c r="H75" t="s">
+        <v>306</v>
+      </c>
+      <c r="I75" t="s">
+        <v>35</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>307</v>
       </c>
       <c r="L75" t="s">
-        <v>48</v>
-      </c>
-      <c r="N75" t="s">
-        <v>49</v>
+        <v>308</v>
+      </c>
+      <c r="M75" t="s">
+        <v>35</v>
       </c>
       <c r="O75" t="s">
-        <v>49</v>
+        <v>309</v>
       </c>
       <c r="P75" t="s">
-        <v>49</v>
-      </c>
-      <c r="R75" t="s">
-        <v>50</v>
+        <v>310</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>304</v>
       </c>
       <c r="S75" t="s">
-        <v>50</v>
+        <v>311</v>
       </c>
       <c r="T75" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
+        <v>311</v>
+      </c>
+      <c r="U75" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76">
         <f t="shared" si="8"/>
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76">
         <v>10</v>
       </c>
-      <c r="J76" t="s">
-        <v>48</v>
+      <c r="G76" t="s">
+        <v>312</v>
+      </c>
+      <c r="H76" t="s">
+        <v>312</v>
+      </c>
+      <c r="I76" t="s">
+        <v>35</v>
       </c>
       <c r="K76" t="s">
-        <v>48</v>
+        <v>313</v>
       </c>
       <c r="L76" t="s">
-        <v>48</v>
-      </c>
-      <c r="N76" t="s">
-        <v>49</v>
+        <v>314</v>
+      </c>
+      <c r="M76" t="s">
+        <v>35</v>
       </c>
       <c r="O76" t="s">
-        <v>49</v>
+        <v>315</v>
       </c>
       <c r="P76" t="s">
-        <v>49</v>
-      </c>
-      <c r="R76" t="s">
-        <v>50</v>
+        <v>316</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>304</v>
       </c>
       <c r="S76" t="s">
-        <v>50</v>
+        <v>317</v>
       </c>
       <c r="T76" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
+        <v>317</v>
+      </c>
+      <c r="U76" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77">
         <f t="shared" si="8"/>
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>9</v>
       </c>
       <c r="E77">
         <v>9</v>
       </c>
-      <c r="J77" t="s">
-        <v>48</v>
+      <c r="G77" t="s">
+        <v>318</v>
+      </c>
+      <c r="H77" t="s">
+        <v>318</v>
+      </c>
+      <c r="I77" t="s">
+        <v>35</v>
       </c>
       <c r="K77" t="s">
-        <v>48</v>
+        <v>319</v>
       </c>
       <c r="L77" t="s">
-        <v>48</v>
-      </c>
-      <c r="N77" t="s">
-        <v>49</v>
+        <v>320</v>
+      </c>
+      <c r="M77" t="s">
+        <v>35</v>
       </c>
       <c r="O77" t="s">
-        <v>49</v>
+        <v>321</v>
       </c>
       <c r="P77" t="s">
-        <v>49</v>
-      </c>
-      <c r="R77" t="s">
-        <v>50</v>
+        <v>322</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>304</v>
       </c>
       <c r="S77" t="s">
-        <v>50</v>
+        <v>323</v>
       </c>
       <c r="T77" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
+        <v>323</v>
+      </c>
+      <c r="U77" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78">
         <f t="shared" si="8"/>
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
         <v>8</v>
       </c>
       <c r="E78">
         <v>8</v>
       </c>
-      <c r="J78" t="s">
-        <v>52</v>
+      <c r="G78" t="s">
+        <v>324</v>
+      </c>
+      <c r="H78" t="s">
+        <v>324</v>
+      </c>
+      <c r="I78" t="s">
+        <v>35</v>
       </c>
       <c r="K78" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L78" t="s">
-        <v>52</v>
-      </c>
-      <c r="N78" t="s">
-        <v>49</v>
+        <v>324</v>
+      </c>
+      <c r="M78" t="s">
+        <v>35</v>
       </c>
       <c r="O78" t="s">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="P78" t="s">
-        <v>49</v>
-      </c>
-      <c r="R78" t="s">
-        <v>53</v>
+        <v>324</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>325</v>
       </c>
       <c r="S78" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="T78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U78" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79">
         <f t="shared" si="8"/>
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>7</v>
       </c>
       <c r="E79">
         <v>7</v>
       </c>
-      <c r="J79" t="s">
-        <v>52</v>
+      <c r="G79" t="s">
+        <v>324</v>
+      </c>
+      <c r="H79" t="s">
+        <v>324</v>
+      </c>
+      <c r="I79" t="s">
+        <v>35</v>
       </c>
       <c r="K79" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L79" t="s">
-        <v>52</v>
-      </c>
-      <c r="N79" t="s">
-        <v>49</v>
+        <v>324</v>
+      </c>
+      <c r="M79" t="s">
+        <v>35</v>
       </c>
       <c r="O79" t="s">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="P79" t="s">
-        <v>49</v>
-      </c>
-      <c r="R79" t="s">
-        <v>53</v>
+        <v>324</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>325</v>
       </c>
       <c r="S79" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="T79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U79" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80">
         <f t="shared" si="8"/>
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>6</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
-      <c r="J80" t="s">
-        <v>52</v>
+      <c r="G80" t="s">
+        <v>324</v>
+      </c>
+      <c r="H80" t="s">
+        <v>324</v>
+      </c>
+      <c r="I80" t="s">
+        <v>35</v>
       </c>
       <c r="K80" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L80" t="s">
-        <v>52</v>
-      </c>
-      <c r="N80" t="s">
-        <v>49</v>
+        <v>324</v>
+      </c>
+      <c r="M80" t="s">
+        <v>326</v>
       </c>
       <c r="O80" t="s">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="P80" t="s">
-        <v>49</v>
-      </c>
-      <c r="R80" t="s">
-        <v>53</v>
+        <v>324</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>325</v>
       </c>
       <c r="S80" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="T80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U80" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81">
         <f t="shared" si="8"/>
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
         <v>5</v>
       </c>
       <c r="E81">
         <v>5</v>
       </c>
-      <c r="J81" t="s">
-        <v>52</v>
+      <c r="G81" t="s">
+        <v>324</v>
+      </c>
+      <c r="H81" t="s">
+        <v>324</v>
+      </c>
+      <c r="I81" t="s">
+        <v>35</v>
       </c>
       <c r="K81" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L81" t="s">
-        <v>52</v>
-      </c>
-      <c r="N81" t="s">
-        <v>49</v>
+        <v>324</v>
+      </c>
+      <c r="M81" t="s">
+        <v>326</v>
       </c>
       <c r="O81" t="s">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="P81" t="s">
-        <v>49</v>
-      </c>
-      <c r="R81" t="s">
-        <v>53</v>
+        <v>324</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>325</v>
       </c>
       <c r="S81" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="T81" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U81" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82">
         <f t="shared" si="8"/>
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>4</v>
       </c>
       <c r="E82">
         <v>4</v>
       </c>
-      <c r="J82" t="s">
-        <v>52</v>
+      <c r="G82" t="s">
+        <v>324</v>
+      </c>
+      <c r="H82" t="s">
+        <v>324</v>
+      </c>
+      <c r="I82" t="s">
+        <v>35</v>
       </c>
       <c r="K82" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L82" t="s">
-        <v>52</v>
-      </c>
-      <c r="N82" t="s">
-        <v>49</v>
+        <v>324</v>
+      </c>
+      <c r="M82" t="s">
+        <v>326</v>
       </c>
       <c r="O82" t="s">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="P82" t="s">
-        <v>49</v>
-      </c>
-      <c r="R82" t="s">
-        <v>53</v>
+        <v>324</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>325</v>
       </c>
       <c r="S82" t="s">
-        <v>53</v>
+        <v>324</v>
       </c>
       <c r="T82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U82" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83">
         <f t="shared" si="8"/>
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
         <v>3</v>
       </c>
       <c r="E83">
         <v>3</v>
       </c>
-      <c r="J83" t="s">
-        <v>52</v>
+      <c r="G83" t="s">
+        <v>324</v>
+      </c>
+      <c r="H83" t="s">
+        <v>324</v>
+      </c>
+      <c r="I83" t="s">
+        <v>35</v>
       </c>
       <c r="K83" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L83" t="s">
-        <v>52</v>
-      </c>
-      <c r="N83" t="s">
-        <v>48</v>
+        <v>324</v>
+      </c>
+      <c r="M83" t="s">
+        <v>326</v>
       </c>
       <c r="O83" t="s">
-        <v>48</v>
+        <v>324</v>
       </c>
       <c r="P83" t="s">
-        <v>48</v>
-      </c>
-      <c r="R83" t="s">
-        <v>55</v>
+        <v>324</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>327</v>
       </c>
       <c r="S83" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="T83" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U83" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84">
         <f t="shared" si="8"/>
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
         <v>2</v>
       </c>
       <c r="E84">
         <v>2</v>
       </c>
-      <c r="J84" t="s">
-        <v>52</v>
+      <c r="G84" t="s">
+        <v>324</v>
+      </c>
+      <c r="H84" t="s">
+        <v>324</v>
+      </c>
+      <c r="I84" t="s">
+        <v>326</v>
       </c>
       <c r="K84" t="s">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="L84" t="s">
-        <v>52</v>
-      </c>
-      <c r="N84" t="s">
-        <v>48</v>
+        <v>324</v>
+      </c>
+      <c r="M84" t="s">
+        <v>326</v>
       </c>
       <c r="O84" t="s">
-        <v>48</v>
+        <v>324</v>
       </c>
       <c r="P84" t="s">
-        <v>48</v>
-      </c>
-      <c r="R84" t="s">
-        <v>55</v>
+        <v>324</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>327</v>
       </c>
       <c r="S84" t="s">
-        <v>55</v>
+        <v>324</v>
       </c>
       <c r="T84" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U84" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85">
         <f t="shared" si="8"/>
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E85">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>58</v>
+        <v>324</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
-      </c>
-      <c r="J85" t="s">
-        <v>59</v>
+        <v>324</v>
+      </c>
+      <c r="I85" t="s">
+        <v>326</v>
       </c>
       <c r="K85" t="s">
-        <v>60</v>
+        <v>324</v>
       </c>
       <c r="L85" t="s">
-        <v>56</v>
-      </c>
-      <c r="N85" t="s">
-        <v>59</v>
+        <v>324</v>
+      </c>
+      <c r="M85" t="s">
+        <v>326</v>
       </c>
       <c r="O85" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="P85" t="s">
-        <v>56</v>
-      </c>
-      <c r="R85" t="s">
-        <v>59</v>
+        <v>324</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>327</v>
       </c>
       <c r="S85" t="s">
-        <v>59</v>
+        <v>324</v>
       </c>
       <c r="T85" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U85" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86">
         <f t="shared" si="8"/>
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
-      <c r="D86" t="s">
-        <v>36</v>
+      <c r="D86" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>61</v>
+        <v>324</v>
       </c>
       <c r="H86" t="s">
-        <v>61</v>
-      </c>
-      <c r="J86" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="I86" t="s">
+        <v>326</v>
       </c>
       <c r="K86" t="s">
-        <v>63</v>
+        <v>324</v>
       </c>
       <c r="L86" t="s">
-        <v>56</v>
-      </c>
-      <c r="N86" t="s">
-        <v>64</v>
+        <v>324</v>
+      </c>
+      <c r="M86" t="s">
+        <v>326</v>
       </c>
       <c r="O86" t="s">
-        <v>62</v>
+        <v>324</v>
       </c>
       <c r="P86" t="s">
-        <v>56</v>
-      </c>
-      <c r="R86" t="s">
-        <v>59</v>
+        <v>324</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>327</v>
       </c>
       <c r="S86" t="s">
-        <v>64</v>
+        <v>324</v>
       </c>
       <c r="T86" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U86" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87">
         <f t="shared" si="8"/>
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
-      <c r="D87" t="s">
-        <v>37</v>
+      <c r="D87" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>61</v>
+        <v>324</v>
       </c>
       <c r="H87" t="s">
-        <v>61</v>
-      </c>
-      <c r="J87" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="I87" t="s">
+        <v>326</v>
       </c>
       <c r="K87" t="s">
-        <v>63</v>
+        <v>324</v>
       </c>
       <c r="L87" t="s">
-        <v>65</v>
-      </c>
-      <c r="N87" t="s">
-        <v>64</v>
+        <v>324</v>
+      </c>
+      <c r="M87" t="s">
+        <v>326</v>
       </c>
       <c r="O87" t="s">
-        <v>62</v>
+        <v>324</v>
       </c>
       <c r="P87" t="s">
-        <v>65</v>
-      </c>
-      <c r="R87" t="s">
-        <v>66</v>
+        <v>324</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>329</v>
       </c>
       <c r="S87" t="s">
-        <v>64</v>
+        <v>324</v>
       </c>
       <c r="T87" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U87" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88">
         <f t="shared" si="8"/>
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D88" t="s">
-        <v>38</v>
+      <c r="D88" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>61</v>
+        <v>324</v>
       </c>
       <c r="H88" t="s">
-        <v>61</v>
-      </c>
-      <c r="J88" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="I88" t="s">
+        <v>326</v>
       </c>
       <c r="K88" t="s">
-        <v>63</v>
+        <v>324</v>
       </c>
       <c r="L88" t="s">
-        <v>65</v>
-      </c>
-      <c r="N88" t="s">
-        <v>64</v>
+        <v>324</v>
+      </c>
+      <c r="M88" t="s">
+        <v>326</v>
       </c>
       <c r="O88" t="s">
-        <v>62</v>
+        <v>324</v>
       </c>
       <c r="P88" t="s">
-        <v>65</v>
-      </c>
-      <c r="R88" t="s">
-        <v>66</v>
+        <v>324</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>329</v>
       </c>
       <c r="S88" t="s">
-        <v>64</v>
+        <v>324</v>
       </c>
       <c r="T88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U88" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89">
         <f t="shared" si="8"/>
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
         <v>10</v>
       </c>
       <c r="E89">
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H89" t="s">
-        <v>61</v>
-      </c>
-      <c r="J89" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="I89" t="s">
+        <v>326</v>
       </c>
       <c r="K89" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="L89" t="s">
-        <v>65</v>
-      </c>
-      <c r="N89" t="s">
-        <v>64</v>
+        <v>324</v>
+      </c>
+      <c r="M89" t="s">
+        <v>326</v>
       </c>
       <c r="O89" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="P89" t="s">
-        <v>65</v>
-      </c>
-      <c r="R89" t="s">
-        <v>66</v>
+        <v>324</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>329</v>
       </c>
       <c r="S89" t="s">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="T89" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U89" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90">
         <f t="shared" si="8"/>
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
         <v>9</v>
       </c>
       <c r="E90">
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H90" t="s">
-        <v>61</v>
-      </c>
-      <c r="J90" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="I90" t="s">
+        <v>326</v>
       </c>
       <c r="K90" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="L90" t="s">
-        <v>67</v>
-      </c>
-      <c r="N90" t="s">
-        <v>64</v>
+        <v>324</v>
+      </c>
+      <c r="M90" t="s">
+        <v>326</v>
       </c>
       <c r="O90" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="P90" t="s">
-        <v>67</v>
-      </c>
-      <c r="R90" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>331</v>
       </c>
       <c r="S90" t="s">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="T90" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U90" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91">
         <f t="shared" si="8"/>
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="1">
         <v>8</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H91" t="s">
-        <v>61</v>
-      </c>
-      <c r="J91" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="I91" t="s">
+        <v>326</v>
       </c>
       <c r="K91" t="s">
-        <v>63</v>
+        <v>330</v>
       </c>
       <c r="L91" t="s">
-        <v>67</v>
-      </c>
-      <c r="N91" t="s">
-        <v>64</v>
+        <v>324</v>
+      </c>
+      <c r="M91" t="s">
+        <v>326</v>
       </c>
       <c r="O91" t="s">
-        <v>62</v>
+        <v>330</v>
       </c>
       <c r="P91" t="s">
-        <v>67</v>
-      </c>
-      <c r="R91" t="s">
-        <v>62</v>
+        <v>324</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>331</v>
       </c>
       <c r="S91" t="s">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="T91" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U91" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92">
         <f t="shared" si="8"/>
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="1">
         <v>7</v>
       </c>
       <c r="E92">
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H92" t="s">
-        <v>61</v>
-      </c>
-      <c r="J92" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="I92" t="s">
+        <v>326</v>
       </c>
       <c r="K92" t="s">
-        <v>69</v>
+        <v>330</v>
       </c>
       <c r="L92" t="s">
-        <v>67</v>
-      </c>
-      <c r="N92" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="M92" t="s">
+        <v>326</v>
       </c>
       <c r="O92" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P92" t="s">
-        <v>67</v>
-      </c>
-      <c r="R92" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>331</v>
       </c>
       <c r="S92" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T92" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U92" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93">
         <f t="shared" si="8"/>
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="1">
         <v>6</v>
       </c>
       <c r="E93">
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H93" t="s">
-        <v>61</v>
-      </c>
-      <c r="J93" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="I93" t="s">
+        <v>326</v>
       </c>
       <c r="K93" t="s">
-        <v>69</v>
+        <v>330</v>
       </c>
       <c r="L93" t="s">
-        <v>70</v>
-      </c>
-      <c r="N93" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="M93" t="s">
+        <v>326</v>
       </c>
       <c r="O93" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P93" t="s">
-        <v>70</v>
-      </c>
-      <c r="R93" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>332</v>
       </c>
       <c r="S93" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T93" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U93" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94">
         <f t="shared" si="8"/>
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
         <v>5</v>
       </c>
       <c r="E94">
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H94" t="s">
-        <v>61</v>
-      </c>
-      <c r="J94" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="I94" t="s">
+        <v>326</v>
       </c>
       <c r="K94" t="s">
-        <v>69</v>
+        <v>330</v>
       </c>
       <c r="L94" t="s">
-        <v>70</v>
-      </c>
-      <c r="N94" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="M94" t="s">
+        <v>326</v>
       </c>
       <c r="O94" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P94" t="s">
-        <v>70</v>
-      </c>
-      <c r="R94" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>332</v>
       </c>
       <c r="S94" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T94" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95">
         <f t="shared" si="8"/>
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>4</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H95" t="s">
-        <v>61</v>
-      </c>
-      <c r="J95" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="I95" t="s">
+        <v>326</v>
       </c>
       <c r="K95" t="s">
-        <v>69</v>
+        <v>330</v>
       </c>
       <c r="L95" t="s">
-        <v>70</v>
-      </c>
-      <c r="N95" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="M95" t="s">
+        <v>326</v>
       </c>
       <c r="O95" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P95" t="s">
-        <v>70</v>
-      </c>
-      <c r="R95" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>332</v>
       </c>
       <c r="S95" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T95" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U95" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96">
         <f t="shared" si="8"/>
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H96" t="s">
-        <v>61</v>
-      </c>
-      <c r="J96" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="I96" t="s">
+        <v>326</v>
       </c>
       <c r="K96" t="s">
-        <v>69</v>
+        <v>330</v>
       </c>
       <c r="L96" t="s">
-        <v>71</v>
-      </c>
-      <c r="N96" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="M96" t="s">
+        <v>326</v>
       </c>
       <c r="O96" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P96" t="s">
-        <v>71</v>
-      </c>
-      <c r="R96" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>98</v>
       </c>
       <c r="S96" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T96" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U96" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97">
         <f t="shared" si="8"/>
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="1">
         <v>2</v>
       </c>
       <c r="E97">
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="H97" t="s">
-        <v>61</v>
-      </c>
-      <c r="J97" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="I97" t="s">
+        <v>326</v>
       </c>
       <c r="K97" t="s">
-        <v>69</v>
+        <v>330</v>
       </c>
       <c r="L97" t="s">
-        <v>71</v>
-      </c>
-      <c r="N97" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="M97" t="s">
+        <v>326</v>
       </c>
       <c r="O97" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P97" t="s">
-        <v>71</v>
-      </c>
-      <c r="R97" t="s">
-        <v>68</v>
+        <v>324</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>98</v>
       </c>
       <c r="S97" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T97" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20">
+        <v>324</v>
+      </c>
+      <c r="U97" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98">
         <f t="shared" si="8"/>
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E98">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="H98" t="s">
-        <v>61</v>
-      </c>
-      <c r="J98" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="I98" t="s">
+        <v>326</v>
       </c>
       <c r="K98" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="L98" t="s">
-        <v>71</v>
-      </c>
-      <c r="N98" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="M98" t="s">
+        <v>326</v>
       </c>
       <c r="O98" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P98" t="s">
-        <v>71</v>
-      </c>
-      <c r="R98" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>98</v>
       </c>
       <c r="S98" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T98" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20">
+        <v>330</v>
+      </c>
+      <c r="U98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99">
         <f t="shared" si="8"/>
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
-      <c r="D99" t="s">
-        <v>36</v>
+      <c r="D99" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="H99" t="s">
-        <v>61</v>
-      </c>
-      <c r="J99" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="I99" t="s">
+        <v>326</v>
       </c>
       <c r="K99" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="L99" t="s">
-        <v>73</v>
-      </c>
-      <c r="N99" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="M99" t="s">
+        <v>326</v>
       </c>
       <c r="O99" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P99" t="s">
-        <v>73</v>
-      </c>
-      <c r="R99" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>334</v>
       </c>
       <c r="S99" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T99" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20">
+        <v>330</v>
+      </c>
+      <c r="U99" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100">
         <f t="shared" si="8"/>
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
-      <c r="D100" t="s">
-        <v>37</v>
+      <c r="D100" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="H100" t="s">
-        <v>61</v>
-      </c>
-      <c r="J100" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="I100" t="s">
+        <v>326</v>
       </c>
       <c r="K100" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="L100" t="s">
-        <v>73</v>
-      </c>
-      <c r="N100" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="M100" t="s">
+        <v>326</v>
       </c>
       <c r="O100" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P100" t="s">
-        <v>73</v>
-      </c>
-      <c r="R100" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>334</v>
       </c>
       <c r="S100" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T100" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20">
+        <v>330</v>
+      </c>
+      <c r="U100" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101">
         <f t="shared" si="8"/>
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D101" t="s">
-        <v>38</v>
+      <c r="D101" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>59</v>
+        <v>330</v>
       </c>
       <c r="H101" t="s">
-        <v>74</v>
-      </c>
-      <c r="J101" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="I101" t="s">
+        <v>326</v>
       </c>
       <c r="K101" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="L101" t="s">
-        <v>73</v>
-      </c>
-      <c r="N101" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="M101" t="s">
+        <v>326</v>
       </c>
       <c r="O101" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="P101" t="s">
-        <v>73</v>
-      </c>
-      <c r="R101" t="s">
-        <v>68</v>
+        <v>330</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>334</v>
       </c>
       <c r="S101" t="s">
-        <v>68</v>
+        <v>330</v>
       </c>
       <c r="T101" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20">
+        <v>330</v>
+      </c>
+      <c r="U101" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102">
         <f t="shared" si="8"/>
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>10</v>
       </c>
       <c r="E102">
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="H102" t="s">
-        <v>74</v>
-      </c>
-      <c r="J102" t="s">
-        <v>68</v>
+        <v>325</v>
+      </c>
+      <c r="I102" t="s">
+        <v>326</v>
       </c>
       <c r="K102" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="L102" t="s">
-        <v>73</v>
-      </c>
-      <c r="N102" t="s">
-        <v>68</v>
+        <v>325</v>
+      </c>
+      <c r="M102" t="s">
+        <v>326</v>
       </c>
       <c r="O102" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="P102" t="s">
-        <v>73</v>
-      </c>
-      <c r="R102" t="s">
-        <v>68</v>
+        <v>325</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>334</v>
       </c>
       <c r="S102" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="T102" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20">
+        <v>325</v>
+      </c>
+      <c r="U102" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103">
         <f t="shared" si="8"/>
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="1">
         <v>9</v>
       </c>
       <c r="E103">
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
+        <v>325</v>
       </c>
       <c r="H103" t="s">
-        <v>75</v>
-      </c>
-      <c r="J103" t="s">
-        <v>68</v>
+        <v>325</v>
+      </c>
+      <c r="I103" t="s">
+        <v>326</v>
       </c>
       <c r="K103" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="L103" t="s">
-        <v>76</v>
-      </c>
-      <c r="N103" t="s">
-        <v>68</v>
+        <v>325</v>
+      </c>
+      <c r="M103" t="s">
+        <v>326</v>
       </c>
       <c r="O103" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="P103" t="s">
-        <v>76</v>
-      </c>
-      <c r="R103" t="s">
-        <v>68</v>
+        <v>325</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>326</v>
       </c>
       <c r="S103" t="s">
-        <v>68</v>
+        <v>325</v>
       </c>
       <c r="T103" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20">
+        <v>325</v>
+      </c>
+      <c r="U103" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104">
         <f t="shared" si="8"/>
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="1">
         <v>8</v>
       </c>
       <c r="E104">
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
+        <v>331</v>
       </c>
       <c r="H104" t="s">
-        <v>77</v>
-      </c>
-      <c r="J104" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="I104" t="s">
+        <v>326</v>
       </c>
       <c r="K104" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="L104" t="s">
-        <v>76</v>
-      </c>
-      <c r="N104" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="M104" t="s">
+        <v>326</v>
       </c>
       <c r="O104" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="P104" t="s">
-        <v>76</v>
-      </c>
-      <c r="R104" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>326</v>
       </c>
       <c r="S104" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="T104" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20">
+        <v>331</v>
+      </c>
+      <c r="U104" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105">
         <f t="shared" si="8"/>
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="1">
         <v>7</v>
       </c>
       <c r="E105">
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>331</v>
       </c>
       <c r="H105" t="s">
-        <v>77</v>
-      </c>
-      <c r="J105" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="I105" t="s">
+        <v>326</v>
       </c>
       <c r="K105" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="L105" t="s">
-        <v>76</v>
-      </c>
-      <c r="N105" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="M105" t="s">
+        <v>326</v>
       </c>
       <c r="O105" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="P105" t="s">
-        <v>76</v>
-      </c>
-      <c r="R105" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>326</v>
       </c>
       <c r="S105" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="T105" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20">
+        <v>331</v>
+      </c>
+      <c r="U105" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106">
         <f t="shared" si="8"/>
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>6</v>
       </c>
       <c r="E106">
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="H106" t="s">
-        <v>79</v>
-      </c>
-      <c r="J106" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="I106" t="s">
+        <v>326</v>
       </c>
       <c r="K106" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="L106" t="s">
-        <v>80</v>
-      </c>
-      <c r="N106" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="M106" t="s">
+        <v>326</v>
       </c>
       <c r="O106" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="P106" t="s">
-        <v>80</v>
-      </c>
-      <c r="R106" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>335</v>
       </c>
       <c r="S106" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="T106" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20">
+        <v>331</v>
+      </c>
+      <c r="U106" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107">
         <f t="shared" si="8"/>
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>5</v>
       </c>
       <c r="E107">
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="H107" t="s">
-        <v>79</v>
-      </c>
-      <c r="J107" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="I107" t="s">
+        <v>326</v>
       </c>
       <c r="K107" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="L107" t="s">
-        <v>80</v>
-      </c>
-      <c r="N107" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="M107" t="s">
+        <v>326</v>
       </c>
       <c r="O107" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="P107" t="s">
-        <v>80</v>
-      </c>
-      <c r="R107" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>335</v>
       </c>
       <c r="S107" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="T107" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20">
+        <v>331</v>
+      </c>
+      <c r="U107" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108">
         <f t="shared" si="8"/>
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="1">
         <v>4</v>
       </c>
       <c r="E108">
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="H108" t="s">
-        <v>81</v>
-      </c>
-      <c r="J108" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="I108" t="s">
+        <v>326</v>
       </c>
       <c r="K108" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="L108" t="s">
-        <v>80</v>
-      </c>
-      <c r="N108" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="M108" t="s">
+        <v>326</v>
       </c>
       <c r="O108" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="P108" t="s">
-        <v>80</v>
-      </c>
-      <c r="R108" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>335</v>
       </c>
       <c r="S108" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="T108" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20">
+        <v>331</v>
+      </c>
+      <c r="U108" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109">
         <f t="shared" si="8"/>
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="H109" t="s">
-        <v>81</v>
-      </c>
-      <c r="J109" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="I109" t="s">
+        <v>326</v>
       </c>
       <c r="K109" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="L109" t="s">
-        <v>80</v>
-      </c>
-      <c r="N109" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="M109" t="s">
+        <v>326</v>
       </c>
       <c r="O109" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="P109" t="s">
-        <v>80</v>
-      </c>
-      <c r="R109" t="s">
-        <v>68</v>
+        <v>331</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>335</v>
       </c>
       <c r="S109" t="s">
-        <v>68</v>
+        <v>331</v>
       </c>
       <c r="T109" t="s">
-        <v>80</v>
+        <v>331</v>
+      </c>
+      <c r="U109" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="465">
   <si>
     <t>ID</t>
   </si>
@@ -151,925 +151,1312 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_500|2_3000|3_0|4_2000</t>
+    <t>1_1000|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1500|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_5000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4000|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4400|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5280|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1485|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4356|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5227|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>1_980|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2744|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4704|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4312|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5174|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_970|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1455|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2716|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4656|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4268|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5122|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2688|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3840|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4608|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5069|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_950|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1425|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4180|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5016|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2632|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4512|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4136|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4963|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_930|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1395|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1860|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2604|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4464|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4092|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4910|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2576|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4416|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4048|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4858|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_910|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1365|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2548|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4368|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4004|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4805|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3600|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2464|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3872|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4646|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_870|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1305|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1740|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2436|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3480|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4176|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3828|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4594|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_860|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1290|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1720|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2408|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4128|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3784|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4541|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2352|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4032|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3696|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4435|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_830|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1245|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2324|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3984|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3652|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4382|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2296|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3280|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3936|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3608|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4330|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_800|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2240|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_790|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1185|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1580|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2212|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3792|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3476|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4171|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2184|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3120|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3744|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3432|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4118|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2128|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3040|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3648|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3344|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4013|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_740|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1110|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1480|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2072|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3552|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3256|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3907|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1080|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3456|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3802|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_700|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1050|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1400|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3080|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_680|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1020|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1360|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1904|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3264|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2992|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3590|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2904|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3485|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_945|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1764|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3024|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3326|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_610|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_915|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_4000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1220|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1708|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2928|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2684|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3221|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_590|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_885|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1180|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1652|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2360|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2832|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2596|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3115|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>1_570|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_855|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1140|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1596|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2280|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2736|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2508|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3010|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_560|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1120|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1568|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2240|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2688|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2464|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2957|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_540|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_810|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1080|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1512|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_2100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2160|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2592|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2376|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2851|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_530|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_795|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1060|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1484|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2120|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2544|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2332|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2798|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_510|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_765|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1020|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1428|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2040|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2448|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2244|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2693|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_500|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_750|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1000|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1400|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2000|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2400|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2200|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2640|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1344|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2304|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2534|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_705|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1316|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2256|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2068|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2482|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_675|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_3000</t>
   </si>
   <si>
     <t>1_0|2_2000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_1000|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1400|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1500|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2250|2_3000|3_0|4_4000</t>
+    <t>1_1800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2376|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1232|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1936|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2323|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1176|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2218|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_615|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1148|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1968|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1804|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2165|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_585|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1092|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1872|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1716|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2059|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_570|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1064|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1824|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1672|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2006|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_300|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_1900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1584|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_345|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_460|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_644|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_1800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1104|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1012|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1214|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_160|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_3100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_448|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_1700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_768|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_704|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_845|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_90|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_135|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_2900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_180|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_252|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_1600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_432|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_396|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_475|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_20|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_30|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_40|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_56|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_1500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_80|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_96|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_88|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_106|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>一对</t>
   </si>
   <si>
     <t>1_0|2_1000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_3000|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>1_495|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1386|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1485|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2228|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_2970|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>1_490|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_980|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1372|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1470|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2205|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2940|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_485|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_970|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1358|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1455|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2183|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2910|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_960|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1344|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2160|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2880|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_475|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_950|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1330|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1425|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2138|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2850|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_940|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1316|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2115|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2820|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_465|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_930|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1302|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1395|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2093|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2790|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_460|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_920|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1288|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1380|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2070|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2760|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_455|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_910|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1274|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1365|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2048|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2730|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2025|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2700|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_880|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1232|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2640|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_435|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_870|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1218|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1305|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1958|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2610|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_430|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_860|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1204|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1290|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1935|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2580|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_840|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1176|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1890|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2520|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_415|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_830|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1162|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1245|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1868|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2490|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_820|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1148|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1845|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2460|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_400|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_800|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1120|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1200|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2400|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_395|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_790|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1106|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1185|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1778|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2370|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_780|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1092|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1755|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2340|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_760|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1064|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1710|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2280|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_370|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_740|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1036|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1110|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1665|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2220|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_360|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1008|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1080|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1620|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2160|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_350|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_700|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1050|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1575|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2100|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_340|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_680|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_952|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1020|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1530|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2040|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_330|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_924|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_315|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_882|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_945|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1418|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1890|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_305|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_610|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_854|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_915|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1373|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1830|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_295|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_590|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_826|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_885|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1328|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1770|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>1_285|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_570|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_798|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_855|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1283|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1710|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_280|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_560|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_784|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_840|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1260|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1680|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_270|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_540|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_756|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_810|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1215|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1620|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_265|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_530|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_742|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_795|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1193|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1590|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_255|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_510|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_714|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_765|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1148|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1530|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_250|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_500|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_700|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_750|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1125|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1500|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_240|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_672|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_235|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_658|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_705|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1058|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_225|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_675|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1013|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_220|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_616|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_210|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_588|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_205|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_574|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_615|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_923|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_195|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_546|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_585|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_878|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>1_190|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_532|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_570|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_855|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_150|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_300|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_115|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_230|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_322|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_345|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_518|2_3000|3_0|4_4000</t>
+    <t>1_0|2_900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>高牌</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_2000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_690|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_80|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_160|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_224|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_240|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_360|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_45|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_90|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_126|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_135|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_203|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_270|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_10|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_20|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_28|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_30|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_45|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_60|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>一对</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>高牌</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_11000|4_0</t>
   </si>
 </sst>
 </file>
@@ -2220,37 +2607,37 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="s">
         <v>34</v>
       </c>
-      <c r="Q5" t="s">
-        <v>35</v>
-      </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2259,7 +2646,7 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -2271,40 +2658,40 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -2313,53 +2700,53 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -2368,53 +2755,53 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -2423,53 +2810,53 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -2478,7 +2865,7 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -2491,40 +2878,40 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -2533,7 +2920,7 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -2546,40 +2933,40 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -2588,7 +2975,7 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -2601,40 +2988,40 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -2643,7 +3030,7 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -2656,40 +3043,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O13" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -2698,7 +3085,7 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -2711,40 +3098,40 @@
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -2753,7 +3140,7 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -2765,40 +3152,40 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O15" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -2807,53 +3194,53 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O16" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -2862,53 +3249,53 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L17" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T17" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -2917,53 +3304,53 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O18" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P18" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T18" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -2972,7 +3359,7 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -2985,40 +3372,40 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O19" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T19" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3027,7 +3414,7 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -3040,40 +3427,40 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M20" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O20" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P20" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T20" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3082,7 +3469,7 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -3095,40 +3482,40 @@
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O21" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P21" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T21" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -3137,7 +3524,7 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -3150,40 +3537,40 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L22" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M22" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O22" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P22" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T22" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -3192,7 +3579,7 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -3205,40 +3592,40 @@
         <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M23" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O23" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P23" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T23" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -3247,7 +3634,7 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -3260,40 +3647,40 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M24" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O24" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P24" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T24" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -3302,7 +3689,7 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -3315,40 +3702,40 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M25" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O25" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T25" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -3357,7 +3744,7 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -3370,40 +3757,40 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K26" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M26" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O26" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P26" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T26" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -3412,7 +3799,7 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -3425,40 +3812,40 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K27" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M27" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O27" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P27" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T27" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -3467,7 +3854,7 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3479,40 +3866,40 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K28" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L28" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M28" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O28" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P28" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T28" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -3521,53 +3908,53 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L29" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M29" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O29" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P29" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="Q29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S29" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="T29" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="U29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -3576,53 +3963,53 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K30" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L30" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="M30" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O30" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="P30" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="Q30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S30" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="T30" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="U30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -3631,53 +4018,53 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H31" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K31" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L31" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="M31" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="P31" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="Q31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S31" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="T31" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="U31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -3686,7 +4073,7 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -3699,40 +4086,40 @@
         <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H32" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L32" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="M32" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="P32" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="Q32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S32" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="T32" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="U32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -3741,7 +4128,7 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -3754,40 +4141,40 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="L33" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M33" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O33" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="P33" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="Q33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S33" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="T33" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="U33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -3796,7 +4183,7 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -3809,40 +4196,40 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K34" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L34" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M34" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O34" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="P34" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="Q34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S34" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="T34" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="U34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -3851,7 +4238,7 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -3864,40 +4251,40 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L35" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M35" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O35" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="Q35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S35" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="T35" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="U35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -3906,7 +4293,7 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -3919,40 +4306,40 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H36" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="L36" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="M36" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O36" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P36" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="Q36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S36" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="T36" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="U36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -3961,7 +4348,7 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -3974,40 +4361,40 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K37" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="L37" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="M37" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="O37" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="Q37" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S37" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="T37" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="U37" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -4016,7 +4403,7 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -4029,40 +4416,40 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="H38" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="K38" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="L38" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="M38" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="O38" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="P38" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="Q38" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S38" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="T38" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="U38" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -4071,7 +4458,7 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -4084,40 +4471,40 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="H39" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="K39" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="L39" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="M39" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="O39" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="Q39" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S39" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="T39" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="U39" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -4126,7 +4513,7 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -4139,40 +4526,40 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="H40" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="K40" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="L40" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="M40" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="O40" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="P40" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="Q40" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S40" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="T40" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="U40" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -4181,7 +4568,7 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -4193,40 +4580,40 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="H41" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="K41" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s">
+        <v>134</v>
+      </c>
+      <c r="M41" t="s">
         <v>108</v>
       </c>
-      <c r="M41" t="s">
-        <v>35</v>
-      </c>
       <c r="O41" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="P41" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="Q41" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S41" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="T41" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="U41" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -4235,53 +4622,53 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="K42" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="L42" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="M42" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="O42" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="P42" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="Q42" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S42" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="T42" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="U42" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -4290,53 +4677,53 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="H43" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="K43" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="L43" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="M43" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="O43" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="P43" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="Q43" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="S43" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="T43" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="U43" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -4345,53 +4732,53 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="K44" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="L44" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="M44" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O44" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="P44" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="Q44" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S44" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="T44" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="U44" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -4400,7 +4787,7 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
@@ -4413,40 +4800,40 @@
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="H45" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="K45" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="M45" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O45" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="P45" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="Q45" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S45" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="T45" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="U45" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -4455,7 +4842,7 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
@@ -4468,40 +4855,40 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="K46" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="L46" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="M46" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O46" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="P46" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="Q46" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S46" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="T46" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="U46" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -4510,7 +4897,7 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
@@ -4523,40 +4910,40 @@
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="H47" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="K47" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="M47" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O47" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="P47" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="Q47" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S47" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="T47" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="U47" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4565,7 +4952,7 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
@@ -4578,40 +4965,40 @@
         <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="H48" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="I48" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="K48" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="M48" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O48" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="P48" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="Q48" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S48" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="T48" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="U48" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -4620,7 +5007,7 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
@@ -4633,40 +5020,40 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="H49" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="K49" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="L49" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="M49" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O49" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="P49" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="Q49" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S49" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="T49" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="U49" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -4675,7 +5062,7 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -4687,40 +5074,40 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="H50" t="s">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="I50" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="K50" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="L50" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="M50" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="O50" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="Q50" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="S50" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="T50" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="U50" t="s">
-        <v>98</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -4729,53 +5116,53 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="H51" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>217</v>
       </c>
       <c r="K51" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="L51" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="M51" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="O51" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="Q51" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="S51" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="T51" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="U51" t="s">
-        <v>98</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -4784,53 +5171,53 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>217</v>
       </c>
       <c r="K52" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="L52" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="M52" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="O52" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="Q52" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="S52" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="T52" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="U52" t="s">
-        <v>98</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -4839,53 +5226,53 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="H53" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="K53" t="s">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M53" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="O53" t="s">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="Q53" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="S53" t="s">
-        <v>183</v>
+        <v>238</v>
       </c>
       <c r="T53" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="U53" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -4894,7 +5281,7 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
@@ -4907,40 +5294,40 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="H54" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="K54" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="L54" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="M54" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="O54" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>244</v>
       </c>
       <c r="Q54" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="S54" t="s">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="T54" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="U54" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -4949,7 +5336,7 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
@@ -4962,40 +5349,40 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>247</v>
       </c>
       <c r="H55" t="s">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>248</v>
       </c>
       <c r="K55" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="L55" t="s">
-        <v>192</v>
+        <v>250</v>
       </c>
       <c r="M55" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="O55" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="P55" t="s">
-        <v>41</v>
+        <v>252</v>
       </c>
       <c r="Q55" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="S55" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="T55" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="U55" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -5004,7 +5391,7 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
@@ -5017,40 +5404,40 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="H56" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>248</v>
       </c>
       <c r="K56" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="L56" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="M56" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="O56" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="Q56" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
       <c r="S56" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="T56" t="s">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="U56" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -5059,7 +5446,7 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
@@ -5072,40 +5459,40 @@
         <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="H57" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="K57" t="s">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="L57" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="M57" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="O57" t="s">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="Q57" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="S57" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="T57" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="U57" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -5114,7 +5501,7 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
@@ -5127,40 +5514,40 @@
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="H58" t="s">
-        <v>207</v>
+        <v>274</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="K58" t="s">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="L58" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="M58" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="O58" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="P58" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="Q58" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="S58" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
       <c r="T58" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="U58" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -5169,7 +5556,7 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -5181,40 +5568,40 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="H59" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="I59" t="s">
-        <v>35</v>
+        <v>284</v>
       </c>
       <c r="K59" t="s">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="L59" t="s">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="M59" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="O59" t="s">
-        <v>217</v>
+        <v>287</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="Q59" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="S59" t="s">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="T59" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
       <c r="U59" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -5223,53 +5610,53 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>291</v>
       </c>
       <c r="H60" t="s">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="I60" t="s">
-        <v>35</v>
+        <v>284</v>
       </c>
       <c r="K60" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="L60" t="s">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="M60" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="O60" t="s">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="Q60" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="S60" t="s">
-        <v>225</v>
+        <v>297</v>
       </c>
       <c r="T60" t="s">
-        <v>225</v>
+        <v>298</v>
       </c>
       <c r="U60" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -5278,53 +5665,53 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>226</v>
+        <v>299</v>
       </c>
       <c r="H61" t="s">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="I61" t="s">
-        <v>35</v>
+        <v>284</v>
       </c>
       <c r="K61" t="s">
-        <v>227</v>
+        <v>301</v>
       </c>
       <c r="L61" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="M61" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O61" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="Q61" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="S61" t="s">
-        <v>231</v>
+        <v>306</v>
       </c>
       <c r="T61" t="s">
-        <v>231</v>
+        <v>307</v>
       </c>
       <c r="U61" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -5333,53 +5720,53 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="H62" t="s">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="I62" t="s">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="K62" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="L62" t="s">
-        <v>234</v>
+        <v>312</v>
       </c>
       <c r="M62" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O62" t="s">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="Q62" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="S62" t="s">
-        <v>237</v>
+        <v>315</v>
       </c>
       <c r="T62" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="U62" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -5388,7 +5775,7 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -5401,40 +5788,40 @@
         <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="H63" t="s">
-        <v>238</v>
+        <v>318</v>
       </c>
       <c r="I63" t="s">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>319</v>
       </c>
       <c r="L63" t="s">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="M63" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O63" t="s">
-        <v>241</v>
+        <v>321</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>322</v>
       </c>
       <c r="Q63" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="S63" t="s">
-        <v>243</v>
+        <v>323</v>
       </c>
       <c r="T63" t="s">
-        <v>243</v>
+        <v>324</v>
       </c>
       <c r="U63" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -5443,7 +5830,7 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -5456,40 +5843,40 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>244</v>
+        <v>325</v>
       </c>
       <c r="H64" t="s">
-        <v>244</v>
+        <v>326</v>
       </c>
       <c r="I64" t="s">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="K64" t="s">
-        <v>245</v>
+        <v>327</v>
       </c>
       <c r="L64" t="s">
-        <v>246</v>
+        <v>328</v>
       </c>
       <c r="M64" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O64" t="s">
-        <v>247</v>
+        <v>329</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="Q64" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="S64" t="s">
-        <v>249</v>
+        <v>331</v>
       </c>
       <c r="T64" t="s">
-        <v>249</v>
+        <v>332</v>
       </c>
       <c r="U64" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -5498,7 +5885,7 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -5511,40 +5898,40 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>250</v>
+        <v>333</v>
       </c>
       <c r="H65" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="I65" t="s">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="K65" t="s">
-        <v>251</v>
+        <v>335</v>
       </c>
       <c r="L65" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="M65" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O65" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>338</v>
       </c>
       <c r="Q65" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="S65" t="s">
-        <v>254</v>
+        <v>339</v>
       </c>
       <c r="T65" t="s">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="U65" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -5553,7 +5940,7 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -5566,40 +5953,40 @@
         <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
       <c r="H66" t="s">
-        <v>255</v>
+        <v>342</v>
       </c>
       <c r="I66" t="s">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="K66" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="L66" t="s">
-        <v>257</v>
+        <v>344</v>
       </c>
       <c r="M66" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O66" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>346</v>
       </c>
       <c r="Q66" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="S66" t="s">
-        <v>260</v>
+        <v>347</v>
       </c>
       <c r="T66" t="s">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="U66" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -5608,7 +5995,7 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -5621,40 +6008,40 @@
         <v>6</v>
       </c>
       <c r="G67" t="s">
-        <v>261</v>
+        <v>349</v>
       </c>
       <c r="H67" t="s">
-        <v>261</v>
+        <v>350</v>
       </c>
       <c r="I67" t="s">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="K67" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="L67" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="M67" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="O67" t="s">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>354</v>
       </c>
       <c r="Q67" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="S67" t="s">
-        <v>265</v>
+        <v>355</v>
       </c>
       <c r="T67" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="U67" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -5663,7 +6050,7 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -5676,40 +6063,40 @@
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>266</v>
+        <v>357</v>
       </c>
       <c r="H68" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="I68" t="s">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="K68" t="s">
-        <v>267</v>
+        <v>358</v>
       </c>
       <c r="L68" t="s">
-        <v>268</v>
+        <v>359</v>
       </c>
       <c r="M68" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="O68" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>361</v>
       </c>
       <c r="Q68" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="S68" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="T68" t="s">
-        <v>270</v>
+        <v>363</v>
       </c>
       <c r="U68" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -5718,7 +6105,7 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -5731,40 +6118,40 @@
         <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>271</v>
+        <v>364</v>
       </c>
       <c r="H69" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="I69" t="s">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="K69" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
       <c r="L69" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="M69" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="O69" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
       <c r="Q69" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="S69" t="s">
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="T69" t="s">
-        <v>275</v>
+        <v>371</v>
       </c>
       <c r="U69" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -5773,7 +6160,7 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -5786,40 +6173,40 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>276</v>
+        <v>372</v>
       </c>
       <c r="H70" t="s">
-        <v>276</v>
+        <v>373</v>
       </c>
       <c r="I70" t="s">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="K70" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="L70" t="s">
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="M70" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="O70" t="s">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>377</v>
       </c>
       <c r="Q70" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="S70" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
       <c r="T70" t="s">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="U70" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -5828,7 +6215,7 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -5841,40 +6228,40 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="H71" t="s">
-        <v>282</v>
+        <v>381</v>
       </c>
       <c r="I71" t="s">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="K71" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="L71" t="s">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="M71" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="O71" t="s">
-        <v>285</v>
+        <v>384</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>385</v>
       </c>
       <c r="Q71" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="S71" t="s">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="T71" t="s">
-        <v>287</v>
+        <v>387</v>
       </c>
       <c r="U71" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -5883,7 +6270,7 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -5895,40 +6282,40 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="H72" t="s">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="I72" t="s">
-        <v>35</v>
+        <v>391</v>
       </c>
       <c r="K72" t="s">
-        <v>290</v>
+        <v>392</v>
       </c>
       <c r="L72" t="s">
-        <v>291</v>
+        <v>393</v>
       </c>
       <c r="M72" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="O72" t="s">
-        <v>292</v>
+        <v>394</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>395</v>
       </c>
       <c r="Q72" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
       <c r="S72" t="s">
-        <v>294</v>
+        <v>396</v>
       </c>
       <c r="T72" t="s">
-        <v>294</v>
+        <v>397</v>
       </c>
       <c r="U72" t="s">
-        <v>98</v>
+        <v>352</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -5937,53 +6324,53 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>295</v>
+        <v>398</v>
       </c>
       <c r="H73" t="s">
-        <v>295</v>
+        <v>349</v>
       </c>
       <c r="I73" t="s">
-        <v>35</v>
+        <v>399</v>
       </c>
       <c r="K73" t="s">
-        <v>296</v>
+        <v>400</v>
       </c>
       <c r="L73" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
       <c r="M73" t="s">
-        <v>35</v>
+        <v>401</v>
       </c>
       <c r="O73" t="s">
-        <v>297</v>
+        <v>402</v>
       </c>
       <c r="P73" t="s">
-        <v>263</v>
+        <v>403</v>
       </c>
       <c r="Q73" t="s">
-        <v>98</v>
+        <v>401</v>
       </c>
       <c r="S73" t="s">
-        <v>298</v>
+        <v>404</v>
       </c>
       <c r="T73" t="s">
-        <v>298</v>
+        <v>405</v>
       </c>
       <c r="U73" t="s">
-        <v>98</v>
+        <v>401</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -5992,53 +6379,53 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>299</v>
+        <v>406</v>
       </c>
       <c r="H74" t="s">
-        <v>299</v>
+        <v>407</v>
       </c>
       <c r="I74" t="s">
-        <v>35</v>
+        <v>408</v>
       </c>
       <c r="K74" t="s">
-        <v>300</v>
+        <v>409</v>
       </c>
       <c r="L74" t="s">
-        <v>301</v>
+        <v>410</v>
       </c>
       <c r="M74" t="s">
-        <v>35</v>
+        <v>411</v>
       </c>
       <c r="O74" t="s">
-        <v>302</v>
+        <v>412</v>
       </c>
       <c r="P74" t="s">
-        <v>303</v>
+        <v>413</v>
       </c>
       <c r="Q74" t="s">
-        <v>304</v>
+        <v>411</v>
       </c>
       <c r="S74" t="s">
-        <v>305</v>
+        <v>414</v>
       </c>
       <c r="T74" t="s">
-        <v>305</v>
+        <v>415</v>
       </c>
       <c r="U74" t="s">
-        <v>304</v>
+        <v>411</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -6047,53 +6434,53 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>306</v>
+        <v>416</v>
       </c>
       <c r="H75" t="s">
-        <v>306</v>
+        <v>417</v>
       </c>
       <c r="I75" t="s">
-        <v>35</v>
+        <v>418</v>
       </c>
       <c r="K75" t="s">
-        <v>307</v>
+        <v>419</v>
       </c>
       <c r="L75" t="s">
-        <v>308</v>
+        <v>420</v>
       </c>
       <c r="M75" t="s">
-        <v>35</v>
+        <v>421</v>
       </c>
       <c r="O75" t="s">
-        <v>309</v>
+        <v>422</v>
       </c>
       <c r="P75" t="s">
-        <v>310</v>
+        <v>423</v>
       </c>
       <c r="Q75" t="s">
-        <v>304</v>
+        <v>421</v>
       </c>
       <c r="S75" t="s">
-        <v>311</v>
+        <v>424</v>
       </c>
       <c r="T75" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="U75" t="s">
-        <v>304</v>
+        <v>421</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -6102,7 +6489,7 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -6115,40 +6502,40 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>312</v>
+        <v>426</v>
       </c>
       <c r="H76" t="s">
-        <v>312</v>
+        <v>427</v>
       </c>
       <c r="I76" t="s">
-        <v>35</v>
+        <v>428</v>
       </c>
       <c r="K76" t="s">
-        <v>313</v>
+        <v>429</v>
       </c>
       <c r="L76" t="s">
-        <v>314</v>
+        <v>430</v>
       </c>
       <c r="M76" t="s">
-        <v>35</v>
+        <v>431</v>
       </c>
       <c r="O76" t="s">
-        <v>315</v>
+        <v>432</v>
       </c>
       <c r="P76" t="s">
-        <v>316</v>
+        <v>433</v>
       </c>
       <c r="Q76" t="s">
-        <v>304</v>
+        <v>431</v>
       </c>
       <c r="S76" t="s">
-        <v>317</v>
+        <v>434</v>
       </c>
       <c r="T76" t="s">
-        <v>317</v>
+        <v>435</v>
       </c>
       <c r="U76" t="s">
-        <v>304</v>
+        <v>431</v>
       </c>
     </row>
     <row r="77" spans="1:21">
@@ -6157,7 +6544,7 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -6170,40 +6557,40 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>318</v>
+        <v>436</v>
       </c>
       <c r="H77" t="s">
-        <v>318</v>
+        <v>437</v>
       </c>
       <c r="I77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K77" t="s">
-        <v>319</v>
+        <v>438</v>
       </c>
       <c r="L77" t="s">
-        <v>320</v>
+        <v>439</v>
       </c>
       <c r="M77" t="s">
-        <v>35</v>
+        <v>440</v>
       </c>
       <c r="O77" t="s">
-        <v>321</v>
+        <v>441</v>
       </c>
       <c r="P77" t="s">
-        <v>322</v>
+        <v>442</v>
       </c>
       <c r="Q77" t="s">
-        <v>304</v>
+        <v>440</v>
       </c>
       <c r="S77" t="s">
-        <v>323</v>
+        <v>443</v>
       </c>
       <c r="T77" t="s">
-        <v>323</v>
+        <v>444</v>
       </c>
       <c r="U77" t="s">
-        <v>304</v>
+        <v>440</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -6212,7 +6599,7 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -6225,40 +6612,40 @@
         <v>8</v>
       </c>
       <c r="G78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I78" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M78" t="s">
-        <v>35</v>
+        <v>440</v>
       </c>
       <c r="O78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q78" t="s">
-        <v>325</v>
+        <v>440</v>
       </c>
       <c r="S78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T78" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U78" t="s">
-        <v>325</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:21">
@@ -6267,7 +6654,7 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -6280,40 +6667,40 @@
         <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I79" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="K79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M79" t="s">
-        <v>35</v>
+        <v>446</v>
       </c>
       <c r="O79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q79" t="s">
-        <v>325</v>
+        <v>446</v>
       </c>
       <c r="S79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T79" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U79" t="s">
-        <v>325</v>
+        <v>446</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -6322,7 +6709,7 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -6335,40 +6722,40 @@
         <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I80" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="K80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M80" t="s">
-        <v>326</v>
+        <v>447</v>
       </c>
       <c r="O80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q80" t="s">
-        <v>325</v>
+        <v>447</v>
       </c>
       <c r="S80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T80" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U80" t="s">
-        <v>325</v>
+        <v>447</v>
       </c>
     </row>
     <row r="81" spans="1:21">
@@ -6377,7 +6764,7 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -6390,40 +6777,40 @@
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I81" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
       <c r="K81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M81" t="s">
-        <v>326</v>
+        <v>447</v>
       </c>
       <c r="O81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q81" t="s">
-        <v>325</v>
+        <v>447</v>
       </c>
       <c r="S81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T81" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U81" t="s">
-        <v>325</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" spans="1:21">
@@ -6432,7 +6819,7 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -6445,40 +6832,40 @@
         <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I82" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="K82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M82" t="s">
-        <v>326</v>
+        <v>448</v>
       </c>
       <c r="O82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q82" t="s">
-        <v>325</v>
+        <v>448</v>
       </c>
       <c r="S82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T82" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U82" t="s">
-        <v>325</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:21">
@@ -6487,7 +6874,7 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -6500,40 +6887,40 @@
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I83" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="K83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M83" t="s">
-        <v>326</v>
+        <v>449</v>
       </c>
       <c r="O83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q83" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
       <c r="S83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T83" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U83" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:21">
@@ -6542,7 +6929,7 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -6555,40 +6942,40 @@
         <v>2</v>
       </c>
       <c r="G84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I84" t="s">
-        <v>326</v>
+        <v>401</v>
       </c>
       <c r="K84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M84" t="s">
-        <v>326</v>
+        <v>449</v>
       </c>
       <c r="O84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q84" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
       <c r="S84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T84" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U84" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" spans="1:21">
@@ -6597,7 +6984,7 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6609,40 +6996,40 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I85" t="s">
-        <v>326</v>
+        <v>411</v>
       </c>
       <c r="K85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M85" t="s">
-        <v>326</v>
+        <v>451</v>
       </c>
       <c r="O85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q85" t="s">
-        <v>327</v>
+        <v>451</v>
       </c>
       <c r="S85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T85" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U85" t="s">
-        <v>327</v>
+        <v>451</v>
       </c>
     </row>
     <row r="86" spans="1:21">
@@ -6651,53 +7038,53 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I86" t="s">
-        <v>326</v>
+        <v>431</v>
       </c>
       <c r="K86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M86" t="s">
-        <v>326</v>
+        <v>452</v>
       </c>
       <c r="O86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q86" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
       <c r="S86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T86" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U86" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" spans="1:21">
@@ -6706,53 +7093,53 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I87" t="s">
-        <v>326</v>
+        <v>446</v>
       </c>
       <c r="K87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M87" t="s">
-        <v>326</v>
+        <v>453</v>
       </c>
       <c r="O87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q87" t="s">
-        <v>329</v>
+        <v>453</v>
       </c>
       <c r="S87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T87" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U87" t="s">
-        <v>329</v>
+        <v>453</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -6761,53 +7148,53 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="H88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I88" t="s">
-        <v>326</v>
+        <v>448</v>
       </c>
       <c r="K88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="L88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M88" t="s">
-        <v>326</v>
+        <v>454</v>
       </c>
       <c r="O88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="P88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q88" t="s">
-        <v>329</v>
+        <v>454</v>
       </c>
       <c r="S88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="T88" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U88" t="s">
-        <v>329</v>
+        <v>454</v>
       </c>
     </row>
     <row r="89" spans="1:21">
@@ -6816,7 +7203,7 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -6829,40 +7216,40 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H89" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I89" t="s">
-        <v>326</v>
+        <v>449</v>
       </c>
       <c r="K89" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L89" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M89" t="s">
-        <v>326</v>
+        <v>455</v>
       </c>
       <c r="O89" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P89" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q89" t="s">
-        <v>329</v>
+        <v>455</v>
       </c>
       <c r="S89" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T89" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U89" t="s">
-        <v>329</v>
+        <v>455</v>
       </c>
     </row>
     <row r="90" spans="1:21">
@@ -6871,7 +7258,7 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -6884,40 +7271,40 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H90" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I90" t="s">
-        <v>326</v>
+        <v>452</v>
       </c>
       <c r="K90" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L90" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M90" t="s">
-        <v>326</v>
+        <v>456</v>
       </c>
       <c r="O90" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P90" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q90" t="s">
-        <v>331</v>
+        <v>456</v>
       </c>
       <c r="S90" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T90" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U90" t="s">
-        <v>331</v>
+        <v>456</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -6926,7 +7313,7 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -6939,40 +7326,40 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H91" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I91" t="s">
-        <v>326</v>
+        <v>453</v>
       </c>
       <c r="K91" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L91" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M91" t="s">
-        <v>326</v>
+        <v>457</v>
       </c>
       <c r="O91" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P91" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q91" t="s">
-        <v>331</v>
+        <v>457</v>
       </c>
       <c r="S91" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T91" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U91" t="s">
-        <v>331</v>
+        <v>457</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -6981,7 +7368,7 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -6994,40 +7381,40 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H92" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I92" t="s">
-        <v>326</v>
+        <v>454</v>
       </c>
       <c r="K92" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L92" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M92" t="s">
-        <v>326</v>
+        <v>458</v>
       </c>
       <c r="O92" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P92" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q92" t="s">
-        <v>331</v>
+        <v>458</v>
       </c>
       <c r="S92" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T92" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U92" t="s">
-        <v>331</v>
+        <v>458</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -7036,7 +7423,7 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -7049,40 +7436,40 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H93" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I93" t="s">
-        <v>326</v>
+        <v>456</v>
       </c>
       <c r="K93" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L93" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M93" t="s">
-        <v>326</v>
+        <v>458</v>
       </c>
       <c r="O93" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P93" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q93" t="s">
-        <v>332</v>
+        <v>458</v>
       </c>
       <c r="S93" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T93" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U93" t="s">
-        <v>332</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:21">
@@ -7091,7 +7478,7 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -7104,40 +7491,40 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H94" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I94" t="s">
-        <v>326</v>
+        <v>457</v>
       </c>
       <c r="K94" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L94" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M94" t="s">
-        <v>326</v>
+        <v>459</v>
       </c>
       <c r="O94" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P94" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q94" t="s">
-        <v>332</v>
+        <v>459</v>
       </c>
       <c r="S94" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T94" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U94" t="s">
-        <v>332</v>
+        <v>459</v>
       </c>
     </row>
     <row r="95" spans="1:21">
@@ -7146,7 +7533,7 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -7159,40 +7546,40 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H95" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I95" t="s">
-        <v>326</v>
+        <v>458</v>
       </c>
       <c r="K95" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L95" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M95" t="s">
-        <v>326</v>
+        <v>459</v>
       </c>
       <c r="O95" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P95" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q95" t="s">
-        <v>332</v>
+        <v>459</v>
       </c>
       <c r="S95" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T95" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U95" t="s">
-        <v>332</v>
+        <v>459</v>
       </c>
     </row>
     <row r="96" spans="1:21">
@@ -7201,7 +7588,7 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -7214,40 +7601,40 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H96" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I96" t="s">
-        <v>326</v>
+        <v>459</v>
       </c>
       <c r="K96" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L96" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M96" t="s">
-        <v>326</v>
+        <v>460</v>
       </c>
       <c r="O96" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P96" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q96" t="s">
-        <v>98</v>
+        <v>460</v>
       </c>
       <c r="S96" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T96" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U96" t="s">
-        <v>98</v>
+        <v>460</v>
       </c>
     </row>
     <row r="97" spans="1:21">
@@ -7256,7 +7643,7 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>450</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -7269,40 +7656,40 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="H97" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="I97" t="s">
-        <v>326</v>
+        <v>459</v>
       </c>
       <c r="K97" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="L97" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="M97" t="s">
-        <v>326</v>
+        <v>460</v>
       </c>
       <c r="O97" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="P97" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="Q97" t="s">
-        <v>98</v>
+        <v>460</v>
       </c>
       <c r="S97" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="T97" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="U97" t="s">
-        <v>98</v>
+        <v>460</v>
       </c>
     </row>
     <row r="98" spans="1:21">
@@ -7311,7 +7698,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -7323,40 +7710,40 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="H98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="I98" t="s">
-        <v>326</v>
+        <v>460</v>
       </c>
       <c r="K98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="L98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="M98" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="P98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="Q98" t="s">
-        <v>98</v>
+        <v>463</v>
       </c>
       <c r="S98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="T98" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="U98" t="s">
-        <v>98</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -7365,53 +7752,53 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="H99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="I99" t="s">
-        <v>326</v>
+        <v>460</v>
       </c>
       <c r="K99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="L99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="M99" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="P99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="Q99" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="S99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="T99" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="U99" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -7420,53 +7807,53 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="H100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="I100" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="L100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="M100" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="P100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="Q100" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="S100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="T100" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="U100" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" spans="1:21">
@@ -7475,53 +7862,53 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="H101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="I101" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="L101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="M101" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="P101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="Q101" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="S101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="T101" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="U101" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
     </row>
     <row r="102" spans="1:21">
@@ -7530,7 +7917,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -7543,40 +7930,40 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="H102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="I102" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="L102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="M102" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="P102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="Q102" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="S102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="T102" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="U102" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:21">
@@ -7585,7 +7972,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -7598,40 +7985,40 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="H103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="I103" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="L103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="M103" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="P103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="Q103" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="S103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="T103" t="s">
-        <v>325</v>
+        <v>462</v>
       </c>
       <c r="U103" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -7640,7 +8027,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -7653,40 +8040,40 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="H104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="I104" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="L104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="M104" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="Q104" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="S104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="T104" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="U104" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
     </row>
     <row r="105" spans="1:21">
@@ -7695,7 +8082,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -7708,40 +8095,40 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="H105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="I105" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="L105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="M105" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="P105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="Q105" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="S105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="T105" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="U105" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -7750,7 +8137,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -7763,40 +8150,40 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="H106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="I106" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="L106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="M106" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="P106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="Q106" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="S106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="T106" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="U106" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
     </row>
     <row r="107" spans="1:21">
@@ -7805,7 +8192,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -7818,40 +8205,40 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="H107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="I107" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="L107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="M107" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="P107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="Q107" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="S107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="T107" t="s">
-        <v>331</v>
+        <v>462</v>
       </c>
       <c r="U107" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
     </row>
     <row r="108" spans="1:21">
@@ -7860,7 +8247,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -7873,40 +8260,40 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="H108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="I108" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="L108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="M108" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="P108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="Q108" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="S108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="T108" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="U108" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
     </row>
     <row r="109" spans="1:21">
@@ -7915,7 +8302,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>461</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -7928,40 +8315,40 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="H109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="I109" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="K109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="L109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="M109" t="s">
-        <v>326</v>
+        <v>463</v>
       </c>
       <c r="O109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="P109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="Q109" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="S109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="T109" t="s">
-        <v>331</v>
+        <v>464</v>
       </c>
       <c r="U109" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="581">
   <si>
     <t>ID</t>
   </si>
@@ -157,1281 +157,1629 @@
     <t>1_1500|2_3000|3_0|4_2000</t>
   </si>
   <si>
+    <t>1_0|2_20000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_15000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4000|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_10000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4400|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5280|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_8000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1485|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4356|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5227|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>1_980|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2744|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4704|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4312|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5174|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_970|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1455|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2716|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4656|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4268|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5122|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2688|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3840|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4608|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5069|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_950|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1425|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4180|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5016|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2632|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4512|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4136|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4963|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_14500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_930|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1395|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1860|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2604|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4464|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4092|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4910|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2576|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4416|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4048|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4858|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_910|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1365|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2548|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4368|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4004|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4805|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3600|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2464|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3872|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4646|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_870|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1305|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1740|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2436|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3480|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4176|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3828|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4594|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_860|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1290|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1720|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2408|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4128|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3784|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4541|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2352|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4032|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3696|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4435|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_830|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1245|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2324|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3984|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3652|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4382|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2296|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3280|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3936|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3608|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4330|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_800|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2240|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_790|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1185|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1580|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2212|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3792|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3476|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4171|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2184|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3120|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3744|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3432|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4118|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2128|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3040|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3648|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3344|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4013|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_740|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1110|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1480|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2072|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3552|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3256|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3907|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1080|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3456|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3802|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_700|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1050|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1400|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3080|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_680|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1020|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1360|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1904|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3264|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2992|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3590|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2904|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3485|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_945|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1764|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3024|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3326|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_610|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_915|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1220|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1708|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2928|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2684|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3221|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_590|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_885|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1180|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1652|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2360|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2832|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2596|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3115|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>1_570|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_855|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1140|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1596|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2280|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2736|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2508|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3010|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_560|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1120|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1568|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2240|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2688|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2464|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2957|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_540|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_810|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1080|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1512|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2160|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2592|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2376|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2851|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_530|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_795|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1060|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1484|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2120|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2544|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2332|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2798|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_510|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_765|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1020|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1428|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2040|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2448|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2244|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2693|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_500|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_750|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1000|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1400|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2400|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2200|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2640|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1344|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2304|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2534|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_705|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1316|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2256|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2068|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2482|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_675|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2376|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1232|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1936|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2323|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1176|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2218|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_615|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1148|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1968|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1804|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2165|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_585|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1092|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1872|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1716|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2059|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_570|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1064|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1824|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1672|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2006|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_300|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1584|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_345|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_460|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_644|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1104|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1012|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1214|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_160|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_448|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_768|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_704|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_845|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
     <t>1_0|2_5000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_2000|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2800|2_3000|3_0|4_3000</t>
+    <t>1_90|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_135|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_180|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_252|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_432|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_396|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_475|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_4700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_20|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_30|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_40|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_56|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_80|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_96|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_88|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_106|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_4500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_10300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_5100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>一对</t>
+  </si>
+  <si>
+    <t>1_0|2_5500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1300|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_2800|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_4000|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4400|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_5280|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1485|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4900|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2772|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2700|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3960|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4752|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4356|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_5227|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>1_980|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1470|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1960|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2744|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3920|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4704|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4312|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_5174|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_970|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1455|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1940|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2716|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3880|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4656|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4268|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_5122|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_960|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1920|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2688|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3840|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4608|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4224|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_5069|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_950|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1425|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4800|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1900|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2660|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4560|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4180|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_5016|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_940|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1880|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2632|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3760|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4512|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4136|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4963|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_930|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1395|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1860|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2604|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3720|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4464|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4092|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4910|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_920|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1380|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1840|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2576|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2600|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3680|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4416|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4048|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4858|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_910|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1365|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4700|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1820|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2548|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3640|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4368|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4004|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4805|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1800|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2520|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3600|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4320|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3960|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4752|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>1_880|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1760|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2464|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3520|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4224|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3872|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4646|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_870|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1305|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4600|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1740|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2436|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3480|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4176|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3828|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4594|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_860|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1290|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1720|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2408|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3440|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4128|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3784|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4541|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_840|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1680|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2352|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2500|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3360|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_4032|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3696|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4435|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_830|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1245|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4500|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1660|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2324|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3320|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3984|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3652|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4382|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_820|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1640|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2296|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3280|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3936|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3608|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4330|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_800|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1200|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1600|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2240|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3200|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3520|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_790|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1185|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4400|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1580|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2212|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3160|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3792|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3476|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4171|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_780|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1560|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2184|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_3120|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3744|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3432|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4118|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>1_760|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1520|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2128|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2400|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3040|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3648|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3344|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_4013|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_740|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1110|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4300|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1480|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2072|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2960|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3552|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3256|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3907|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1080|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2016|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2880|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3456|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3168|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3802|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_700|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1050|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4200|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1400|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2300|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_2800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3080|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_680|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1020|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1360|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1904|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2720|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3264|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2992|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3590|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4100|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1848|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2640|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3168|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2904|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3485|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_945|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1764|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2520|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_3024|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2772|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3326|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_610|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_915|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_4000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1220|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1708|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2200|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_2440|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2928|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2684|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3221|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_590|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_885|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1180|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1652|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2360|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2832|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2596|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3115|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>1_570|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_855|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3900|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1140|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1596|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2280|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2736|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2508|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_3010|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_560|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_840|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1120|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1568|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2240|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2688|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2464|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2957|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_540|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_810|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1080|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1512|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
     <t>1_0|2_2100|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_2160|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2592|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2376|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2851|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_530|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_795|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3800|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1060|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1484|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2120|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2544|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2332|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2798|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_510|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_765|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1020|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1428|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2040|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2448|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2244|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2693|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_500|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_750|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_1000|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1400|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_2000|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2400|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2200|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2640|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3700|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_960|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1344|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1920|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2304|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2112|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2534|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_705|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_940|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1316|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1880|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2256|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2068|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2482|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_675|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_2000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2160|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2376|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_880|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1232|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1760|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2112|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1936|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2323|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3600|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_840|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1176|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1680|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2016|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1848|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2218|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_615|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_820|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1148|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1640|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1968|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1804|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2165|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_585|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_780|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1092|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1560|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1872|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1716|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2059|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_570|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3500|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_760|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1064|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1520|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1824|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1672|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_2006|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_300|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3400|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_600|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_1900|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_1200|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_1584|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_230|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_345|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3200|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_460|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_644|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_1800|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_920|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1104|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1012|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_1214|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_160|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_240|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_3100|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_320|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_448|2_3000|3_0|4_3000</t>
+    <t>1_0|2_1400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1100|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_1700|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_640|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_768|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_704|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_845|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_90|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_135|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_0|2_2900|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_180|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_252|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_1600|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_360|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_432|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_396|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_475|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_20|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_30|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_40|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_56|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_0|2_1500|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_80|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_96|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_88|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_106|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_1400|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_1300|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_1200|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_1100|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>一对</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_10000|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_900|3_10000|4_0</t>
   </si>
   <si>
+    <t>1_0|2_700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_600|3_10000|4_0</t>
+  </si>
+  <si>
     <t>1_0|2_800|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_0|2_700|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_600|3_10000|4_0</t>
-  </si>
-  <si>
     <t>1_0|2_500|3_10000|4_0</t>
   </si>
   <si>
@@ -1441,19 +1789,19 @@
     <t>1_0|2_300|3_10000|4_0</t>
   </si>
   <si>
+    <t>高牌</t>
+  </si>
+  <si>
     <t>1_0|2_200|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_100|3_10000|4_0</t>
   </si>
   <si>
-    <t>高牌</t>
+    <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_3000|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_2000|4_0</t>
@@ -2628,16 +2976,16 @@
         <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2646,7 +2994,7 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -2658,40 +3006,40 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -2700,53 +3048,53 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -2755,53 +3103,53 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -2810,53 +3158,53 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U9" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -2865,7 +3213,7 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -2878,40 +3226,40 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -2920,7 +3268,7 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -2933,40 +3281,40 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -2975,7 +3323,7 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -2988,40 +3336,40 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -3030,7 +3378,7 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -3043,40 +3391,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -3085,7 +3433,7 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -3098,40 +3446,40 @@
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U14" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -3140,7 +3488,7 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -3152,40 +3500,40 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -3194,53 +3542,53 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U16" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -3249,53 +3597,53 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q17" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S17" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U17" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -3304,53 +3652,53 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U18" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -3359,7 +3707,7 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -3372,40 +3720,40 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q19" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U19" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3414,7 +3762,7 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -3427,40 +3775,40 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q20" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U20" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3469,7 +3817,7 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -3482,40 +3830,40 @@
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q21" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U21" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -3524,7 +3872,7 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -3537,40 +3885,40 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q22" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T22" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U22" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -3579,7 +3927,7 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -3592,40 +3940,40 @@
         <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O23" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q23" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U23" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -3634,7 +3982,7 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -3647,40 +3995,40 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q24" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T24" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U24" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -3689,7 +4037,7 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -3702,40 +4050,40 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q25" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T25" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U25" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -3744,7 +4092,7 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -3757,40 +4105,40 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q26" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T26" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U26" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -3799,7 +4147,7 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -3812,40 +4160,40 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q27" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U27" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -3854,7 +4202,7 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3866,40 +4214,40 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L28" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q28" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T28" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U28" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -3908,53 +4256,53 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I29" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="K29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M29" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="O29" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P29" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S29" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="T29" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U29" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -3963,53 +4311,53 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K30" t="s">
+        <v>72</v>
+      </c>
+      <c r="L30" t="s">
+        <v>73</v>
+      </c>
+      <c r="M30" t="s">
         <v>64</v>
       </c>
-      <c r="I30" t="s">
-        <v>42</v>
-      </c>
-      <c r="K30" t="s">
-        <v>65</v>
-      </c>
-      <c r="L30" t="s">
-        <v>66</v>
-      </c>
-      <c r="M30" t="s">
-        <v>45</v>
-      </c>
       <c r="O30" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="P30" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="Q30" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="S30" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="T30" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="U30" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -4018,53 +4366,53 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L31" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M31" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="O31" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="P31" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q31" t="s">
         <v>76</v>
       </c>
-      <c r="Q31" t="s">
-        <v>45</v>
-      </c>
       <c r="S31" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="T31" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="U31" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -4073,7 +4421,7 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -4086,40 +4434,40 @@
         <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L32" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M32" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="O32" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="P32" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q32" t="s">
         <v>76</v>
       </c>
-      <c r="Q32" t="s">
-        <v>45</v>
-      </c>
       <c r="S32" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="T32" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="U32" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -4128,7 +4476,7 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -4141,40 +4489,40 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="L33" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="M33" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="O33" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="P33" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="Q33" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="S33" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="T33" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="U33" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -4183,7 +4531,7 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -4196,40 +4544,40 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H34" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="I34" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="K34" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="M34" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="O34" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="Q34" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="S34" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="T34" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="U34" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -4238,7 +4586,7 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -4251,40 +4599,40 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H35" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="I35" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="M35" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="O35" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="Q35" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="S35" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="T35" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="U35" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -4293,7 +4641,7 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -4306,40 +4654,40 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="H36" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="I36" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="K36" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="L36" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="M36" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="O36" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="P36" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="Q36" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="S36" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="T36" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="U36" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -4348,7 +4696,7 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -4361,40 +4709,40 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H37" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="I37" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="K37" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="L37" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="M37" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O37" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="P37" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>120</v>
+      </c>
+      <c r="S37" t="s">
+        <v>130</v>
+      </c>
+      <c r="T37" t="s">
+        <v>131</v>
+      </c>
+      <c r="U37" t="s">
         <v>110</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>108</v>
-      </c>
-      <c r="S37" t="s">
-        <v>111</v>
-      </c>
-      <c r="T37" t="s">
-        <v>112</v>
-      </c>
-      <c r="U37" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -4403,7 +4751,7 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -4416,40 +4764,40 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H38" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="K38" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="O38" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="P38" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="Q38" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="S38" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="T38" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="U38" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -4458,7 +4806,7 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -4471,40 +4819,40 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="K39" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="O39" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="P39" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="Q39" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="S39" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="T39" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="U39" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -4513,7 +4861,7 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -4526,40 +4874,40 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="I40" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="K40" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="L40" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="M40" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="O40" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="P40" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="Q40" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="S40" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="T40" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="U40" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -4568,7 +4916,7 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -4580,40 +4928,40 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="H41" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="I41" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="K41" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="L41" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="M41" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="O41" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="P41" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="Q41" t="s">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="S41" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="T41" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="U41" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -4622,53 +4970,53 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="I42" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="K42" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="O42" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="P42" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="Q42" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="S42" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="T42" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="U42" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -4677,53 +5025,53 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="H43" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="I43" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="K43" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L43" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="M43" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="O43" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="P43" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="Q43" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="S43" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="T43" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="U43" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -4732,53 +5080,53 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="H44" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="I44" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="K44" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="O44" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="P44" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="Q44" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="S44" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="T44" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="U44" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -4787,7 +5135,7 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
@@ -4800,40 +5148,40 @@
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="H45" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="I45" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="K45" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="L45" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="M45" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="O45" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="P45" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="Q45" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="S45" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="T45" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="U45" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -4842,7 +5190,7 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
@@ -4855,40 +5203,40 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="H46" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="I46" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="K46" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="M46" t="s">
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="O46" t="s">
-        <v>178</v>
+        <v>218</v>
       </c>
       <c r="P46" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="Q46" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="S46" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="T46" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="U46" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -4897,7 +5245,7 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
@@ -4910,40 +5258,40 @@
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="H47" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="I47" t="s">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="K47" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="L47" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="M47" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="O47" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="P47" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q47" t="s">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="S47" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="T47" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="U47" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4952,7 +5300,7 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
@@ -4965,40 +5313,40 @@
         <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="I48" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="K48" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="M48" t="s">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="O48" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="Q48" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="S48" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="T48" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="U48" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -5007,7 +5355,7 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
@@ -5020,40 +5368,40 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="H49" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="I49" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="K49" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="L49" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="M49" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="O49" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="P49" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="Q49" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="S49" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="T49" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="U49" t="s">
-        <v>160</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -5062,7 +5410,7 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -5074,40 +5422,40 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="H50" t="s">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="I50" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
       <c r="K50" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="L50" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="M50" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="O50" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="P50" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="Q50" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="S50" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="T50" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="U50" t="s">
-        <v>210</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -5116,53 +5464,53 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="H51" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="I51" t="s">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="K51" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="L51" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="M51" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="O51" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="Q51" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="S51" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="T51" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="U51" t="s">
-        <v>210</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -5171,53 +5519,53 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="H52" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="I52" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="K52" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="L52" t="s">
-        <v>227</v>
+        <v>281</v>
       </c>
       <c r="M52" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="O52" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="Q52" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="S52" t="s">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="T52" t="s">
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="U52" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -5226,53 +5574,53 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="H53" t="s">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="I53" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="K53" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="L53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M53" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="O53" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="P53" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="Q53" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="S53" t="s">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="T53" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="U53" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -5281,7 +5629,7 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
@@ -5294,40 +5642,40 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="H54" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="I54" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="K54" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="L54" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="M54" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="O54" t="s">
-        <v>243</v>
+        <v>304</v>
       </c>
       <c r="P54" t="s">
-        <v>244</v>
+        <v>305</v>
       </c>
       <c r="Q54" t="s">
-        <v>236</v>
+        <v>306</v>
       </c>
       <c r="S54" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="T54" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="U54" t="s">
-        <v>236</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -5336,7 +5684,7 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
@@ -5349,40 +5697,40 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="K55" t="s">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="L55" t="s">
-        <v>250</v>
+        <v>313</v>
       </c>
       <c r="M55" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="O55" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="P55" t="s">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="Q55" t="s">
-        <v>236</v>
+        <v>317</v>
       </c>
       <c r="S55" t="s">
-        <v>253</v>
+        <v>318</v>
       </c>
       <c r="T55" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="U55" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -5391,7 +5739,7 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
@@ -5404,40 +5752,40 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="H56" t="s">
-        <v>256</v>
+        <v>322</v>
       </c>
       <c r="I56" t="s">
-        <v>248</v>
+        <v>323</v>
       </c>
       <c r="K56" t="s">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="L56" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="M56" t="s">
-        <v>236</v>
+        <v>326</v>
       </c>
       <c r="O56" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="Q56" t="s">
-        <v>236</v>
+        <v>329</v>
       </c>
       <c r="S56" t="s">
-        <v>261</v>
+        <v>330</v>
       </c>
       <c r="T56" t="s">
-        <v>262</v>
+        <v>331</v>
       </c>
       <c r="U56" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -5446,7 +5794,7 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
@@ -5459,40 +5807,40 @@
         <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>263</v>
+        <v>332</v>
       </c>
       <c r="H57" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="I57" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
       <c r="K57" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="L57" t="s">
-        <v>267</v>
+        <v>336</v>
       </c>
       <c r="M57" t="s">
-        <v>268</v>
+        <v>337</v>
       </c>
       <c r="O57" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
       <c r="P57" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
       <c r="Q57" t="s">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="S57" t="s">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="T57" t="s">
-        <v>272</v>
+        <v>342</v>
       </c>
       <c r="U57" t="s">
-        <v>268</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -5501,7 +5849,7 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
@@ -5514,40 +5862,40 @@
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="H58" t="s">
-        <v>274</v>
+        <v>345</v>
       </c>
       <c r="I58" t="s">
-        <v>265</v>
+        <v>346</v>
       </c>
       <c r="K58" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="L58" t="s">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="M58" t="s">
-        <v>268</v>
+        <v>349</v>
       </c>
       <c r="O58" t="s">
-        <v>277</v>
+        <v>350</v>
       </c>
       <c r="P58" t="s">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="Q58" t="s">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="S58" t="s">
-        <v>279</v>
+        <v>352</v>
       </c>
       <c r="T58" t="s">
-        <v>280</v>
+        <v>353</v>
       </c>
       <c r="U58" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -5556,7 +5904,7 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -5568,40 +5916,40 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>282</v>
+        <v>356</v>
       </c>
       <c r="H59" t="s">
-        <v>283</v>
+        <v>357</v>
       </c>
       <c r="I59" t="s">
-        <v>284</v>
+        <v>358</v>
       </c>
       <c r="K59" t="s">
-        <v>285</v>
+        <v>359</v>
       </c>
       <c r="L59" t="s">
-        <v>286</v>
+        <v>360</v>
       </c>
       <c r="M59" t="s">
-        <v>268</v>
+        <v>361</v>
       </c>
       <c r="O59" t="s">
-        <v>287</v>
+        <v>362</v>
       </c>
       <c r="P59" t="s">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="Q59" t="s">
-        <v>268</v>
+        <v>53</v>
       </c>
       <c r="S59" t="s">
-        <v>289</v>
+        <v>364</v>
       </c>
       <c r="T59" t="s">
-        <v>290</v>
+        <v>365</v>
       </c>
       <c r="U59" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -5610,53 +5958,53 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>291</v>
+        <v>367</v>
       </c>
       <c r="H60" t="s">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="I60" t="s">
-        <v>284</v>
+        <v>369</v>
       </c>
       <c r="K60" t="s">
-        <v>293</v>
+        <v>370</v>
       </c>
       <c r="L60" t="s">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="M60" t="s">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="O60" t="s">
-        <v>295</v>
+        <v>373</v>
       </c>
       <c r="P60" t="s">
-        <v>296</v>
+        <v>374</v>
       </c>
       <c r="Q60" t="s">
-        <v>268</v>
+        <v>53</v>
       </c>
       <c r="S60" t="s">
-        <v>297</v>
+        <v>375</v>
       </c>
       <c r="T60" t="s">
-        <v>298</v>
+        <v>376</v>
       </c>
       <c r="U60" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -5665,53 +6013,53 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="H61" t="s">
-        <v>300</v>
+        <v>378</v>
       </c>
       <c r="I61" t="s">
-        <v>284</v>
+        <v>379</v>
       </c>
       <c r="K61" t="s">
-        <v>301</v>
+        <v>380</v>
       </c>
       <c r="L61" t="s">
-        <v>302</v>
+        <v>381</v>
       </c>
       <c r="M61" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="O61" t="s">
-        <v>304</v>
+        <v>383</v>
       </c>
       <c r="P61" t="s">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="Q61" t="s">
-        <v>303</v>
+        <v>89</v>
       </c>
       <c r="S61" t="s">
-        <v>306</v>
+        <v>385</v>
       </c>
       <c r="T61" t="s">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="U61" t="s">
-        <v>303</v>
+        <v>387</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -5720,53 +6068,53 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>308</v>
+        <v>388</v>
       </c>
       <c r="H62" t="s">
-        <v>309</v>
+        <v>389</v>
       </c>
       <c r="I62" t="s">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="K62" t="s">
-        <v>311</v>
+        <v>391</v>
       </c>
       <c r="L62" t="s">
-        <v>312</v>
+        <v>392</v>
       </c>
       <c r="M62" t="s">
-        <v>303</v>
+        <v>393</v>
       </c>
       <c r="O62" t="s">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="P62" t="s">
-        <v>314</v>
+        <v>395</v>
       </c>
       <c r="Q62" t="s">
-        <v>303</v>
+        <v>110</v>
       </c>
       <c r="S62" t="s">
-        <v>315</v>
+        <v>396</v>
       </c>
       <c r="T62" t="s">
-        <v>316</v>
+        <v>397</v>
       </c>
       <c r="U62" t="s">
-        <v>303</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -5775,7 +6123,7 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -5788,40 +6136,40 @@
         <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>317</v>
+        <v>398</v>
       </c>
       <c r="H63" t="s">
-        <v>318</v>
+        <v>399</v>
       </c>
       <c r="I63" t="s">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="K63" t="s">
-        <v>319</v>
+        <v>401</v>
       </c>
       <c r="L63" t="s">
-        <v>320</v>
+        <v>402</v>
       </c>
       <c r="M63" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
       <c r="O63" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
       <c r="P63" t="s">
-        <v>322</v>
+        <v>405</v>
       </c>
       <c r="Q63" t="s">
-        <v>303</v>
+        <v>110</v>
       </c>
       <c r="S63" t="s">
-        <v>323</v>
+        <v>406</v>
       </c>
       <c r="T63" t="s">
-        <v>324</v>
+        <v>407</v>
       </c>
       <c r="U63" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -5830,7 +6178,7 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -5843,40 +6191,40 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>325</v>
+        <v>409</v>
       </c>
       <c r="H64" t="s">
-        <v>326</v>
+        <v>410</v>
       </c>
       <c r="I64" t="s">
-        <v>310</v>
+        <v>411</v>
       </c>
       <c r="K64" t="s">
-        <v>327</v>
+        <v>412</v>
       </c>
       <c r="L64" t="s">
-        <v>328</v>
+        <v>413</v>
       </c>
       <c r="M64" t="s">
-        <v>303</v>
+        <v>414</v>
       </c>
       <c r="O64" t="s">
-        <v>329</v>
+        <v>415</v>
       </c>
       <c r="P64" t="s">
-        <v>330</v>
+        <v>416</v>
       </c>
       <c r="Q64" t="s">
-        <v>303</v>
+        <v>143</v>
       </c>
       <c r="S64" t="s">
-        <v>331</v>
+        <v>417</v>
       </c>
       <c r="T64" t="s">
-        <v>332</v>
+        <v>418</v>
       </c>
       <c r="U64" t="s">
-        <v>303</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -5885,7 +6233,7 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -5898,40 +6246,40 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>333</v>
+        <v>419</v>
       </c>
       <c r="H65" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="I65" t="s">
-        <v>334</v>
+        <v>420</v>
       </c>
       <c r="K65" t="s">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="L65" t="s">
-        <v>336</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s">
-        <v>303</v>
+        <v>423</v>
       </c>
       <c r="O65" t="s">
-        <v>337</v>
+        <v>424</v>
       </c>
       <c r="P65" t="s">
-        <v>338</v>
+        <v>425</v>
       </c>
       <c r="Q65" t="s">
-        <v>303</v>
+        <v>166</v>
       </c>
       <c r="S65" t="s">
-        <v>339</v>
+        <v>426</v>
       </c>
       <c r="T65" t="s">
-        <v>340</v>
+        <v>427</v>
       </c>
       <c r="U65" t="s">
-        <v>303</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -5940,7 +6288,7 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -5953,40 +6301,40 @@
         <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>341</v>
+        <v>429</v>
       </c>
       <c r="H66" t="s">
-        <v>342</v>
+        <v>430</v>
       </c>
       <c r="I66" t="s">
-        <v>334</v>
+        <v>34</v>
       </c>
       <c r="K66" t="s">
-        <v>343</v>
+        <v>431</v>
       </c>
       <c r="L66" t="s">
-        <v>344</v>
+        <v>432</v>
       </c>
       <c r="M66" t="s">
-        <v>303</v>
+        <v>433</v>
       </c>
       <c r="O66" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="P66" t="s">
-        <v>346</v>
+        <v>435</v>
       </c>
       <c r="Q66" t="s">
-        <v>303</v>
+        <v>166</v>
       </c>
       <c r="S66" t="s">
-        <v>347</v>
+        <v>436</v>
       </c>
       <c r="T66" t="s">
-        <v>348</v>
+        <v>437</v>
       </c>
       <c r="U66" t="s">
-        <v>303</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -5995,7 +6343,7 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -6008,40 +6356,40 @@
         <v>6</v>
       </c>
       <c r="G67" t="s">
-        <v>349</v>
+        <v>438</v>
       </c>
       <c r="H67" t="s">
-        <v>350</v>
+        <v>439</v>
       </c>
       <c r="I67" t="s">
-        <v>334</v>
+        <v>47</v>
       </c>
       <c r="K67" t="s">
-        <v>351</v>
+        <v>440</v>
       </c>
       <c r="L67" t="s">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="M67" t="s">
-        <v>352</v>
+        <v>433</v>
       </c>
       <c r="O67" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="P67" t="s">
-        <v>354</v>
+        <v>442</v>
       </c>
       <c r="Q67" t="s">
-        <v>352</v>
+        <v>188</v>
       </c>
       <c r="S67" t="s">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="T67" t="s">
-        <v>356</v>
+        <v>444</v>
       </c>
       <c r="U67" t="s">
-        <v>352</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -6050,7 +6398,7 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -6063,40 +6411,40 @@
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>357</v>
+        <v>446</v>
       </c>
       <c r="H68" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="I68" t="s">
-        <v>334</v>
+        <v>64</v>
       </c>
       <c r="K68" t="s">
-        <v>358</v>
+        <v>447</v>
       </c>
       <c r="L68" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="O68" t="s">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="P68" t="s">
-        <v>361</v>
+        <v>451</v>
       </c>
       <c r="Q68" t="s">
-        <v>352</v>
+        <v>188</v>
       </c>
       <c r="S68" t="s">
-        <v>362</v>
+        <v>452</v>
       </c>
       <c r="T68" t="s">
-        <v>363</v>
+        <v>453</v>
       </c>
       <c r="U68" t="s">
-        <v>352</v>
+        <v>445</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -6105,7 +6453,7 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -6118,40 +6466,40 @@
         <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>364</v>
+        <v>454</v>
       </c>
       <c r="H69" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="I69" t="s">
-        <v>365</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s">
-        <v>366</v>
+        <v>455</v>
       </c>
       <c r="L69" t="s">
-        <v>367</v>
+        <v>456</v>
       </c>
       <c r="M69" t="s">
-        <v>352</v>
+        <v>457</v>
       </c>
       <c r="O69" t="s">
-        <v>368</v>
+        <v>458</v>
       </c>
       <c r="P69" t="s">
-        <v>369</v>
+        <v>459</v>
       </c>
       <c r="Q69" t="s">
-        <v>352</v>
+        <v>211</v>
       </c>
       <c r="S69" t="s">
-        <v>370</v>
+        <v>460</v>
       </c>
       <c r="T69" t="s">
-        <v>371</v>
+        <v>461</v>
       </c>
       <c r="U69" t="s">
-        <v>352</v>
+        <v>462</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -6160,7 +6508,7 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -6173,40 +6521,40 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>372</v>
+        <v>463</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>464</v>
       </c>
       <c r="I70" t="s">
-        <v>365</v>
+        <v>111</v>
       </c>
       <c r="K70" t="s">
-        <v>374</v>
+        <v>465</v>
       </c>
       <c r="L70" t="s">
-        <v>375</v>
+        <v>466</v>
       </c>
       <c r="M70" t="s">
-        <v>352</v>
+        <v>467</v>
       </c>
       <c r="O70" t="s">
-        <v>376</v>
+        <v>468</v>
       </c>
       <c r="P70" t="s">
-        <v>377</v>
+        <v>469</v>
       </c>
       <c r="Q70" t="s">
-        <v>352</v>
+        <v>222</v>
       </c>
       <c r="S70" t="s">
-        <v>378</v>
+        <v>470</v>
       </c>
       <c r="T70" t="s">
-        <v>379</v>
+        <v>471</v>
       </c>
       <c r="U70" t="s">
-        <v>352</v>
+        <v>462</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -6215,7 +6563,7 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -6228,40 +6576,40 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>380</v>
+        <v>472</v>
       </c>
       <c r="H71" t="s">
-        <v>381</v>
+        <v>473</v>
       </c>
       <c r="I71" t="s">
-        <v>365</v>
+        <v>117</v>
       </c>
       <c r="K71" t="s">
-        <v>382</v>
+        <v>474</v>
       </c>
       <c r="L71" t="s">
-        <v>383</v>
+        <v>475</v>
       </c>
       <c r="M71" t="s">
-        <v>352</v>
+        <v>476</v>
       </c>
       <c r="O71" t="s">
-        <v>384</v>
+        <v>477</v>
       </c>
       <c r="P71" t="s">
-        <v>385</v>
+        <v>478</v>
       </c>
       <c r="Q71" t="s">
-        <v>352</v>
+        <v>222</v>
       </c>
       <c r="S71" t="s">
-        <v>386</v>
+        <v>479</v>
       </c>
       <c r="T71" t="s">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="U71" t="s">
-        <v>352</v>
+        <v>481</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -6270,7 +6618,7 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -6282,40 +6630,40 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>389</v>
+        <v>483</v>
       </c>
       <c r="H72" t="s">
-        <v>390</v>
+        <v>484</v>
       </c>
       <c r="I72" t="s">
-        <v>391</v>
+        <v>149</v>
       </c>
       <c r="K72" t="s">
-        <v>392</v>
+        <v>485</v>
       </c>
       <c r="L72" t="s">
-        <v>393</v>
+        <v>486</v>
       </c>
       <c r="M72" t="s">
-        <v>352</v>
+        <v>487</v>
       </c>
       <c r="O72" t="s">
-        <v>394</v>
+        <v>488</v>
       </c>
       <c r="P72" t="s">
-        <v>395</v>
+        <v>489</v>
       </c>
       <c r="Q72" t="s">
-        <v>352</v>
+        <v>243</v>
       </c>
       <c r="S72" t="s">
-        <v>396</v>
+        <v>490</v>
       </c>
       <c r="T72" t="s">
-        <v>397</v>
+        <v>491</v>
       </c>
       <c r="U72" t="s">
-        <v>352</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -6324,53 +6672,53 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>398</v>
+        <v>492</v>
       </c>
       <c r="H73" t="s">
-        <v>349</v>
+        <v>438</v>
       </c>
       <c r="I73" t="s">
-        <v>399</v>
+        <v>217</v>
       </c>
       <c r="K73" t="s">
-        <v>400</v>
+        <v>493</v>
       </c>
       <c r="L73" t="s">
-        <v>366</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s">
-        <v>401</v>
+        <v>494</v>
       </c>
       <c r="O73" t="s">
-        <v>402</v>
+        <v>495</v>
       </c>
       <c r="P73" t="s">
-        <v>403</v>
+        <v>496</v>
       </c>
       <c r="Q73" t="s">
-        <v>401</v>
+        <v>297</v>
       </c>
       <c r="S73" t="s">
-        <v>404</v>
+        <v>497</v>
       </c>
       <c r="T73" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="U73" t="s">
-        <v>401</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -6379,53 +6727,53 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>406</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
-        <v>407</v>
+        <v>501</v>
       </c>
       <c r="I74" t="s">
-        <v>408</v>
+        <v>271</v>
       </c>
       <c r="K74" t="s">
-        <v>409</v>
+        <v>502</v>
       </c>
       <c r="L74" t="s">
-        <v>410</v>
+        <v>503</v>
       </c>
       <c r="M74" t="s">
-        <v>411</v>
+        <v>76</v>
       </c>
       <c r="O74" t="s">
-        <v>412</v>
+        <v>504</v>
       </c>
       <c r="P74" t="s">
-        <v>413</v>
+        <v>505</v>
       </c>
       <c r="Q74" t="s">
-        <v>411</v>
+        <v>343</v>
       </c>
       <c r="S74" t="s">
-        <v>414</v>
+        <v>506</v>
       </c>
       <c r="T74" t="s">
-        <v>415</v>
+        <v>507</v>
       </c>
       <c r="U74" t="s">
-        <v>411</v>
+        <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -6434,53 +6782,53 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>416</v>
+        <v>509</v>
       </c>
       <c r="H75" t="s">
-        <v>417</v>
+        <v>510</v>
       </c>
       <c r="I75" t="s">
-        <v>418</v>
+        <v>314</v>
       </c>
       <c r="K75" t="s">
-        <v>419</v>
+        <v>511</v>
       </c>
       <c r="L75" t="s">
-        <v>420</v>
+        <v>512</v>
       </c>
       <c r="M75" t="s">
-        <v>421</v>
+        <v>175</v>
       </c>
       <c r="O75" t="s">
-        <v>422</v>
+        <v>513</v>
       </c>
       <c r="P75" t="s">
-        <v>423</v>
+        <v>514</v>
       </c>
       <c r="Q75" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="S75" t="s">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="T75" t="s">
-        <v>425</v>
+        <v>516</v>
       </c>
       <c r="U75" t="s">
-        <v>421</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -6489,7 +6837,7 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -6502,40 +6850,40 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>426</v>
+        <v>518</v>
       </c>
       <c r="H76" t="s">
-        <v>427</v>
+        <v>519</v>
       </c>
       <c r="I76" t="s">
-        <v>428</v>
+        <v>361</v>
       </c>
       <c r="K76" t="s">
-        <v>429</v>
+        <v>520</v>
       </c>
       <c r="L76" t="s">
-        <v>430</v>
+        <v>521</v>
       </c>
       <c r="M76" t="s">
-        <v>431</v>
+        <v>240</v>
       </c>
       <c r="O76" t="s">
-        <v>432</v>
+        <v>522</v>
       </c>
       <c r="P76" t="s">
-        <v>433</v>
+        <v>523</v>
       </c>
       <c r="Q76" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="S76" t="s">
-        <v>434</v>
+        <v>524</v>
       </c>
       <c r="T76" t="s">
-        <v>435</v>
+        <v>525</v>
       </c>
       <c r="U76" t="s">
-        <v>431</v>
+        <v>526</v>
       </c>
     </row>
     <row r="77" spans="1:21">
@@ -6544,7 +6892,7 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -6557,40 +6905,40 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>436</v>
+        <v>527</v>
       </c>
       <c r="H77" t="s">
-        <v>437</v>
+        <v>528</v>
       </c>
       <c r="I77" t="s">
-        <v>34</v>
+        <v>414</v>
       </c>
       <c r="K77" t="s">
-        <v>438</v>
+        <v>529</v>
       </c>
       <c r="L77" t="s">
-        <v>439</v>
+        <v>530</v>
       </c>
       <c r="M77" t="s">
-        <v>440</v>
+        <v>295</v>
       </c>
       <c r="O77" t="s">
-        <v>441</v>
+        <v>531</v>
       </c>
       <c r="P77" t="s">
-        <v>442</v>
+        <v>532</v>
       </c>
       <c r="Q77" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="S77" t="s">
-        <v>443</v>
+        <v>533</v>
       </c>
       <c r="T77" t="s">
-        <v>444</v>
+        <v>534</v>
       </c>
       <c r="U77" t="s">
-        <v>440</v>
+        <v>535</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -6599,7 +6947,7 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -6612,40 +6960,40 @@
         <v>8</v>
       </c>
       <c r="G78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I78" t="s">
-        <v>45</v>
+        <v>476</v>
       </c>
       <c r="K78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M78" t="s">
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="O78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q78" t="s">
-        <v>440</v>
+        <v>499</v>
       </c>
       <c r="S78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T78" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U78" t="s">
-        <v>440</v>
+        <v>537</v>
       </c>
     </row>
     <row r="79" spans="1:21">
@@ -6654,7 +7002,7 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -6667,40 +7015,40 @@
         <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I79" t="s">
-        <v>160</v>
+        <v>538</v>
       </c>
       <c r="K79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M79" t="s">
-        <v>446</v>
+        <v>110</v>
       </c>
       <c r="O79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q79" t="s">
-        <v>446</v>
+        <v>539</v>
       </c>
       <c r="S79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T79" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U79" t="s">
-        <v>446</v>
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -6709,7 +7057,7 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -6722,40 +7070,40 @@
         <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I80" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="K80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M80" t="s">
-        <v>447</v>
+        <v>211</v>
       </c>
       <c r="O80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q80" t="s">
-        <v>447</v>
+        <v>541</v>
       </c>
       <c r="S80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T80" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U80" t="s">
-        <v>447</v>
+        <v>542</v>
       </c>
     </row>
     <row r="81" spans="1:21">
@@ -6764,7 +7112,7 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -6777,40 +7125,40 @@
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I81" t="s">
-        <v>236</v>
+        <v>175</v>
       </c>
       <c r="K81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M81" t="s">
-        <v>447</v>
+        <v>288</v>
       </c>
       <c r="O81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q81" t="s">
-        <v>447</v>
+        <v>543</v>
       </c>
       <c r="S81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T81" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U81" t="s">
-        <v>447</v>
+        <v>544</v>
       </c>
     </row>
     <row r="82" spans="1:21">
@@ -6819,7 +7167,7 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -6832,40 +7180,40 @@
         <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I82" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="K82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M82" t="s">
-        <v>448</v>
+        <v>320</v>
       </c>
       <c r="O82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q82" t="s">
-        <v>448</v>
+        <v>545</v>
       </c>
       <c r="S82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T82" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U82" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
     </row>
     <row r="83" spans="1:21">
@@ -6874,7 +7222,7 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -6887,40 +7235,40 @@
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I83" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="K83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M83" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="O83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q83" t="s">
-        <v>449</v>
+        <v>540</v>
       </c>
       <c r="S83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T83" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U83" t="s">
-        <v>449</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:21">
@@ -6929,7 +7277,7 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -6942,40 +7290,40 @@
         <v>2</v>
       </c>
       <c r="G84" t="s">
+        <v>536</v>
+      </c>
+      <c r="H84" t="s">
+        <v>536</v>
+      </c>
+      <c r="I84" t="s">
+        <v>53</v>
+      </c>
+      <c r="K84" t="s">
+        <v>536</v>
+      </c>
+      <c r="L84" t="s">
+        <v>536</v>
+      </c>
+      <c r="M84" t="s">
         <v>445</v>
       </c>
-      <c r="H84" t="s">
-        <v>445</v>
-      </c>
-      <c r="I84" t="s">
-        <v>401</v>
-      </c>
-      <c r="K84" t="s">
-        <v>445</v>
-      </c>
-      <c r="L84" t="s">
-        <v>445</v>
-      </c>
-      <c r="M84" t="s">
-        <v>449</v>
-      </c>
       <c r="O84" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P84" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q84" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="S84" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T84" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U84" t="s">
-        <v>449</v>
+        <v>548</v>
       </c>
     </row>
     <row r="85" spans="1:21">
@@ -6984,7 +7332,7 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6996,40 +7344,40 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I85" t="s">
-        <v>411</v>
+        <v>188</v>
       </c>
       <c r="K85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M85" t="s">
-        <v>451</v>
+        <v>550</v>
       </c>
       <c r="O85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q85" t="s">
-        <v>451</v>
+        <v>544</v>
       </c>
       <c r="S85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T85" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U85" t="s">
-        <v>451</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" spans="1:21">
@@ -7038,53 +7386,53 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I86" t="s">
-        <v>431</v>
+        <v>320</v>
       </c>
       <c r="K86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M86" t="s">
-        <v>452</v>
+        <v>541</v>
       </c>
       <c r="O86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q86" t="s">
-        <v>452</v>
+        <v>547</v>
       </c>
       <c r="S86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T86" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U86" t="s">
-        <v>452</v>
+        <v>552</v>
       </c>
     </row>
     <row r="87" spans="1:21">
@@ -7093,53 +7441,53 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
+        <v>536</v>
+      </c>
+      <c r="H87" t="s">
+        <v>536</v>
+      </c>
+      <c r="I87" t="s">
         <v>445</v>
       </c>
-      <c r="H87" t="s">
-        <v>445</v>
-      </c>
-      <c r="I87" t="s">
-        <v>446</v>
-      </c>
       <c r="K87" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L87" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M87" t="s">
-        <v>453</v>
+        <v>545</v>
       </c>
       <c r="O87" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P87" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q87" t="s">
-        <v>453</v>
+        <v>551</v>
       </c>
       <c r="S87" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T87" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U87" t="s">
-        <v>453</v>
+        <v>553</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -7148,53 +7496,53 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I88" t="s">
-        <v>448</v>
+        <v>539</v>
       </c>
       <c r="K88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M88" t="s">
-        <v>454</v>
+        <v>554</v>
       </c>
       <c r="O88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q88" t="s">
-        <v>454</v>
+        <v>555</v>
       </c>
       <c r="S88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T88" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U88" t="s">
-        <v>454</v>
+        <v>556</v>
       </c>
     </row>
     <row r="89" spans="1:21">
@@ -7203,7 +7551,7 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -7216,40 +7564,40 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I89" t="s">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="K89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M89" t="s">
-        <v>455</v>
+        <v>547</v>
       </c>
       <c r="O89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q89" t="s">
-        <v>455</v>
+        <v>557</v>
       </c>
       <c r="S89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T89" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U89" t="s">
-        <v>455</v>
+        <v>558</v>
       </c>
     </row>
     <row r="90" spans="1:21">
@@ -7258,7 +7606,7 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -7271,40 +7619,40 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I90" t="s">
-        <v>452</v>
+        <v>542</v>
       </c>
       <c r="K90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M90" t="s">
-        <v>456</v>
+        <v>551</v>
       </c>
       <c r="O90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q90" t="s">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="S90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T90" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U90" t="s">
-        <v>456</v>
+        <v>560</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -7313,7 +7661,7 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -7326,40 +7674,40 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I91" t="s">
-        <v>453</v>
+        <v>547</v>
       </c>
       <c r="K91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M91" t="s">
-        <v>457</v>
+        <v>555</v>
       </c>
       <c r="O91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q91" t="s">
-        <v>457</v>
+        <v>561</v>
       </c>
       <c r="S91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T91" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U91" t="s">
-        <v>457</v>
+        <v>562</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -7368,7 +7716,7 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -7381,40 +7729,40 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I92" t="s">
-        <v>454</v>
+        <v>563</v>
       </c>
       <c r="K92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M92" t="s">
-        <v>458</v>
+        <v>564</v>
       </c>
       <c r="O92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q92" t="s">
-        <v>458</v>
+        <v>565</v>
       </c>
       <c r="S92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T92" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U92" t="s">
-        <v>458</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -7423,7 +7771,7 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -7436,40 +7784,40 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I93" t="s">
-        <v>456</v>
+        <v>553</v>
       </c>
       <c r="K93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M93" t="s">
-        <v>458</v>
+        <v>567</v>
       </c>
       <c r="O93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q93" t="s">
-        <v>458</v>
+        <v>566</v>
       </c>
       <c r="S93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T93" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U93" t="s">
-        <v>458</v>
+        <v>568</v>
       </c>
     </row>
     <row r="94" spans="1:21">
@@ -7478,7 +7826,7 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -7491,40 +7839,40 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I94" t="s">
-        <v>457</v>
+        <v>558</v>
       </c>
       <c r="K94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M94" t="s">
-        <v>459</v>
+        <v>565</v>
       </c>
       <c r="O94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q94" t="s">
-        <v>459</v>
+        <v>568</v>
       </c>
       <c r="S94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T94" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U94" t="s">
-        <v>459</v>
+        <v>569</v>
       </c>
     </row>
     <row r="95" spans="1:21">
@@ -7533,7 +7881,7 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -7546,40 +7894,40 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I95" t="s">
-        <v>458</v>
+        <v>560</v>
       </c>
       <c r="K95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M95" t="s">
-        <v>459</v>
+        <v>566</v>
       </c>
       <c r="O95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q95" t="s">
-        <v>459</v>
+        <v>569</v>
       </c>
       <c r="S95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T95" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U95" t="s">
-        <v>459</v>
+        <v>570</v>
       </c>
     </row>
     <row r="96" spans="1:21">
@@ -7588,7 +7936,7 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -7601,40 +7949,40 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I96" t="s">
-        <v>459</v>
+        <v>566</v>
       </c>
       <c r="K96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M96" t="s">
-        <v>460</v>
+        <v>571</v>
       </c>
       <c r="O96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q96" t="s">
-        <v>460</v>
+        <v>572</v>
       </c>
       <c r="S96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T96" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U96" t="s">
-        <v>460</v>
+        <v>573</v>
       </c>
     </row>
     <row r="97" spans="1:21">
@@ -7643,7 +7991,7 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -7656,40 +8004,40 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="H97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="I97" t="s">
-        <v>459</v>
+        <v>571</v>
       </c>
       <c r="K97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="L97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="M97" t="s">
-        <v>460</v>
+        <v>570</v>
       </c>
       <c r="O97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="P97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q97" t="s">
-        <v>460</v>
+        <v>573</v>
       </c>
       <c r="S97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="T97" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="U97" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98" spans="1:21">
@@ -7698,7 +8046,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -7710,40 +8058,40 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="H98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="I98" t="s">
-        <v>460</v>
+        <v>572</v>
       </c>
       <c r="K98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="L98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="M98" t="s">
-        <v>463</v>
+        <v>573</v>
       </c>
       <c r="O98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="P98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="Q98" t="s">
-        <v>463</v>
+        <v>576</v>
       </c>
       <c r="S98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="T98" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="U98" t="s">
-        <v>463</v>
+        <v>576</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -7752,53 +8100,53 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="H99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="I99" t="s">
-        <v>460</v>
+        <v>573</v>
       </c>
       <c r="K99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="L99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="M99" t="s">
-        <v>463</v>
+        <v>574</v>
       </c>
       <c r="O99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="P99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="Q99" t="s">
-        <v>463</v>
+        <v>576</v>
       </c>
       <c r="S99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="T99" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="U99" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -7807,53 +8155,53 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="H100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="I100" t="s">
-        <v>463</v>
+        <v>576</v>
       </c>
       <c r="K100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="L100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="M100" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="O100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="P100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="Q100" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="S100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="T100" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="U100" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
     </row>
     <row r="101" spans="1:21">
@@ -7862,53 +8210,53 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="H101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="I101" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="K101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="L101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="M101" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="O101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="P101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="Q101" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="T101" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="U101" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="102" spans="1:21">
@@ -7917,7 +8265,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -7930,40 +8278,40 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="H102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="I102" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="L102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="M102" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="P102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="Q102" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="T102" t="s">
-        <v>462</v>
+        <v>536</v>
       </c>
       <c r="U102" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="103" spans="1:21">
@@ -7972,7 +8320,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -7985,40 +8333,40 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="H103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="I103" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="L103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="M103" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="P103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="Q103" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="T103" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="U103" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -8027,7 +8375,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -8040,40 +8388,40 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="H104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="I104" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="L104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="M104" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="P104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="Q104" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="T104" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="U104" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="105" spans="1:21">
@@ -8082,7 +8430,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -8095,40 +8443,40 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="H105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="I105" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="L105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="M105" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="P105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="Q105" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="T105" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="U105" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -8137,7 +8485,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -8150,40 +8498,40 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="H106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="I106" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="L106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="M106" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="P106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="Q106" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="T106" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="U106" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="107" spans="1:21">
@@ -8192,7 +8540,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -8205,40 +8553,40 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="H107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="I107" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="L107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="M107" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="P107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="Q107" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="T107" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="U107" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="108" spans="1:21">
@@ -8247,7 +8595,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -8260,40 +8608,40 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="H108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="I108" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="L108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="M108" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="P108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="Q108" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="T108" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="U108" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" spans="1:21">
@@ -8302,7 +8650,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -8315,40 +8663,40 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="H109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="I109" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="K109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="L109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="M109" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="O109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="P109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="Q109" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
       <c r="S109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="T109" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="U109" t="s">
-        <v>463</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/chessTexasStrategy.xlsx
+++ b/poker/resources/sample/chessTexasStrategy.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="581">
   <si>
     <t>ID</t>
   </si>
@@ -151,925 +151,1660 @@
     <t>A</t>
   </si>
   <si>
-    <t>1_500|2_3000|3_0|4_2000</t>
+    <t>1_1000|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1500|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_20000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_15000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4000|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_10000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4400|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5280|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_8000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>1_990|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1485|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4356|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5227|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>1_980|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2744|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4704|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4312|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5174|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_970|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1455|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2716|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4656|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4268|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5122|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2688|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3840|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4608|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5069|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_950|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1425|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4180|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_5016|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2632|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4512|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4136|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4963|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_14500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_930|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1395|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1860|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2604|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4464|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4092|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4910|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2576|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4416|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4048|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4858|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_910|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1365|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2548|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4368|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_4004|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4805|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1350|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_19000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3600|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3960|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4752|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2464|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4224|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3872|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4646|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_870|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1305|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1740|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2436|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_14000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3480|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4176|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3828|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4594|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_860|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1290|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1720|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2408|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4128|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3784|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4541|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2352|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_4032|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3696|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4435|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_830|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1245|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1660|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2324|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3320|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3984|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3652|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4382|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2296|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3280|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3936|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3608|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4330|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_800|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_18100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2240|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_9000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3520|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_790|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1185|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1580|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2212|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3792|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3476|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4171|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1170|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2184|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3120|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3744|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3432|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4118|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1140|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2128|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_3040|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3648|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3344|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_4013|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_7000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_740|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1110|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1480|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2072|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2960|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3552|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3256|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3907|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_720|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1080|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_13000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3456|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3802|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_700|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1050|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_17100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1400|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_3080|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_680|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_1020|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1360|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1904|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2720|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3264|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2992|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3590|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_660|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3168|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2904|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3485|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_630|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_945|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1260|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1764|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_3024|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2772|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3326|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_610|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_915|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1220|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1708|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2928|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_0|2_8100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2684|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3221|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_590|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_885|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_16100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1180|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1652|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_12100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2360|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2832|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2596|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3115|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>1_570|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_855|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1140|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1596|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2280|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2736|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2508|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_3010|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_560|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1120|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1568|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2240|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2688|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2464|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2957|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_540|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_810|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1080|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1512|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2160|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2592|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2376|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2851|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_530|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_795|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1060|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1484|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2120|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2544|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2332|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2798|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_510|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_765|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1020|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1428|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2040|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2448|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2244|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2693|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_500|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_750|2_2000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1000|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1400|2_2000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_2000|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2400|2_2000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2200|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2640|2_2000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_480|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_0|2_15100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_960|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1344|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2304|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2534|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_6000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_470|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_705|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_940|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1316|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1880|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2256|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2068|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2482|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_450|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_675|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_900|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1800|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2160|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1980|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2376|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_440|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_880|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1232|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1760|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2112|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1936|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2323|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_420|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_840|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1176|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_11000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1680|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_2016|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1848|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2218|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_410|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_615|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_820|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1148|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1968|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1804|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2165|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_390|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_585|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_780|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1092|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1560|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1872|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1716|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2059|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>1_380|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_570|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_760|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_1064|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1520|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1824|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1672|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_2006|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_300|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_600|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_0|2_10200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_1200|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1440|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1320|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1584|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_230|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_345|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_460|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_644|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_920|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1104|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_1012|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_1214|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_160|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_240|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_320|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_448|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_640|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_768|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_704|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_845|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_5000|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_90|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_135|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_180|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_252|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_360|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_432|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_396|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_475|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_4700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_20|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_30|2_3000|3_0|4_2000</t>
+  </si>
+  <si>
+    <t>1_40|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_56|2_3000|3_0|4_3000</t>
+  </si>
+  <si>
+    <t>1_80|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_96|2_3000|3_0|4_4000</t>
+  </si>
+  <si>
+    <t>1_88|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_106|2_3000|3_0|4_6000</t>
+  </si>
+  <si>
+    <t>1_0|2_4500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_0|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_10300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_5100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_4400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>一对</t>
+  </si>
+  <si>
+    <t>1_0|2_5500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2500|3_10000|4_0</t>
   </si>
   <si>
     <t>1_0|2_2000|3_10000|4_0</t>
   </si>
   <si>
-    <t>1_1000|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1400|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1500|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2250|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_3000|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>1_495|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1386|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1485|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2228|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_0|2_1000|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_2970|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>葫芦</t>
-  </si>
-  <si>
-    <t>1_490|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_980|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1372|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1470|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2205|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2940|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_485|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_970|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1358|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1455|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2183|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2910|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_960|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1344|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2160|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2880|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_475|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_950|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1330|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1425|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2138|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2850|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_940|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1316|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2115|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2820|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_465|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_930|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1302|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1395|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2093|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2790|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_460|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_920|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1288|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1380|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2070|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2760|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_455|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_910|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1274|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1365|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2048|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2730|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_8000|4_0</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2025|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2700|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_880|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1232|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2640|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_435|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_870|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1218|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1305|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1958|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2610|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_430|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_860|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1204|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1290|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1935|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2580|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_840|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1176|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1890|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2520|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_415|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_830|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1162|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1245|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1868|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2490|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_820|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1148|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1845|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2460|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_400|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_800|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1120|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1200|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1800|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2400|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_395|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_790|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1106|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1185|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1778|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2370|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_780|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1092|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1755|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2340|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_760|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1064|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1710|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2280|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_370|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_740|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1036|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1110|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1665|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2220|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_360|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1008|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1080|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1620|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2160|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_350|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_700|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1050|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1575|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2100|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_340|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_680|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_952|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_1020|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1530|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_2040|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_330|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_924|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_990|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1980|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_315|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_882|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_945|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1418|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1890|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_305|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_610|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_854|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_915|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1373|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1830|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_295|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_590|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_826|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_885|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1328|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1770|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>1_285|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_570|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_798|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_855|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1283|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1710|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_280|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_560|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_784|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_840|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1260|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1680|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_270|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_540|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_756|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_810|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1215|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1620|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_265|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_530|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_742|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_795|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1193|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1590|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_255|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_510|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_714|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_765|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1148|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1530|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_250|2_2000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_500|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_700|2_2000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_750|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1125|2_2000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1500|2_2000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_240|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_672|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_720|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1440|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_235|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_470|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_658|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_705|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1058|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1410|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_225|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_675|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1013|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1350|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_220|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_440|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_616|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_660|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1320|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_210|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_420|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_588|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_630|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1260|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_205|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_410|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_574|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_615|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_923|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1230|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_195|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_390|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_546|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_585|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_878|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1170|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>1_190|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_380|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_532|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_570|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_855|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_1140|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_150|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_300|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_450|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_900|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_115|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_230|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_322|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_345|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_518|2_3000|3_0|4_4000</t>
+    <t>1_0|2_2200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_2100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_1700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_900|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_700|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_600|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_800|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_500|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_400|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_300|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>高牌</t>
+  </si>
+  <si>
+    <t>1_0|2_200|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_100|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_0|3_10000|4_0</t>
+  </si>
+  <si>
+    <t>1_0|2_3000|3_2000|4_0</t>
   </si>
   <si>
     <t>1_0|2_0|3_2000|4_0</t>
-  </si>
-  <si>
-    <t>1_690|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_80|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_160|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_224|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_240|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_360|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_480|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_45|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_90|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_126|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_135|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_203|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_270|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_10|2_3000|3_0|4_2000</t>
-  </si>
-  <si>
-    <t>1_20|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_28|2_3000|3_0|4_3000</t>
-  </si>
-  <si>
-    <t>1_30|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_45|2_3000|3_0|4_4000</t>
-  </si>
-  <si>
-    <t>1_60|2_3000|3_0|4_6000</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_0|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_10000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_4000|4_0</t>
-  </si>
-  <si>
-    <t>一对</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_5000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_3000|3_3000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_6000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_7000|4_0</t>
-  </si>
-  <si>
-    <t>高牌</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_9000|4_0</t>
-  </si>
-  <si>
-    <t>1_0|2_0|3_11000|4_0</t>
   </si>
 </sst>
 </file>
@@ -2220,37 +2955,37 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="S5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2259,7 +2994,7 @@
         <v>108014</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -2271,40 +3006,40 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -2313,53 +3048,53 @@
         <v>108013</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C14" si="1">C6</f>
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E7">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -2368,53 +3103,53 @@
         <v>108012</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E8">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -2423,53 +3158,53 @@
         <v>108011</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -2478,7 +3213,7 @@
         <v>108010</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -2491,40 +3226,40 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S10" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -2533,7 +3268,7 @@
         <v>108009</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -2546,40 +3281,40 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -2588,7 +3323,7 @@
         <v>108008</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -2601,40 +3336,40 @@
         <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U12" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -2643,7 +3378,7 @@
         <v>108007</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -2656,40 +3391,40 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O13" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S13" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -2698,7 +3433,7 @@
         <v>108006</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -2711,40 +3446,40 @@
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O14" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q14" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U14" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -2753,7 +3488,7 @@
         <v>107014</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -2765,40 +3500,40 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L15" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q15" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S15" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T15" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U15" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -2807,53 +3542,53 @@
         <v>107013</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <f>C15</f>
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O16" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q16" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S16" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U16" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -2862,53 +3597,53 @@
         <v>107012</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C27" si="2">C16</f>
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O17" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P17" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S17" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T17" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U17" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -2917,53 +3652,53 @@
         <v>107011</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E18">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O18" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P18" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q18" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S18" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T18" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U18" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -2972,7 +3707,7 @@
         <v>107010</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -2985,40 +3720,40 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q19" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U19" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3027,7 +3762,7 @@
         <v>107009</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -3040,40 +3775,40 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L20" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O20" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P20" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q20" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S20" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U20" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3082,7 +3817,7 @@
         <v>107008</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -3095,40 +3830,40 @@
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K21" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L21" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O21" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P21" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q21" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U21" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -3137,7 +3872,7 @@
         <v>107007</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -3150,40 +3885,40 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L22" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O22" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q22" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U22" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -3192,7 +3927,7 @@
         <v>107006</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -3205,40 +3940,40 @@
         <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O23" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P23" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q23" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S23" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U23" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -3247,7 +3982,7 @@
         <v>107005</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -3260,40 +3995,40 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O24" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P24" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q24" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U24" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -3302,7 +4037,7 @@
         <v>107004</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -3315,40 +4050,40 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L25" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O25" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q25" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S25" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T25" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U25" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -3357,7 +4092,7 @@
         <v>107003</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -3370,40 +4105,40 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K26" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L26" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O26" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P26" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q26" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S26" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T26" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -3412,7 +4147,7 @@
         <v>107002</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -3425,40 +4160,40 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K27" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O27" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P27" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q27" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S27" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T27" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U27" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -3467,7 +4202,7 @@
         <v>106014</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3479,40 +4214,40 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K28" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O28" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="P28" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q28" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S28" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T28" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -3521,53 +4256,53 @@
         <v>106013</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <f>C28</f>
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
       <c r="G29" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" t="s">
+        <v>61</v>
+      </c>
+      <c r="K29" t="s">
+        <v>62</v>
+      </c>
+      <c r="L29" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" t="s">
+        <v>64</v>
+      </c>
+      <c r="O29" t="s">
+        <v>65</v>
+      </c>
+      <c r="P29" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q29" t="s">
         <v>50</v>
       </c>
-      <c r="H29" t="s">
-        <v>50</v>
-      </c>
-      <c r="I29" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" t="s">
-        <v>51</v>
-      </c>
-      <c r="L29" t="s">
-        <v>52</v>
-      </c>
-      <c r="M29" t="s">
-        <v>35</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="S29" t="s">
+        <v>67</v>
+      </c>
+      <c r="T29" t="s">
+        <v>68</v>
+      </c>
+      <c r="U29" t="s">
         <v>53</v>
-      </c>
-      <c r="P29" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>43</v>
-      </c>
-      <c r="S29" t="s">
-        <v>55</v>
-      </c>
-      <c r="T29" t="s">
-        <v>55</v>
-      </c>
-      <c r="U29" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -3576,53 +4311,53 @@
         <v>106012</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:C40" si="3">C29</f>
         <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E30">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="K30" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L30" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="M30" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="O30" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="P30" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q30" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="S30" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="T30" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="U30" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -3631,53 +4366,53 @@
         <v>106011</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E31">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L31" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="M31" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="O31" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="Q31" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="S31" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="T31" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="U31" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -3686,7 +4421,7 @@
         <v>106010</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -3699,40 +4434,40 @@
         <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L32" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="M32" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="O32" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="P32" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="Q32" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="S32" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="T32" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="U32" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -3741,7 +4476,7 @@
         <v>106009</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -3754,40 +4489,40 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="L33" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="M33" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="O33" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P33" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q33" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="S33" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="T33" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="U33" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -3796,7 +4531,7 @@
         <v>106008</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -3809,40 +4544,40 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="K34" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="M34" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="O34" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="Q34" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="S34" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="T34" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="U34" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -3851,7 +4586,7 @@
         <v>106007</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -3864,40 +4599,40 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="K35" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="M35" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="O35" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="Q35" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="S35" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="T35" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="U35" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -3906,7 +4641,7 @@
         <v>106006</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -3919,40 +4654,40 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="H36" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L36" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="M36" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="O36" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="P36" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="Q36" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="S36" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="T36" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="U36" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -3961,7 +4696,7 @@
         <v>106005</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -3974,40 +4709,40 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="K37" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="L37" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="M37" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="O37" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="P37" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="Q37" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="S37" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="T37" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="U37" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -4016,7 +4751,7 @@
         <v>106004</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -4029,40 +4764,40 @@
         <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="H38" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="K38" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="O38" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="P38" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="Q38" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="S38" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="T38" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="U38" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -4071,7 +4806,7 @@
         <v>106003</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -4084,40 +4819,40 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="K39" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="O39" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="P39" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="Q39" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="S39" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="T39" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="U39" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -4126,7 +4861,7 @@
         <v>106002</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -4139,40 +4874,40 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="K40" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="L40" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="M40" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="O40" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="P40" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="Q40" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="S40" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="T40" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="U40" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -4181,7 +4916,7 @@
         <v>105014</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -4193,40 +4928,40 @@
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="H41" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="K41" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="L41" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="M41" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="O41" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="P41" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="Q41" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="S41" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="T41" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="U41" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -4235,53 +4970,53 @@
         <v>105013</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C42">
         <f>C41</f>
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E42">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="K42" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="O42" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="P42" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="Q42" t="s">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="S42" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="T42" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="U42" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -4290,53 +5025,53 @@
         <v>105012</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:C49" si="5">C42</f>
         <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="H43" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="K43" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="L43" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="M43" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="O43" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="P43" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="Q43" t="s">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="S43" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="T43" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="U43" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -4345,53 +5080,53 @@
         <v>105011</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C44">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E44">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="H44" t="s">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>191</v>
       </c>
       <c r="K44" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="O44" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="P44" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="Q44" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="S44" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="T44" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="U44" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -4400,7 +5135,7 @@
         <v>105010</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C45">
         <f t="shared" si="5"/>
@@ -4413,40 +5148,40 @@
         <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="H45" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>202</v>
       </c>
       <c r="K45" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="L45" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="M45" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="O45" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="P45" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="Q45" t="s">
-        <v>43</v>
+        <v>208</v>
       </c>
       <c r="S45" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="T45" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="U45" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -4455,7 +5190,7 @@
         <v>105009</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C46">
         <f t="shared" si="5"/>
@@ -4468,40 +5203,40 @@
         <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>214</v>
       </c>
       <c r="K46" t="s">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="M46" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="O46" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="P46" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="Q46" t="s">
-        <v>43</v>
+        <v>208</v>
       </c>
       <c r="S46" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="T46" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="U46" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -4510,7 +5245,7 @@
         <v>105008</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C47">
         <f t="shared" si="5"/>
@@ -4523,40 +5258,40 @@
         <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="H47" t="s">
-        <v>142</v>
+        <v>224</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="K47" t="s">
-        <v>143</v>
+        <v>226</v>
       </c>
       <c r="L47" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="M47" t="s">
-        <v>35</v>
+        <v>228</v>
       </c>
       <c r="O47" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="P47" t="s">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="Q47" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="S47" t="s">
-        <v>147</v>
+        <v>231</v>
       </c>
       <c r="T47" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="U47" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4565,7 +5300,7 @@
         <v>105007</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C48">
         <f t="shared" si="5"/>
@@ -4578,40 +5313,40 @@
         <v>7</v>
       </c>
       <c r="G48" t="s">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="I48" t="s">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="K48" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="M48" t="s">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c r="O48" t="s">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="P48" t="s">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="Q48" t="s">
-        <v>43</v>
+        <v>240</v>
       </c>
       <c r="S48" t="s">
-        <v>153</v>
+        <v>241</v>
       </c>
       <c r="T48" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="U48" t="s">
-        <v>98</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -4620,7 +5355,7 @@
         <v>105006</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C49">
         <f t="shared" si="5"/>
@@ -4633,40 +5368,40 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="H49" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>246</v>
       </c>
       <c r="K49" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="L49" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="M49" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="O49" t="s">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="P49" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="Q49" t="s">
-        <v>43</v>
+        <v>240</v>
       </c>
       <c r="S49" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="T49" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="U49" t="s">
-        <v>98</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -4675,7 +5410,7 @@
         <v>104014</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -4687,40 +5422,40 @@
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>255</v>
       </c>
       <c r="H50" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="I50" t="s">
-        <v>30</v>
+        <v>257</v>
       </c>
       <c r="K50" t="s">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="L50" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="M50" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="O50" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>261</v>
       </c>
       <c r="Q50" t="s">
-        <v>43</v>
+        <v>262</v>
       </c>
       <c r="S50" t="s">
-        <v>166</v>
+        <v>263</v>
       </c>
       <c r="T50" t="s">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="U50" t="s">
-        <v>98</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -4729,53 +5464,53 @@
         <v>104013</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C51">
         <f>C50</f>
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E51">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>167</v>
+        <v>266</v>
       </c>
       <c r="H51" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>268</v>
       </c>
       <c r="K51" t="s">
-        <v>168</v>
+        <v>269</v>
       </c>
       <c r="L51" t="s">
-        <v>169</v>
+        <v>270</v>
       </c>
       <c r="M51" t="s">
-        <v>35</v>
+        <v>271</v>
       </c>
       <c r="O51" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>273</v>
       </c>
       <c r="Q51" t="s">
-        <v>43</v>
+        <v>274</v>
       </c>
       <c r="S51" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="T51" t="s">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="U51" t="s">
-        <v>98</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -4784,53 +5519,53 @@
         <v>104012</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C52">
         <f t="shared" ref="C52:C58" si="6">C51</f>
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E52">
         <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>278</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="K52" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="L52" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="M52" t="s">
-        <v>35</v>
+        <v>282</v>
       </c>
       <c r="O52" t="s">
-        <v>176</v>
+        <v>283</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="Q52" t="s">
-        <v>43</v>
+        <v>285</v>
       </c>
       <c r="S52" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="T52" t="s">
-        <v>178</v>
+        <v>287</v>
       </c>
       <c r="U52" t="s">
-        <v>98</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -4839,53 +5574,53 @@
         <v>104011</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C53">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E53">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>289</v>
       </c>
       <c r="H53" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>291</v>
       </c>
       <c r="K53" t="s">
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="L53" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M53" t="s">
-        <v>35</v>
+        <v>293</v>
       </c>
       <c r="O53" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="Q53" t="s">
-        <v>43</v>
+        <v>295</v>
       </c>
       <c r="S53" t="s">
-        <v>183</v>
+        <v>296</v>
       </c>
       <c r="T53" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="U53" t="s">
-        <v>98</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -4894,7 +5629,7 @@
         <v>104010</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C54">
         <f t="shared" si="6"/>
@@ -4907,40 +5642,40 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="H54" t="s">
-        <v>184</v>
+        <v>299</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="K54" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="L54" t="s">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="M54" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="O54" t="s">
-        <v>187</v>
+        <v>304</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="Q54" t="s">
-        <v>43</v>
+        <v>306</v>
       </c>
       <c r="S54" t="s">
-        <v>189</v>
+        <v>307</v>
       </c>
       <c r="T54" t="s">
-        <v>189</v>
+        <v>308</v>
       </c>
       <c r="U54" t="s">
-        <v>98</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -4949,7 +5684,7 @@
         <v>104009</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C55">
         <f t="shared" si="6"/>
@@ -4962,40 +5697,40 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="H55" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>311</v>
       </c>
       <c r="K55" t="s">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="L55" t="s">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="M55" t="s">
-        <v>35</v>
+        <v>314</v>
       </c>
       <c r="O55" t="s">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="P55" t="s">
-        <v>41</v>
+        <v>316</v>
       </c>
       <c r="Q55" t="s">
-        <v>43</v>
+        <v>317</v>
       </c>
       <c r="S55" t="s">
-        <v>194</v>
+        <v>318</v>
       </c>
       <c r="T55" t="s">
-        <v>194</v>
+        <v>319</v>
       </c>
       <c r="U55" t="s">
-        <v>98</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -5004,7 +5739,7 @@
         <v>104008</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C56">
         <f t="shared" si="6"/>
@@ -5017,40 +5752,40 @@
         <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="H56" t="s">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>323</v>
       </c>
       <c r="K56" t="s">
-        <v>196</v>
+        <v>324</v>
       </c>
       <c r="L56" t="s">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="M56" t="s">
-        <v>35</v>
+        <v>326</v>
       </c>
       <c r="O56" t="s">
-        <v>198</v>
+        <v>327</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>328</v>
       </c>
       <c r="Q56" t="s">
-        <v>98</v>
+        <v>329</v>
       </c>
       <c r="S56" t="s">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="T56" t="s">
-        <v>200</v>
+        <v>331</v>
       </c>
       <c r="U56" t="s">
-        <v>98</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -5059,7 +5794,7 @@
         <v>104007</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C57">
         <f t="shared" si="6"/>
@@ -5072,40 +5807,40 @@
         <v>7</v>
       </c>
       <c r="G57" t="s">
-        <v>201</v>
+        <v>332</v>
       </c>
       <c r="H57" t="s">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>334</v>
       </c>
       <c r="K57" t="s">
-        <v>202</v>
+        <v>335</v>
       </c>
       <c r="L57" t="s">
-        <v>203</v>
+        <v>336</v>
       </c>
       <c r="M57" t="s">
-        <v>35</v>
+        <v>337</v>
       </c>
       <c r="O57" t="s">
-        <v>204</v>
+        <v>338</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>339</v>
       </c>
       <c r="Q57" t="s">
-        <v>98</v>
+        <v>340</v>
       </c>
       <c r="S57" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="T57" t="s">
-        <v>206</v>
+        <v>342</v>
       </c>
       <c r="U57" t="s">
-        <v>98</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -5114,7 +5849,7 @@
         <v>104006</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="C58">
         <f t="shared" si="6"/>
@@ -5127,40 +5862,40 @@
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>207</v>
+        <v>344</v>
       </c>
       <c r="H58" t="s">
-        <v>207</v>
+        <v>345</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>346</v>
       </c>
       <c r="K58" t="s">
-        <v>208</v>
+        <v>347</v>
       </c>
       <c r="L58" t="s">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="M58" t="s">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="O58" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="P58" t="s">
-        <v>211</v>
+        <v>351</v>
       </c>
       <c r="Q58" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="S58" t="s">
-        <v>212</v>
+        <v>352</v>
       </c>
       <c r="T58" t="s">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="U58" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -5169,7 +5904,7 @@
         <v>103014</v>
       </c>
       <c r="B59" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -5181,40 +5916,40 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>214</v>
+        <v>356</v>
       </c>
       <c r="H59" t="s">
-        <v>214</v>
+        <v>357</v>
       </c>
       <c r="I59" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="K59" t="s">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="L59" t="s">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="M59" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="O59" t="s">
-        <v>217</v>
+        <v>362</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>363</v>
       </c>
       <c r="Q59" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="S59" t="s">
-        <v>219</v>
+        <v>364</v>
       </c>
       <c r="T59" t="s">
-        <v>219</v>
+        <v>365</v>
       </c>
       <c r="U59" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -5223,53 +5958,53 @@
         <v>103013</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C60">
         <f>C59</f>
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E60">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>220</v>
+        <v>367</v>
       </c>
       <c r="H60" t="s">
-        <v>220</v>
+        <v>368</v>
       </c>
       <c r="I60" t="s">
-        <v>35</v>
+        <v>369</v>
       </c>
       <c r="K60" t="s">
-        <v>221</v>
+        <v>370</v>
       </c>
       <c r="L60" t="s">
-        <v>222</v>
+        <v>371</v>
       </c>
       <c r="M60" t="s">
-        <v>35</v>
+        <v>372</v>
       </c>
       <c r="O60" t="s">
-        <v>223</v>
+        <v>373</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="Q60" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="S60" t="s">
-        <v>225</v>
+        <v>375</v>
       </c>
       <c r="T60" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
       <c r="U60" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -5278,53 +6013,53 @@
         <v>103012</v>
       </c>
       <c r="B61" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C61">
         <f t="shared" ref="C61:C71" si="7">C60</f>
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>226</v>
+        <v>377</v>
       </c>
       <c r="H61" t="s">
-        <v>226</v>
+        <v>378</v>
       </c>
       <c r="I61" t="s">
-        <v>35</v>
+        <v>379</v>
       </c>
       <c r="K61" t="s">
-        <v>227</v>
+        <v>380</v>
       </c>
       <c r="L61" t="s">
-        <v>228</v>
+        <v>381</v>
       </c>
       <c r="M61" t="s">
-        <v>35</v>
+        <v>382</v>
       </c>
       <c r="O61" t="s">
-        <v>229</v>
+        <v>383</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>384</v>
       </c>
       <c r="Q61" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="S61" t="s">
-        <v>231</v>
+        <v>385</v>
       </c>
       <c r="T61" t="s">
-        <v>231</v>
+        <v>386</v>
       </c>
       <c r="U61" t="s">
-        <v>98</v>
+        <v>387</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -5333,53 +6068,53 @@
         <v>103011</v>
       </c>
       <c r="B62" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C62">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E62">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>232</v>
+        <v>388</v>
       </c>
       <c r="H62" t="s">
-        <v>232</v>
+        <v>389</v>
       </c>
       <c r="I62" t="s">
-        <v>35</v>
+        <v>390</v>
       </c>
       <c r="K62" t="s">
-        <v>233</v>
+        <v>391</v>
       </c>
       <c r="L62" t="s">
-        <v>234</v>
+        <v>392</v>
       </c>
       <c r="M62" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
       <c r="O62" t="s">
-        <v>235</v>
+        <v>394</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>395</v>
       </c>
       <c r="Q62" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="S62" t="s">
-        <v>237</v>
+        <v>396</v>
       </c>
       <c r="T62" t="s">
-        <v>237</v>
+        <v>397</v>
       </c>
       <c r="U62" t="s">
-        <v>98</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -5388,7 +6123,7 @@
         <v>103010</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C63">
         <f t="shared" si="7"/>
@@ -5401,40 +6136,40 @@
         <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="H63" t="s">
-        <v>238</v>
+        <v>399</v>
       </c>
       <c r="I63" t="s">
-        <v>35</v>
+        <v>400</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>401</v>
       </c>
       <c r="L63" t="s">
-        <v>240</v>
+        <v>402</v>
       </c>
       <c r="M63" t="s">
-        <v>35</v>
+        <v>403</v>
       </c>
       <c r="O63" t="s">
-        <v>241</v>
+        <v>404</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>405</v>
       </c>
       <c r="Q63" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="S63" t="s">
-        <v>243</v>
+        <v>406</v>
       </c>
       <c r="T63" t="s">
-        <v>243</v>
+        <v>407</v>
       </c>
       <c r="U63" t="s">
-        <v>98</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -5443,7 +6178,7 @@
         <v>103009</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C64">
         <f t="shared" si="7"/>
@@ -5456,40 +6191,40 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>244</v>
+        <v>409</v>
       </c>
       <c r="H64" t="s">
-        <v>244</v>
+        <v>410</v>
       </c>
       <c r="I64" t="s">
-        <v>35</v>
+        <v>411</v>
       </c>
       <c r="K64" t="s">
-        <v>245</v>
+        <v>412</v>
       </c>
       <c r="L64" t="s">
-        <v>246</v>
+        <v>413</v>
       </c>
       <c r="M64" t="s">
-        <v>35</v>
+        <v>414</v>
       </c>
       <c r="O64" t="s">
-        <v>247</v>
+        <v>415</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>416</v>
       </c>
       <c r="Q64" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="S64" t="s">
-        <v>249</v>
+        <v>417</v>
       </c>
       <c r="T64" t="s">
-        <v>249</v>
+        <v>418</v>
       </c>
       <c r="U64" t="s">
-        <v>98</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -5498,7 +6233,7 @@
         <v>103008</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C65">
         <f t="shared" si="7"/>
@@ -5511,40 +6246,40 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>250</v>
+        <v>419</v>
       </c>
       <c r="H65" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="I65" t="s">
-        <v>35</v>
+        <v>420</v>
       </c>
       <c r="K65" t="s">
-        <v>251</v>
+        <v>421</v>
       </c>
       <c r="L65" t="s">
-        <v>252</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s">
-        <v>35</v>
+        <v>423</v>
       </c>
       <c r="O65" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>425</v>
       </c>
       <c r="Q65" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="S65" t="s">
-        <v>254</v>
+        <v>426</v>
       </c>
       <c r="T65" t="s">
-        <v>254</v>
+        <v>427</v>
       </c>
       <c r="U65" t="s">
-        <v>98</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -5553,7 +6288,7 @@
         <v>103007</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C66">
         <f t="shared" si="7"/>
@@ -5566,40 +6301,40 @@
         <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>429</v>
       </c>
       <c r="H66" t="s">
-        <v>255</v>
+        <v>430</v>
       </c>
       <c r="I66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K66" t="s">
-        <v>256</v>
+        <v>431</v>
       </c>
       <c r="L66" t="s">
-        <v>257</v>
+        <v>432</v>
       </c>
       <c r="M66" t="s">
-        <v>35</v>
+        <v>433</v>
       </c>
       <c r="O66" t="s">
-        <v>258</v>
+        <v>434</v>
       </c>
       <c r="P66" t="s">
-        <v>259</v>
+        <v>435</v>
       </c>
       <c r="Q66" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="S66" t="s">
-        <v>260</v>
+        <v>436</v>
       </c>
       <c r="T66" t="s">
-        <v>260</v>
+        <v>437</v>
       </c>
       <c r="U66" t="s">
-        <v>98</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -5608,7 +6343,7 @@
         <v>103006</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C67">
         <f t="shared" si="7"/>
@@ -5621,40 +6356,40 @@
         <v>6</v>
       </c>
       <c r="G67" t="s">
-        <v>261</v>
+        <v>438</v>
       </c>
       <c r="H67" t="s">
-        <v>261</v>
+        <v>439</v>
       </c>
       <c r="I67" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K67" t="s">
-        <v>262</v>
+        <v>440</v>
       </c>
       <c r="L67" t="s">
-        <v>196</v>
+        <v>324</v>
       </c>
       <c r="M67" t="s">
-        <v>35</v>
+        <v>433</v>
       </c>
       <c r="O67" t="s">
-        <v>263</v>
+        <v>441</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>442</v>
       </c>
       <c r="Q67" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="S67" t="s">
-        <v>265</v>
+        <v>443</v>
       </c>
       <c r="T67" t="s">
-        <v>265</v>
+        <v>444</v>
       </c>
       <c r="U67" t="s">
-        <v>98</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -5663,7 +6398,7 @@
         <v>103005</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C68">
         <f t="shared" si="7"/>
@@ -5676,40 +6411,40 @@
         <v>5</v>
       </c>
       <c r="G68" t="s">
-        <v>266</v>
+        <v>446</v>
       </c>
       <c r="H68" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="I68" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="K68" t="s">
-        <v>267</v>
+        <v>447</v>
       </c>
       <c r="L68" t="s">
-        <v>268</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s">
-        <v>35</v>
+        <v>449</v>
       </c>
       <c r="O68" t="s">
-        <v>269</v>
+        <v>450</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>451</v>
       </c>
       <c r="Q68" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="S68" t="s">
-        <v>270</v>
+        <v>452</v>
       </c>
       <c r="T68" t="s">
-        <v>270</v>
+        <v>453</v>
       </c>
       <c r="U68" t="s">
-        <v>98</v>
+        <v>445</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -5718,7 +6453,7 @@
         <v>103004</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C69">
         <f t="shared" si="7"/>
@@ -5731,40 +6466,40 @@
         <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>271</v>
+        <v>454</v>
       </c>
       <c r="H69" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="I69" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s">
-        <v>272</v>
+        <v>455</v>
       </c>
       <c r="L69" t="s">
-        <v>273</v>
+        <v>456</v>
       </c>
       <c r="M69" t="s">
-        <v>35</v>
+        <v>457</v>
       </c>
       <c r="O69" t="s">
-        <v>274</v>
+        <v>458</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>459</v>
       </c>
       <c r="Q69" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="S69" t="s">
-        <v>275</v>
+        <v>460</v>
       </c>
       <c r="T69" t="s">
-        <v>275</v>
+        <v>461</v>
       </c>
       <c r="U69" t="s">
-        <v>98</v>
+        <v>462</v>
       </c>
     </row>
     <row r="70" spans="1:21">
@@ -5773,7 +6508,7 @@
         <v>103003</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C70">
         <f t="shared" si="7"/>
@@ -5786,40 +6521,40 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>276</v>
+        <v>463</v>
       </c>
       <c r="H70" t="s">
-        <v>276</v>
+        <v>464</v>
       </c>
       <c r="I70" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="K70" t="s">
-        <v>277</v>
+        <v>465</v>
       </c>
       <c r="L70" t="s">
-        <v>278</v>
+        <v>466</v>
       </c>
       <c r="M70" t="s">
-        <v>35</v>
+        <v>467</v>
       </c>
       <c r="O70" t="s">
-        <v>279</v>
+        <v>468</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>469</v>
       </c>
       <c r="Q70" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="S70" t="s">
-        <v>281</v>
+        <v>470</v>
       </c>
       <c r="T70" t="s">
-        <v>281</v>
+        <v>471</v>
       </c>
       <c r="U70" t="s">
-        <v>98</v>
+        <v>462</v>
       </c>
     </row>
     <row r="71" spans="1:21">
@@ -5828,7 +6563,7 @@
         <v>103002</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="C71">
         <f t="shared" si="7"/>
@@ -5841,40 +6576,40 @@
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>282</v>
+        <v>472</v>
       </c>
       <c r="H71" t="s">
-        <v>282</v>
+        <v>473</v>
       </c>
       <c r="I71" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="K71" t="s">
-        <v>283</v>
+        <v>474</v>
       </c>
       <c r="L71" t="s">
-        <v>284</v>
+        <v>475</v>
       </c>
       <c r="M71" t="s">
-        <v>35</v>
+        <v>476</v>
       </c>
       <c r="O71" t="s">
-        <v>285</v>
+        <v>477</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>478</v>
       </c>
       <c r="Q71" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="S71" t="s">
-        <v>287</v>
+        <v>479</v>
       </c>
       <c r="T71" t="s">
-        <v>287</v>
+        <v>480</v>
       </c>
       <c r="U71" t="s">
-        <v>98</v>
+        <v>481</v>
       </c>
     </row>
     <row r="72" spans="1:21">
@@ -5883,7 +6618,7 @@
         <v>102014</v>
       </c>
       <c r="B72" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -5895,40 +6630,40 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>289</v>
+        <v>483</v>
       </c>
       <c r="H72" t="s">
-        <v>289</v>
+        <v>484</v>
       </c>
       <c r="I72" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="K72" t="s">
-        <v>290</v>
+        <v>485</v>
       </c>
       <c r="L72" t="s">
-        <v>291</v>
+        <v>486</v>
       </c>
       <c r="M72" t="s">
-        <v>35</v>
+        <v>487</v>
       </c>
       <c r="O72" t="s">
-        <v>292</v>
+        <v>488</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>489</v>
       </c>
       <c r="Q72" t="s">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="S72" t="s">
-        <v>294</v>
+        <v>490</v>
       </c>
       <c r="T72" t="s">
-        <v>294</v>
+        <v>491</v>
       </c>
       <c r="U72" t="s">
-        <v>98</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" spans="1:21">
@@ -5937,53 +6672,53 @@
         <v>102013</v>
       </c>
       <c r="B73" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C73">
         <f>C72</f>
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E73">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>295</v>
+        <v>492</v>
       </c>
       <c r="H73" t="s">
-        <v>295</v>
+        <v>438</v>
       </c>
       <c r="I73" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="K73" t="s">
-        <v>296</v>
+        <v>493</v>
       </c>
       <c r="L73" t="s">
-        <v>272</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s">
-        <v>35</v>
+        <v>494</v>
       </c>
       <c r="O73" t="s">
+        <v>495</v>
+      </c>
+      <c r="P73" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q73" t="s">
         <v>297</v>
       </c>
-      <c r="P73" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>98</v>
-      </c>
       <c r="S73" t="s">
-        <v>298</v>
+        <v>497</v>
       </c>
       <c r="T73" t="s">
-        <v>298</v>
+        <v>498</v>
       </c>
       <c r="U73" t="s">
-        <v>98</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:21">
@@ -5992,53 +6727,53 @@
         <v>102012</v>
       </c>
       <c r="B74" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C74">
         <f t="shared" ref="C74:C84" si="9">C73</f>
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E74">
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>299</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
-        <v>299</v>
+        <v>501</v>
       </c>
       <c r="I74" t="s">
-        <v>35</v>
+        <v>271</v>
       </c>
       <c r="K74" t="s">
-        <v>300</v>
+        <v>502</v>
       </c>
       <c r="L74" t="s">
-        <v>301</v>
+        <v>503</v>
       </c>
       <c r="M74" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="O74" t="s">
-        <v>302</v>
+        <v>504</v>
       </c>
       <c r="P74" t="s">
-        <v>303</v>
+        <v>505</v>
       </c>
       <c r="Q74" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="S74" t="s">
-        <v>305</v>
+        <v>506</v>
       </c>
       <c r="T74" t="s">
-        <v>305</v>
+        <v>507</v>
       </c>
       <c r="U74" t="s">
-        <v>304</v>
+        <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:21">
@@ -6047,53 +6782,53 @@
         <v>102011</v>
       </c>
       <c r="B75" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C75">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E75">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>306</v>
+        <v>509</v>
       </c>
       <c r="H75" t="s">
-        <v>306</v>
+        <v>510</v>
       </c>
       <c r="I75" t="s">
-        <v>35</v>
+        <v>314</v>
       </c>
       <c r="K75" t="s">
-        <v>307</v>
+        <v>511</v>
       </c>
       <c r="L75" t="s">
-        <v>308</v>
+        <v>512</v>
       </c>
       <c r="M75" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="O75" t="s">
-        <v>309</v>
+        <v>513</v>
       </c>
       <c r="P75" t="s">
-        <v>310</v>
+        <v>514</v>
       </c>
       <c r="Q75" t="s">
-        <v>304</v>
+        <v>387</v>
       </c>
       <c r="S75" t="s">
-        <v>311</v>
+        <v>515</v>
       </c>
       <c r="T75" t="s">
-        <v>311</v>
+        <v>516</v>
       </c>
       <c r="U75" t="s">
-        <v>304</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:21">
@@ -6102,7 +6837,7 @@
         <v>102010</v>
       </c>
       <c r="B76" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C76">
         <f t="shared" si="9"/>
@@ -6115,40 +6850,40 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>312</v>
+        <v>518</v>
       </c>
       <c r="H76" t="s">
-        <v>312</v>
+        <v>519</v>
       </c>
       <c r="I76" t="s">
-        <v>35</v>
+        <v>361</v>
       </c>
       <c r="K76" t="s">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="L76" t="s">
-        <v>314</v>
+        <v>521</v>
       </c>
       <c r="M76" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="O76" t="s">
-        <v>315</v>
+        <v>522</v>
       </c>
       <c r="P76" t="s">
-        <v>316</v>
+        <v>523</v>
       </c>
       <c r="Q76" t="s">
-        <v>304</v>
+        <v>445</v>
       </c>
       <c r="S76" t="s">
-        <v>317</v>
+        <v>524</v>
       </c>
       <c r="T76" t="s">
-        <v>317</v>
+        <v>525</v>
       </c>
       <c r="U76" t="s">
-        <v>304</v>
+        <v>526</v>
       </c>
     </row>
     <row r="77" spans="1:21">
@@ -6157,7 +6892,7 @@
         <v>102009</v>
       </c>
       <c r="B77" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C77">
         <f t="shared" si="9"/>
@@ -6170,40 +6905,40 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>318</v>
+        <v>527</v>
       </c>
       <c r="H77" t="s">
-        <v>318</v>
+        <v>528</v>
       </c>
       <c r="I77" t="s">
-        <v>35</v>
+        <v>414</v>
       </c>
       <c r="K77" t="s">
-        <v>319</v>
+        <v>529</v>
       </c>
       <c r="L77" t="s">
-        <v>320</v>
+        <v>530</v>
       </c>
       <c r="M77" t="s">
-        <v>35</v>
+        <v>295</v>
       </c>
       <c r="O77" t="s">
-        <v>321</v>
+        <v>531</v>
       </c>
       <c r="P77" t="s">
-        <v>322</v>
+        <v>532</v>
       </c>
       <c r="Q77" t="s">
-        <v>304</v>
+        <v>481</v>
       </c>
       <c r="S77" t="s">
-        <v>323</v>
+        <v>533</v>
       </c>
       <c r="T77" t="s">
-        <v>323</v>
+        <v>534</v>
       </c>
       <c r="U77" t="s">
-        <v>304</v>
+        <v>535</v>
       </c>
     </row>
     <row r="78" spans="1:21">
@@ -6212,7 +6947,7 @@
         <v>102008</v>
       </c>
       <c r="B78" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C78">
         <f t="shared" si="9"/>
@@ -6225,40 +6960,40 @@
         <v>8</v>
       </c>
       <c r="G78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I78" t="s">
-        <v>35</v>
+        <v>476</v>
       </c>
       <c r="K78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M78" t="s">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="O78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q78" t="s">
-        <v>325</v>
+        <v>499</v>
       </c>
       <c r="S78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T78" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U78" t="s">
-        <v>325</v>
+        <v>537</v>
       </c>
     </row>
     <row r="79" spans="1:21">
@@ -6267,7 +7002,7 @@
         <v>102007</v>
       </c>
       <c r="B79" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C79">
         <f t="shared" si="9"/>
@@ -6280,40 +7015,40 @@
         <v>7</v>
       </c>
       <c r="G79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I79" t="s">
-        <v>35</v>
+        <v>538</v>
       </c>
       <c r="K79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M79" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="O79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q79" t="s">
-        <v>325</v>
+        <v>539</v>
       </c>
       <c r="S79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T79" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U79" t="s">
-        <v>325</v>
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="1:21">
@@ -6322,7 +7057,7 @@
         <v>102006</v>
       </c>
       <c r="B80" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C80">
         <f t="shared" si="9"/>
@@ -6335,40 +7070,40 @@
         <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I80" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="K80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M80" t="s">
-        <v>326</v>
+        <v>211</v>
       </c>
       <c r="O80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q80" t="s">
-        <v>325</v>
+        <v>541</v>
       </c>
       <c r="S80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T80" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U80" t="s">
-        <v>325</v>
+        <v>542</v>
       </c>
     </row>
     <row r="81" spans="1:21">
@@ -6377,7 +7112,7 @@
         <v>102005</v>
       </c>
       <c r="B81" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C81">
         <f t="shared" si="9"/>
@@ -6390,40 +7125,40 @@
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I81" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="K81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M81" t="s">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="O81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q81" t="s">
-        <v>325</v>
+        <v>543</v>
       </c>
       <c r="S81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T81" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U81" t="s">
-        <v>325</v>
+        <v>544</v>
       </c>
     </row>
     <row r="82" spans="1:21">
@@ -6432,7 +7167,7 @@
         <v>102004</v>
       </c>
       <c r="B82" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C82">
         <f t="shared" si="9"/>
@@ -6445,40 +7180,40 @@
         <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I82" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="K82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M82" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q82" t="s">
-        <v>325</v>
+        <v>545</v>
       </c>
       <c r="S82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T82" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U82" t="s">
-        <v>325</v>
+        <v>546</v>
       </c>
     </row>
     <row r="83" spans="1:21">
@@ -6487,7 +7222,7 @@
         <v>102003</v>
       </c>
       <c r="B83" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C83">
         <f t="shared" si="9"/>
@@ -6500,40 +7235,40 @@
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I83" t="s">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="K83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M83" t="s">
-        <v>326</v>
+        <v>387</v>
       </c>
       <c r="O83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q83" t="s">
-        <v>327</v>
+        <v>540</v>
       </c>
       <c r="S83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T83" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U83" t="s">
-        <v>327</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:21">
@@ -6542,7 +7277,7 @@
         <v>102002</v>
       </c>
       <c r="B84" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="C84">
         <f t="shared" si="9"/>
@@ -6555,40 +7290,40 @@
         <v>2</v>
       </c>
       <c r="G84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I84" t="s">
-        <v>326</v>
+        <v>53</v>
       </c>
       <c r="K84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s">
-        <v>326</v>
+        <v>445</v>
       </c>
       <c r="O84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q84" t="s">
-        <v>327</v>
+        <v>542</v>
       </c>
       <c r="S84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T84" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U84" t="s">
-        <v>327</v>
+        <v>548</v>
       </c>
     </row>
     <row r="85" spans="1:21">
@@ -6597,7 +7332,7 @@
         <v>101014</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6609,40 +7344,40 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I85" t="s">
-        <v>326</v>
+        <v>188</v>
       </c>
       <c r="K85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M85" t="s">
-        <v>326</v>
+        <v>550</v>
       </c>
       <c r="O85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q85" t="s">
-        <v>327</v>
+        <v>544</v>
       </c>
       <c r="S85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T85" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U85" t="s">
-        <v>327</v>
+        <v>551</v>
       </c>
     </row>
     <row r="86" spans="1:21">
@@ -6651,53 +7386,53 @@
         <v>101013</v>
       </c>
       <c r="B86" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C86">
         <f>C85</f>
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E86">
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I86" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="K86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M86" t="s">
-        <v>326</v>
+        <v>541</v>
       </c>
       <c r="O86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q86" t="s">
-        <v>327</v>
+        <v>547</v>
       </c>
       <c r="S86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T86" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U86" t="s">
-        <v>327</v>
+        <v>552</v>
       </c>
     </row>
     <row r="87" spans="1:21">
@@ -6706,53 +7441,53 @@
         <v>101012</v>
       </c>
       <c r="B87" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C87">
         <f t="shared" ref="C87:C97" si="10">C86</f>
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E87">
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I87" t="s">
-        <v>326</v>
+        <v>445</v>
       </c>
       <c r="K87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M87" t="s">
-        <v>326</v>
+        <v>545</v>
       </c>
       <c r="O87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q87" t="s">
-        <v>329</v>
+        <v>551</v>
       </c>
       <c r="S87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T87" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U87" t="s">
-        <v>329</v>
+        <v>553</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -6761,53 +7496,53 @@
         <v>101011</v>
       </c>
       <c r="B88" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C88">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E88">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="H88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I88" t="s">
-        <v>326</v>
+        <v>539</v>
       </c>
       <c r="K88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="L88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M88" t="s">
-        <v>326</v>
+        <v>554</v>
       </c>
       <c r="O88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="P88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q88" t="s">
-        <v>329</v>
+        <v>555</v>
       </c>
       <c r="S88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="T88" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U88" t="s">
-        <v>329</v>
+        <v>556</v>
       </c>
     </row>
     <row r="89" spans="1:21">
@@ -6816,7 +7551,7 @@
         <v>101010</v>
       </c>
       <c r="B89" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C89">
         <f t="shared" si="10"/>
@@ -6829,40 +7564,40 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H89" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I89" t="s">
-        <v>326</v>
+        <v>535</v>
       </c>
       <c r="K89" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L89" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M89" t="s">
-        <v>326</v>
+        <v>547</v>
       </c>
       <c r="O89" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P89" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q89" t="s">
-        <v>329</v>
+        <v>557</v>
       </c>
       <c r="S89" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T89" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U89" t="s">
-        <v>329</v>
+        <v>558</v>
       </c>
     </row>
     <row r="90" spans="1:21">
@@ -6871,7 +7606,7 @@
         <v>101009</v>
       </c>
       <c r="B90" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C90">
         <f t="shared" si="10"/>
@@ -6884,40 +7619,40 @@
         <v>9</v>
       </c>
       <c r="G90" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H90" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I90" t="s">
-        <v>326</v>
+        <v>542</v>
       </c>
       <c r="K90" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L90" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M90" t="s">
-        <v>326</v>
+        <v>551</v>
       </c>
       <c r="O90" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P90" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q90" t="s">
-        <v>331</v>
+        <v>559</v>
       </c>
       <c r="S90" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T90" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U90" t="s">
-        <v>331</v>
+        <v>560</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -6926,7 +7661,7 @@
         <v>101008</v>
       </c>
       <c r="B91" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C91">
         <f t="shared" si="10"/>
@@ -6939,40 +7674,40 @@
         <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H91" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I91" t="s">
-        <v>326</v>
+        <v>547</v>
       </c>
       <c r="K91" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L91" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M91" t="s">
-        <v>326</v>
+        <v>555</v>
       </c>
       <c r="O91" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P91" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q91" t="s">
-        <v>331</v>
+        <v>561</v>
       </c>
       <c r="S91" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T91" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U91" t="s">
-        <v>331</v>
+        <v>562</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -6981,7 +7716,7 @@
         <v>101007</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C92">
         <f t="shared" si="10"/>
@@ -6994,40 +7729,40 @@
         <v>7</v>
       </c>
       <c r="G92" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H92" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I92" t="s">
-        <v>326</v>
+        <v>563</v>
       </c>
       <c r="K92" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L92" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M92" t="s">
-        <v>326</v>
+        <v>564</v>
       </c>
       <c r="O92" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P92" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q92" t="s">
-        <v>331</v>
+        <v>565</v>
       </c>
       <c r="S92" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T92" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U92" t="s">
-        <v>331</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:21">
@@ -7036,7 +7771,7 @@
         <v>101006</v>
       </c>
       <c r="B93" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C93">
         <f t="shared" si="10"/>
@@ -7049,40 +7784,40 @@
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H93" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I93" t="s">
-        <v>326</v>
+        <v>553</v>
       </c>
       <c r="K93" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L93" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M93" t="s">
-        <v>326</v>
+        <v>567</v>
       </c>
       <c r="O93" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P93" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q93" t="s">
-        <v>332</v>
+        <v>566</v>
       </c>
       <c r="S93" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T93" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U93" t="s">
-        <v>332</v>
+        <v>568</v>
       </c>
     </row>
     <row r="94" spans="1:21">
@@ -7091,7 +7826,7 @@
         <v>101005</v>
       </c>
       <c r="B94" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C94">
         <f t="shared" si="10"/>
@@ -7104,40 +7839,40 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H94" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I94" t="s">
-        <v>326</v>
+        <v>558</v>
       </c>
       <c r="K94" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L94" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M94" t="s">
-        <v>326</v>
+        <v>565</v>
       </c>
       <c r="O94" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P94" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q94" t="s">
-        <v>332</v>
+        <v>568</v>
       </c>
       <c r="S94" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T94" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U94" t="s">
-        <v>332</v>
+        <v>569</v>
       </c>
     </row>
     <row r="95" spans="1:21">
@@ -7146,7 +7881,7 @@
         <v>101004</v>
       </c>
       <c r="B95" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C95">
         <f t="shared" si="10"/>
@@ -7159,40 +7894,40 @@
         <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H95" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I95" t="s">
-        <v>326</v>
+        <v>560</v>
       </c>
       <c r="K95" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L95" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M95" t="s">
-        <v>326</v>
+        <v>566</v>
       </c>
       <c r="O95" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P95" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q95" t="s">
-        <v>332</v>
+        <v>569</v>
       </c>
       <c r="S95" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T95" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U95" t="s">
-        <v>332</v>
+        <v>570</v>
       </c>
     </row>
     <row r="96" spans="1:21">
@@ -7201,7 +7936,7 @@
         <v>101003</v>
       </c>
       <c r="B96" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C96">
         <f t="shared" si="10"/>
@@ -7214,40 +7949,40 @@
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H96" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I96" t="s">
-        <v>326</v>
+        <v>566</v>
       </c>
       <c r="K96" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L96" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M96" t="s">
-        <v>326</v>
+        <v>571</v>
       </c>
       <c r="O96" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P96" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q96" t="s">
-        <v>98</v>
+        <v>572</v>
       </c>
       <c r="S96" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T96" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U96" t="s">
-        <v>98</v>
+        <v>573</v>
       </c>
     </row>
     <row r="97" spans="1:21">
@@ -7256,7 +7991,7 @@
         <v>101002</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>549</v>
       </c>
       <c r="C97">
         <f t="shared" si="10"/>
@@ -7269,40 +8004,40 @@
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H97" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="I97" t="s">
-        <v>326</v>
+        <v>571</v>
       </c>
       <c r="K97" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L97" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="M97" t="s">
-        <v>326</v>
+        <v>570</v>
       </c>
       <c r="O97" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P97" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="Q97" t="s">
-        <v>98</v>
+        <v>573</v>
       </c>
       <c r="S97" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T97" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="U97" t="s">
-        <v>98</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98" spans="1:21">
@@ -7311,7 +8046,7 @@
         <v>100014</v>
       </c>
       <c r="B98" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -7323,40 +8058,40 @@
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="I98" t="s">
-        <v>326</v>
+        <v>572</v>
       </c>
       <c r="K98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="M98" t="s">
-        <v>326</v>
+        <v>573</v>
       </c>
       <c r="O98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="Q98" t="s">
-        <v>98</v>
+        <v>576</v>
       </c>
       <c r="S98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T98" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="U98" t="s">
-        <v>98</v>
+        <v>576</v>
       </c>
     </row>
     <row r="99" spans="1:21">
@@ -7365,53 +8100,53 @@
         <v>100013</v>
       </c>
       <c r="B99" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C99">
         <f>C98</f>
         <v>0</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E99">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="I99" t="s">
-        <v>326</v>
+        <v>573</v>
       </c>
       <c r="K99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="M99" t="s">
-        <v>326</v>
+        <v>574</v>
       </c>
       <c r="O99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="Q99" t="s">
-        <v>334</v>
+        <v>576</v>
       </c>
       <c r="S99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T99" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="U99" t="s">
-        <v>334</v>
+        <v>577</v>
       </c>
     </row>
     <row r="100" spans="1:21">
@@ -7420,53 +8155,53 @@
         <v>100012</v>
       </c>
       <c r="B100" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C100">
         <f t="shared" ref="C100:C109" si="11">C99</f>
         <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E100">
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="I100" t="s">
-        <v>326</v>
+        <v>576</v>
       </c>
       <c r="K100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="M100" t="s">
-        <v>326</v>
+        <v>577</v>
       </c>
       <c r="O100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="Q100" t="s">
-        <v>334</v>
+        <v>577</v>
       </c>
       <c r="S100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T100" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="U100" t="s">
-        <v>334</v>
+        <v>577</v>
       </c>
     </row>
     <row r="101" spans="1:21">
@@ -7475,53 +8210,53 @@
         <v>100011</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E101">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="H101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="I101" t="s">
-        <v>326</v>
+        <v>577</v>
       </c>
       <c r="K101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="L101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="M101" t="s">
-        <v>326</v>
+        <v>577</v>
       </c>
       <c r="O101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="P101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="Q101" t="s">
-        <v>334</v>
+        <v>578</v>
       </c>
       <c r="S101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="T101" t="s">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="U101" t="s">
-        <v>334</v>
+        <v>578</v>
       </c>
     </row>
     <row r="102" spans="1:21">
@@ -7530,7 +8265,7 @@
         <v>100010</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C102">
         <f t="shared" si="11"/>
@@ -7543,40 +8278,40 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="H102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="I102" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="L102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="M102" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="P102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="Q102" t="s">
-        <v>334</v>
+        <v>578</v>
       </c>
       <c r="S102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="T102" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="U102" t="s">
-        <v>334</v>
+        <v>578</v>
       </c>
     </row>
     <row r="103" spans="1:21">
@@ -7585,7 +8320,7 @@
         <v>100009</v>
       </c>
       <c r="B103" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C103">
         <f t="shared" si="11"/>
@@ -7598,40 +8333,40 @@
         <v>9</v>
       </c>
       <c r="G103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="H103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="I103" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="L103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="M103" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="P103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="Q103" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="S103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="T103" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="U103" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
     </row>
     <row r="104" spans="1:21">
@@ -7640,7 +8375,7 @@
         <v>100008</v>
       </c>
       <c r="B104" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C104">
         <f t="shared" si="11"/>
@@ -7653,40 +8388,40 @@
         <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="H104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="I104" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="L104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="M104" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="Q104" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="S104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="T104" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="U104" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
     </row>
     <row r="105" spans="1:21">
@@ -7695,7 +8430,7 @@
         <v>100007</v>
       </c>
       <c r="B105" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C105">
         <f t="shared" si="11"/>
@@ -7708,40 +8443,40 @@
         <v>7</v>
       </c>
       <c r="G105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="H105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="I105" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="L105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="M105" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="P105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="Q105" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="S105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="T105" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="U105" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
     </row>
     <row r="106" spans="1:21">
@@ -7750,7 +8485,7 @@
         <v>100006</v>
       </c>
       <c r="B106" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C106">
         <f t="shared" si="11"/>
@@ -7763,40 +8498,40 @@
         <v>6</v>
       </c>
       <c r="G106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="H106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="I106" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="L106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="M106" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="P106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="Q106" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
       <c r="S106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="T106" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="U106" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
     </row>
     <row r="107" spans="1:21">
@@ -7805,7 +8540,7 @@
         <v>100005</v>
       </c>
       <c r="B107" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C107">
         <f t="shared" si="11"/>
@@ -7818,40 +8553,40 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="H107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="I107" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="L107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="M107" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="P107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="Q107" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
       <c r="S107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="T107" t="s">
-        <v>331</v>
+        <v>579</v>
       </c>
       <c r="U107" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
     </row>
     <row r="108" spans="1:21">
@@ -7860,7 +8595,7 @@
         <v>100004</v>
       </c>
       <c r="B108" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C108">
         <f t="shared" si="11"/>
@@ -7873,40 +8608,40 @@
         <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="H108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="I108" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="L108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="M108" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="P108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="Q108" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
       <c r="S108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="T108" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="U108" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" spans="1:21">
@@ -7915,7 +8650,7 @@
         <v>100003</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>575</v>
       </c>
       <c r="C109">
         <f t="shared" si="11"/>
@@ -7928,40 +8663,40 @@
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="H109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="I109" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="K109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="L109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="M109" t="s">
-        <v>326</v>
+        <v>578</v>
       </c>
       <c r="O109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="P109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="Q109" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
       <c r="S109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="T109" t="s">
-        <v>331</v>
+        <v>580</v>
       </c>
       <c r="U109" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
